--- a/docs/finance/TownCore-LRP.xlsx
+++ b/docs/finance/TownCore-LRP.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="360">
   <si>
     <t xml:space="preserve">TownCore long-range plan, FY2027-FY2031</t>
   </si>
@@ -172,19 +172,46 @@
     <t xml:space="preserve">Scales per-town direct costs and launch costs.</t>
   </si>
   <si>
-    <t xml:space="preserve">Town rollout (by fiscal year)</t>
+    <t xml:space="preserve">Launch capacity: how many towns can launch, and how fast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US incorporated places with 5,000+ people</t>
+  </si>
+  <si>
+    <t xml:space="preserve">places</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Census Vintage 2025 city estimates (sub-est2025.csv, SUMLEV 162). Florida: 229. The §10a floor is 5,000 people. New England towns (county subdivisions) are not counted.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share that pass readiness (Rule 7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estimate, and the biggest unknown. Today almost none pass: Boca makes about 0.8 real items a day against a bar of 10, Delray 0.53 against 3. Getting here needs more sources per town (permits, police and fire feeds, property sales, schools, sports) or a lower bar (owner call).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share allowed by the naming neighbor rule</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Towns within 50 miles must use different name patterns (§10b). Computed on the Census gazetteer, largest towns first: the original 6 patterns allowed 41% (2,021 places); the 22 patterns adopted 2026-10-17 allow 74% (3,636; Florida 185 of 229). The rest sit in metros with more than 22 towns within 50 miles of each other.</t>
   </si>
   <si>
     <t xml:space="preserve">Fiscal year</t>
   </si>
   <si>
-    <t xml:space="preserve">New towns launched (base case)</t>
+    <t xml:space="preserve">Launches the team can do in a year</t>
   </si>
   <si>
     <t xml:space="preserve">towns</t>
   </si>
   <si>
-    <t xml:space="preserve">Management target; CLAUDE.md goal is thousands of towns, one command per launch. Scaled by the launch multiplier.</t>
+    <t xml:space="preserve">About 100 a month: the launcher is automated, each launch needs ~45 minutes of people (approval, Facebook page, Google Publisher Center). A pacing choice too: launching hundreds of AI-written sites at once invites Google's scaled-content review. Scaled by the launch multiplier.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Launches per launch operator per year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~45 minutes of hands-on work per launch, plus fixes and follow-up. Estimate.</t>
   </si>
   <si>
     <t xml:space="preserve">Town size mix and size-driven inputs (CLAUDE.md §5 tiers)</t>
@@ -205,13 +232,13 @@
     <t xml:space="preserve">Share of launches</t>
   </si>
   <si>
-    <t xml:space="preserve">Ranked list (CLAUDE.md §10a) skews to smaller towns; population floor 5,000.</t>
+    <t xml:space="preserve">Census 2025, places of 5,000+: 3,535 under 30,000 (small), 1,023 of 30,000-100,000 (mid), 343 of 100,000+ (large); tiers from packages/config/src/launch.ts.</t>
   </si>
   <si>
     <t xml:space="preserve">Households per town</t>
   </si>
   <si>
-    <t xml:space="preserve">Estimate from Census place sizes; Boca Raton (large) is roughly 45,000 households.</t>
+    <t xml:space="preserve">Median town population by tier (10,371 / 48,420 / 157,113, Census 2025) / ~2.5 people a household.</t>
   </si>
   <si>
     <t xml:space="preserve">Directory listings per town</t>
@@ -622,7 +649,7 @@
     <t xml:space="preserve">Equity raised</t>
   </si>
   <si>
-    <t xml:space="preserve">Plan: seed in FY2027, Series A in FY2028, Series B in FY2030. Adjust to keep cash above zero.</t>
+    <t xml:space="preserve">Plan: $10M in FY2027 and $6M in FY2028, sized to the launch pace. Adjust to keep cash above zero.</t>
   </si>
   <si>
     <t xml:space="preserve">Town rollout</t>
@@ -634,6 +661,9 @@
     <t xml:space="preserve">New towns launched</t>
   </si>
   <si>
+    <t xml:space="preserve">The smaller of the team's capacity and the towns left in the pool.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cumulative towns launched</t>
   </si>
   <si>
@@ -646,6 +676,15 @@
     <t xml:space="preserve">Used for people ratios.</t>
   </si>
   <si>
+    <t xml:space="preserve">Launchable towns (pool)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Places of 5,000+ x readiness pass rate x naming rule (x launch multiplier).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pool left at year end</t>
+  </si>
+  <si>
     <t xml:space="preserve">Unit economics: one average launched town, by age</t>
   </si>
   <si>
@@ -838,6 +877,9 @@
     <t xml:space="preserve">Account executives</t>
   </si>
   <si>
+    <t xml:space="preserve">Launch operations</t>
+  </si>
+  <si>
     <t xml:space="preserve">Total heads</t>
   </si>
   <si>
@@ -881,6 +923,9 @@
   </si>
   <si>
     <t xml:space="preserve">Support and success (people)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Launch operations (people)</t>
   </si>
   <si>
     <t xml:space="preserve">Launch marketing and launch AI</t>
@@ -1323,7 +1368,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1331,11 +1376,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1760,23 +1805,23 @@
       <c r="B7" s="2"/>
       <c r="C7" s="8" t="n">
         <f aca="false">Rollout!C7</f>
-        <v>20</v>
+        <v>1200</v>
       </c>
       <c r="D7" s="8" t="n">
         <f aca="false">Rollout!D7</f>
-        <v>99.4</v>
+        <v>1777</v>
       </c>
       <c r="E7" s="8" t="n">
         <f aca="false">Rollout!E7</f>
-        <v>296.6</v>
+        <v>1734.61</v>
       </c>
       <c r="F7" s="8" t="n">
         <f aca="false">Rollout!F7</f>
-        <v>688.8</v>
+        <v>1710.35</v>
       </c>
       <c r="G7" s="8" t="n">
         <f aca="false">Rollout!G7</f>
-        <v>1371.8</v>
+        <v>1692.22</v>
       </c>
       <c r="H7" s="2"/>
     </row>
@@ -1787,23 +1832,23 @@
       <c r="B8" s="2"/>
       <c r="C8" s="8" t="n">
         <f aca="false">KPIs!C8</f>
-        <v>4200</v>
+        <v>199260</v>
       </c>
       <c r="D8" s="8" t="n">
         <f aca="false">KPIs!D8</f>
-        <v>27664</v>
+        <v>617207.85</v>
       </c>
       <c r="E8" s="8" t="n">
         <f aca="false">KPIs!E8</f>
-        <v>101416</v>
+        <v>1020481.308</v>
       </c>
       <c r="F8" s="8" t="n">
         <f aca="false">KPIs!F8</f>
-        <v>276220</v>
+        <v>1323318.87</v>
       </c>
       <c r="G8" s="8" t="n">
         <f aca="false">KPIs!G8</f>
-        <v>624974</v>
+        <v>1528506.855</v>
       </c>
       <c r="H8" s="2"/>
     </row>
@@ -1814,23 +1859,23 @@
       <c r="B9" s="2"/>
       <c r="C9" s="9" t="n">
         <f aca="false">'P&amp;L'!C5</f>
-        <v>18028.56</v>
+        <v>879057.72</v>
       </c>
       <c r="D9" s="9" t="n">
         <f aca="false">'P&amp;L'!D5</f>
-        <v>217104.8736</v>
+        <v>7578011.8893</v>
       </c>
       <c r="E9" s="9" t="n">
         <f aca="false">'P&amp;L'!E5</f>
-        <v>1084578.1344</v>
+        <v>19487904.15096</v>
       </c>
       <c r="F9" s="9" t="n">
         <f aca="false">'P&amp;L'!F5</f>
-        <v>3547797.98496</v>
+        <v>29622252.2451</v>
       </c>
       <c r="G9" s="9" t="n">
         <f aca="false">'P&amp;L'!G5</f>
-        <v>9061606.73472</v>
+        <v>36790077.802794</v>
       </c>
       <c r="H9" s="2"/>
     </row>
@@ -1841,23 +1886,23 @@
       <c r="B10" s="2"/>
       <c r="C10" s="10" t="n">
         <f aca="false">'P&amp;L'!C8</f>
-        <v>0.558152495817747</v>
+        <v>0.49110097698704</v>
       </c>
       <c r="D10" s="10" t="n">
         <f aca="false">'P&amp;L'!D8</f>
-        <v>0.77079367597209</v>
+        <v>0.839158058580218</v>
       </c>
       <c r="E10" s="10" t="n">
         <f aca="false">'P&amp;L'!E8</f>
-        <v>0.841645038989641</v>
+        <v>0.916720423459067</v>
       </c>
       <c r="F10" s="10" t="n">
         <f aca="false">'P&amp;L'!F8</f>
-        <v>0.875179278962009</v>
+        <v>0.939676114980231</v>
       </c>
       <c r="G10" s="10" t="n">
         <f aca="false">'P&amp;L'!G8</f>
-        <v>0.89447292180238</v>
+        <v>0.947779974695033</v>
       </c>
       <c r="H10" s="2"/>
     </row>
@@ -1868,23 +1913,23 @@
       <c r="B11" s="2"/>
       <c r="C11" s="9" t="n">
         <f aca="false">'P&amp;L'!C16</f>
-        <v>-1221781.31424</v>
+        <v>-8022028.59488</v>
       </c>
       <c r="D11" s="9" t="n">
         <f aca="false">'P&amp;L'!D16</f>
-        <v>-2165908.7096064</v>
+        <v>-6129956.1503272</v>
       </c>
       <c r="E11" s="9" t="n">
         <f aca="false">'P&amp;L'!E16</f>
-        <v>-3533796.4665856</v>
+        <v>3082762.55895776</v>
       </c>
       <c r="F11" s="9" t="n">
         <f aca="false">'P&amp;L'!F16</f>
-        <v>-5134437.42521984</v>
+        <v>11223323.30919</v>
       </c>
       <c r="G11" s="9" t="n">
         <f aca="false">'P&amp;L'!G16</f>
-        <v>-6049621.93095213</v>
+        <v>16306536.8800641</v>
       </c>
       <c r="H11" s="2"/>
     </row>
@@ -1895,23 +1940,23 @@
       <c r="B12" s="2"/>
       <c r="C12" s="10" t="n">
         <f aca="false">'P&amp;L'!C17</f>
-        <v>-67.7692125294533</v>
+        <v>-9.12571314984868</v>
       </c>
       <c r="D12" s="10" t="n">
         <f aca="false">'P&amp;L'!D17</f>
-        <v>-9.97632468443306</v>
+        <v>-0.8089135039472</v>
       </c>
       <c r="E12" s="10" t="n">
         <f aca="false">'P&amp;L'!E17</f>
-        <v>-3.25822211835437</v>
+        <v>0.158188511965044</v>
       </c>
       <c r="F12" s="10" t="n">
         <f aca="false">'P&amp;L'!F17</f>
-        <v>-1.44721809048486</v>
+        <v>0.378881498149639</v>
       </c>
       <c r="G12" s="10" t="n">
         <f aca="false">'P&amp;L'!G17</f>
-        <v>-0.667610293412172</v>
+        <v>0.443231921592342</v>
       </c>
       <c r="H12" s="2"/>
     </row>
@@ -1922,23 +1967,23 @@
       <c r="B13" s="2"/>
       <c r="C13" s="9" t="n">
         <f aca="false">'P&amp;L'!C25</f>
-        <v>-1229281.31424</v>
+        <v>-8096195.26154667</v>
       </c>
       <c r="D13" s="9" t="n">
         <f aca="false">'P&amp;L'!D25</f>
-        <v>-2179242.04293973</v>
+        <v>-6238289.48366053</v>
       </c>
       <c r="E13" s="9" t="n">
         <f aca="false">'P&amp;L'!E25</f>
-        <v>-3562129.79991893</v>
+        <v>2974429.22562442</v>
       </c>
       <c r="F13" s="9" t="n">
         <f aca="false">'P&amp;L'!F25</f>
-        <v>-5181104.09188651</v>
+        <v>11185823.30919</v>
       </c>
       <c r="G13" s="9" t="n">
         <f aca="false">'P&amp;L'!G25</f>
-        <v>-6132955.26428547</v>
+        <v>12268460.7126463</v>
       </c>
       <c r="H13" s="2"/>
     </row>
@@ -1949,23 +1994,23 @@
       <c r="B14" s="2"/>
       <c r="C14" s="9" t="n">
         <f aca="false">'Cash Flow'!C13</f>
-        <v>1005177.82896</v>
+        <v>1979099.67352</v>
       </c>
       <c r="D14" s="9" t="n">
         <f aca="false">'Cash Flow'!D13</f>
-        <v>6815796.8299456</v>
+        <v>1545674.8981138</v>
       </c>
       <c r="E14" s="9" t="n">
         <f aca="false">'Cash Flow'!E13</f>
-        <v>3210976.165536</v>
+        <v>4271140.68922176</v>
       </c>
       <c r="F14" s="9" t="n">
         <f aca="false">'Cash Flow'!F13</f>
-        <v>12925142.1447994</v>
+        <v>15180433.5555876</v>
       </c>
       <c r="G14" s="9" t="n">
         <f aca="false">'Cash Flow'!G13</f>
-        <v>6582605.95135443</v>
+        <v>27230526.1681697</v>
       </c>
       <c r="H14" s="2"/>
     </row>
@@ -1976,23 +2021,23 @@
       <c r="B15" s="2"/>
       <c r="C15" s="9" t="n">
         <f aca="false">KPIs!C22</f>
-        <v>-613580.34690271</v>
+        <v>17170813.8057806</v>
       </c>
       <c r="D15" s="9" t="n">
         <f aca="false">KPIs!D22</f>
-        <v>294083.175893533</v>
+        <v>25231246.9857268</v>
       </c>
       <c r="E15" s="9" t="n">
         <f aca="false">KPIs!E22</f>
-        <v>3244622.20543282</v>
+        <v>23594736.5567876</v>
       </c>
       <c r="F15" s="9" t="n">
         <f aca="false">KPIs!F22</f>
-        <v>9695346.41517068</v>
+        <v>21818314.6293474</v>
       </c>
       <c r="G15" s="9" t="n">
         <f aca="false">KPIs!G22</f>
-        <v>21904049.6855681</v>
+        <v>20070116.8074734</v>
       </c>
       <c r="H15" s="2"/>
     </row>
@@ -2187,7 +2232,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>320</v>
+        <v>335</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2199,7 +2244,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>321</v>
+        <v>336</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2221,7 +2266,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="7" t="s">
@@ -2243,7 +2288,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
-        <v>322</v>
+        <v>337</v>
       </c>
       <c r="B5" s="16"/>
       <c r="C5" s="16"/>
@@ -2255,28 +2300,28 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>323</v>
+        <v>338</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="33" t="n">
         <f aca="false">Rollout!C5</f>
-        <v>20</v>
+        <v>1200</v>
       </c>
       <c r="D6" s="33" t="n">
         <f aca="false">Rollout!D5</f>
-        <v>80</v>
+        <v>613</v>
       </c>
       <c r="E6" s="33" t="n">
         <f aca="false">Rollout!E5</f>
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F6" s="33" t="n">
         <f aca="false">Rollout!F5</f>
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="G6" s="33" t="n">
         <f aca="false">Rollout!G5</f>
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="H6" s="2"/>
     </row>
@@ -2287,83 +2332,83 @@
       <c r="B7" s="2"/>
       <c r="C7" s="33" t="n">
         <f aca="false">Rollout!C7</f>
-        <v>20</v>
+        <v>1200</v>
       </c>
       <c r="D7" s="33" t="n">
         <f aca="false">Rollout!D7</f>
-        <v>99.4</v>
+        <v>1777</v>
       </c>
       <c r="E7" s="33" t="n">
         <f aca="false">Rollout!E7</f>
-        <v>296.6</v>
+        <v>1734.61</v>
       </c>
       <c r="F7" s="33" t="n">
         <f aca="false">Rollout!F7</f>
-        <v>688.8</v>
+        <v>1710.35</v>
       </c>
       <c r="G7" s="33" t="n">
         <f aca="false">Rollout!G7</f>
-        <v>1371.8</v>
+        <v>1692.22</v>
       </c>
       <c r="H7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="33" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$C$10</f>
-        <v>4200</v>
+        <v>199260</v>
       </c>
       <c r="D8" s="33" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$D$10+Rollout!$D$5*'Unit Economics'!$C$10</f>
-        <v>27664</v>
+        <v>617207.85</v>
       </c>
       <c r="E8" s="33" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$E$10+Rollout!$D$5*'Unit Economics'!$D$10+Rollout!$E$5*'Unit Economics'!$C$10</f>
-        <v>101416</v>
+        <v>1020481.308</v>
       </c>
       <c r="F8" s="33" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$F$10+Rollout!$D$5*'Unit Economics'!$E$10+Rollout!$E$5*'Unit Economics'!$D$10+Rollout!$F$5*'Unit Economics'!$C$10</f>
-        <v>276220</v>
+        <v>1323318.87</v>
       </c>
       <c r="G8" s="33" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$G$10+Rollout!$D$5*'Unit Economics'!$F$10+Rollout!$E$5*'Unit Economics'!$E$10+Rollout!$F$5*'Unit Economics'!$D$10+Rollout!$G$5*'Unit Economics'!$C$10</f>
-        <v>624974</v>
+        <v>1528506.855</v>
       </c>
       <c r="H8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>324</v>
+        <v>339</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="33" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$C$12</f>
-        <v>1680000</v>
+        <v>79704000</v>
       </c>
       <c r="D9" s="33" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$D$12+Rollout!$D$5*'Unit Economics'!$C$12</f>
-        <v>13238400</v>
+        <v>349966980</v>
       </c>
       <c r="E9" s="33" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$E$12+Rollout!$D$5*'Unit Economics'!$D$12+Rollout!$E$5*'Unit Economics'!$C$12</f>
-        <v>52449600</v>
+        <v>612288784.8</v>
       </c>
       <c r="F9" s="33" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$F$12+Rollout!$D$5*'Unit Economics'!$E$12+Rollout!$E$5*'Unit Economics'!$D$12+Rollout!$F$5*'Unit Economics'!$C$12</f>
-        <v>148142400</v>
+        <v>756530442</v>
       </c>
       <c r="G9" s="33" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$G$12+Rollout!$D$5*'Unit Economics'!$F$12+Rollout!$E$5*'Unit Economics'!$E$12+Rollout!$F$5*'Unit Economics'!$D$12+Rollout!$G$5*'Unit Economics'!$C$12</f>
-        <v>341644800</v>
+        <v>860905486.8</v>
       </c>
       <c r="H9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
-        <v>325</v>
+        <v>340</v>
       </c>
       <c r="B10" s="16"/>
       <c r="C10" s="16"/>
@@ -2375,61 +2420,61 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>326</v>
+        <v>341</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="33" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$C$17</f>
-        <v>109.92</v>
+        <v>6122.88</v>
       </c>
       <c r="D11" s="33" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$D$17+Rollout!$D$5*'Unit Economics'!$C$17</f>
-        <v>789.268</v>
+        <v>22384.9872</v>
       </c>
       <c r="E11" s="33" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$E$17+Rollout!$D$5*'Unit Economics'!$D$17+Rollout!$E$5*'Unit Economics'!$C$17</f>
-        <v>3107.832</v>
+        <v>43088.74784</v>
       </c>
       <c r="F11" s="33" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$F$17+Rollout!$D$5*'Unit Economics'!$E$17+Rollout!$E$5*'Unit Economics'!$D$17+Rollout!$F$5*'Unit Economics'!$C$17</f>
-        <v>8941.732</v>
+        <v>60648.6088</v>
       </c>
       <c r="G11" s="33" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$G$17+Rollout!$D$5*'Unit Economics'!$F$17+Rollout!$E$5*'Unit Economics'!$E$17+Rollout!$F$5*'Unit Economics'!$D$17+Rollout!$G$5*'Unit Economics'!$C$17</f>
-        <v>21138.3056</v>
+        <v>74647.40216</v>
       </c>
       <c r="H11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>327</v>
+        <v>342</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="42" t="n">
         <f aca="false">IF(C11=0,0,(Revenue!C5+Revenue!C6+Revenue!C7)/C11/12)</f>
-        <v>9.0509461426492</v>
+        <v>8.24490435873315</v>
       </c>
       <c r="D12" s="42" t="n">
         <f aca="false">IF(D11=0,0,(Revenue!D5+Revenue!D6+Revenue!D7)/D11/12)</f>
-        <v>14.6726749342429</v>
+        <v>18.5326371953431</v>
       </c>
       <c r="E12" s="42" t="n">
         <f aca="false">IF(E11=0,0,(Revenue!E5+Revenue!E6+Revenue!E7)/E11/12)</f>
-        <v>17.6454233047346</v>
+        <v>21.7373985142939</v>
       </c>
       <c r="F12" s="42" t="n">
         <f aca="false">IF(F11=0,0,(Revenue!F5+Revenue!F6+Revenue!F7)/F11/12)</f>
-        <v>19.4599572073956</v>
+        <v>23.1203316571377</v>
       </c>
       <c r="G12" s="42" t="n">
         <f aca="false">IF(G11=0,0,(Revenue!G5+Revenue!G6+Revenue!G7)/G11/12)</f>
-        <v>20.677289979193</v>
+        <v>23.8246888107378</v>
       </c>
       <c r="H12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
-        <v>328</v>
+        <v>343</v>
       </c>
       <c r="B13" s="16"/>
       <c r="C13" s="16"/>
@@ -2446,50 +2491,50 @@
       <c r="B14" s="2"/>
       <c r="C14" s="37" t="n">
         <f aca="false">'P&amp;L'!C5</f>
-        <v>18028.56</v>
+        <v>879057.72</v>
       </c>
       <c r="D14" s="37" t="n">
         <f aca="false">'P&amp;L'!D5</f>
-        <v>217104.8736</v>
+        <v>7578011.8893</v>
       </c>
       <c r="E14" s="37" t="n">
         <f aca="false">'P&amp;L'!E5</f>
-        <v>1084578.1344</v>
+        <v>19487904.15096</v>
       </c>
       <c r="F14" s="37" t="n">
         <f aca="false">'P&amp;L'!F5</f>
-        <v>3547797.98496</v>
+        <v>29622252.2451</v>
       </c>
       <c r="G14" s="37" t="n">
         <f aca="false">'P&amp;L'!G5</f>
-        <v>9061606.73472</v>
+        <v>36790077.802794</v>
       </c>
       <c r="H14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>329</v>
+        <v>344</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="37" t="n">
         <f aca="false">IF(Rollout!C8=0,0,'P&amp;L'!C5/Rollout!C8)</f>
-        <v>1802.856</v>
+        <v>1465.0962</v>
       </c>
       <c r="D15" s="37" t="n">
         <f aca="false">IF(Rollout!D8=0,0,'P&amp;L'!D5/Rollout!D8)</f>
-        <v>3636.59754773869</v>
+        <v>5091.03922693987</v>
       </c>
       <c r="E15" s="37" t="n">
         <f aca="false">IF(Rollout!E8=0,0,'P&amp;L'!E5/Rollout!E8)</f>
-        <v>5477.66734545454</v>
+        <v>11099.1278364967</v>
       </c>
       <c r="F15" s="37" t="n">
         <f aca="false">IF(Rollout!F8=0,0,'P&amp;L'!F5/Rollout!F8)</f>
-        <v>7200.72657795819</v>
+        <v>17197.4433636965</v>
       </c>
       <c r="G15" s="37" t="n">
         <f aca="false">IF(Rollout!G8=0,0,'P&amp;L'!G5/Rollout!G8)</f>
-        <v>8795.11475756576</v>
+        <v>21624.8763745016</v>
       </c>
       <c r="H15" s="2"/>
     </row>
@@ -2500,23 +2545,23 @@
       <c r="B16" s="2"/>
       <c r="C16" s="34" t="n">
         <f aca="false">'P&amp;L'!C8</f>
-        <v>0.558152495817747</v>
+        <v>0.49110097698704</v>
       </c>
       <c r="D16" s="34" t="n">
         <f aca="false">'P&amp;L'!D8</f>
-        <v>0.77079367597209</v>
+        <v>0.839158058580218</v>
       </c>
       <c r="E16" s="34" t="n">
         <f aca="false">'P&amp;L'!E8</f>
-        <v>0.841645038989641</v>
+        <v>0.916720423459067</v>
       </c>
       <c r="F16" s="34" t="n">
         <f aca="false">'P&amp;L'!F8</f>
-        <v>0.875179278962009</v>
+        <v>0.939676114980231</v>
       </c>
       <c r="G16" s="34" t="n">
         <f aca="false">'P&amp;L'!G8</f>
-        <v>0.89447292180238</v>
+        <v>0.947779974695033</v>
       </c>
       <c r="H16" s="2"/>
     </row>
@@ -2527,23 +2572,23 @@
       <c r="B17" s="2"/>
       <c r="C17" s="37" t="n">
         <f aca="false">'P&amp;L'!C16</f>
-        <v>-1221781.31424</v>
+        <v>-8022028.59488</v>
       </c>
       <c r="D17" s="37" t="n">
         <f aca="false">'P&amp;L'!D16</f>
-        <v>-2165908.7096064</v>
+        <v>-6129956.1503272</v>
       </c>
       <c r="E17" s="37" t="n">
         <f aca="false">'P&amp;L'!E16</f>
-        <v>-3533796.4665856</v>
+        <v>3082762.55895776</v>
       </c>
       <c r="F17" s="37" t="n">
         <f aca="false">'P&amp;L'!F16</f>
-        <v>-5134437.42521984</v>
+        <v>11223323.30919</v>
       </c>
       <c r="G17" s="37" t="n">
         <f aca="false">'P&amp;L'!G16</f>
-        <v>-6049621.93095213</v>
+        <v>16306536.8800641</v>
       </c>
       <c r="H17" s="2"/>
     </row>
@@ -2554,23 +2599,23 @@
       <c r="B18" s="2"/>
       <c r="C18" s="34" t="n">
         <f aca="false">'P&amp;L'!C17</f>
-        <v>-67.7692125294533</v>
+        <v>-9.12571314984868</v>
       </c>
       <c r="D18" s="34" t="n">
         <f aca="false">'P&amp;L'!D17</f>
-        <v>-9.97632468443306</v>
+        <v>-0.8089135039472</v>
       </c>
       <c r="E18" s="34" t="n">
         <f aca="false">'P&amp;L'!E17</f>
-        <v>-3.25822211835437</v>
+        <v>0.158188511965044</v>
       </c>
       <c r="F18" s="34" t="n">
         <f aca="false">'P&amp;L'!F17</f>
-        <v>-1.44721809048486</v>
+        <v>0.378881498149639</v>
       </c>
       <c r="G18" s="34" t="n">
         <f aca="false">'P&amp;L'!G17</f>
-        <v>-0.667610293412172</v>
+        <v>0.443231921592342</v>
       </c>
       <c r="H18" s="2"/>
     </row>
@@ -2581,135 +2626,135 @@
       <c r="B19" s="2"/>
       <c r="C19" s="37" t="n">
         <f aca="false">'Cash Flow'!C13</f>
-        <v>1005177.82896</v>
+        <v>1979099.67352</v>
       </c>
       <c r="D19" s="37" t="n">
         <f aca="false">'Cash Flow'!D13</f>
-        <v>6815796.8299456</v>
+        <v>1545674.8981138</v>
       </c>
       <c r="E19" s="37" t="n">
         <f aca="false">'Cash Flow'!E13</f>
-        <v>3210976.165536</v>
+        <v>4271140.68922176</v>
       </c>
       <c r="F19" s="37" t="n">
         <f aca="false">'Cash Flow'!F13</f>
-        <v>12925142.1447994</v>
+        <v>15180433.5555876</v>
       </c>
       <c r="G19" s="37" t="n">
         <f aca="false">'Cash Flow'!G13</f>
-        <v>6582605.95135443</v>
+        <v>27230526.1681697</v>
       </c>
       <c r="H19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>330</v>
+        <v>345</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="34" t="n">
         <f aca="false">IF('P&amp;L'!C5=0,0,Costs!C6/'P&amp;L'!C5)</f>
-        <v>0.225131679956691</v>
+        <v>0.247735268168739</v>
       </c>
       <c r="D20" s="34" t="n">
         <f aca="false">IF('P&amp;L'!D5=0,0,Costs!D6/'P&amp;L'!D5)</f>
-        <v>0.111048967258191</v>
+        <v>0.0704309792326417</v>
       </c>
       <c r="E20" s="34" t="n">
         <f aca="false">IF('P&amp;L'!E5=0,0,Costs!E6/'P&amp;L'!E5)</f>
-        <v>0.0735733143321611</v>
+        <v>0.0323065580722792</v>
       </c>
       <c r="F20" s="34" t="n">
         <f aca="false">IF('P&amp;L'!F5=0,0,Costs!F6/'P&amp;L'!F5)</f>
-        <v>0.0559203609791319</v>
+        <v>0.0209566034838788</v>
       </c>
       <c r="G20" s="34" t="n">
         <f aca="false">IF('P&amp;L'!G5=0,0,Costs!G6/'P&amp;L'!G5)</f>
-        <v>0.0457676211450391</v>
+        <v>0.0166947568203662</v>
       </c>
       <c r="H20" s="17" t="s">
-        <v>331</v>
+        <v>346</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>332</v>
+        <v>347</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" s="37" t="n">
-        <f aca="false">Costs!C21+Costs!C22+Costs!C23+Costs!C20+Assumptions!C$92+Costs!C25</f>
-        <v>1018250</v>
+        <f aca="false">Costs!C22+Costs!C23+Costs!C24+Costs!C21+Assumptions!C$97+Costs!C26</f>
+        <v>1258250</v>
       </c>
       <c r="D21" s="37" t="n">
-        <f aca="false">Costs!D21+Costs!D22+Costs!D23+Costs!D20+Assumptions!D$92+Costs!D25</f>
-        <v>1717125</v>
+        <f aca="false">Costs!D22+Costs!D23+Costs!D24+Costs!D21+Assumptions!D$97+Costs!D26</f>
+        <v>2059125</v>
       </c>
       <c r="E21" s="37" t="n">
-        <f aca="false">Costs!E21+Costs!E22+Costs!E23+Costs!E20+Assumptions!E$92+Costs!E25</f>
-        <v>2756628.75</v>
+        <f aca="false">Costs!E22+Costs!E23+Costs!E24+Costs!E21+Assumptions!E$97+Costs!E26</f>
+        <v>3044628.75</v>
       </c>
       <c r="F21" s="37" t="n">
-        <f aca="false">Costs!F21+Costs!F22+Costs!F23+Costs!F20+Assumptions!F$92+Costs!F25</f>
-        <v>4241476.4375</v>
+        <f aca="false">Costs!F22+Costs!F23+Costs!F24+Costs!F21+Assumptions!F$97+Costs!F26</f>
+        <v>4448476.4375</v>
       </c>
       <c r="G21" s="37" t="n">
-        <f aca="false">Costs!G21+Costs!G22+Costs!G23+Costs!G20+Assumptions!G$92+Costs!G25</f>
-        <v>5852241.820375</v>
+        <f aca="false">Costs!G22+Costs!G23+Costs!G24+Costs!G21+Assumptions!G$97+Costs!G26</f>
+        <v>5918241.820375</v>
       </c>
       <c r="H21" s="2"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>333</v>
+        <v>348</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="37" t="n">
         <f aca="false">Rollout!C7/'Unit Economics'!$G$7*'Unit Economics'!$G$42-C21</f>
-        <v>-613580.34690271</v>
+        <v>17170813.8057806</v>
       </c>
       <c r="D22" s="37" t="n">
         <f aca="false">Rollout!D7/'Unit Economics'!$G$7*'Unit Economics'!$G$42-D21</f>
-        <v>294083.175893533</v>
+        <v>25231246.9857268</v>
       </c>
       <c r="E22" s="37" t="n">
         <f aca="false">Rollout!E7/'Unit Economics'!$G$7*'Unit Economics'!$G$42-E21</f>
-        <v>3244622.20543282</v>
+        <v>23594736.5567876</v>
       </c>
       <c r="F22" s="37" t="n">
         <f aca="false">Rollout!F7/'Unit Economics'!$G$7*'Unit Economics'!$G$42-F21</f>
-        <v>9695346.41517068</v>
+        <v>21818314.6293474</v>
       </c>
       <c r="G22" s="37" t="n">
         <f aca="false">Rollout!G7/'Unit Economics'!$G$7*'Unit Economics'!$G$42-G21</f>
-        <v>21904049.6855681</v>
+        <v>20070116.8074734</v>
       </c>
       <c r="H22" s="17" t="s">
-        <v>334</v>
+        <v>349</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>335</v>
+        <v>350</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" s="33" t="n">
         <f aca="false">IF('Unit Economics'!$G$42&lt;=0,0,C21/('Unit Economics'!$G$42/'Unit Economics'!$G$7))</f>
-        <v>50.3249992781244</v>
+        <v>81.9303691122058</v>
       </c>
       <c r="D23" s="33" t="n">
         <f aca="false">IF('Unit Economics'!$G$42&lt;=0,0,D21/('Unit Economics'!$G$42/'Unit Economics'!$G$7))</f>
-        <v>84.8655186697269</v>
+        <v>134.078975798268</v>
       </c>
       <c r="E23" s="33" t="n">
         <f aca="false">IF('Unit Economics'!$G$42&lt;=0,0,E21/('Unit Economics'!$G$42/'Unit Economics'!$G$7))</f>
-        <v>136.240942650437</v>
+        <v>198.249598487688</v>
       </c>
       <c r="F23" s="33" t="n">
         <f aca="false">IF('Unit Economics'!$G$42&lt;=0,0,F21/('Unit Economics'!$G$42/'Unit Economics'!$G$7))</f>
-        <v>209.626612968691</v>
+        <v>289.660493948997</v>
       </c>
       <c r="G23" s="33" t="n">
         <f aca="false">IF('Unit Economics'!$G$42&lt;=0,0,G21/('Unit Economics'!$G$42/'Unit Economics'!$G$7))</f>
-        <v>289.235517196937</v>
+        <v>385.363589778356</v>
       </c>
       <c r="H23" s="2"/>
     </row>
@@ -2725,7 +2770,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="15" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="B25" s="16"/>
       <c r="C25" s="16"/>
@@ -2737,12 +2782,12 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>337</v>
+        <v>352</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" s="9" t="n">
         <f aca="false">'Unit Economics'!G25</f>
-        <v>26374.633344</v>
+        <v>21494.26602</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
@@ -2752,12 +2797,12 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>338</v>
+        <v>353</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" s="9" t="n">
         <f aca="false">'Unit Economics'!G42</f>
-        <v>18817.138869024</v>
+        <v>14282.52444948</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
@@ -2767,12 +2812,12 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>339</v>
+        <v>354</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" s="10" t="n">
         <f aca="false">'Unit Economics'!G43</f>
-        <v>0.713455941684389</v>
+        <v>0.664480677599802</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
@@ -2782,7 +2827,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>340</v>
+        <v>355</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" s="9" t="n">
@@ -2797,7 +2842,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>341</v>
+        <v>356</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="41" t="n">
@@ -2809,17 +2854,17 @@
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
       <c r="H30" s="17" t="s">
-        <v>342</v>
+        <v>357</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>343</v>
+        <v>358</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" s="2" t="str">
         <f aca="false">IFERROR(INDEX(C4:G4,MATCH(TRUE(),INDEX(C17:G17&gt;0,0),0)),"Not by FY2031")</f>
-        <v>Not by FY2031</v>
+        <v>2029</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>
@@ -2829,12 +2874,12 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>344</v>
+        <v>359</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" s="9" t="n">
         <f aca="false">'Cash Flow'!C17</f>
-        <v>18667394.0486456</v>
+        <v>14704325.1018862</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" s="2"/>
@@ -2858,7 +2903,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H104"/>
+  <dimension ref="A1:H109"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
@@ -3061,112 +3106,109 @@
       <c r="H12" s="16"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="B13" s="6"/>
-      <c r="C13" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H13" s="6"/>
+      <c r="B13" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" s="21" t="n">
+        <v>4901</v>
+      </c>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="17" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="B14" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="C14" s="21" t="n">
-        <v>20</v>
-      </c>
-      <c r="D14" s="21" t="n">
-        <v>80</v>
-      </c>
-      <c r="E14" s="21" t="n">
-        <v>200</v>
-      </c>
-      <c r="F14" s="21" t="n">
-        <v>400</v>
-      </c>
-      <c r="G14" s="21" t="n">
-        <v>700</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="B14" s="17"/>
+      <c r="C14" s="22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
       <c r="H14" s="17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
+      <c r="A15" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B15" s="17"/>
+      <c r="C15" s="22" t="n">
+        <v>0.74</v>
+      </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
+      <c r="H15" s="17" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="B16" s="16"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="16"/>
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="D17" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="E17" s="18" t="s">
+      <c r="A17" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="F17" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="H17" s="6"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="B18" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="B18" s="2"/>
-      <c r="C18" s="22" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D18" s="22" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E18" s="22" t="n">
-        <v>0.15</v>
+      <c r="C18" s="23" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D18" s="23" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E18" s="23" t="n">
+        <v>1200</v>
       </c>
       <c r="F18" s="23" t="n">
-        <f aca="false">SUM(C18:E18)</f>
-        <v>1</v>
-      </c>
-      <c r="G18" s="2"/>
+        <v>1200</v>
+      </c>
+      <c r="G18" s="23" t="n">
+        <v>1200</v>
+      </c>
       <c r="H18" s="17" t="s">
         <v>58</v>
       </c>
@@ -3175,476 +3217,475 @@
       <c r="A19" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="B19" s="2"/>
-      <c r="C19" s="24" t="n">
-        <v>4000</v>
-      </c>
-      <c r="D19" s="24" t="n">
-        <v>15000</v>
-      </c>
-      <c r="E19" s="24" t="n">
-        <v>45000</v>
-      </c>
-      <c r="F19" s="25" t="n">
-        <f aca="false">SUMPRODUCT(C19:E19,$C$18:$E$18)</f>
-        <v>14000</v>
-      </c>
+      <c r="B19" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="C19" s="21" t="n">
+        <v>400</v>
+      </c>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
       <c r="G19" s="2"/>
       <c r="H19" s="17" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="11" t="s">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="B20" s="2"/>
-      <c r="C20" s="24" t="n">
-        <v>300</v>
-      </c>
-      <c r="D20" s="24" t="n">
-        <v>900</v>
-      </c>
-      <c r="E20" s="24" t="n">
-        <v>2300</v>
-      </c>
-      <c r="F20" s="25" t="n">
-        <f aca="false">SUMPRODUCT(C20:E20,$C$18:$E$18)</f>
-        <v>810</v>
-      </c>
-      <c r="G20" s="2"/>
-      <c r="H20" s="17" t="s">
+      <c r="B21" s="16"/>
+      <c r="C21" s="16"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="16"/>
+      <c r="F21" s="16"/>
+      <c r="G21" s="16"/>
+      <c r="H21" s="16"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="18" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="11" t="s">
+      <c r="D22" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="B21" s="2"/>
-      <c r="C21" s="24" t="n">
-        <v>3</v>
-      </c>
-      <c r="D21" s="24" t="n">
-        <v>6</v>
-      </c>
-      <c r="E21" s="24" t="n">
-        <v>10</v>
-      </c>
-      <c r="F21" s="25" t="n">
-        <f aca="false">SUMPRODUCT(C21:E21,$C$18:$E$18)</f>
-        <v>5.1</v>
-      </c>
-      <c r="G21" s="2"/>
-      <c r="H21" s="17" t="s">
+      <c r="E22" s="18" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="11" t="s">
+      <c r="F22" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="B22" s="2"/>
-      <c r="C22" s="26" t="n">
-        <v>150</v>
-      </c>
-      <c r="D22" s="26" t="n">
-        <v>400</v>
-      </c>
-      <c r="E22" s="26" t="n">
-        <v>900</v>
-      </c>
-      <c r="F22" s="27" t="n">
-        <f aca="false">SUMPRODUCT(C22:E22,$C$18:$E$18)</f>
-        <v>350</v>
-      </c>
       <c r="G22" s="2"/>
-      <c r="H22" s="17" t="s">
+      <c r="H22" s="2"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="11" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2"/>
       <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
+      <c r="C23" s="22" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="D23" s="22" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="E23" s="22" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="F23" s="24" t="n">
+        <f aca="false">SUM(C23:E23)</f>
+        <v>1</v>
+      </c>
       <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
+      <c r="H23" s="17" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="B24" s="16"/>
-      <c r="C24" s="16"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="16"/>
-      <c r="G24" s="16"/>
-      <c r="H24" s="16"/>
+      <c r="A24" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="B24" s="2"/>
+      <c r="C24" s="21" t="n">
+        <v>4000</v>
+      </c>
+      <c r="D24" s="21" t="n">
+        <v>19000</v>
+      </c>
+      <c r="E24" s="21" t="n">
+        <v>60000</v>
+      </c>
+      <c r="F24" s="25" t="n">
+        <f aca="false">SUMPRODUCT(C24:E24,$C$23:$E$23)</f>
+        <v>11070</v>
+      </c>
+      <c r="G24" s="2"/>
+      <c r="H24" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="B25" s="6"/>
-      <c r="C25" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="D25" s="7" t="s">
+      <c r="A25" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="E25" s="7" t="s">
+      <c r="B25" s="2"/>
+      <c r="C25" s="21" t="n">
+        <v>200</v>
+      </c>
+      <c r="D25" s="21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E25" s="21" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F25" s="25" t="n">
+        <f aca="false">SUMPRODUCT(C25:E25,$C$23:$E$23)</f>
+        <v>564</v>
+      </c>
+      <c r="G25" s="2"/>
+      <c r="H25" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="F25" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="G25" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="H25" s="6"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="B26" s="17"/>
-      <c r="C26" s="22" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="D26" s="22" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="E26" s="22" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="F26" s="22" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="G26" s="22" t="n">
-        <v>0.085</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="B26" s="2"/>
+      <c r="C26" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="E26" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="F26" s="25" t="n">
+        <f aca="false">SUMPRODUCT(C26:E26,$C$23:$E$23)</f>
+        <v>4.12</v>
+      </c>
+      <c r="G26" s="2"/>
       <c r="H26" s="17" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="B27" s="2"/>
+      <c r="C27" s="26" t="n">
+        <v>150</v>
+      </c>
+      <c r="D27" s="26" t="n">
+        <v>400</v>
+      </c>
+      <c r="E27" s="26" t="n">
+        <v>900</v>
+      </c>
+      <c r="F27" s="27" t="n">
+        <f aca="false">SUMPRODUCT(C27:E27,$C$23:$E$23)</f>
+        <v>255</v>
+      </c>
+      <c r="G27" s="2"/>
+      <c r="H27" s="17" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="2"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="B27" s="17"/>
-      <c r="C27" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="E27" s="28" t="n">
-        <v>3</v>
-      </c>
-      <c r="F27" s="28" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="G27" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="H27" s="17" t="s">
+      <c r="B29" s="16"/>
+      <c r="C29" s="16"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="16"/>
+      <c r="G29" s="16"/>
+      <c r="H29" s="16"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="5" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="11" t="s">
+      <c r="B30" s="6"/>
+      <c r="C30" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="B28" s="17"/>
-      <c r="C28" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="D28" s="29" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="E28" s="29" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F28" s="29" t="n">
-        <v>0.94</v>
-      </c>
-      <c r="G28" s="29" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="H28" s="17" t="s">
+      <c r="D30" s="7" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="2"/>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="15" t="s">
+      <c r="E30" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="B30" s="16"/>
-      <c r="C30" s="16"/>
-      <c r="D30" s="16"/>
-      <c r="E30" s="16"/>
-      <c r="F30" s="16"/>
-      <c r="G30" s="16"/>
-      <c r="H30" s="16"/>
+      <c r="F30" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="G30" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="H30" s="6"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="B31" s="6"/>
-      <c r="C31" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="E31" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="F31" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="G31" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="H31" s="6"/>
+      <c r="A31" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="B31" s="17"/>
+      <c r="C31" s="22" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D31" s="22" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E31" s="22" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F31" s="22" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="G31" s="22" t="n">
+        <v>0.085</v>
+      </c>
+      <c r="H31" s="17" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="11" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B32" s="17"/>
-      <c r="C32" s="22" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="D32" s="22" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="E32" s="22" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="F32" s="22" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="G32" s="22" t="n">
-        <v>0.38</v>
+      <c r="C32" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="E32" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="F32" s="28" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G32" s="28" t="n">
+        <v>4</v>
       </c>
       <c r="H32" s="17" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="11" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B33" s="17"/>
       <c r="C33" s="29" t="n">
-        <v>0.02</v>
+        <v>1</v>
       </c>
       <c r="D33" s="29" t="n">
-        <v>0.05</v>
+        <v>0.97</v>
       </c>
       <c r="E33" s="29" t="n">
-        <v>0.08</v>
+        <v>0.95</v>
       </c>
       <c r="F33" s="29" t="n">
-        <v>0.1</v>
+        <v>0.94</v>
       </c>
       <c r="G33" s="29" t="n">
-        <v>0.12</v>
+        <v>0.93</v>
       </c>
       <c r="H33" s="17" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="B34" s="17"/>
-      <c r="C34" s="22" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="D34" s="22" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="E34" s="22" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="F34" s="22" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="G34" s="22" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="H34" s="17" t="s">
-        <v>86</v>
-      </c>
+      <c r="A34" s="2"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="B35" s="17"/>
-      <c r="C35" s="29" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D35" s="29" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E35" s="29" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="F35" s="29" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="G35" s="29" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H35" s="17" t="s">
-        <v>88</v>
-      </c>
+      <c r="A35" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="B35" s="16"/>
+      <c r="C35" s="16"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="16"/>
+      <c r="F35" s="16"/>
+      <c r="G35" s="16"/>
+      <c r="H35" s="16"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="B36" s="17"/>
-      <c r="C36" s="29" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D36" s="29" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E36" s="29" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F36" s="29" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="G36" s="29" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="H36" s="17" t="s">
-        <v>90</v>
-      </c>
+      <c r="A36" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B36" s="6"/>
+      <c r="C36" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="G36" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="H36" s="6"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="B37" s="17"/>
+      <c r="C37" s="22" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D37" s="22" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E37" s="22" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F37" s="22" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="G37" s="22" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="H37" s="17" t="s">
         <v>91</v>
-      </c>
-      <c r="B37" s="17"/>
-      <c r="C37" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" s="29" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="E37" s="29" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F37" s="29" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="G37" s="29" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H37" s="17" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="B38" s="17"/>
+      <c r="C38" s="29" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D38" s="29" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E38" s="29" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="F38" s="29" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G38" s="29" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H38" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="B38" s="17"/>
-      <c r="C38" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="F38" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="G38" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="H38" s="17" t="s">
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="11" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="2"/>
-      <c r="B39" s="2"/>
-      <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="2"/>
-      <c r="G39" s="2"/>
-      <c r="H39" s="2"/>
+      <c r="B39" s="17"/>
+      <c r="C39" s="22" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="D39" s="22" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E39" s="22" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F39" s="22" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="G39" s="22" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H39" s="17" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="B40" s="16"/>
-      <c r="C40" s="16"/>
-      <c r="D40" s="16"/>
-      <c r="E40" s="16"/>
-      <c r="F40" s="16"/>
-      <c r="G40" s="16"/>
-      <c r="H40" s="16"/>
+      <c r="A40" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="B40" s="17"/>
+      <c r="C40" s="29" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D40" s="29" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E40" s="29" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F40" s="29" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G40" s="29" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H40" s="17" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="B41" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="C41" s="24" t="n">
-        <v>28</v>
-      </c>
-      <c r="D41" s="2"/>
-      <c r="E41" s="2"/>
-      <c r="F41" s="2"/>
-      <c r="G41" s="2"/>
+        <v>98</v>
+      </c>
+      <c r="B41" s="17"/>
+      <c r="C41" s="29" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D41" s="29" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E41" s="29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F41" s="29" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G41" s="29" t="n">
+        <v>0.65</v>
+      </c>
       <c r="H41" s="17" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="B42" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="C42" s="26" t="n">
-        <v>38</v>
-      </c>
-      <c r="D42" s="2"/>
-      <c r="E42" s="2"/>
-      <c r="F42" s="2"/>
-      <c r="G42" s="2"/>
+      <c r="B42" s="17"/>
+      <c r="C42" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="29" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E42" s="29" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F42" s="29" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G42" s="29" t="n">
+        <v>0.1</v>
+      </c>
       <c r="H42" s="17" t="s">
         <v>101</v>
       </c>
@@ -3653,98 +3694,92 @@
       <c r="A43" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="B43" s="17" t="s">
+      <c r="B43" s="17"/>
+      <c r="C43" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H43" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="C43" s="24" t="n">
-        <v>30</v>
-      </c>
-      <c r="D43" s="2"/>
-      <c r="E43" s="2"/>
-      <c r="F43" s="2"/>
-      <c r="G43" s="2"/>
-      <c r="H43" s="17" t="s">
-        <v>104</v>
-      </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="B44" s="17"/>
-      <c r="C44" s="29" t="n">
-        <v>0.08</v>
-      </c>
+      <c r="A44" s="2"/>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
       <c r="D44" s="2"/>
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
-      <c r="H44" s="17" t="s">
-        <v>106</v>
-      </c>
+      <c r="H44" s="2"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="B45" s="17" t="s">
-        <v>100</v>
-      </c>
-      <c r="C45" s="26" t="n">
-        <v>39</v>
-      </c>
-      <c r="D45" s="2"/>
-      <c r="E45" s="2"/>
-      <c r="F45" s="2"/>
-      <c r="G45" s="2"/>
-      <c r="H45" s="17" t="s">
-        <v>108</v>
-      </c>
+      <c r="A45" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="B45" s="16"/>
+      <c r="C45" s="16"/>
+      <c r="D45" s="16"/>
+      <c r="E45" s="16"/>
+      <c r="F45" s="16"/>
+      <c r="G45" s="16"/>
+      <c r="H45" s="16"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="11" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B46" s="17" t="s">
-        <v>100</v>
-      </c>
-      <c r="C46" s="26" t="n">
-        <v>99</v>
+        <v>106</v>
+      </c>
+      <c r="C46" s="21" t="n">
+        <v>28</v>
       </c>
       <c r="D46" s="2"/>
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
       <c r="H46" s="17" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="11" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B47" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="C47" s="24" t="n">
-        <v>300</v>
+        <v>109</v>
+      </c>
+      <c r="C47" s="26" t="n">
+        <v>38</v>
       </c>
       <c r="D47" s="2"/>
       <c r="E47" s="2"/>
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
       <c r="H47" s="17" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="11" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B48" s="17" t="s">
-        <v>115</v>
-      </c>
-      <c r="C48" s="26" t="n">
+        <v>112</v>
+      </c>
+      <c r="C48" s="21" t="n">
         <v>30</v>
       </c>
       <c r="D48" s="2"/>
@@ -3752,64 +3787,78 @@
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
       <c r="H48" s="17" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="B49" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="C49" s="30" t="n">
-        <v>6</v>
+        <v>114</v>
+      </c>
+      <c r="B49" s="17"/>
+      <c r="C49" s="29" t="n">
+        <v>0.08</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" s="2"/>
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
       <c r="H49" s="17" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="B50" s="17"/>
-      <c r="C50" s="29" t="n">
-        <v>0.8</v>
+        <v>116</v>
+      </c>
+      <c r="B50" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="C50" s="26" t="n">
+        <v>39</v>
       </c>
       <c r="D50" s="2"/>
       <c r="E50" s="2"/>
       <c r="F50" s="2"/>
       <c r="G50" s="2"/>
       <c r="H50" s="17" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="2"/>
-      <c r="B51" s="2"/>
-      <c r="C51" s="2"/>
+      <c r="A51" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="B51" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="C51" s="26" t="n">
+        <v>99</v>
+      </c>
       <c r="D51" s="2"/>
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
       <c r="G51" s="2"/>
-      <c r="H51" s="2"/>
+      <c r="H51" s="17" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="15" t="s">
+      <c r="A52" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="B52" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="C52" s="21" t="n">
+        <v>300</v>
+      </c>
+      <c r="D52" s="2"/>
+      <c r="E52" s="2"/>
+      <c r="F52" s="2"/>
+      <c r="G52" s="2"/>
+      <c r="H52" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="B52" s="16"/>
-      <c r="C52" s="16"/>
-      <c r="D52" s="16"/>
-      <c r="E52" s="16"/>
-      <c r="F52" s="16"/>
-      <c r="G52" s="16"/>
-      <c r="H52" s="16"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="11" t="s">
@@ -3818,8 +3867,8 @@
       <c r="B53" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="C53" s="31" t="n">
-        <v>0.12</v>
+      <c r="C53" s="26" t="n">
+        <v>30</v>
       </c>
       <c r="D53" s="2"/>
       <c r="E53" s="2"/>
@@ -3837,7 +3886,7 @@
         <v>127</v>
       </c>
       <c r="C54" s="30" t="n">
-        <v>0.5</v>
+        <v>6</v>
       </c>
       <c r="D54" s="2"/>
       <c r="E54" s="2"/>
@@ -3851,11 +3900,9 @@
       <c r="A55" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="B55" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="C55" s="30" t="n">
-        <v>5</v>
+      <c r="B55" s="17"/>
+      <c r="C55" s="29" t="n">
+        <v>0.8</v>
       </c>
       <c r="D55" s="2"/>
       <c r="E55" s="2"/>
@@ -3866,99 +3913,87 @@
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="B56" s="17" t="s">
-        <v>100</v>
-      </c>
-      <c r="C56" s="26" t="n">
-        <v>25</v>
-      </c>
+      <c r="A56" s="2"/>
+      <c r="B56" s="2"/>
+      <c r="C56" s="2"/>
       <c r="D56" s="2"/>
       <c r="E56" s="2"/>
       <c r="F56" s="2"/>
       <c r="G56" s="2"/>
-      <c r="H56" s="17" t="s">
-        <v>132</v>
-      </c>
+      <c r="H56" s="2"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="B57" s="17" t="s">
-        <v>134</v>
-      </c>
-      <c r="C57" s="30" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D57" s="2"/>
-      <c r="E57" s="2"/>
-      <c r="F57" s="2"/>
-      <c r="G57" s="2"/>
-      <c r="H57" s="17" t="s">
-        <v>135</v>
-      </c>
+      <c r="A57" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="B57" s="16"/>
+      <c r="C57" s="16"/>
+      <c r="D57" s="16"/>
+      <c r="E57" s="16"/>
+      <c r="F57" s="16"/>
+      <c r="G57" s="16"/>
+      <c r="H57" s="16"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="B58" s="17"/>
-      <c r="C58" s="29" t="n">
-        <v>0.029</v>
+        <v>132</v>
+      </c>
+      <c r="B58" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="C58" s="31" t="n">
+        <v>0.12</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" s="2"/>
       <c r="F58" s="2"/>
       <c r="G58" s="2"/>
       <c r="H58" s="17" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="11" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B59" s="17" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C59" s="30" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="D59" s="2"/>
       <c r="E59" s="2"/>
       <c r="F59" s="2"/>
       <c r="G59" s="2"/>
       <c r="H59" s="17" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="11" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B60" s="17" t="s">
-        <v>142</v>
-      </c>
-      <c r="C60" s="26" t="n">
-        <v>20</v>
+        <v>136</v>
+      </c>
+      <c r="C60" s="30" t="n">
+        <v>5</v>
       </c>
       <c r="D60" s="2"/>
       <c r="E60" s="2"/>
       <c r="F60" s="2"/>
       <c r="G60" s="2"/>
       <c r="H60" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="11" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B61" s="17" t="s">
-        <v>145</v>
+        <v>109</v>
       </c>
       <c r="C61" s="26" t="n">
         <v>25</v>
@@ -3968,523 +4003,515 @@
       <c r="F61" s="2"/>
       <c r="G61" s="2"/>
       <c r="H61" s="17" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="11" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="B62" s="17" t="s">
-        <v>145</v>
-      </c>
-      <c r="C62" s="26" t="n">
-        <v>15</v>
+        <v>143</v>
+      </c>
+      <c r="C62" s="30" t="n">
+        <v>0.1</v>
       </c>
       <c r="D62" s="2"/>
       <c r="E62" s="2"/>
       <c r="F62" s="2"/>
       <c r="G62" s="2"/>
       <c r="H62" s="17" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="11" t="s">
-        <v>148</v>
-      </c>
-      <c r="B63" s="17" t="s">
         <v>145</v>
       </c>
-      <c r="C63" s="32" t="n">
-        <v>1500</v>
+      <c r="B63" s="17"/>
+      <c r="C63" s="29" t="n">
+        <v>0.029</v>
       </c>
       <c r="D63" s="2"/>
       <c r="E63" s="2"/>
       <c r="F63" s="2"/>
       <c r="G63" s="2"/>
       <c r="H63" s="17" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="11" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B64" s="17" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C64" s="30" t="n">
-        <v>2</v>
+        <v>0.3</v>
       </c>
       <c r="D64" s="2"/>
       <c r="E64" s="2"/>
       <c r="F64" s="2"/>
       <c r="G64" s="2"/>
       <c r="H64" s="17" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="11" t="s">
-        <v>152</v>
-      </c>
-      <c r="B65" s="17"/>
-      <c r="C65" s="29" t="n">
-        <v>0.4</v>
+        <v>150</v>
+      </c>
+      <c r="B65" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="C65" s="26" t="n">
+        <v>20</v>
       </c>
       <c r="D65" s="2"/>
       <c r="E65" s="2"/>
       <c r="F65" s="2"/>
       <c r="G65" s="2"/>
       <c r="H65" s="17" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="11" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="2"/>
-      <c r="B66" s="2"/>
-      <c r="C66" s="2"/>
+      <c r="B66" s="17" t="s">
+        <v>154</v>
+      </c>
+      <c r="C66" s="26" t="n">
+        <v>25</v>
+      </c>
       <c r="D66" s="2"/>
       <c r="E66" s="2"/>
       <c r="F66" s="2"/>
       <c r="G66" s="2"/>
-      <c r="H66" s="2"/>
+      <c r="H66" s="17" t="s">
+        <v>155</v>
+      </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="15" t="s">
+      <c r="A67" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="B67" s="17" t="s">
         <v>154</v>
       </c>
-      <c r="B67" s="16"/>
-      <c r="C67" s="16"/>
-      <c r="D67" s="16"/>
-      <c r="E67" s="16"/>
-      <c r="F67" s="16"/>
-      <c r="G67" s="16"/>
-      <c r="H67" s="16"/>
+      <c r="C67" s="26" t="n">
+        <v>15</v>
+      </c>
+      <c r="D67" s="2"/>
+      <c r="E67" s="2"/>
+      <c r="F67" s="2"/>
+      <c r="G67" s="2"/>
+      <c r="H67" s="17" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="11" t="s">
-        <v>155</v>
-      </c>
-      <c r="B68" s="17"/>
-      <c r="C68" s="29" t="n">
-        <v>0.25</v>
+        <v>157</v>
+      </c>
+      <c r="B68" s="17" t="s">
+        <v>154</v>
+      </c>
+      <c r="C68" s="32" t="n">
+        <v>1500</v>
       </c>
       <c r="D68" s="2"/>
       <c r="E68" s="2"/>
       <c r="F68" s="2"/>
       <c r="G68" s="2"/>
       <c r="H68" s="17" t="s">
-        <v>143</v>
+        <v>158</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="11" t="s">
-        <v>156</v>
-      </c>
-      <c r="B69" s="17"/>
-      <c r="C69" s="29" t="n">
-        <v>0.03</v>
+        <v>159</v>
+      </c>
+      <c r="B69" s="17" t="s">
+        <v>160</v>
+      </c>
+      <c r="C69" s="30" t="n">
+        <v>2</v>
       </c>
       <c r="D69" s="2"/>
       <c r="E69" s="2"/>
       <c r="F69" s="2"/>
       <c r="G69" s="2"/>
       <c r="H69" s="17" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="11" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B70" s="17"/>
       <c r="C70" s="29" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="D70" s="2"/>
       <c r="E70" s="2"/>
       <c r="F70" s="2"/>
       <c r="G70" s="2"/>
       <c r="H70" s="17" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="B71" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="C71" s="21" t="n">
-        <v>40</v>
-      </c>
+      <c r="A71" s="2"/>
+      <c r="B71" s="2"/>
+      <c r="C71" s="2"/>
       <c r="D71" s="2"/>
       <c r="E71" s="2"/>
       <c r="F71" s="2"/>
       <c r="G71" s="2"/>
-      <c r="H71" s="17" t="s">
-        <v>160</v>
-      </c>
+      <c r="H71" s="2"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="11" t="s">
-        <v>161</v>
-      </c>
-      <c r="B72" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="C72" s="21" t="n">
-        <v>30</v>
-      </c>
-      <c r="D72" s="2"/>
-      <c r="E72" s="2"/>
-      <c r="F72" s="2"/>
-      <c r="G72" s="2"/>
-      <c r="H72" s="17" t="s">
-        <v>162</v>
-      </c>
+      <c r="A72" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="B72" s="16"/>
+      <c r="C72" s="16"/>
+      <c r="D72" s="16"/>
+      <c r="E72" s="16"/>
+      <c r="F72" s="16"/>
+      <c r="G72" s="16"/>
+      <c r="H72" s="16"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="11" t="s">
-        <v>163</v>
-      </c>
-      <c r="B73" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="C73" s="24" t="n">
-        <v>120</v>
+        <v>164</v>
+      </c>
+      <c r="B73" s="17"/>
+      <c r="C73" s="29" t="n">
+        <v>0.25</v>
       </c>
       <c r="D73" s="2"/>
       <c r="E73" s="2"/>
       <c r="F73" s="2"/>
       <c r="G73" s="2"/>
       <c r="H73" s="17" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="2"/>
-      <c r="B74" s="2"/>
-      <c r="C74" s="2"/>
+      <c r="A74" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="B74" s="17"/>
+      <c r="C74" s="29" t="n">
+        <v>0.03</v>
+      </c>
       <c r="D74" s="2"/>
       <c r="E74" s="2"/>
       <c r="F74" s="2"/>
       <c r="G74" s="2"/>
-      <c r="H74" s="2"/>
+      <c r="H74" s="17" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="15" t="s">
-        <v>164</v>
-      </c>
-      <c r="B75" s="16"/>
-      <c r="C75" s="16"/>
-      <c r="D75" s="16"/>
-      <c r="E75" s="16"/>
-      <c r="F75" s="16"/>
-      <c r="G75" s="16"/>
-      <c r="H75" s="16"/>
+      <c r="A75" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="B75" s="17"/>
+      <c r="C75" s="29" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D75" s="2"/>
+      <c r="E75" s="2"/>
+      <c r="F75" s="2"/>
+      <c r="G75" s="2"/>
+      <c r="H75" s="17" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="11" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B76" s="17" t="s">
-        <v>142</v>
-      </c>
-      <c r="C76" s="26" t="n">
-        <v>160000</v>
+        <v>57</v>
+      </c>
+      <c r="C76" s="23" t="n">
+        <v>40</v>
       </c>
       <c r="D76" s="2"/>
       <c r="E76" s="2"/>
       <c r="F76" s="2"/>
       <c r="G76" s="2"/>
       <c r="H76" s="17" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="11" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B77" s="17" t="s">
-        <v>142</v>
-      </c>
-      <c r="C77" s="26" t="n">
-        <v>170000</v>
+        <v>57</v>
+      </c>
+      <c r="C77" s="23" t="n">
+        <v>30</v>
       </c>
       <c r="D77" s="2"/>
       <c r="E77" s="2"/>
       <c r="F77" s="2"/>
       <c r="G77" s="2"/>
       <c r="H77" s="17" t="s">
-        <v>143</v>
+        <v>171</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="11" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B78" s="17" t="s">
-        <v>142</v>
-      </c>
-      <c r="C78" s="26" t="n">
-        <v>70000</v>
+        <v>57</v>
+      </c>
+      <c r="C78" s="21" t="n">
+        <v>120</v>
       </c>
       <c r="D78" s="2"/>
       <c r="E78" s="2"/>
       <c r="F78" s="2"/>
       <c r="G78" s="2"/>
       <c r="H78" s="17" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="B79" s="17" t="s">
-        <v>142</v>
-      </c>
-      <c r="C79" s="26" t="n">
-        <v>65000</v>
-      </c>
+      <c r="A79" s="2"/>
+      <c r="B79" s="2"/>
+      <c r="C79" s="2"/>
       <c r="D79" s="2"/>
       <c r="E79" s="2"/>
       <c r="F79" s="2"/>
       <c r="G79" s="2"/>
-      <c r="H79" s="17" t="s">
-        <v>143</v>
-      </c>
+      <c r="H79" s="2"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="11" t="s">
-        <v>169</v>
-      </c>
-      <c r="B80" s="17" t="s">
-        <v>142</v>
-      </c>
-      <c r="C80" s="26" t="n">
-        <v>55000</v>
-      </c>
-      <c r="D80" s="2"/>
-      <c r="E80" s="2"/>
-      <c r="F80" s="2"/>
-      <c r="G80" s="2"/>
-      <c r="H80" s="17" t="s">
-        <v>143</v>
-      </c>
+      <c r="A80" s="15" t="s">
+        <v>173</v>
+      </c>
+      <c r="B80" s="16"/>
+      <c r="C80" s="16"/>
+      <c r="D80" s="16"/>
+      <c r="E80" s="16"/>
+      <c r="F80" s="16"/>
+      <c r="G80" s="16"/>
+      <c r="H80" s="16"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="11" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B81" s="17" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="C81" s="26" t="n">
-        <v>110000</v>
+        <v>160000</v>
       </c>
       <c r="D81" s="2"/>
       <c r="E81" s="2"/>
       <c r="F81" s="2"/>
       <c r="G81" s="2"/>
       <c r="H81" s="17" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="2"/>
-      <c r="B82" s="2"/>
-      <c r="C82" s="2"/>
+      <c r="A82" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="B82" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="C82" s="26" t="n">
+        <v>170000</v>
+      </c>
       <c r="D82" s="2"/>
       <c r="E82" s="2"/>
       <c r="F82" s="2"/>
       <c r="G82" s="2"/>
-      <c r="H82" s="2"/>
+      <c r="H82" s="17" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="B83" s="16"/>
-      <c r="C83" s="16"/>
-      <c r="D83" s="16"/>
-      <c r="E83" s="16"/>
-      <c r="F83" s="16"/>
-      <c r="G83" s="16"/>
-      <c r="H83" s="16"/>
+      <c r="A83" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="B83" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="C83" s="26" t="n">
+        <v>70000</v>
+      </c>
+      <c r="D83" s="2"/>
+      <c r="E83" s="2"/>
+      <c r="F83" s="2"/>
+      <c r="G83" s="2"/>
+      <c r="H83" s="17" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B84" s="6"/>
-      <c r="C84" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="D84" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="E84" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F84" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G84" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H84" s="6"/>
+      <c r="A84" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="B84" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="C84" s="26" t="n">
+        <v>65000</v>
+      </c>
+      <c r="D84" s="2"/>
+      <c r="E84" s="2"/>
+      <c r="F84" s="2"/>
+      <c r="G84" s="2"/>
+      <c r="H84" s="17" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="11" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="B85" s="17" t="s">
-        <v>172</v>
-      </c>
-      <c r="C85" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="D85" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="E85" s="24" t="n">
-        <v>3</v>
-      </c>
-      <c r="F85" s="24" t="n">
-        <v>4</v>
-      </c>
-      <c r="G85" s="24" t="n">
-        <v>5</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="C85" s="26" t="n">
+        <v>55000</v>
+      </c>
+      <c r="D85" s="2"/>
+      <c r="E85" s="2"/>
+      <c r="F85" s="2"/>
+      <c r="G85" s="2"/>
       <c r="H85" s="17" t="s">
-        <v>173</v>
+        <v>152</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="B86" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="C86" s="26" t="n">
+        <v>110000</v>
+      </c>
+      <c r="D86" s="2"/>
+      <c r="E86" s="2"/>
+      <c r="F86" s="2"/>
+      <c r="G86" s="2"/>
+      <c r="H86" s="17" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="2"/>
+      <c r="B87" s="2"/>
+      <c r="C87" s="2"/>
+      <c r="D87" s="2"/>
+      <c r="E87" s="2"/>
+      <c r="F87" s="2"/>
+      <c r="G87" s="2"/>
+      <c r="H87" s="2"/>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="B88" s="16"/>
+      <c r="C88" s="16"/>
+      <c r="D88" s="16"/>
+      <c r="E88" s="16"/>
+      <c r="F88" s="16"/>
+      <c r="G88" s="16"/>
+      <c r="H88" s="16"/>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B89" s="6"/>
+      <c r="C89" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D89" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E89" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F89" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="G89" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="H89" s="6"/>
+    </row>
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="11" t="s">
         <v>174</v>
       </c>
-      <c r="B86" s="17" t="s">
-        <v>172</v>
-      </c>
-      <c r="C86" s="24" t="n">
+      <c r="B90" s="17" t="s">
+        <v>181</v>
+      </c>
+      <c r="C90" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D90" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E90" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="D86" s="24" t="n">
+      <c r="F90" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="G90" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="E86" s="24" t="n">
-        <v>8</v>
-      </c>
-      <c r="F86" s="24" t="n">
-        <v>11</v>
-      </c>
-      <c r="G86" s="24" t="n">
-        <v>14</v>
-      </c>
-      <c r="H86" s="17" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="11" t="s">
-        <v>170</v>
-      </c>
-      <c r="B87" s="17" t="s">
-        <v>172</v>
-      </c>
-      <c r="C87" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="D87" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E87" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="F87" s="24" t="n">
-        <v>3</v>
-      </c>
-      <c r="G87" s="24" t="n">
-        <v>4</v>
-      </c>
-      <c r="H87" s="17" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="2"/>
-      <c r="B88" s="2"/>
-      <c r="C88" s="2"/>
-      <c r="D88" s="2"/>
-      <c r="E88" s="2"/>
-      <c r="F88" s="2"/>
-      <c r="G88" s="2"/>
-      <c r="H88" s="2"/>
-    </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="15" t="s">
-        <v>175</v>
-      </c>
-      <c r="B89" s="16"/>
-      <c r="C89" s="16"/>
-      <c r="D89" s="16"/>
-      <c r="E89" s="16"/>
-      <c r="F89" s="16"/>
-      <c r="G89" s="16"/>
-      <c r="H89" s="16"/>
-    </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B90" s="6"/>
-      <c r="C90" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="D90" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="E90" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F90" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G90" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H90" s="6"/>
+      <c r="H90" s="17" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="11" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="B91" s="17" t="s">
-        <v>177</v>
-      </c>
-      <c r="C91" s="26" t="n">
-        <v>50000</v>
-      </c>
-      <c r="D91" s="26" t="n">
-        <v>150000</v>
-      </c>
-      <c r="E91" s="26" t="n">
-        <v>300000</v>
-      </c>
-      <c r="F91" s="26" t="n">
-        <v>500000</v>
-      </c>
-      <c r="G91" s="26" t="n">
-        <v>700000</v>
+        <v>181</v>
+      </c>
+      <c r="C91" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D91" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="E91" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="F91" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="G91" s="21" t="n">
+        <v>14</v>
       </c>
       <c r="H91" s="17" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4492,169 +4519,193 @@
         <v>179</v>
       </c>
       <c r="B92" s="17" t="s">
-        <v>177</v>
-      </c>
-      <c r="C92" s="26" t="n">
-        <v>60000</v>
-      </c>
-      <c r="D92" s="26" t="n">
-        <v>90000</v>
-      </c>
-      <c r="E92" s="26" t="n">
-        <v>140000</v>
-      </c>
-      <c r="F92" s="26" t="n">
-        <v>200000</v>
-      </c>
-      <c r="G92" s="26" t="n">
-        <v>260000</v>
+        <v>181</v>
+      </c>
+      <c r="C92" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D92" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E92" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="F92" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="G92" s="21" t="n">
+        <v>4</v>
       </c>
       <c r="H92" s="17" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="B93" s="17" t="s">
-        <v>182</v>
-      </c>
-      <c r="C93" s="26" t="n">
-        <v>100</v>
-      </c>
+      <c r="A93" s="2"/>
+      <c r="B93" s="2"/>
+      <c r="C93" s="2"/>
       <c r="D93" s="2"/>
       <c r="E93" s="2"/>
       <c r="F93" s="2"/>
       <c r="G93" s="2"/>
-      <c r="H93" s="17" t="s">
-        <v>143</v>
-      </c>
+      <c r="H93" s="2"/>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="11" t="s">
-        <v>183</v>
-      </c>
-      <c r="B94" s="17" t="s">
-        <v>142</v>
-      </c>
-      <c r="C94" s="26" t="n">
-        <v>3000</v>
-      </c>
-      <c r="D94" s="2"/>
-      <c r="E94" s="2"/>
-      <c r="F94" s="2"/>
-      <c r="G94" s="2"/>
-      <c r="H94" s="17" t="s">
-        <v>143</v>
-      </c>
+      <c r="A94" s="15" t="s">
+        <v>184</v>
+      </c>
+      <c r="B94" s="16"/>
+      <c r="C94" s="16"/>
+      <c r="D94" s="16"/>
+      <c r="E94" s="16"/>
+      <c r="F94" s="16"/>
+      <c r="G94" s="16"/>
+      <c r="H94" s="16"/>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="B95" s="17" t="s">
-        <v>185</v>
-      </c>
-      <c r="C95" s="26" t="n">
-        <v>2500</v>
-      </c>
-      <c r="D95" s="2"/>
-      <c r="E95" s="2"/>
-      <c r="F95" s="2"/>
-      <c r="G95" s="2"/>
-      <c r="H95" s="17" t="s">
-        <v>143</v>
-      </c>
+      <c r="A95" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B95" s="6"/>
+      <c r="C95" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D95" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E95" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F95" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="G95" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="H95" s="6"/>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="B96" s="17" t="s">
         <v>186</v>
       </c>
-      <c r="B96" s="17" t="s">
+      <c r="C96" s="26" t="n">
+        <v>50000</v>
+      </c>
+      <c r="D96" s="26" t="n">
+        <v>150000</v>
+      </c>
+      <c r="E96" s="26" t="n">
+        <v>300000</v>
+      </c>
+      <c r="F96" s="26" t="n">
+        <v>500000</v>
+      </c>
+      <c r="G96" s="26" t="n">
+        <v>700000</v>
+      </c>
+      <c r="H96" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="C96" s="24" t="n">
-        <v>3</v>
-      </c>
-      <c r="D96" s="2"/>
-      <c r="E96" s="2"/>
-      <c r="F96" s="2"/>
-      <c r="G96" s="2"/>
-      <c r="H96" s="17" t="s">
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="11" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="2"/>
-      <c r="B97" s="2"/>
-      <c r="C97" s="2"/>
-      <c r="D97" s="2"/>
-      <c r="E97" s="2"/>
-      <c r="F97" s="2"/>
-      <c r="G97" s="2"/>
-      <c r="H97" s="2"/>
+      <c r="B97" s="17" t="s">
+        <v>186</v>
+      </c>
+      <c r="C97" s="26" t="n">
+        <v>60000</v>
+      </c>
+      <c r="D97" s="26" t="n">
+        <v>90000</v>
+      </c>
+      <c r="E97" s="26" t="n">
+        <v>140000</v>
+      </c>
+      <c r="F97" s="26" t="n">
+        <v>200000</v>
+      </c>
+      <c r="G97" s="26" t="n">
+        <v>260000</v>
+      </c>
+      <c r="H97" s="17" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="15" t="s">
-        <v>189</v>
-      </c>
-      <c r="B98" s="16"/>
-      <c r="C98" s="16"/>
-      <c r="D98" s="16"/>
-      <c r="E98" s="16"/>
-      <c r="F98" s="16"/>
-      <c r="G98" s="16"/>
-      <c r="H98" s="16"/>
+      <c r="A98" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="B98" s="17" t="s">
+        <v>191</v>
+      </c>
+      <c r="C98" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="D98" s="2"/>
+      <c r="E98" s="2"/>
+      <c r="F98" s="2"/>
+      <c r="G98" s="2"/>
+      <c r="H98" s="17" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="11" t="s">
-        <v>190</v>
-      </c>
-      <c r="B99" s="17"/>
-      <c r="C99" s="29" t="n">
-        <v>0.25</v>
+        <v>192</v>
+      </c>
+      <c r="B99" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="C99" s="26" t="n">
+        <v>3000</v>
       </c>
       <c r="D99" s="2"/>
       <c r="E99" s="2"/>
       <c r="F99" s="2"/>
       <c r="G99" s="2"/>
       <c r="H99" s="17" t="s">
-        <v>191</v>
+        <v>152</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="11" t="s">
-        <v>192</v>
-      </c>
-      <c r="B100" s="17"/>
-      <c r="C100" s="29" t="n">
-        <v>0.03</v>
+        <v>193</v>
+      </c>
+      <c r="B100" s="17" t="s">
+        <v>194</v>
+      </c>
+      <c r="C100" s="26" t="n">
+        <v>2500</v>
       </c>
       <c r="D100" s="2"/>
       <c r="E100" s="2"/>
       <c r="F100" s="2"/>
       <c r="G100" s="2"/>
       <c r="H100" s="17" t="s">
-        <v>193</v>
+        <v>152</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="11" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B101" s="17" t="s">
-        <v>177</v>
-      </c>
-      <c r="C101" s="32" t="n">
-        <v>250000</v>
+        <v>196</v>
+      </c>
+      <c r="C101" s="21" t="n">
+        <v>3</v>
       </c>
       <c r="D101" s="2"/>
       <c r="E101" s="2"/>
       <c r="F101" s="2"/>
       <c r="G101" s="2"/>
       <c r="H101" s="17" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4668,51 +4719,123 @@
       <c r="H102" s="2"/>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B103" s="6"/>
-      <c r="C103" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="D103" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="E103" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F103" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G103" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H103" s="6"/>
+      <c r="A103" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="B103" s="16"/>
+      <c r="C103" s="16"/>
+      <c r="D103" s="16"/>
+      <c r="E103" s="16"/>
+      <c r="F103" s="16"/>
+      <c r="G103" s="16"/>
+      <c r="H103" s="16"/>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="B104" s="17" t="s">
-        <v>177</v>
-      </c>
-      <c r="C104" s="32" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="D104" s="32" t="n">
-        <v>8000000</v>
-      </c>
-      <c r="E104" s="32" t="n">
+        <v>199</v>
+      </c>
+      <c r="B104" s="17"/>
+      <c r="C104" s="29" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D104" s="2"/>
+      <c r="E104" s="2"/>
+      <c r="F104" s="2"/>
+      <c r="G104" s="2"/>
+      <c r="H104" s="17" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="B105" s="17"/>
+      <c r="C105" s="29" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D105" s="2"/>
+      <c r="E105" s="2"/>
+      <c r="F105" s="2"/>
+      <c r="G105" s="2"/>
+      <c r="H105" s="17" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="B106" s="17" t="s">
+        <v>186</v>
+      </c>
+      <c r="C106" s="32" t="n">
+        <v>250000</v>
+      </c>
+      <c r="D106" s="2"/>
+      <c r="E106" s="2"/>
+      <c r="F106" s="2"/>
+      <c r="G106" s="2"/>
+      <c r="H106" s="17" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="2"/>
+      <c r="B107" s="2"/>
+      <c r="C107" s="2"/>
+      <c r="D107" s="2"/>
+      <c r="E107" s="2"/>
+      <c r="F107" s="2"/>
+      <c r="G107" s="2"/>
+      <c r="H107" s="2"/>
+    </row>
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B108" s="6"/>
+      <c r="C108" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D108" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E108" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F108" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="G108" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="H108" s="6"/>
+    </row>
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="11" t="s">
+        <v>205</v>
+      </c>
+      <c r="B109" s="17" t="s">
+        <v>186</v>
+      </c>
+      <c r="C109" s="32" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="D109" s="32" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="E109" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="F104" s="32" t="n">
-        <v>15000000</v>
-      </c>
-      <c r="G104" s="32" t="n">
+      <c r="F109" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="H104" s="17" t="s">
-        <v>197</v>
+      <c r="G109" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" s="17" t="s">
+        <v>206</v>
       </c>
     </row>
   </sheetData>
@@ -4731,7 +4854,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
@@ -4742,7 +4865,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -4754,7 +4877,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4776,7 +4899,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="7" t="s">
@@ -4798,55 +4921,57 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="B5" s="2"/>
-      <c r="C5" s="8" t="n">
-        <f aca="false">ROUND(Assumptions!C$14*Assumptions!$F$7,0)</f>
-        <v>20</v>
-      </c>
-      <c r="D5" s="8" t="n">
-        <f aca="false">ROUND(Assumptions!D$14*Assumptions!$F$7,0)</f>
-        <v>80</v>
-      </c>
-      <c r="E5" s="8" t="n">
-        <f aca="false">ROUND(Assumptions!E$14*Assumptions!$F$7,0)</f>
-        <v>200</v>
-      </c>
-      <c r="F5" s="8" t="n">
-        <f aca="false">ROUND(Assumptions!F$14*Assumptions!$F$7,0)</f>
-        <v>400</v>
-      </c>
-      <c r="G5" s="8" t="n">
-        <f aca="false">ROUND(Assumptions!G$14*Assumptions!$F$7,0)</f>
-        <v>700</v>
-      </c>
-      <c r="H5" s="2"/>
+      <c r="C5" s="33" t="n">
+        <f aca="false">MAX(0,MIN(ROUND(Assumptions!C$18*Assumptions!$F$7,0),$C$10))</f>
+        <v>1200</v>
+      </c>
+      <c r="D5" s="33" t="n">
+        <f aca="false">MAX(0,MIN(ROUND(Assumptions!D$18*Assumptions!$F$7,0),$C$10-C6))</f>
+        <v>613</v>
+      </c>
+      <c r="E5" s="33" t="n">
+        <f aca="false">MAX(0,MIN(ROUND(Assumptions!E$18*Assumptions!$F$7,0),$C$10-D6))</f>
+        <v>0</v>
+      </c>
+      <c r="F5" s="33" t="n">
+        <f aca="false">MAX(0,MIN(ROUND(Assumptions!F$18*Assumptions!$F$7,0),$C$10-E6))</f>
+        <v>0</v>
+      </c>
+      <c r="G5" s="33" t="n">
+        <f aca="false">MAX(0,MIN(ROUND(Assumptions!G$18*Assumptions!$F$7,0),$C$10-F6))</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="33" t="n">
         <f aca="false">C5</f>
-        <v>20</v>
+        <v>1200</v>
       </c>
       <c r="D6" s="33" t="n">
         <f aca="false">C6+D5</f>
-        <v>100</v>
+        <v>1813</v>
       </c>
       <c r="E6" s="33" t="n">
         <f aca="false">D6+E5</f>
-        <v>300</v>
+        <v>1813</v>
       </c>
       <c r="F6" s="33" t="n">
         <f aca="false">E6+F5</f>
-        <v>700</v>
+        <v>1813</v>
       </c>
       <c r="G6" s="33" t="n">
         <f aca="false">F6+G5</f>
-        <v>1400</v>
+        <v>1813</v>
       </c>
       <c r="H6" s="2"/>
     </row>
@@ -4856,57 +4981,111 @@
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="33" t="n">
-        <f aca="false">C$5*Assumptions!$C$28</f>
-        <v>20</v>
+        <f aca="false">C$5*Assumptions!$C$33</f>
+        <v>1200</v>
       </c>
       <c r="D7" s="33" t="n">
-        <f aca="false">C$5*Assumptions!$D$28+D$5*Assumptions!$C$28</f>
-        <v>99.4</v>
+        <f aca="false">C$5*Assumptions!$D$33+D$5*Assumptions!$C$33</f>
+        <v>1777</v>
       </c>
       <c r="E7" s="33" t="n">
-        <f aca="false">C$5*Assumptions!$E$28+D$5*Assumptions!$D$28+E$5*Assumptions!$C$28</f>
-        <v>296.6</v>
+        <f aca="false">C$5*Assumptions!$E$33+D$5*Assumptions!$D$33+E$5*Assumptions!$C$33</f>
+        <v>1734.61</v>
       </c>
       <c r="F7" s="33" t="n">
-        <f aca="false">C$5*Assumptions!$F$28+D$5*Assumptions!$E$28+E$5*Assumptions!$D$28+F$5*Assumptions!$C$28</f>
-        <v>688.8</v>
+        <f aca="false">C$5*Assumptions!$F$33+D$5*Assumptions!$E$33+E$5*Assumptions!$D$33+F$5*Assumptions!$C$33</f>
+        <v>1710.35</v>
       </c>
       <c r="G7" s="33" t="n">
-        <f aca="false">C$5*Assumptions!$G$28+D$5*Assumptions!$F$28+E$5*Assumptions!$E$28+F$5*Assumptions!$D$28+G$5*Assumptions!$C$28</f>
-        <v>1371.8</v>
+        <f aca="false">C$5*Assumptions!$G$33+D$5*Assumptions!$F$33+E$5*Assumptions!$E$33+F$5*Assumptions!$D$33+G$5*Assumptions!$C$33</f>
+        <v>1692.22</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="33" t="n">
         <f aca="false">C7/2</f>
-        <v>10</v>
+        <v>600</v>
       </c>
       <c r="D8" s="33" t="n">
         <f aca="false">(C7+D7)/2</f>
-        <v>59.7</v>
+        <v>1488.5</v>
       </c>
       <c r="E8" s="33" t="n">
         <f aca="false">(D7+E7)/2</f>
-        <v>198</v>
+        <v>1755.805</v>
       </c>
       <c r="F8" s="33" t="n">
         <f aca="false">(E7+F7)/2</f>
-        <v>492.7</v>
+        <v>1722.48</v>
       </c>
       <c r="G8" s="33" t="n">
         <f aca="false">(F7+G7)/2</f>
-        <v>1030.3</v>
+        <v>1701.285</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>204</v>
-      </c>
+        <v>214</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" s="25" t="n">
+        <f aca="false">ROUND(MIN(Assumptions!$C$13,Assumptions!$C$13*Assumptions!$C$14*Assumptions!$C$15*Assumptions!$F$7),0)</f>
+        <v>1813</v>
+      </c>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="B11" s="2"/>
+      <c r="C11" s="33" t="n">
+        <f aca="false">$C$10-C6</f>
+        <v>613</v>
+      </c>
+      <c r="D11" s="33" t="n">
+        <f aca="false">$C$10-D6</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="33" t="n">
+        <f aca="false">$C$10-E6</f>
+        <v>0</v>
+      </c>
+      <c r="F11" s="33" t="n">
+        <f aca="false">$C$10-F6</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="33" t="n">
+        <f aca="false">$C$10-G6</f>
+        <v>0</v>
+      </c>
+      <c r="H11" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -4935,7 +5114,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -4947,7 +5126,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4969,29 +5148,29 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="7" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="H4" s="6"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
-        <v>207</v>
+        <v>220</v>
       </c>
       <c r="B5" s="16"/>
       <c r="C5" s="16"/>
@@ -5003,7 +5182,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>208</v>
+        <v>221</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="34" t="n">
@@ -5027,39 +5206,39 @@
         <v>1</v>
       </c>
       <c r="H6" s="17" t="s">
-        <v>209</v>
+        <v>222</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="34" t="n">
-        <f aca="false">Assumptions!C$28</f>
+        <f aca="false">Assumptions!C$33</f>
         <v>1</v>
       </c>
       <c r="D7" s="34" t="n">
-        <f aca="false">Assumptions!D$28</f>
+        <f aca="false">Assumptions!D$33</f>
         <v>0.97</v>
       </c>
       <c r="E7" s="34" t="n">
-        <f aca="false">Assumptions!E$28</f>
+        <f aca="false">Assumptions!E$33</f>
         <v>0.95</v>
       </c>
       <c r="F7" s="34" t="n">
-        <f aca="false">Assumptions!F$28</f>
+        <f aca="false">Assumptions!F$33</f>
         <v>0.94</v>
       </c>
       <c r="G7" s="34" t="n">
-        <f aca="false">Assumptions!G$28</f>
+        <f aca="false">Assumptions!G$33</f>
         <v>0.93</v>
       </c>
       <c r="H7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>210</v>
+        <v>223</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="35" t="n">
@@ -5086,7 +5265,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="B9" s="16"/>
       <c r="C9" s="16"/>
@@ -5098,88 +5277,88 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="33" t="n">
-        <f aca="false">Assumptions!$F$19*Assumptions!C$26*Assumptions!$F$8*C7</f>
-        <v>210</v>
+        <f aca="false">Assumptions!$F$24*Assumptions!C$31*Assumptions!$F$8*C7</f>
+        <v>166.05</v>
       </c>
       <c r="D10" s="33" t="n">
-        <f aca="false">Assumptions!$F$19*Assumptions!D$26*Assumptions!$F$8*D7</f>
-        <v>543.2</v>
+        <f aca="false">Assumptions!$F$24*Assumptions!D$31*Assumptions!$F$8*D7</f>
+        <v>429.516</v>
       </c>
       <c r="E10" s="33" t="n">
-        <f aca="false">Assumptions!$F$19*Assumptions!E$26*Assumptions!$F$8*E7</f>
-        <v>798</v>
+        <f aca="false">Assumptions!$F$24*Assumptions!E$31*Assumptions!$F$8*E7</f>
+        <v>630.99</v>
       </c>
       <c r="F10" s="33" t="n">
-        <f aca="false">Assumptions!$F$19*Assumptions!F$26*Assumptions!$F$8*F7</f>
-        <v>987</v>
+        <f aca="false">Assumptions!$F$24*Assumptions!F$31*Assumptions!$F$8*F7</f>
+        <v>780.435</v>
       </c>
       <c r="G10" s="33" t="n">
-        <f aca="false">Assumptions!$F$19*Assumptions!G$26*Assumptions!$F$8*G7</f>
-        <v>1106.7</v>
+        <f aca="false">Assumptions!$F$24*Assumptions!G$31*Assumptions!$F$8*G7</f>
+        <v>875.0835</v>
       </c>
       <c r="H10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="33" t="n">
         <f aca="false">C10</f>
-        <v>210</v>
+        <v>166.05</v>
       </c>
       <c r="D11" s="33" t="n">
         <f aca="false">MAX(0,D10-C10)</f>
-        <v>333.2</v>
+        <v>263.466</v>
       </c>
       <c r="E11" s="33" t="n">
         <f aca="false">MAX(0,E10-D10)</f>
-        <v>254.8</v>
+        <v>201.474</v>
       </c>
       <c r="F11" s="33" t="n">
         <f aca="false">MAX(0,F10-E10)</f>
-        <v>189</v>
+        <v>149.445</v>
       </c>
       <c r="G11" s="33" t="n">
         <f aca="false">MAX(0,G10-F10)</f>
-        <v>119.7</v>
+        <v>94.6485000000001</v>
       </c>
       <c r="H11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="33" t="n">
-        <f aca="false">Assumptions!$F$19*Assumptions!C$27*Assumptions!$F$8*12*C8</f>
-        <v>84000</v>
+        <f aca="false">Assumptions!$F$24*Assumptions!C$32*Assumptions!$F$8*12*C8</f>
+        <v>66420</v>
       </c>
       <c r="D12" s="33" t="n">
-        <f aca="false">Assumptions!$F$19*Assumptions!D$27*Assumptions!$F$8*12*D8</f>
-        <v>325920</v>
+        <f aca="false">Assumptions!$F$24*Assumptions!D$32*Assumptions!$F$8*12*D8</f>
+        <v>257709.6</v>
       </c>
       <c r="E12" s="33" t="n">
-        <f aca="false">Assumptions!$F$19*Assumptions!E$27*Assumptions!$F$8*12*E8</f>
-        <v>478800</v>
+        <f aca="false">Assumptions!$F$24*Assumptions!E$32*Assumptions!$F$8*12*E8</f>
+        <v>378594</v>
       </c>
       <c r="F12" s="33" t="n">
-        <f aca="false">Assumptions!$F$19*Assumptions!F$27*Assumptions!$F$8*12*F8</f>
-        <v>552720</v>
+        <f aca="false">Assumptions!$F$24*Assumptions!F$32*Assumptions!$F$8*12*F8</f>
+        <v>437043.6</v>
       </c>
       <c r="G12" s="33" t="n">
-        <f aca="false">Assumptions!$F$19*Assumptions!G$27*Assumptions!$F$8*12*G8</f>
-        <v>624960</v>
+        <f aca="false">Assumptions!$F$24*Assumptions!G$32*Assumptions!$F$8*12*G8</f>
+        <v>494164.8</v>
       </c>
       <c r="H12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="B13" s="16"/>
       <c r="C13" s="16"/>
@@ -5191,117 +5370,117 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="36" t="n">
-        <f aca="false">Assumptions!$C$41*3*MIN(1,Assumptions!C$32*Assumptions!$F$9)*C7</f>
+        <f aca="false">Assumptions!$C$46*3*MIN(1,Assumptions!C$37*Assumptions!$F$9)*C7</f>
         <v>4.2</v>
       </c>
       <c r="D14" s="36" t="n">
-        <f aca="false">Assumptions!$C$41*3*MIN(1,Assumptions!D$32*Assumptions!$F$9)*D7</f>
+        <f aca="false">Assumptions!$C$46*3*MIN(1,Assumptions!D$37*Assumptions!$F$9)*D7</f>
         <v>12.222</v>
       </c>
       <c r="E14" s="36" t="n">
-        <f aca="false">Assumptions!$C$41*3*MIN(1,Assumptions!E$32*Assumptions!$F$9)*E7</f>
+        <f aca="false">Assumptions!$C$46*3*MIN(1,Assumptions!E$37*Assumptions!$F$9)*E7</f>
         <v>19.95</v>
       </c>
       <c r="F14" s="36" t="n">
-        <f aca="false">Assumptions!$C$41*3*MIN(1,Assumptions!F$32*Assumptions!$F$9)*F7</f>
+        <f aca="false">Assumptions!$C$46*3*MIN(1,Assumptions!F$37*Assumptions!$F$9)*F7</f>
         <v>25.2672</v>
       </c>
       <c r="G14" s="36" t="n">
-        <f aca="false">Assumptions!$C$41*3*MIN(1,Assumptions!G$32*Assumptions!$F$9)*G7</f>
+        <f aca="false">Assumptions!$C$46*3*MIN(1,Assumptions!G$37*Assumptions!$F$9)*G7</f>
         <v>29.6856</v>
       </c>
       <c r="H14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="36" t="n">
-        <f aca="false">Assumptions!$F$20*Assumptions!C$33*MIN(1,Assumptions!C$34*Assumptions!$F$9)*C7</f>
-        <v>1.296</v>
+        <f aca="false">Assumptions!$F$25*Assumptions!C$38*MIN(1,Assumptions!C$39*Assumptions!$F$9)*C7</f>
+        <v>0.9024</v>
       </c>
       <c r="D15" s="36" t="n">
-        <f aca="false">Assumptions!$F$20*Assumptions!D$33*MIN(1,Assumptions!D$34*Assumptions!$F$9)*D7</f>
-        <v>4.7142</v>
+        <f aca="false">Assumptions!$F$25*Assumptions!D$38*MIN(1,Assumptions!D$39*Assumptions!$F$9)*D7</f>
+        <v>3.28248</v>
       </c>
       <c r="E15" s="36" t="n">
-        <f aca="false">Assumptions!$F$20*Assumptions!E$33*MIN(1,Assumptions!E$34*Assumptions!$F$9)*E7</f>
-        <v>9.234</v>
+        <f aca="false">Assumptions!$F$25*Assumptions!E$38*MIN(1,Assumptions!E$39*Assumptions!$F$9)*E7</f>
+        <v>6.4296</v>
       </c>
       <c r="F15" s="36" t="n">
-        <f aca="false">Assumptions!$F$20*Assumptions!F$33*MIN(1,Assumptions!F$34*Assumptions!$F$9)*F7</f>
-        <v>12.9438</v>
+        <f aca="false">Assumptions!$F$25*Assumptions!F$38*MIN(1,Assumptions!F$39*Assumptions!$F$9)*F7</f>
+        <v>9.01272</v>
       </c>
       <c r="G15" s="36" t="n">
-        <f aca="false">Assumptions!$F$20*Assumptions!G$33*MIN(1,Assumptions!G$34*Assumptions!$F$9)*G7</f>
-        <v>16.27128</v>
+        <f aca="false">Assumptions!$F$25*Assumptions!G$38*MIN(1,Assumptions!G$39*Assumptions!$F$9)*G7</f>
+        <v>11.329632</v>
       </c>
       <c r="H15" s="2"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="36" t="n">
-        <f aca="false">Assumptions!$C$41*MIN(1,Assumptions!C$37*Assumptions!$F$9)*C7</f>
+        <f aca="false">Assumptions!$C$46*MIN(1,Assumptions!C$42*Assumptions!$F$9)*C7</f>
         <v>0</v>
       </c>
       <c r="D16" s="36" t="n">
-        <f aca="false">Assumptions!$C$41*MIN(1,Assumptions!D$37*Assumptions!$F$9)*D7</f>
+        <f aca="false">Assumptions!$C$46*MIN(1,Assumptions!D$42*Assumptions!$F$9)*D7</f>
         <v>0.5432</v>
       </c>
       <c r="E16" s="36" t="n">
-        <f aca="false">Assumptions!$C$41*MIN(1,Assumptions!E$37*Assumptions!$F$9)*E7</f>
+        <f aca="false">Assumptions!$C$46*MIN(1,Assumptions!E$42*Assumptions!$F$9)*E7</f>
         <v>1.33</v>
       </c>
       <c r="F16" s="36" t="n">
-        <f aca="false">Assumptions!$C$41*MIN(1,Assumptions!F$37*Assumptions!$F$9)*F7</f>
+        <f aca="false">Assumptions!$C$46*MIN(1,Assumptions!F$42*Assumptions!$F$9)*F7</f>
         <v>2.1056</v>
       </c>
       <c r="G16" s="36" t="n">
-        <f aca="false">Assumptions!$C$41*MIN(1,Assumptions!G$37*Assumptions!$F$9)*G7</f>
+        <f aca="false">Assumptions!$C$46*MIN(1,Assumptions!G$42*Assumptions!$F$9)*G7</f>
         <v>2.604</v>
       </c>
       <c r="H16" s="2"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="36" t="n">
         <f aca="false">C14+C15+C16</f>
-        <v>5.496</v>
+        <v>5.1024</v>
       </c>
       <c r="D17" s="36" t="n">
         <f aca="false">D14+D15+D16</f>
-        <v>17.4794</v>
+        <v>16.04768</v>
       </c>
       <c r="E17" s="36" t="n">
         <f aca="false">E14+E15+E16</f>
-        <v>30.514</v>
+        <v>27.7096</v>
       </c>
       <c r="F17" s="36" t="n">
         <f aca="false">F14+F15+F16</f>
-        <v>40.3166</v>
+        <v>36.38552</v>
       </c>
       <c r="G17" s="36" t="n">
         <f aca="false">G14+G15+G16</f>
-        <v>48.56088</v>
+        <v>43.619232</v>
       </c>
       <c r="H17" s="17" t="s">
-        <v>220</v>
+        <v>233</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="15" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="B18" s="16"/>
       <c r="C18" s="16"/>
@@ -5313,254 +5492,254 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>222</v>
+        <v>235</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="37" t="n">
-        <f aca="false">C14/3*Assumptions!$C$42*12*(1-Assumptions!$C$44)*C6</f>
+        <f aca="false">C14/3*Assumptions!$C$47*12*(1-Assumptions!$C$49)*C6</f>
         <v>293.664</v>
       </c>
       <c r="D19" s="37" t="n">
-        <f aca="false">D14/3*Assumptions!$C$42*12*(1-Assumptions!$C$44)*D6</f>
+        <f aca="false">D14/3*Assumptions!$C$47*12*(1-Assumptions!$C$49)*D6</f>
         <v>1709.12448</v>
       </c>
       <c r="E19" s="37" t="n">
-        <f aca="false">E14/3*Assumptions!$C$42*12*(1-Assumptions!$C$44)*E6</f>
+        <f aca="false">E14/3*Assumptions!$C$47*12*(1-Assumptions!$C$49)*E6</f>
         <v>2789.808</v>
       </c>
       <c r="F19" s="37" t="n">
-        <f aca="false">F14/3*Assumptions!$C$42*12*(1-Assumptions!$C$44)*F6</f>
+        <f aca="false">F14/3*Assumptions!$C$47*12*(1-Assumptions!$C$49)*F6</f>
         <v>3533.365248</v>
       </c>
       <c r="G19" s="37" t="n">
-        <f aca="false">G14/3*Assumptions!$C$42*12*(1-Assumptions!$C$44)*G6</f>
+        <f aca="false">G14/3*Assumptions!$C$47*12*(1-Assumptions!$C$49)*G6</f>
         <v>4151.234304</v>
       </c>
       <c r="H19" s="17" t="s">
-        <v>223</v>
+        <v>236</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="37" t="n">
-        <f aca="false">C15*Assumptions!$C$45*12*C6</f>
-        <v>303.264</v>
+        <f aca="false">C15*Assumptions!$C$50*12*C6</f>
+        <v>211.1616</v>
       </c>
       <c r="D20" s="37" t="n">
-        <f aca="false">D15*Assumptions!$C$45*12*D6</f>
-        <v>2206.2456</v>
+        <f aca="false">D15*Assumptions!$C$50*12*D6</f>
+        <v>1536.20064</v>
       </c>
       <c r="E20" s="37" t="n">
-        <f aca="false">E15*Assumptions!$C$45*12*E6</f>
-        <v>4321.512</v>
+        <f aca="false">E15*Assumptions!$C$50*12*E6</f>
+        <v>3009.0528</v>
       </c>
       <c r="F20" s="37" t="n">
-        <f aca="false">F15*Assumptions!$C$45*12*F6</f>
-        <v>6057.6984</v>
+        <f aca="false">F15*Assumptions!$C$50*12*F6</f>
+        <v>4217.95296</v>
       </c>
       <c r="G20" s="37" t="n">
-        <f aca="false">G15*Assumptions!$C$45*12*G6</f>
-        <v>7614.95904</v>
+        <f aca="false">G15*Assumptions!$C$50*12*G6</f>
+        <v>5302.267776</v>
       </c>
       <c r="H20" s="2"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" s="37" t="n">
-        <f aca="false">C16*Assumptions!$C$46*12*C6</f>
+        <f aca="false">C16*Assumptions!$C$51*12*C6</f>
         <v>0</v>
       </c>
       <c r="D21" s="37" t="n">
-        <f aca="false">D16*Assumptions!$C$46*12*D6</f>
+        <f aca="false">D16*Assumptions!$C$51*12*D6</f>
         <v>645.3216</v>
       </c>
       <c r="E21" s="37" t="n">
-        <f aca="false">E16*Assumptions!$C$46*12*E6</f>
+        <f aca="false">E16*Assumptions!$C$51*12*E6</f>
         <v>1580.04</v>
       </c>
       <c r="F21" s="37" t="n">
-        <f aca="false">F16*Assumptions!$C$46*12*F6</f>
+        <f aca="false">F16*Assumptions!$C$51*12*F6</f>
         <v>2501.4528</v>
       </c>
       <c r="G21" s="37" t="n">
-        <f aca="false">G16*Assumptions!$C$46*12*G6</f>
+        <f aca="false">G16*Assumptions!$C$51*12*G6</f>
         <v>3093.552</v>
       </c>
       <c r="H21" s="2"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="11" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="37" t="n">
-        <f aca="false">C10/1000*Assumptions!$C$48*Assumptions!$C$47*MIN(1,Assumptions!C$35*Assumptions!$F$9)*C6</f>
-        <v>94.5</v>
+        <f aca="false">C10/1000*Assumptions!$C$53*Assumptions!$C$52*MIN(1,Assumptions!C$40*Assumptions!$F$9)*C6</f>
+        <v>74.7225</v>
       </c>
       <c r="D22" s="37" t="n">
-        <f aca="false">D10/1000*Assumptions!$C$48*Assumptions!$C$47*MIN(1,Assumptions!D$35*Assumptions!$F$9)*D6</f>
-        <v>1466.64</v>
+        <f aca="false">D10/1000*Assumptions!$C$53*Assumptions!$C$52*MIN(1,Assumptions!D$40*Assumptions!$F$9)*D6</f>
+        <v>1159.6932</v>
       </c>
       <c r="E22" s="37" t="n">
-        <f aca="false">E10/1000*Assumptions!$C$48*Assumptions!$C$47*MIN(1,Assumptions!E$35*Assumptions!$F$9)*E6</f>
-        <v>3231.9</v>
+        <f aca="false">E10/1000*Assumptions!$C$53*Assumptions!$C$52*MIN(1,Assumptions!E$40*Assumptions!$F$9)*E6</f>
+        <v>2555.5095</v>
       </c>
       <c r="F22" s="37" t="n">
-        <f aca="false">F10/1000*Assumptions!$C$48*Assumptions!$C$47*MIN(1,Assumptions!F$35*Assumptions!$F$9)*F6</f>
-        <v>4885.65</v>
+        <f aca="false">F10/1000*Assumptions!$C$53*Assumptions!$C$52*MIN(1,Assumptions!F$40*Assumptions!$F$9)*F6</f>
+        <v>3863.15325</v>
       </c>
       <c r="G22" s="37" t="n">
-        <f aca="false">G10/1000*Assumptions!$C$48*Assumptions!$C$47*MIN(1,Assumptions!G$35*Assumptions!$F$9)*G6</f>
-        <v>5976.18</v>
+        <f aca="false">G10/1000*Assumptions!$C$53*Assumptions!$C$52*MIN(1,Assumptions!G$40*Assumptions!$F$9)*G6</f>
+        <v>4725.4509</v>
       </c>
       <c r="H22" s="17" t="s">
-        <v>227</v>
+        <v>240</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>228</v>
+        <v>241</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" s="37" t="n">
-        <f aca="false">Assumptions!$F$22*12*MIN(1,Assumptions!C$36*Assumptions!$F$9)*C8</f>
-        <v>210</v>
+        <f aca="false">Assumptions!$F$27*12*MIN(1,Assumptions!C$41*Assumptions!$F$9)*C8</f>
+        <v>153</v>
       </c>
       <c r="D23" s="37" t="n">
-        <f aca="false">Assumptions!$F$22*12*MIN(1,Assumptions!D$36*Assumptions!$F$9)*D8</f>
-        <v>1222.2</v>
+        <f aca="false">Assumptions!$F$27*12*MIN(1,Assumptions!D$41*Assumptions!$F$9)*D8</f>
+        <v>890.46</v>
       </c>
       <c r="E23" s="37" t="n">
-        <f aca="false">Assumptions!$F$22*12*MIN(1,Assumptions!E$36*Assumptions!$F$9)*E8</f>
-        <v>1995</v>
+        <f aca="false">Assumptions!$F$27*12*MIN(1,Assumptions!E$41*Assumptions!$F$9)*E8</f>
+        <v>1453.5</v>
       </c>
       <c r="F23" s="37" t="n">
-        <f aca="false">Assumptions!$F$22*12*MIN(1,Assumptions!F$36*Assumptions!$F$9)*F8</f>
-        <v>2368.8</v>
+        <f aca="false">Assumptions!$F$27*12*MIN(1,Assumptions!F$41*Assumptions!$F$9)*F8</f>
+        <v>1725.84</v>
       </c>
       <c r="G23" s="37" t="n">
-        <f aca="false">Assumptions!$F$22*12*MIN(1,Assumptions!G$36*Assumptions!$F$9)*G8</f>
-        <v>2538.9</v>
+        <f aca="false">Assumptions!$F$27*12*MIN(1,Assumptions!G$41*Assumptions!$F$9)*G8</f>
+        <v>1849.77</v>
       </c>
       <c r="H23" s="2"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
-        <v>229</v>
+        <v>242</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" s="37" t="n">
-        <f aca="false">C12/1000*Assumptions!$C$49*Assumptions!$C$50*Assumptions!C$38</f>
+        <f aca="false">C12/1000*Assumptions!$C$54*Assumptions!$C$55*Assumptions!C$43</f>
         <v>0</v>
       </c>
       <c r="D24" s="37" t="n">
-        <f aca="false">D12/1000*Assumptions!$C$49*Assumptions!$C$50*Assumptions!D$38</f>
+        <f aca="false">D12/1000*Assumptions!$C$54*Assumptions!$C$55*Assumptions!D$43</f>
         <v>0</v>
       </c>
       <c r="E24" s="37" t="n">
-        <f aca="false">E12/1000*Assumptions!$C$49*Assumptions!$C$50*Assumptions!E$38</f>
-        <v>2298.24</v>
+        <f aca="false">E12/1000*Assumptions!$C$54*Assumptions!$C$55*Assumptions!E$43</f>
+        <v>1817.2512</v>
       </c>
       <c r="F24" s="37" t="n">
-        <f aca="false">F12/1000*Assumptions!$C$49*Assumptions!$C$50*Assumptions!F$38</f>
-        <v>2653.056</v>
+        <f aca="false">F12/1000*Assumptions!$C$54*Assumptions!$C$55*Assumptions!F$43</f>
+        <v>2097.80928</v>
       </c>
       <c r="G24" s="37" t="n">
-        <f aca="false">G12/1000*Assumptions!$C$49*Assumptions!$C$50*Assumptions!G$38</f>
-        <v>2999.808</v>
+        <f aca="false">G12/1000*Assumptions!$C$54*Assumptions!$C$55*Assumptions!G$43</f>
+        <v>2371.99104</v>
       </c>
       <c r="H24" s="2"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" s="38" t="n">
         <f aca="false">SUM(C19:C24)</f>
-        <v>901.428</v>
+        <v>732.5481</v>
       </c>
       <c r="D25" s="38" t="n">
         <f aca="false">SUM(D19:D24)</f>
-        <v>7249.53168</v>
+        <v>5940.79992</v>
       </c>
       <c r="E25" s="38" t="n">
         <f aca="false">SUM(E19:E24)</f>
-        <v>16216.5</v>
+        <v>13205.1615</v>
       </c>
       <c r="F25" s="38" t="n">
         <f aca="false">SUM(F19:F24)</f>
-        <v>22000.022448</v>
+        <v>17939.573538</v>
       </c>
       <c r="G25" s="38" t="n">
         <f aca="false">SUM(G19:G24)</f>
-        <v>26374.633344</v>
+        <v>21494.26602</v>
       </c>
       <c r="H25" s="2"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="s">
-        <v>231</v>
+        <v>244</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" s="37" t="n">
         <f aca="false">C19+C20</f>
-        <v>596.928</v>
+        <v>504.8256</v>
       </c>
       <c r="D26" s="37" t="n">
         <f aca="false">D19+D20</f>
-        <v>3915.37008</v>
+        <v>3245.32512</v>
       </c>
       <c r="E26" s="37" t="n">
         <f aca="false">E19+E20</f>
-        <v>7111.32</v>
+        <v>5798.8608</v>
       </c>
       <c r="F26" s="37" t="n">
         <f aca="false">F19+F20</f>
-        <v>9591.063648</v>
+        <v>7751.318208</v>
       </c>
       <c r="G26" s="37" t="n">
         <f aca="false">G19+G20</f>
-        <v>11766.193344</v>
+        <v>9453.50208</v>
       </c>
       <c r="H26" s="2"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
-        <v>232</v>
+        <v>245</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" s="37" t="n">
         <f aca="false">C21+C22+C23</f>
-        <v>304.5</v>
+        <v>227.7225</v>
       </c>
       <c r="D27" s="37" t="n">
         <f aca="false">D21+D22+D23</f>
-        <v>3334.1616</v>
+        <v>2695.4748</v>
       </c>
       <c r="E27" s="37" t="n">
         <f aca="false">E21+E22+E23</f>
-        <v>6806.94</v>
+        <v>5589.0495</v>
       </c>
       <c r="F27" s="37" t="n">
         <f aca="false">F21+F22+F23</f>
-        <v>9755.9028</v>
+        <v>8090.44605</v>
       </c>
       <c r="G27" s="37" t="n">
         <f aca="false">G21+G22+G23</f>
-        <v>11608.632</v>
+        <v>9668.7729</v>
       </c>
       <c r="H27" s="2"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="15" t="s">
-        <v>233</v>
+        <v>246</v>
       </c>
       <c r="B28" s="16"/>
       <c r="C28" s="16"/>
@@ -5572,117 +5751,117 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="11" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" s="37" t="n">
-        <f aca="false">MIN(Assumptions!$C$55,Assumptions!$F$21*Assumptions!$C$53+Assumptions!$C$54)*Assumptions!$F$10*365*C8</f>
-        <v>202.94</v>
+        <f aca="false">MIN(Assumptions!$C$60,Assumptions!$F$26*Assumptions!$C$58+Assumptions!$C$59)*Assumptions!$F$10*365*C8</f>
+        <v>181.478</v>
       </c>
       <c r="D29" s="37" t="n">
-        <f aca="false">MIN(Assumptions!$C$55,Assumptions!$F$21*Assumptions!$C$53+Assumptions!$C$54)*Assumptions!$F$10*365*D8</f>
-        <v>393.7036</v>
+        <f aca="false">MIN(Assumptions!$C$60,Assumptions!$F$26*Assumptions!$C$58+Assumptions!$C$59)*Assumptions!$F$10*365*D8</f>
+        <v>352.06732</v>
       </c>
       <c r="E29" s="37" t="n">
-        <f aca="false">MIN(Assumptions!$C$55,Assumptions!$F$21*Assumptions!$C$53+Assumptions!$C$54)*Assumptions!$F$10*365*E8</f>
-        <v>385.586</v>
+        <f aca="false">MIN(Assumptions!$C$60,Assumptions!$F$26*Assumptions!$C$58+Assumptions!$C$59)*Assumptions!$F$10*365*E8</f>
+        <v>344.8082</v>
       </c>
       <c r="F29" s="37" t="n">
-        <f aca="false">MIN(Assumptions!$C$55,Assumptions!$F$21*Assumptions!$C$53+Assumptions!$C$54)*Assumptions!$F$10*365*F8</f>
-        <v>381.5272</v>
+        <f aca="false">MIN(Assumptions!$C$60,Assumptions!$F$26*Assumptions!$C$58+Assumptions!$C$59)*Assumptions!$F$10*365*F8</f>
+        <v>341.17864</v>
       </c>
       <c r="G29" s="37" t="n">
-        <f aca="false">MIN(Assumptions!$C$55,Assumptions!$F$21*Assumptions!$C$53+Assumptions!$C$54)*Assumptions!$F$10*365*G8</f>
-        <v>377.4684</v>
+        <f aca="false">MIN(Assumptions!$C$60,Assumptions!$F$26*Assumptions!$C$58+Assumptions!$C$59)*Assumptions!$F$10*365*G8</f>
+        <v>337.54908</v>
       </c>
       <c r="H29" s="17" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="11" t="s">
-        <v>236</v>
+        <v>249</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="37" t="n">
-        <f aca="false">Assumptions!$C$56*12*Assumptions!$F$10*C8</f>
+        <f aca="false">Assumptions!$C$61*12*Assumptions!$F$10*C8</f>
         <v>150</v>
       </c>
       <c r="D30" s="37" t="n">
-        <f aca="false">Assumptions!$C$56*12*Assumptions!$F$10*D8</f>
+        <f aca="false">Assumptions!$C$61*12*Assumptions!$F$10*D8</f>
         <v>291</v>
       </c>
       <c r="E30" s="37" t="n">
-        <f aca="false">Assumptions!$C$56*12*Assumptions!$F$10*E8</f>
+        <f aca="false">Assumptions!$C$61*12*Assumptions!$F$10*E8</f>
         <v>285</v>
       </c>
       <c r="F30" s="37" t="n">
-        <f aca="false">Assumptions!$C$56*12*Assumptions!$F$10*F8</f>
+        <f aca="false">Assumptions!$C$61*12*Assumptions!$F$10*F8</f>
         <v>282</v>
       </c>
       <c r="G30" s="37" t="n">
-        <f aca="false">Assumptions!$C$56*12*Assumptions!$F$10*G8</f>
+        <f aca="false">Assumptions!$C$61*12*Assumptions!$F$10*G8</f>
         <v>279</v>
       </c>
       <c r="H30" s="2"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="11" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" s="37" t="n">
-        <f aca="false">C10*Assumptions!$C$47/1000*Assumptions!$C$57*C6</f>
-        <v>3.15</v>
+        <f aca="false">C10*Assumptions!$C$52/1000*Assumptions!$C$62*C6</f>
+        <v>2.49075</v>
       </c>
       <c r="D31" s="37" t="n">
-        <f aca="false">D10*Assumptions!$C$47/1000*Assumptions!$C$57*D6</f>
-        <v>16.296</v>
+        <f aca="false">D10*Assumptions!$C$52/1000*Assumptions!$C$62*D6</f>
+        <v>12.88548</v>
       </c>
       <c r="E31" s="37" t="n">
-        <f aca="false">E10*Assumptions!$C$47/1000*Assumptions!$C$57*E6</f>
-        <v>23.94</v>
+        <f aca="false">E10*Assumptions!$C$52/1000*Assumptions!$C$62*E6</f>
+        <v>18.9297</v>
       </c>
       <c r="F31" s="37" t="n">
-        <f aca="false">F10*Assumptions!$C$47/1000*Assumptions!$C$57*F6</f>
-        <v>29.61</v>
+        <f aca="false">F10*Assumptions!$C$52/1000*Assumptions!$C$62*F6</f>
+        <v>23.41305</v>
       </c>
       <c r="G31" s="37" t="n">
-        <f aca="false">G10*Assumptions!$C$47/1000*Assumptions!$C$57*G6</f>
-        <v>33.201</v>
+        <f aca="false">G10*Assumptions!$C$52/1000*Assumptions!$C$62*G6</f>
+        <v>26.252505</v>
       </c>
       <c r="H31" s="2"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="11" t="s">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" s="37" t="n">
-        <f aca="false">C26*Assumptions!$C$58+(C14+C15)*12*Assumptions!$C$59*C6</f>
-        <v>27.203712</v>
+        <f aca="false">C26*Assumptions!$C$63+(C14+C15)*12*Assumptions!$C$64*C6</f>
+        <v>23.8242624</v>
       </c>
       <c r="D32" s="37" t="n">
-        <f aca="false">D26*Assumptions!$C$58+(D14+D15)*12*Assumptions!$C$59*D6</f>
-        <v>174.51605232</v>
+        <f aca="false">D26*Assumptions!$C$63+(D14+D15)*12*Assumptions!$C$64*D6</f>
+        <v>149.93055648</v>
       </c>
       <c r="E32" s="37" t="n">
-        <f aca="false">E26*Assumptions!$C$58+(E14+E15)*12*Assumptions!$C$59*E6</f>
-        <v>311.29068</v>
+        <f aca="false">E26*Assumptions!$C$63+(E14+E15)*12*Assumptions!$C$64*E6</f>
+        <v>263.1335232</v>
       </c>
       <c r="F32" s="37" t="n">
-        <f aca="false">F26*Assumptions!$C$58+(F14+F15)*12*Assumptions!$C$59*F6</f>
-        <v>415.700445792</v>
+        <f aca="false">F26*Assumptions!$C$63+(F14+F15)*12*Assumptions!$C$64*F6</f>
+        <v>348.195940032</v>
       </c>
       <c r="G32" s="37" t="n">
-        <f aca="false">G26*Assumptions!$C$58+(G14+G15)*12*Assumptions!$C$59*G6</f>
-        <v>506.664374976</v>
+        <f aca="false">G26*Assumptions!$C$63+(G14+G15)*12*Assumptions!$C$64*G6</f>
+        <v>421.80639552</v>
       </c>
       <c r="H32" s="2"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="11" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" s="37" t="n">
@@ -5690,76 +5869,76 @@
         <v>0</v>
       </c>
       <c r="D33" s="37" t="n">
-        <f aca="false">Assumptions!$C$60*D7</f>
+        <f aca="false">Assumptions!$C$65*D7</f>
         <v>19.4</v>
       </c>
       <c r="E33" s="37" t="n">
-        <f aca="false">Assumptions!$C$60*E7</f>
+        <f aca="false">Assumptions!$C$65*E7</f>
         <v>19</v>
       </c>
       <c r="F33" s="37" t="n">
-        <f aca="false">Assumptions!$C$60*F7</f>
+        <f aca="false">Assumptions!$C$65*F7</f>
         <v>18.8</v>
       </c>
       <c r="G33" s="37" t="n">
-        <f aca="false">Assumptions!$C$60*G7</f>
+        <f aca="false">Assumptions!$C$65*G7</f>
         <v>18.6</v>
       </c>
       <c r="H33" s="17" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" s="38" t="n">
         <f aca="false">SUM(C29:C33)</f>
-        <v>383.293712</v>
+        <v>357.7930124</v>
       </c>
       <c r="D34" s="38" t="n">
         <f aca="false">SUM(D29:D33)</f>
-        <v>894.91565232</v>
+        <v>825.28335648</v>
       </c>
       <c r="E34" s="38" t="n">
         <f aca="false">SUM(E29:E33)</f>
-        <v>1024.81668</v>
+        <v>930.8714232</v>
       </c>
       <c r="F34" s="38" t="n">
         <f aca="false">SUM(F29:F33)</f>
-        <v>1127.637645792</v>
+        <v>1013.587630032</v>
       </c>
       <c r="G34" s="38" t="n">
         <f aca="false">SUM(G29:G33)</f>
-        <v>1214.933774976</v>
+        <v>1083.20798052</v>
       </c>
       <c r="H34" s="2"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" s="27" t="n">
         <f aca="false">C25-C34</f>
-        <v>518.134288</v>
+        <v>374.7550876</v>
       </c>
       <c r="D35" s="27" t="n">
         <f aca="false">D25-D34</f>
-        <v>6354.61602768</v>
+        <v>5115.51656352</v>
       </c>
       <c r="E35" s="27" t="n">
         <f aca="false">E25-E34</f>
-        <v>15191.68332</v>
+        <v>12274.2900768</v>
       </c>
       <c r="F35" s="27" t="n">
         <f aca="false">F25-F34</f>
-        <v>20872.384802208</v>
+        <v>16925.985907968</v>
       </c>
       <c r="G35" s="27" t="n">
         <f aca="false">G25-G34</f>
-        <v>25159.699569024</v>
+        <v>20411.05803948</v>
       </c>
       <c r="H35" s="2"/>
     </row>
@@ -5770,29 +5949,29 @@
       <c r="B36" s="2"/>
       <c r="C36" s="34" t="n">
         <f aca="false">IF(C25=0,0,C35/C25)</f>
-        <v>0.574792759932019</v>
+        <v>0.511577448088392</v>
       </c>
       <c r="D36" s="34" t="n">
         <f aca="false">IF(D25=0,0,D35/D25)</f>
-        <v>0.87655538428932</v>
+        <v>0.861082115608431</v>
       </c>
       <c r="E36" s="34" t="n">
         <f aca="false">IF(E25=0,0,E35/E25)</f>
-        <v>0.936804077328647</v>
+        <v>0.929507002000695</v>
       </c>
       <c r="F36" s="34" t="n">
         <f aca="false">IF(F25=0,0,F35/F25)</f>
-        <v>0.948743795673058</v>
+        <v>0.943499903836343</v>
       </c>
       <c r="G36" s="34" t="n">
         <f aca="false">IF(G25=0,0,G35/G25)</f>
-        <v>0.953935519818235</v>
+        <v>0.949604793226617</v>
       </c>
       <c r="H36" s="2"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="15" t="s">
-        <v>243</v>
+        <v>256</v>
       </c>
       <c r="B37" s="16"/>
       <c r="C37" s="16"/>
@@ -5804,173 +5983,173 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="11" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" s="37" t="n">
-        <f aca="false">Assumptions!$C$78*(1+Assumptions!$C$68)/Assumptions!$C$71*C8</f>
+        <f aca="false">Assumptions!$C$83*(1+Assumptions!$C$73)/Assumptions!$C$76*C8</f>
         <v>1093.75</v>
       </c>
       <c r="D38" s="37" t="n">
-        <f aca="false">Assumptions!$C$78*(1+Assumptions!$C$68)/Assumptions!$C$71*D8</f>
+        <f aca="false">Assumptions!$C$83*(1+Assumptions!$C$73)/Assumptions!$C$76*D8</f>
         <v>2121.875</v>
       </c>
       <c r="E38" s="37" t="n">
-        <f aca="false">Assumptions!$C$78*(1+Assumptions!$C$68)/Assumptions!$C$71*E8</f>
+        <f aca="false">Assumptions!$C$83*(1+Assumptions!$C$73)/Assumptions!$C$76*E8</f>
         <v>2078.125</v>
       </c>
       <c r="F38" s="37" t="n">
-        <f aca="false">Assumptions!$C$78*(1+Assumptions!$C$68)/Assumptions!$C$71*F8</f>
+        <f aca="false">Assumptions!$C$83*(1+Assumptions!$C$73)/Assumptions!$C$76*F8</f>
         <v>2056.25</v>
       </c>
       <c r="G38" s="37" t="n">
-        <f aca="false">Assumptions!$C$78*(1+Assumptions!$C$68)/Assumptions!$C$71*G8</f>
+        <f aca="false">Assumptions!$C$83*(1+Assumptions!$C$73)/Assumptions!$C$76*G8</f>
         <v>2034.375</v>
       </c>
       <c r="H38" s="2"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="11" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" s="37" t="n">
-        <f aca="false">Assumptions!$C$79*(1+Assumptions!$C$68)/Assumptions!$C$72*C8+C27*Assumptions!$C$70</f>
-        <v>1384.61666666667</v>
+        <f aca="false">Assumptions!$C$84*(1+Assumptions!$C$73)/Assumptions!$C$77*C8+C27*Assumptions!$C$75</f>
+        <v>1376.93891666667</v>
       </c>
       <c r="D39" s="37" t="n">
-        <f aca="false">Assumptions!$C$79*(1+Assumptions!$C$68)/Assumptions!$C$72*D8+D27*Assumptions!$C$70</f>
-        <v>2960.49949333333</v>
+        <f aca="false">Assumptions!$C$84*(1+Assumptions!$C$73)/Assumptions!$C$77*D8+D27*Assumptions!$C$75</f>
+        <v>2896.63081333333</v>
       </c>
       <c r="E39" s="37" t="n">
-        <f aca="false">Assumptions!$C$79*(1+Assumptions!$C$68)/Assumptions!$C$72*E8+E27*Assumptions!$C$70</f>
-        <v>3253.61066666667</v>
+        <f aca="false">Assumptions!$C$84*(1+Assumptions!$C$73)/Assumptions!$C$77*E8+E27*Assumptions!$C$75</f>
+        <v>3131.82161666667</v>
       </c>
       <c r="F39" s="37" t="n">
-        <f aca="false">Assumptions!$C$79*(1+Assumptions!$C$68)/Assumptions!$C$72*F8+F27*Assumptions!$C$70</f>
-        <v>3521.42361333333</v>
+        <f aca="false">Assumptions!$C$84*(1+Assumptions!$C$73)/Assumptions!$C$77*F8+F27*Assumptions!$C$75</f>
+        <v>3354.87793833333</v>
       </c>
       <c r="G39" s="37" t="n">
-        <f aca="false">Assumptions!$C$79*(1+Assumptions!$C$68)/Assumptions!$C$72*G8+G27*Assumptions!$C$70</f>
-        <v>3679.6132</v>
+        <f aca="false">Assumptions!$C$84*(1+Assumptions!$C$73)/Assumptions!$C$77*G8+G27*Assumptions!$C$75</f>
+        <v>3485.62729</v>
       </c>
       <c r="H39" s="2"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="11" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" s="37" t="n">
-        <f aca="false">Assumptions!$C$80*(1+Assumptions!$C$68)/Assumptions!$C$73*C8</f>
+        <f aca="false">Assumptions!$C$85*(1+Assumptions!$C$73)/Assumptions!$C$78*C8</f>
         <v>286.458333333333</v>
       </c>
       <c r="D40" s="37" t="n">
-        <f aca="false">Assumptions!$C$80*(1+Assumptions!$C$68)/Assumptions!$C$73*D8</f>
+        <f aca="false">Assumptions!$C$85*(1+Assumptions!$C$73)/Assumptions!$C$78*D8</f>
         <v>555.729166666667</v>
       </c>
       <c r="E40" s="37" t="n">
-        <f aca="false">Assumptions!$C$80*(1+Assumptions!$C$68)/Assumptions!$C$73*E8</f>
+        <f aca="false">Assumptions!$C$85*(1+Assumptions!$C$73)/Assumptions!$C$78*E8</f>
         <v>544.270833333333</v>
       </c>
       <c r="F40" s="37" t="n">
-        <f aca="false">Assumptions!$C$80*(1+Assumptions!$C$68)/Assumptions!$C$73*F8</f>
+        <f aca="false">Assumptions!$C$85*(1+Assumptions!$C$73)/Assumptions!$C$78*F8</f>
         <v>538.541666666667</v>
       </c>
       <c r="G40" s="37" t="n">
-        <f aca="false">Assumptions!$C$80*(1+Assumptions!$C$68)/Assumptions!$C$73*G8</f>
+        <f aca="false">Assumptions!$C$85*(1+Assumptions!$C$73)/Assumptions!$C$78*G8</f>
         <v>532.8125</v>
       </c>
       <c r="H40" s="2"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="11" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="B41" s="2"/>
       <c r="C41" s="37" t="n">
-        <f aca="false">C11*Assumptions!$C$65*Assumptions!$C$64</f>
-        <v>168</v>
+        <f aca="false">C11*Assumptions!$C$70*Assumptions!$C$69</f>
+        <v>132.84</v>
       </c>
       <c r="D41" s="37" t="n">
-        <f aca="false">D11*Assumptions!$C$65*Assumptions!$C$64</f>
-        <v>266.56</v>
+        <f aca="false">D11*Assumptions!$C$70*Assumptions!$C$69</f>
+        <v>210.7728</v>
       </c>
       <c r="E41" s="37" t="n">
-        <f aca="false">E11*Assumptions!$C$65*Assumptions!$C$64</f>
-        <v>203.84</v>
+        <f aca="false">E11*Assumptions!$C$70*Assumptions!$C$69</f>
+        <v>161.1792</v>
       </c>
       <c r="F41" s="37" t="n">
-        <f aca="false">F11*Assumptions!$C$65*Assumptions!$C$64</f>
-        <v>151.2</v>
+        <f aca="false">F11*Assumptions!$C$70*Assumptions!$C$69</f>
+        <v>119.556</v>
       </c>
       <c r="G41" s="37" t="n">
-        <f aca="false">G11*Assumptions!$C$65*Assumptions!$C$64</f>
-        <v>95.7600000000001</v>
+        <f aca="false">G11*Assumptions!$C$70*Assumptions!$C$69</f>
+        <v>75.7188000000001</v>
       </c>
       <c r="H41" s="2"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="s">
-        <v>248</v>
+        <v>261</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" s="38" t="n">
         <f aca="false">C35-SUM(C38:C41)</f>
-        <v>-2414.690712</v>
+        <v>-2515.2321624</v>
       </c>
       <c r="D42" s="38" t="n">
         <f aca="false">D35-SUM(D38:D41)</f>
-        <v>449.952367679998</v>
+        <v>-669.491216480001</v>
       </c>
       <c r="E42" s="38" t="n">
         <f aca="false">E35-SUM(E38:E41)</f>
-        <v>9111.83682</v>
+        <v>6358.8934268</v>
       </c>
       <c r="F42" s="38" t="n">
         <f aca="false">F35-SUM(F38:F41)</f>
-        <v>14604.969522208</v>
+        <v>10856.760302968</v>
       </c>
       <c r="G42" s="38" t="n">
         <f aca="false">G35-SUM(G38:G41)</f>
-        <v>18817.138869024</v>
+        <v>14282.52444948</v>
       </c>
       <c r="H42" s="2"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="11" t="s">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="B43" s="2"/>
       <c r="C43" s="34" t="n">
         <f aca="false">IF(C25=0,0,C42/C25)</f>
-        <v>-2.67873941346397</v>
+        <v>-3.43353857910491</v>
       </c>
       <c r="D43" s="34" t="n">
         <f aca="false">IF(D25=0,0,D42/D25)</f>
-        <v>0.0620664047749907</v>
+        <v>-0.112693782907269</v>
       </c>
       <c r="E43" s="34" t="n">
         <f aca="false">IF(E25=0,0,E42/E25)</f>
-        <v>0.56188677088151</v>
+        <v>0.481546055063393</v>
       </c>
       <c r="F43" s="34" t="n">
         <f aca="false">IF(F25=0,0,F42/F25)</f>
-        <v>0.663861573629245</v>
+        <v>0.605184971647791</v>
       </c>
       <c r="G43" s="34" t="n">
         <f aca="false">IF(G25=0,0,G42/G25)</f>
-        <v>0.713455941684389</v>
+        <v>0.664480677599802</v>
       </c>
       <c r="H43" s="2"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="11" t="s">
-        <v>250</v>
+        <v>263</v>
       </c>
       <c r="B44" s="2"/>
       <c r="C44" s="37" t="n">
-        <f aca="false">(Assumptions!$C$61+Assumptions!$C$62+Assumptions!$C$63)*Assumptions!$F$10</f>
+        <f aca="false">(Assumptions!$C$66+Assumptions!$C$67+Assumptions!$C$68)*Assumptions!$F$10</f>
         <v>1540</v>
       </c>
       <c r="D44" s="37" t="n">
@@ -5993,31 +6172,31 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="4" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="B45" s="2"/>
       <c r="C45" s="27" t="n">
         <f aca="false">C42-C44</f>
-        <v>-3954.690712</v>
+        <v>-4055.2321624</v>
       </c>
       <c r="D45" s="27" t="n">
         <f aca="false">C45+D42-D44</f>
-        <v>-3504.73834432</v>
+        <v>-4724.72337888</v>
       </c>
       <c r="E45" s="27" t="n">
         <f aca="false">D45+E42-E44</f>
-        <v>5607.09847568</v>
+        <v>1634.17004792</v>
       </c>
       <c r="F45" s="27" t="n">
         <f aca="false">E45+F42-F44</f>
-        <v>20212.067997888</v>
+        <v>12490.930350888</v>
       </c>
       <c r="G45" s="27" t="n">
         <f aca="false">F45+G42-G44</f>
-        <v>39029.206866912</v>
+        <v>26773.454800368</v>
       </c>
       <c r="H45" s="17" t="s">
-        <v>252</v>
+        <v>265</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6032,7 +6211,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="17" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -6069,7 +6248,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -6081,7 +6260,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>255</v>
+        <v>268</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -6103,7 +6282,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="7" t="s">
@@ -6125,61 +6304,61 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>222</v>
+        <v>235</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$C$19</f>
-        <v>5873.28</v>
+        <v>352396.8</v>
       </c>
       <c r="D5" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$D$19+Rollout!$D$5*'Unit Economics'!$C$19</f>
-        <v>57675.6096</v>
+        <v>2230965.408</v>
       </c>
       <c r="E5" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$E$19+Rollout!$D$5*'Unit Economics'!$D$19+Rollout!$E$5*'Unit Economics'!$C$19</f>
-        <v>251258.9184</v>
+        <v>4395462.90624</v>
       </c>
       <c r="F5" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$F$19+Rollout!$D$5*'Unit Economics'!$E$19+Rollout!$E$5*'Unit Economics'!$D$19+Rollout!$F$5*'Unit Economics'!$C$19</f>
-        <v>753142.44096</v>
+        <v>5950190.6016</v>
       </c>
       <c r="G5" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$G$19+Rollout!$D$5*'Unit Economics'!$F$19+Rollout!$E$5*'Unit Economics'!$E$19+Rollout!$F$5*'Unit Economics'!$D$19+Rollout!$G$5*'Unit Economics'!$C$19</f>
-        <v>1812870.09792</v>
+        <v>7147434.061824</v>
       </c>
       <c r="H5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$C$20</f>
-        <v>6065.28</v>
+        <v>253393.92</v>
       </c>
       <c r="D6" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$D$20+Rollout!$D$5*'Unit Economics'!$C$20</f>
-        <v>68386.032</v>
+        <v>1972882.8288</v>
       </c>
       <c r="E6" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$E$20+Rollout!$D$5*'Unit Economics'!$D$20+Rollout!$E$5*'Unit Economics'!$C$20</f>
-        <v>323582.688</v>
+        <v>4552554.35232</v>
       </c>
       <c r="F6" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$F$20+Rollout!$D$5*'Unit Economics'!$E$20+Rollout!$E$5*'Unit Economics'!$D$20+Rollout!$F$5*'Unit Economics'!$C$20</f>
-        <v>1029429.648</v>
+        <v>6906092.9184</v>
       </c>
       <c r="G6" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$G$20+Rollout!$D$5*'Unit Economics'!$F$20+Rollout!$E$5*'Unit Economics'!$E$20+Rollout!$F$5*'Unit Economics'!$D$20+Rollout!$G$5*'Unit Economics'!$C$20</f>
-        <v>2596000.4928</v>
+        <v>8948326.49568</v>
       </c>
       <c r="H6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="37" t="n">
@@ -6188,79 +6367,79 @@
       </c>
       <c r="D7" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$D$21+Rollout!$D$5*'Unit Economics'!$C$21</f>
-        <v>12906.432</v>
+        <v>774385.92</v>
       </c>
       <c r="E7" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$E$21+Rollout!$D$5*'Unit Economics'!$D$21+Rollout!$E$5*'Unit Economics'!$C$21</f>
-        <v>83226.528</v>
+        <v>2291630.1408</v>
       </c>
       <c r="F7" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$F$21+Rollout!$D$5*'Unit Economics'!$E$21+Rollout!$E$5*'Unit Economics'!$D$21+Rollout!$F$5*'Unit Economics'!$C$21</f>
-        <v>305496.576</v>
+        <v>3970307.88</v>
       </c>
       <c r="G7" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$G$21+Rollout!$D$5*'Unit Economics'!$F$21+Rollout!$E$5*'Unit Economics'!$E$21+Rollout!$F$5*'Unit Economics'!$D$21+Rollout!$G$5*'Unit Economics'!$C$21</f>
-        <v>836123.904</v>
+        <v>5245652.9664</v>
       </c>
       <c r="H7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$C$22</f>
-        <v>1890</v>
+        <v>89667</v>
       </c>
       <c r="D8" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$D$22+Rollout!$D$5*'Unit Economics'!$C$22</f>
-        <v>36892.8</v>
+        <v>1437436.7325</v>
       </c>
       <c r="E8" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$E$22+Rollout!$D$5*'Unit Economics'!$D$22+Rollout!$E$5*'Unit Economics'!$C$22</f>
-        <v>200869.2</v>
+        <v>3777503.3316</v>
       </c>
       <c r="F8" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$F$22+Rollout!$D$5*'Unit Economics'!$E$22+Rollout!$E$5*'Unit Economics'!$D$22+Rollout!$F$5*'Unit Economics'!$C$22</f>
-        <v>687393</v>
+        <v>6202311.2235</v>
       </c>
       <c r="G8" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$G$22+Rollout!$D$5*'Unit Economics'!$F$22+Rollout!$E$5*'Unit Economics'!$E$22+Rollout!$F$5*'Unit Economics'!$D$22+Rollout!$G$5*'Unit Economics'!$C$22</f>
-        <v>1809561.6</v>
+        <v>8038654.02225</v>
       </c>
       <c r="H8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$C$23</f>
-        <v>4200</v>
+        <v>183600</v>
       </c>
       <c r="D9" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$D$23+Rollout!$D$5*'Unit Economics'!$C$23</f>
-        <v>41244</v>
+        <v>1162341</v>
       </c>
       <c r="E9" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$E$23+Rollout!$D$5*'Unit Economics'!$D$23+Rollout!$E$5*'Unit Economics'!$C$23</f>
-        <v>179676</v>
+        <v>2290051.98</v>
       </c>
       <c r="F9" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$F$23+Rollout!$D$5*'Unit Economics'!$E$23+Rollout!$E$5*'Unit Economics'!$D$23+Rollout!$F$5*'Unit Economics'!$C$23</f>
-        <v>535416</v>
+        <v>2962003.5</v>
       </c>
       <c r="G9" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$G$23+Rollout!$D$5*'Unit Economics'!$F$23+Rollout!$E$5*'Unit Economics'!$E$23+Rollout!$F$5*'Unit Economics'!$D$23+Rollout!$G$5*'Unit Economics'!$C$23</f>
-        <v>1275162</v>
+        <v>3277663.92</v>
       </c>
       <c r="H9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>229</v>
+        <v>242</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="37" t="n">
@@ -6273,48 +6452,48 @@
       </c>
       <c r="E10" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$E$24+Rollout!$D$5*'Unit Economics'!$D$24+Rollout!$E$5*'Unit Economics'!$C$24</f>
-        <v>45964.8</v>
+        <v>2180701.44</v>
       </c>
       <c r="F10" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$F$24+Rollout!$D$5*'Unit Economics'!$E$24+Rollout!$E$5*'Unit Economics'!$D$24+Rollout!$F$5*'Unit Economics'!$C$24</f>
-        <v>236920.32</v>
+        <v>3631346.1216</v>
       </c>
       <c r="G10" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$G$24+Rollout!$D$5*'Unit Economics'!$F$24+Rollout!$E$5*'Unit Economics'!$E$24+Rollout!$F$5*'Unit Economics'!$D$24+Rollout!$G$5*'Unit Economics'!$C$24</f>
-        <v>731888.64</v>
+        <v>4132346.33664</v>
       </c>
       <c r="H10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>257</v>
+        <v>270</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="38" t="n">
         <f aca="false">SUM(C5:C10)</f>
-        <v>18028.56</v>
+        <v>879057.72</v>
       </c>
       <c r="D11" s="38" t="n">
         <f aca="false">SUM(D5:D10)</f>
-        <v>217104.8736</v>
+        <v>7578011.8893</v>
       </c>
       <c r="E11" s="38" t="n">
         <f aca="false">SUM(E5:E10)</f>
-        <v>1084578.1344</v>
+        <v>19487904.15096</v>
       </c>
       <c r="F11" s="38" t="n">
         <f aca="false">SUM(F5:F10)</f>
-        <v>3547797.98496</v>
+        <v>29622252.2451</v>
       </c>
       <c r="G11" s="38" t="n">
         <f aca="false">SUM(G5:G10)</f>
-        <v>9061606.73472</v>
+        <v>36790077.802794</v>
       </c>
       <c r="H11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="34" t="n">
@@ -6323,19 +6502,19 @@
       </c>
       <c r="D12" s="34" t="n">
         <f aca="false">IF(C11=0,0,D11/C11-1)</f>
-        <v>11.0422747906655</v>
+        <v>7.62060785871945</v>
       </c>
       <c r="E12" s="34" t="n">
         <f aca="false">IF(D11=0,0,E11/D11-1)</f>
-        <v>3.99564158287048</v>
+        <v>1.57163810715005</v>
       </c>
       <c r="F12" s="34" t="n">
         <f aca="false">IF(E11=0,0,F11/E11-1)</f>
-        <v>2.27113176306351</v>
+        <v>0.520032734953736</v>
       </c>
       <c r="G12" s="34" t="n">
         <f aca="false">IF(F11=0,0,G11/F11-1)</f>
-        <v>1.5541495804255</v>
+        <v>0.241974360976542</v>
       </c>
       <c r="H12" s="2"/>
     </row>
@@ -6351,7 +6530,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>259</v>
+        <v>272</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -6363,61 +6542,61 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="34" t="n">
         <f aca="false">IF(C$11=0,0,C5/C$11)</f>
-        <v>0.325776434723572</v>
+        <v>0.400880160633821</v>
       </c>
       <c r="D15" s="34" t="n">
         <f aca="false">IF(D$11=0,0,D5/D$11)</f>
-        <v>0.265657829986181</v>
+        <v>0.294399829479032</v>
       </c>
       <c r="E15" s="34" t="n">
         <f aca="false">IF(E$11=0,0,E5/E$11)</f>
-        <v>0.231665115154658</v>
+        <v>0.225548261741808</v>
       </c>
       <c r="F15" s="34" t="n">
         <f aca="false">IF(F$11=0,0,F5/F$11)</f>
-        <v>0.212284477344189</v>
+        <v>0.200868946505722</v>
       </c>
       <c r="G15" s="34" t="n">
         <f aca="false">IF(G$11=0,0,G5/G$11)</f>
-        <v>0.200060557800848</v>
+        <v>0.194276133367709</v>
       </c>
       <c r="H15" s="2"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="34" t="n">
         <f aca="false">IF(C$11=0,0,C6/C$11)</f>
-        <v>0.336426203756706</v>
+        <v>0.288256293341011</v>
       </c>
       <c r="D16" s="34" t="n">
         <f aca="false">IF(D$11=0,0,D6/D$11)</f>
-        <v>0.314990773196535</v>
+        <v>0.260343063275695</v>
       </c>
       <c r="E16" s="34" t="n">
         <f aca="false">IF(E$11=0,0,E6/E$11)</f>
-        <v>0.298348895055873</v>
+        <v>0.233609233556074</v>
       </c>
       <c r="F16" s="34" t="n">
         <f aca="false">IF(F$11=0,0,F6/F$11)</f>
-        <v>0.290160164801944</v>
+        <v>0.233138684434178</v>
       </c>
       <c r="G16" s="34" t="n">
         <f aca="false">IF(G$11=0,0,G6/G$11)</f>
-        <v>0.286483464665631</v>
+        <v>0.24322662603884</v>
       </c>
       <c r="H16" s="2"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="34" t="n">
@@ -6426,79 +6605,79 @@
       </c>
       <c r="D17" s="34" t="n">
         <f aca="false">IF(D$11=0,0,D7/D$11)</f>
-        <v>0.0594479146690146</v>
+        <v>0.102188533260738</v>
       </c>
       <c r="E17" s="34" t="n">
         <f aca="false">IF(E$11=0,0,E7/E$11)</f>
-        <v>0.076736313742893</v>
+        <v>0.117592436982871</v>
       </c>
       <c r="F17" s="34" t="n">
         <f aca="false">IF(F$11=0,0,F7/F$11)</f>
-        <v>0.0861087855889981</v>
+        <v>0.134031262955596</v>
       </c>
       <c r="G17" s="34" t="n">
         <f aca="false">IF(G$11=0,0,G7/G$11)</f>
-        <v>0.092271042926234</v>
+        <v>0.142583361593262</v>
       </c>
       <c r="H17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="34" t="n">
         <f aca="false">IF(C$11=0,0,C8/C$11)</f>
-        <v>0.104833663919914</v>
+        <v>0.102003540791383</v>
       </c>
       <c r="D18" s="34" t="n">
         <f aca="false">IF(D$11=0,0,D8/D$11)</f>
-        <v>0.169930777638701</v>
+        <v>0.189685204179955</v>
       </c>
       <c r="E18" s="34" t="n">
         <f aca="false">IF(E$11=0,0,E8/E$11)</f>
-        <v>0.185204913900577</v>
+        <v>0.193838357492841</v>
       </c>
       <c r="F18" s="34" t="n">
         <f aca="false">IF(F$11=0,0,F8/F$11)</f>
-        <v>0.193752012632633</v>
+        <v>0.209380136668236</v>
       </c>
       <c r="G18" s="34" t="n">
         <f aca="false">IF(G$11=0,0,G8/G$11)</f>
-        <v>0.199695446180265</v>
+        <v>0.218500598594535</v>
       </c>
       <c r="H18" s="2"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="34" t="n">
         <f aca="false">IF(C$11=0,0,C9/C$11)</f>
-        <v>0.232963697599808</v>
+        <v>0.208860005233786</v>
       </c>
       <c r="D19" s="34" t="n">
         <f aca="false">IF(D$11=0,0,D9/D$11)</f>
-        <v>0.189972704509568</v>
+        <v>0.153383369804579</v>
       </c>
       <c r="E19" s="34" t="n">
         <f aca="false">IF(E$11=0,0,E9/E$11)</f>
-        <v>0.165664413011054</v>
+        <v>0.117511455426939</v>
       </c>
       <c r="F19" s="34" t="n">
         <f aca="false">IF(F$11=0,0,F9/F$11)</f>
-        <v>0.150915018913073</v>
+        <v>0.0999925149341054</v>
       </c>
       <c r="G19" s="34" t="n">
         <f aca="false">IF(G$11=0,0,G9/G$11)</f>
-        <v>0.140721401549479</v>
+        <v>0.0890909754953299</v>
       </c>
       <c r="H19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>263</v>
+        <v>276</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="34" t="n">
@@ -6511,15 +6690,15 @@
       </c>
       <c r="E20" s="34" t="n">
         <f aca="false">IF(E$11=0,0,E10/E$11)</f>
-        <v>0.0423803491349457</v>
+        <v>0.111900254799466</v>
       </c>
       <c r="F20" s="34" t="n">
         <f aca="false">IF(F$11=0,0,F10/F$11)</f>
-        <v>0.0667795407191628</v>
+        <v>0.122588454502162</v>
       </c>
       <c r="G20" s="34" t="n">
         <f aca="false">IF(G$11=0,0,G10/G$11)</f>
-        <v>0.0807680868775437</v>
+        <v>0.112322304910325</v>
       </c>
       <c r="H20" s="2"/>
     </row>
@@ -6539,7 +6718,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
@@ -6550,7 +6729,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -6562,7 +6741,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>265</v>
+        <v>278</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -6584,7 +6763,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="7" t="s">
@@ -6606,7 +6785,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -6618,234 +6797,249 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="8" t="n">
-        <f aca="false">Assumptions!C$85</f>
+        <f aca="false">Assumptions!C$90</f>
         <v>2</v>
       </c>
       <c r="D6" s="8" t="n">
-        <f aca="false">Assumptions!D$85</f>
+        <f aca="false">Assumptions!D$90</f>
         <v>2</v>
       </c>
       <c r="E6" s="8" t="n">
-        <f aca="false">Assumptions!E$85</f>
+        <f aca="false">Assumptions!E$90</f>
         <v>3</v>
       </c>
       <c r="F6" s="8" t="n">
-        <f aca="false">Assumptions!F$85</f>
+        <f aca="false">Assumptions!F$90</f>
         <v>4</v>
       </c>
       <c r="G6" s="8" t="n">
-        <f aca="false">Assumptions!G$85</f>
+        <f aca="false">Assumptions!G$90</f>
         <v>5</v>
       </c>
       <c r="H6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="8" t="n">
-        <f aca="false">Assumptions!C$86</f>
+        <f aca="false">Assumptions!C$91</f>
         <v>3</v>
       </c>
       <c r="D7" s="8" t="n">
-        <f aca="false">Assumptions!D$86</f>
+        <f aca="false">Assumptions!D$91</f>
         <v>5</v>
       </c>
       <c r="E7" s="8" t="n">
-        <f aca="false">Assumptions!E$86</f>
+        <f aca="false">Assumptions!E$91</f>
         <v>8</v>
       </c>
       <c r="F7" s="8" t="n">
-        <f aca="false">Assumptions!F$86</f>
+        <f aca="false">Assumptions!F$91</f>
         <v>11</v>
       </c>
       <c r="G7" s="8" t="n">
-        <f aca="false">Assumptions!G$86</f>
+        <f aca="false">Assumptions!G$91</f>
         <v>14</v>
       </c>
       <c r="H7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="8" t="n">
-        <f aca="false">Assumptions!C$87</f>
+        <f aca="false">Assumptions!C$92</f>
         <v>1</v>
       </c>
       <c r="D8" s="8" t="n">
-        <f aca="false">Assumptions!D$87</f>
+        <f aca="false">Assumptions!D$92</f>
         <v>1</v>
       </c>
       <c r="E8" s="8" t="n">
-        <f aca="false">Assumptions!E$87</f>
+        <f aca="false">Assumptions!E$92</f>
         <v>2</v>
       </c>
       <c r="F8" s="8" t="n">
-        <f aca="false">Assumptions!F$87</f>
+        <f aca="false">Assumptions!F$92</f>
         <v>3</v>
       </c>
       <c r="G8" s="8" t="n">
-        <f aca="false">Assumptions!G$87</f>
+        <f aca="false">Assumptions!G$92</f>
         <v>4</v>
       </c>
       <c r="H8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>267</v>
+        <v>280</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="33" t="n">
-        <f aca="false">IF(Rollout!C$7=0,0,MAX(1,ROUNDUP(Rollout!C$7/Assumptions!$C$71,0)))</f>
-        <v>1</v>
+        <f aca="false">IF(Rollout!C$7=0,0,MAX(1,ROUNDUP(Rollout!C$7/Assumptions!$C$76,0)))</f>
+        <v>30</v>
       </c>
       <c r="D9" s="33" t="n">
-        <f aca="false">IF(Rollout!D$7=0,0,MAX(1,ROUNDUP(Rollout!D$7/Assumptions!$C$71,0)))</f>
-        <v>3</v>
+        <f aca="false">IF(Rollout!D$7=0,0,MAX(1,ROUNDUP(Rollout!D$7/Assumptions!$C$76,0)))</f>
+        <v>45</v>
       </c>
       <c r="E9" s="33" t="n">
-        <f aca="false">IF(Rollout!E$7=0,0,MAX(1,ROUNDUP(Rollout!E$7/Assumptions!$C$71,0)))</f>
-        <v>8</v>
+        <f aca="false">IF(Rollout!E$7=0,0,MAX(1,ROUNDUP(Rollout!E$7/Assumptions!$C$76,0)))</f>
+        <v>44</v>
       </c>
       <c r="F9" s="33" t="n">
-        <f aca="false">IF(Rollout!F$7=0,0,MAX(1,ROUNDUP(Rollout!F$7/Assumptions!$C$71,0)))</f>
-        <v>18</v>
+        <f aca="false">IF(Rollout!F$7=0,0,MAX(1,ROUNDUP(Rollout!F$7/Assumptions!$C$76,0)))</f>
+        <v>43</v>
       </c>
       <c r="G9" s="33" t="n">
-        <f aca="false">IF(Rollout!G$7=0,0,MAX(1,ROUNDUP(Rollout!G$7/Assumptions!$C$71,0)))</f>
-        <v>35</v>
+        <f aca="false">IF(Rollout!G$7=0,0,MAX(1,ROUNDUP(Rollout!G$7/Assumptions!$C$76,0)))</f>
+        <v>43</v>
       </c>
       <c r="H9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>268</v>
+        <v>281</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="33" t="n">
-        <f aca="false">IF(Rollout!C$7=0,0,MAX(1,ROUNDUP(Rollout!C$7/Assumptions!$C$72,0)))</f>
-        <v>1</v>
+        <f aca="false">IF(Rollout!C$7=0,0,MAX(1,ROUNDUP(Rollout!C$7/Assumptions!$C$77,0)))</f>
+        <v>40</v>
       </c>
       <c r="D10" s="33" t="n">
-        <f aca="false">IF(Rollout!D$7=0,0,MAX(1,ROUNDUP(Rollout!D$7/Assumptions!$C$72,0)))</f>
-        <v>4</v>
+        <f aca="false">IF(Rollout!D$7=0,0,MAX(1,ROUNDUP(Rollout!D$7/Assumptions!$C$77,0)))</f>
+        <v>60</v>
       </c>
       <c r="E10" s="33" t="n">
-        <f aca="false">IF(Rollout!E$7=0,0,MAX(1,ROUNDUP(Rollout!E$7/Assumptions!$C$72,0)))</f>
-        <v>10</v>
+        <f aca="false">IF(Rollout!E$7=0,0,MAX(1,ROUNDUP(Rollout!E$7/Assumptions!$C$77,0)))</f>
+        <v>58</v>
       </c>
       <c r="F10" s="33" t="n">
-        <f aca="false">IF(Rollout!F$7=0,0,MAX(1,ROUNDUP(Rollout!F$7/Assumptions!$C$72,0)))</f>
-        <v>23</v>
+        <f aca="false">IF(Rollout!F$7=0,0,MAX(1,ROUNDUP(Rollout!F$7/Assumptions!$C$77,0)))</f>
+        <v>58</v>
       </c>
       <c r="G10" s="33" t="n">
-        <f aca="false">IF(Rollout!G$7=0,0,MAX(1,ROUNDUP(Rollout!G$7/Assumptions!$C$72,0)))</f>
-        <v>46</v>
+        <f aca="false">IF(Rollout!G$7=0,0,MAX(1,ROUNDUP(Rollout!G$7/Assumptions!$C$77,0)))</f>
+        <v>57</v>
       </c>
       <c r="H10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="33" t="n">
-        <f aca="false">IF(Rollout!C$7=0,0,MAX(1,ROUNDUP(Rollout!C$7/Assumptions!$C$73,0)))</f>
-        <v>1</v>
+        <f aca="false">IF(Rollout!C$7=0,0,MAX(1,ROUNDUP(Rollout!C$7/Assumptions!$C$78,0)))</f>
+        <v>10</v>
       </c>
       <c r="D11" s="33" t="n">
-        <f aca="false">IF(Rollout!D$7=0,0,MAX(1,ROUNDUP(Rollout!D$7/Assumptions!$C$73,0)))</f>
-        <v>1</v>
+        <f aca="false">IF(Rollout!D$7=0,0,MAX(1,ROUNDUP(Rollout!D$7/Assumptions!$C$78,0)))</f>
+        <v>15</v>
       </c>
       <c r="E11" s="33" t="n">
-        <f aca="false">IF(Rollout!E$7=0,0,MAX(1,ROUNDUP(Rollout!E$7/Assumptions!$C$73,0)))</f>
+        <f aca="false">IF(Rollout!E$7=0,0,MAX(1,ROUNDUP(Rollout!E$7/Assumptions!$C$78,0)))</f>
+        <v>15</v>
+      </c>
+      <c r="F11" s="33" t="n">
+        <f aca="false">IF(Rollout!F$7=0,0,MAX(1,ROUNDUP(Rollout!F$7/Assumptions!$C$78,0)))</f>
+        <v>15</v>
+      </c>
+      <c r="G11" s="33" t="n">
+        <f aca="false">IF(Rollout!G$7=0,0,MAX(1,ROUNDUP(Rollout!G$7/Assumptions!$C$78,0)))</f>
+        <v>15</v>
+      </c>
+      <c r="H11" s="2"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="B12" s="2"/>
+      <c r="C12" s="33" t="n">
+        <f aca="false">IF(Rollout!C$5=0,0,ROUNDUP(Rollout!C$5/Assumptions!$C$19,0))</f>
         <v>3</v>
       </c>
-      <c r="F11" s="33" t="n">
-        <f aca="false">IF(Rollout!F$7=0,0,MAX(1,ROUNDUP(Rollout!F$7/Assumptions!$C$73,0)))</f>
-        <v>6</v>
-      </c>
-      <c r="G11" s="33" t="n">
-        <f aca="false">IF(Rollout!G$7=0,0,MAX(1,ROUNDUP(Rollout!G$7/Assumptions!$C$73,0)))</f>
-        <v>12</v>
-      </c>
-      <c r="H11" s="2"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
-        <v>269</v>
-      </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="39" t="n">
-        <f aca="false">SUM(C6:C11)</f>
-        <v>9</v>
-      </c>
-      <c r="D12" s="39" t="n">
-        <f aca="false">SUM(D6:D11)</f>
-        <v>16</v>
-      </c>
-      <c r="E12" s="39" t="n">
-        <f aca="false">SUM(E6:E11)</f>
-        <v>34</v>
-      </c>
-      <c r="F12" s="39" t="n">
-        <f aca="false">SUM(F6:F11)</f>
-        <v>65</v>
-      </c>
-      <c r="G12" s="39" t="n">
-        <f aca="false">SUM(G6:G11)</f>
-        <v>116</v>
+      <c r="D12" s="33" t="n">
+        <f aca="false">IF(Rollout!D$5=0,0,ROUNDUP(Rollout!D$5/Assumptions!$C$19,0))</f>
+        <v>2</v>
+      </c>
+      <c r="E12" s="33" t="n">
+        <f aca="false">IF(Rollout!E$5=0,0,ROUNDUP(Rollout!E$5/Assumptions!$C$19,0))</f>
+        <v>0</v>
+      </c>
+      <c r="F12" s="33" t="n">
+        <f aca="false">IF(Rollout!F$5=0,0,ROUNDUP(Rollout!F$5/Assumptions!$C$19,0))</f>
+        <v>0</v>
+      </c>
+      <c r="G12" s="33" t="n">
+        <f aca="false">IF(Rollout!G$5=0,0,ROUNDUP(Rollout!G$5/Assumptions!$C$19,0))</f>
+        <v>0</v>
       </c>
       <c r="H12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
-        <v>270</v>
+      <c r="A13" s="4" t="s">
+        <v>283</v>
       </c>
       <c r="B13" s="2"/>
-      <c r="C13" s="33" t="n">
-        <f aca="false">C12</f>
-        <v>9</v>
-      </c>
-      <c r="D13" s="33" t="n">
-        <f aca="false">MAX(0,D12-C12)</f>
-        <v>7</v>
-      </c>
-      <c r="E13" s="33" t="n">
-        <f aca="false">MAX(0,E12-D12)</f>
-        <v>18</v>
-      </c>
-      <c r="F13" s="33" t="n">
-        <f aca="false">MAX(0,F12-E12)</f>
-        <v>31</v>
-      </c>
-      <c r="G13" s="33" t="n">
-        <f aca="false">MAX(0,G12-F12)</f>
-        <v>51</v>
+      <c r="C13" s="39" t="n">
+        <f aca="false">SUM(C6:C12)</f>
+        <v>89</v>
+      </c>
+      <c r="D13" s="39" t="n">
+        <f aca="false">SUM(D6:D12)</f>
+        <v>130</v>
+      </c>
+      <c r="E13" s="39" t="n">
+        <f aca="false">SUM(E6:E12)</f>
+        <v>130</v>
+      </c>
+      <c r="F13" s="39" t="n">
+        <f aca="false">SUM(F6:F12)</f>
+        <v>134</v>
+      </c>
+      <c r="G13" s="39" t="n">
+        <f aca="false">SUM(G6:G12)</f>
+        <v>138</v>
       </c>
       <c r="H13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2"/>
+      <c r="A14" s="2" t="s">
+        <v>284</v>
+      </c>
       <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
+      <c r="C14" s="33" t="n">
+        <f aca="false">C13</f>
+        <v>89</v>
+      </c>
+      <c r="D14" s="33" t="n">
+        <f aca="false">MAX(0,D13-C13)</f>
+        <v>41</v>
+      </c>
+      <c r="E14" s="33" t="n">
+        <f aca="false">MAX(0,E13-D13)</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="33" t="n">
+        <f aca="false">MAX(0,F13-E13)</f>
+        <v>4</v>
+      </c>
+      <c r="G14" s="33" t="n">
+        <f aca="false">MAX(0,G13-F13)</f>
+        <v>4</v>
+      </c>
       <c r="H14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
-        <v>271</v>
-      </c>
+      <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
@@ -6855,30 +7049,15 @@
       <c r="H15" s="2"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="s">
-        <v>165</v>
+      <c r="A16" s="4" t="s">
+        <v>285</v>
       </c>
       <c r="B16" s="2"/>
-      <c r="C16" s="37" t="n">
-        <f aca="false">C6*0.75*Assumptions!$C$76*(1+Assumptions!$C$68)*(1+Assumptions!$C$69)^0</f>
-        <v>300000</v>
-      </c>
-      <c r="D16" s="37" t="n">
-        <f aca="false">(C6+D6)/2*Assumptions!$C$76*(1+Assumptions!$C$68)*(1+Assumptions!$C$69)^1</f>
-        <v>412000</v>
-      </c>
-      <c r="E16" s="37" t="n">
-        <f aca="false">(D6+E6)/2*Assumptions!$C$76*(1+Assumptions!$C$68)*(1+Assumptions!$C$69)^2</f>
-        <v>530450</v>
-      </c>
-      <c r="F16" s="37" t="n">
-        <f aca="false">(E6+F6)/2*Assumptions!$C$76*(1+Assumptions!$C$68)*(1+Assumptions!$C$69)^3</f>
-        <v>764908.9</v>
-      </c>
-      <c r="G16" s="37" t="n">
-        <f aca="false">(F6+G6)/2*Assumptions!$C$76*(1+Assumptions!$C$68)*(1+Assumptions!$C$69)^4</f>
-        <v>1012957.929</v>
-      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
       <c r="H16" s="2"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6887,183 +7066,237 @@
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="37" t="n">
-        <f aca="false">C7*0.75*Assumptions!$C$77*(1+Assumptions!$C$68)*(1+Assumptions!$C$69)^0</f>
-        <v>478125</v>
+        <f aca="false">C6*0.75*Assumptions!$C$81*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^0</f>
+        <v>300000</v>
       </c>
       <c r="D17" s="37" t="n">
-        <f aca="false">(C7+D7)/2*Assumptions!$C$77*(1+Assumptions!$C$68)*(1+Assumptions!$C$69)^1</f>
-        <v>875500</v>
+        <f aca="false">(C6+D6)/2*Assumptions!$C$81*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^1</f>
+        <v>412000</v>
       </c>
       <c r="E17" s="37" t="n">
-        <f aca="false">(D7+E7)/2*Assumptions!$C$77*(1+Assumptions!$C$68)*(1+Assumptions!$C$69)^2</f>
-        <v>1465368.125</v>
+        <f aca="false">(D6+E6)/2*Assumptions!$C$81*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^2</f>
+        <v>530450</v>
       </c>
       <c r="F17" s="37" t="n">
-        <f aca="false">(E7+F7)/2*Assumptions!$C$77*(1+Assumptions!$C$68)*(1+Assumptions!$C$69)^3</f>
-        <v>2205942.63125</v>
+        <f aca="false">(E6+F6)/2*Assumptions!$C$81*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^3</f>
+        <v>764908.9</v>
       </c>
       <c r="G17" s="37" t="n">
-        <f aca="false">(F7+G7)/2*Assumptions!$C$77*(1+Assumptions!$C$68)*(1+Assumptions!$C$69)^4</f>
-        <v>2989632.7765625</v>
+        <f aca="false">(F6+G6)/2*Assumptions!$C$81*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^4</f>
+        <v>1012957.929</v>
       </c>
       <c r="H17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="37" t="n">
-        <f aca="false">C8*0.75*Assumptions!$C$81*(1+Assumptions!$C$68)*(1+Assumptions!$C$69)^0</f>
-        <v>103125</v>
+        <f aca="false">C7*0.75*Assumptions!$C$82*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^0</f>
+        <v>478125</v>
       </c>
       <c r="D18" s="37" t="n">
-        <f aca="false">(C8+D8)/2*Assumptions!$C$81*(1+Assumptions!$C$68)*(1+Assumptions!$C$69)^1</f>
-        <v>141625</v>
+        <f aca="false">(C7+D7)/2*Assumptions!$C$82*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^1</f>
+        <v>875500</v>
       </c>
       <c r="E18" s="37" t="n">
-        <f aca="false">(D8+E8)/2*Assumptions!$C$81*(1+Assumptions!$C$68)*(1+Assumptions!$C$69)^2</f>
-        <v>218810.625</v>
+        <f aca="false">(D7+E7)/2*Assumptions!$C$82*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^2</f>
+        <v>1465368.125</v>
       </c>
       <c r="F18" s="37" t="n">
-        <f aca="false">(E8+F8)/2*Assumptions!$C$81*(1+Assumptions!$C$68)*(1+Assumptions!$C$69)^3</f>
-        <v>375624.90625</v>
+        <f aca="false">(E7+F7)/2*Assumptions!$C$82*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^3</f>
+        <v>2205942.63125</v>
       </c>
       <c r="G18" s="37" t="n">
-        <f aca="false">(F8+G8)/2*Assumptions!$C$81*(1+Assumptions!$C$68)*(1+Assumptions!$C$69)^4</f>
-        <v>541651.1148125</v>
+        <f aca="false">(F7+G7)/2*Assumptions!$C$82*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^4</f>
+        <v>2989632.7765625</v>
       </c>
       <c r="H18" s="2"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>267</v>
+        <v>179</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="37" t="n">
-        <f aca="false">C9*0.75*Assumptions!$C$78*(1+Assumptions!$C$68)*(1+Assumptions!$C$69)^0</f>
-        <v>65625</v>
+        <f aca="false">C8*0.75*Assumptions!$C$86*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^0</f>
+        <v>103125</v>
       </c>
       <c r="D19" s="37" t="n">
-        <f aca="false">(C9+D9)/2*Assumptions!$C$78*(1+Assumptions!$C$68)*(1+Assumptions!$C$69)^1</f>
-        <v>180250</v>
+        <f aca="false">(C8+D8)/2*Assumptions!$C$86*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^1</f>
+        <v>141625</v>
       </c>
       <c r="E19" s="37" t="n">
-        <f aca="false">(D9+E9)/2*Assumptions!$C$78*(1+Assumptions!$C$68)*(1+Assumptions!$C$69)^2</f>
-        <v>510558.125</v>
+        <f aca="false">(D8+E8)/2*Assumptions!$C$86*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^2</f>
+        <v>218810.625</v>
       </c>
       <c r="F19" s="37" t="n">
-        <f aca="false">(E9+F9)/2*Assumptions!$C$78*(1+Assumptions!$C$68)*(1+Assumptions!$C$69)^3</f>
-        <v>1242976.9625</v>
+        <f aca="false">(E8+F8)/2*Assumptions!$C$86*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^3</f>
+        <v>375624.90625</v>
       </c>
       <c r="G19" s="37" t="n">
-        <f aca="false">(F9+G9)/2*Assumptions!$C$78*(1+Assumptions!$C$68)*(1+Assumptions!$C$69)^4</f>
-        <v>2609773.5531875</v>
+        <f aca="false">(F8+G8)/2*Assumptions!$C$86*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^4</f>
+        <v>541651.1148125</v>
       </c>
       <c r="H19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="37" t="n">
-        <f aca="false">C10*0.75*Assumptions!$C$79*(1+Assumptions!$C$68)*(1+Assumptions!$C$69)^0</f>
-        <v>60937.5</v>
+        <f aca="false">C9*0.75*Assumptions!$C$83*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^0</f>
+        <v>1968750</v>
       </c>
       <c r="D20" s="37" t="n">
-        <f aca="false">(C10+D10)/2*Assumptions!$C$79*(1+Assumptions!$C$68)*(1+Assumptions!$C$69)^1</f>
-        <v>209218.75</v>
+        <f aca="false">(C9+D9)/2*Assumptions!$C$83*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^1</f>
+        <v>3379687.5</v>
       </c>
       <c r="E20" s="37" t="n">
-        <f aca="false">(D10+E10)/2*Assumptions!$C$79*(1+Assumptions!$C$68)*(1+Assumptions!$C$69)^2</f>
-        <v>603386.875</v>
+        <f aca="false">(D9+E9)/2*Assumptions!$C$83*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^2</f>
+        <v>4130879.375</v>
       </c>
       <c r="F20" s="37" t="n">
-        <f aca="false">(E10+F10)/2*Assumptions!$C$79*(1+Assumptions!$C$68)*(1+Assumptions!$C$69)^3</f>
-        <v>1464937.134375</v>
+        <f aca="false">(E9+F9)/2*Assumptions!$C$83*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^3</f>
+        <v>4159192.14375</v>
       </c>
       <c r="G20" s="37" t="n">
-        <f aca="false">(F10+G10)/2*Assumptions!$C$79*(1+Assumptions!$C$68)*(1+Assumptions!$C$69)^4</f>
-        <v>3154941.88303125</v>
+        <f aca="false">(F9+G9)/2*Assumptions!$C$83*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^4</f>
+        <v>4234726.897625</v>
       </c>
       <c r="H20" s="2"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>169</v>
+        <v>281</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" s="37" t="n">
-        <f aca="false">C11*0.75*Assumptions!$C$80*(1+Assumptions!$C$68)*(1+Assumptions!$C$69)^0</f>
-        <v>51562.5</v>
+        <f aca="false">C10*0.75*Assumptions!$C$84*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^0</f>
+        <v>2437500</v>
       </c>
       <c r="D21" s="37" t="n">
-        <f aca="false">(C11+D11)/2*Assumptions!$C$80*(1+Assumptions!$C$68)*(1+Assumptions!$C$69)^1</f>
-        <v>70812.5</v>
+        <f aca="false">(C10+D10)/2*Assumptions!$C$84*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^1</f>
+        <v>4184375</v>
       </c>
       <c r="E21" s="37" t="n">
-        <f aca="false">(D11+E11)/2*Assumptions!$C$80*(1+Assumptions!$C$68)*(1+Assumptions!$C$69)^2</f>
-        <v>145873.75</v>
+        <f aca="false">(D10+E10)/2*Assumptions!$C$84*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^2</f>
+        <v>5085689.375</v>
       </c>
       <c r="F21" s="37" t="n">
-        <f aca="false">(E11+F11)/2*Assumptions!$C$80*(1+Assumptions!$C$68)*(1+Assumptions!$C$69)^3</f>
-        <v>338062.415625</v>
+        <f aca="false">(E10+F10)/2*Assumptions!$C$84*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^3</f>
+        <v>5149475.9875</v>
       </c>
       <c r="G21" s="37" t="n">
-        <f aca="false">(F11+G11)/2*Assumptions!$C$80*(1+Assumptions!$C$68)*(1+Assumptions!$C$69)^4</f>
-        <v>696408.5761875</v>
+        <f aca="false">(F10+G10)/2*Assumptions!$C$84*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^4</f>
+        <v>5258236.47171875</v>
       </c>
       <c r="H21" s="2"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4" t="s">
-        <v>272</v>
+      <c r="A22" s="2" t="s">
+        <v>178</v>
       </c>
       <c r="B22" s="2"/>
-      <c r="C22" s="38" t="n">
-        <f aca="false">SUM(C16:C21)</f>
-        <v>1059375</v>
-      </c>
-      <c r="D22" s="38" t="n">
-        <f aca="false">SUM(D16:D21)</f>
-        <v>1889406.25</v>
-      </c>
-      <c r="E22" s="38" t="n">
-        <f aca="false">SUM(E16:E21)</f>
-        <v>3474447.5</v>
-      </c>
-      <c r="F22" s="38" t="n">
-        <f aca="false">SUM(F16:F21)</f>
-        <v>6392452.95</v>
-      </c>
-      <c r="G22" s="38" t="n">
-        <f aca="false">SUM(G16:G21)</f>
-        <v>11005365.8327813</v>
+      <c r="C22" s="37" t="n">
+        <f aca="false">C11*0.75*Assumptions!$C$85*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^0</f>
+        <v>515625</v>
+      </c>
+      <c r="D22" s="37" t="n">
+        <f aca="false">(C11+D11)/2*Assumptions!$C$85*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^1</f>
+        <v>885156.25</v>
+      </c>
+      <c r="E22" s="37" t="n">
+        <f aca="false">(D11+E11)/2*Assumptions!$C$85*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^2</f>
+        <v>1094053.125</v>
+      </c>
+      <c r="F22" s="37" t="n">
+        <f aca="false">(E11+F11)/2*Assumptions!$C$85*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^3</f>
+        <v>1126874.71875</v>
+      </c>
+      <c r="G22" s="37" t="n">
+        <f aca="false">(F11+G11)/2*Assumptions!$C$85*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^4</f>
+        <v>1160680.9603125</v>
       </c>
       <c r="H22" s="2"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2"/>
+      <c r="A23" s="2" t="s">
+        <v>282</v>
+      </c>
       <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
+      <c r="C23" s="37" t="n">
+        <f aca="false">C12*0.75*Assumptions!$C$83*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^0</f>
+        <v>196875</v>
+      </c>
+      <c r="D23" s="37" t="n">
+        <f aca="false">(C12+D12)/2*Assumptions!$C$83*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^1</f>
+        <v>225312.5</v>
+      </c>
+      <c r="E23" s="37" t="n">
+        <f aca="false">(D12+E12)/2*Assumptions!$C$83*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^2</f>
+        <v>92828.75</v>
+      </c>
+      <c r="F23" s="37" t="n">
+        <f aca="false">(E12+F12)/2*Assumptions!$C$83*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^3</f>
+        <v>0</v>
+      </c>
+      <c r="G23" s="37" t="n">
+        <f aca="false">(F12+G12)/2*Assumptions!$C$83*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^4</f>
+        <v>0</v>
+      </c>
       <c r="H23" s="2"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="17" t="s">
-        <v>273</v>
+      <c r="A24" s="4" t="s">
+        <v>286</v>
       </c>
       <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
+      <c r="C24" s="38" t="n">
+        <f aca="false">SUM(C17:C23)</f>
+        <v>6000000</v>
+      </c>
+      <c r="D24" s="38" t="n">
+        <f aca="false">SUM(D17:D23)</f>
+        <v>10103656.25</v>
+      </c>
+      <c r="E24" s="38" t="n">
+        <f aca="false">SUM(E17:E23)</f>
+        <v>12618079.375</v>
+      </c>
+      <c r="F24" s="38" t="n">
+        <f aca="false">SUM(F17:F23)</f>
+        <v>13782019.2875</v>
+      </c>
+      <c r="G24" s="38" t="n">
+        <f aca="false">SUM(G17:G23)</f>
+        <v>15197886.1500313</v>
+      </c>
       <c r="H24" s="2"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="17" t="s">
+        <v>287</v>
+      </c>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -7081,7 +7314,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
@@ -7092,7 +7325,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>274</v>
+        <v>288</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -7104,7 +7337,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>275</v>
+        <v>289</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -7126,7 +7359,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="7" t="s">
@@ -7148,7 +7381,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
-        <v>276</v>
+        <v>290</v>
       </c>
       <c r="B5" s="16"/>
       <c r="C5" s="16"/>
@@ -7160,163 +7393,163 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$C$29</f>
-        <v>4058.8</v>
+        <v>217773.6</v>
       </c>
       <c r="D6" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$D$29+Rollout!$D$5*'Unit Economics'!$C$29</f>
-        <v>24109.272</v>
+        <v>533726.798</v>
       </c>
       <c r="E6" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$E$29+Rollout!$D$5*'Unit Economics'!$D$29+Rollout!$E$5*'Unit Economics'!$C$29</f>
-        <v>79796.008</v>
+        <v>629587.10716</v>
       </c>
       <c r="F6" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$F$29+Rollout!$D$5*'Unit Economics'!$E$29+Rollout!$E$5*'Unit Economics'!$D$29+Rollout!$F$5*'Unit Economics'!$C$29</f>
-        <v>198394.144</v>
+        <v>620781.7946</v>
       </c>
       <c r="G6" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$G$29+Rollout!$D$5*'Unit Economics'!$F$29+Rollout!$E$5*'Unit Economics'!$E$29+Rollout!$F$5*'Unit Economics'!$D$29+Rollout!$G$5*'Unit Economics'!$C$29</f>
-        <v>414728.184</v>
+        <v>614201.40232</v>
       </c>
       <c r="H6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>236</v>
+        <v>249</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$C$30</f>
-        <v>3000</v>
+        <v>180000</v>
       </c>
       <c r="D7" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$D$30+Rollout!$D$5*'Unit Economics'!$C$30</f>
-        <v>17820</v>
+        <v>441150</v>
       </c>
       <c r="E7" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$E$30+Rollout!$D$5*'Unit Economics'!$D$30+Rollout!$E$5*'Unit Economics'!$C$30</f>
-        <v>58980</v>
+        <v>520383</v>
       </c>
       <c r="F7" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$F$30+Rollout!$D$5*'Unit Economics'!$E$30+Rollout!$E$5*'Unit Economics'!$D$30+Rollout!$F$5*'Unit Economics'!$C$30</f>
-        <v>146640</v>
+        <v>513105</v>
       </c>
       <c r="G7" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$G$30+Rollout!$D$5*'Unit Economics'!$F$30+Rollout!$E$5*'Unit Economics'!$E$30+Rollout!$F$5*'Unit Economics'!$D$30+Rollout!$G$5*'Unit Economics'!$C$30</f>
-        <v>306540</v>
+        <v>507666</v>
       </c>
       <c r="H7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$C$31</f>
-        <v>63</v>
+        <v>2988.9</v>
       </c>
       <c r="D8" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$D$31+Rollout!$D$5*'Unit Economics'!$C$31</f>
-        <v>577.92</v>
+        <v>16989.40575</v>
       </c>
       <c r="E8" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$E$31+Rollout!$D$5*'Unit Economics'!$D$31+Rollout!$E$5*'Unit Economics'!$C$31</f>
-        <v>2412.48</v>
+        <v>30614.43924</v>
       </c>
       <c r="F8" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$F$31+Rollout!$D$5*'Unit Economics'!$E$31+Rollout!$E$5*'Unit Economics'!$D$31+Rollout!$F$5*'Unit Economics'!$C$31</f>
-        <v>7026.6</v>
+        <v>39699.5661</v>
       </c>
       <c r="G8" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$G$31+Rollout!$D$5*'Unit Economics'!$F$31+Rollout!$E$5*'Unit Economics'!$E$31+Rollout!$F$5*'Unit Economics'!$D$31+Rollout!$G$5*'Unit Economics'!$C$31</f>
-        <v>16544.22</v>
+        <v>45855.20565</v>
       </c>
       <c r="H8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$C$32</f>
-        <v>544.07424</v>
+        <v>28589.11488</v>
       </c>
       <c r="D9" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$D$32+Rollout!$D$5*'Unit Economics'!$C$32</f>
-        <v>5666.6180064</v>
+        <v>194520.9406272</v>
       </c>
       <c r="E9" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$E$32+Rollout!$D$5*'Unit Economics'!$D$32+Rollout!$E$5*'Unit Economics'!$C$32</f>
-        <v>25627.8401856</v>
+        <v>407667.65896224</v>
       </c>
       <c r="F9" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$F$32+Rollout!$D$5*'Unit Economics'!$E$32+Rollout!$E$5*'Unit Economics'!$D$32+Rollout!$F$5*'Unit Economics'!$C$32</f>
-        <v>79001.95857984</v>
+        <v>579135.97776</v>
       </c>
       <c r="G9" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$G$32+Rollout!$D$5*'Unit Economics'!$F$32+Rollout!$E$5*'Unit Economics'!$E$32+Rollout!$F$5*'Unit Economics'!$D$32+Rollout!$G$5*'Unit Economics'!$C$32</f>
-        <v>194496.47849088</v>
+        <v>719611.785863616</v>
       </c>
       <c r="H9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>277</v>
+        <v>291</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="37" t="n">
-        <f aca="false">Rollout!$C$5*'Unit Economics'!$C$33+Rollout!C5*Assumptions!$C$62*Assumptions!$F$10</f>
-        <v>300</v>
+        <f aca="false">Rollout!$C$5*'Unit Economics'!$C$33+Rollout!C5*Assumptions!$C$67*Assumptions!$F$10</f>
+        <v>18000</v>
       </c>
       <c r="D10" s="37" t="n">
-        <f aca="false">Rollout!$C$5*'Unit Economics'!$D$33+Rollout!$D$5*'Unit Economics'!$C$33+Rollout!D5*Assumptions!$C$62*Assumptions!$F$10</f>
-        <v>1588</v>
+        <f aca="false">Rollout!$C$5*'Unit Economics'!$D$33+Rollout!$D$5*'Unit Economics'!$C$33+Rollout!D5*Assumptions!$C$67*Assumptions!$F$10</f>
+        <v>32475</v>
       </c>
       <c r="E10" s="37" t="n">
-        <f aca="false">Rollout!$C$5*'Unit Economics'!$E$33+Rollout!$D$5*'Unit Economics'!$D$33+Rollout!$E$5*'Unit Economics'!$C$33+Rollout!E5*Assumptions!$C$62*Assumptions!$F$10</f>
-        <v>4932</v>
+        <f aca="false">Rollout!$C$5*'Unit Economics'!$E$33+Rollout!$D$5*'Unit Economics'!$D$33+Rollout!$E$5*'Unit Economics'!$C$33+Rollout!E5*Assumptions!$C$67*Assumptions!$F$10</f>
+        <v>34692.2</v>
       </c>
       <c r="F10" s="37" t="n">
-        <f aca="false">Rollout!$C$5*'Unit Economics'!$F$33+Rollout!$D$5*'Unit Economics'!$E$33+Rollout!$E$5*'Unit Economics'!$D$33+Rollout!$F$5*'Unit Economics'!$C$33+Rollout!F5*Assumptions!$C$62*Assumptions!$F$10</f>
-        <v>11776</v>
+        <f aca="false">Rollout!$C$5*'Unit Economics'!$F$33+Rollout!$D$5*'Unit Economics'!$E$33+Rollout!$E$5*'Unit Economics'!$D$33+Rollout!$F$5*'Unit Economics'!$C$33+Rollout!F5*Assumptions!$C$67*Assumptions!$F$10</f>
+        <v>34207</v>
       </c>
       <c r="G10" s="37" t="n">
-        <f aca="false">Rollout!$C$5*'Unit Economics'!$G$33+Rollout!$D$5*'Unit Economics'!$F$33+Rollout!$E$5*'Unit Economics'!$E$33+Rollout!$F$5*'Unit Economics'!$D$33+Rollout!$G$5*'Unit Economics'!$C$33+Rollout!G5*Assumptions!$C$62*Assumptions!$F$10</f>
-        <v>23936</v>
+        <f aca="false">Rollout!$C$5*'Unit Economics'!$G$33+Rollout!$D$5*'Unit Economics'!$F$33+Rollout!$E$5*'Unit Economics'!$E$33+Rollout!$F$5*'Unit Economics'!$D$33+Rollout!$G$5*'Unit Economics'!$C$33+Rollout!G5*Assumptions!$C$67*Assumptions!$F$10</f>
+        <v>33844.4</v>
       </c>
       <c r="H10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="38" t="n">
         <f aca="false">SUM(C6:C10)</f>
-        <v>7965.87424</v>
+        <v>447351.61488</v>
       </c>
       <c r="D11" s="38" t="n">
         <f aca="false">SUM(D6:D10)</f>
-        <v>49761.8100064</v>
+        <v>1218862.1443772</v>
       </c>
       <c r="E11" s="38" t="n">
         <f aca="false">SUM(E6:E10)</f>
-        <v>171748.3281856</v>
+        <v>1622944.40536224</v>
       </c>
       <c r="F11" s="38" t="n">
         <f aca="false">SUM(F6:F10)</f>
-        <v>442838.70257984</v>
+        <v>1786929.33846</v>
       </c>
       <c r="G11" s="38" t="n">
         <f aca="false">SUM(G6:G10)</f>
-        <v>956244.88249088</v>
+        <v>1921178.79383362</v>
       </c>
       <c r="H11" s="2"/>
     </row>
@@ -7332,7 +7565,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
-        <v>279</v>
+        <v>293</v>
       </c>
       <c r="B13" s="16"/>
       <c r="C13" s="16"/>
@@ -7344,354 +7577,381 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>280</v>
+        <v>294</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="9" t="n">
-        <f aca="false">Headcount!C19</f>
-        <v>65625</v>
+        <f aca="false">Headcount!C20</f>
+        <v>1968750</v>
       </c>
       <c r="D14" s="9" t="n">
-        <f aca="false">Headcount!D19</f>
-        <v>180250</v>
+        <f aca="false">Headcount!D20</f>
+        <v>3379687.5</v>
       </c>
       <c r="E14" s="9" t="n">
-        <f aca="false">Headcount!E19</f>
-        <v>510558.125</v>
+        <f aca="false">Headcount!E20</f>
+        <v>4130879.375</v>
       </c>
       <c r="F14" s="9" t="n">
-        <f aca="false">Headcount!F19</f>
-        <v>1242976.9625</v>
+        <f aca="false">Headcount!F20</f>
+        <v>4159192.14375</v>
       </c>
       <c r="G14" s="9" t="n">
-        <f aca="false">Headcount!G19</f>
-        <v>2609773.5531875</v>
+        <f aca="false">Headcount!G20</f>
+        <v>4234726.897625</v>
       </c>
       <c r="H14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>281</v>
+        <v>295</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="9" t="n">
-        <f aca="false">Headcount!C20</f>
-        <v>60937.5</v>
+        <f aca="false">Headcount!C21</f>
+        <v>2437500</v>
       </c>
       <c r="D15" s="9" t="n">
-        <f aca="false">Headcount!D20</f>
-        <v>209218.75</v>
+        <f aca="false">Headcount!D21</f>
+        <v>4184375</v>
       </c>
       <c r="E15" s="9" t="n">
-        <f aca="false">Headcount!E20</f>
-        <v>603386.875</v>
+        <f aca="false">Headcount!E21</f>
+        <v>5085689.375</v>
       </c>
       <c r="F15" s="9" t="n">
-        <f aca="false">Headcount!F20</f>
-        <v>1464937.134375</v>
+        <f aca="false">Headcount!F21</f>
+        <v>5149475.9875</v>
       </c>
       <c r="G15" s="9" t="n">
-        <f aca="false">Headcount!G20</f>
-        <v>3154941.88303125</v>
+        <f aca="false">Headcount!G21</f>
+        <v>5258236.47171875</v>
       </c>
       <c r="H15" s="2"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>282</v>
+        <v>296</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="37" t="n">
-        <f aca="false">(Rollout!$C$5*'Unit Economics'!$C$27)*Assumptions!$C$70</f>
-        <v>609</v>
+        <f aca="false">(Rollout!$C$5*'Unit Economics'!$C$27)*Assumptions!$C$75</f>
+        <v>27326.7</v>
       </c>
       <c r="D16" s="37" t="n">
-        <f aca="false">(Rollout!$C$5*'Unit Economics'!$D$27+Rollout!$D$5*'Unit Economics'!$C$27)*Assumptions!$C$70</f>
-        <v>9104.3232</v>
+        <f aca="false">(Rollout!$C$5*'Unit Economics'!$D$27+Rollout!$D$5*'Unit Economics'!$C$27)*Assumptions!$C$75</f>
+        <v>337416.36525</v>
       </c>
       <c r="E16" s="37" t="n">
-        <f aca="false">(Rollout!$C$5*'Unit Economics'!$E$27+Rollout!$D$5*'Unit Economics'!$D$27+Rollout!$E$5*'Unit Economics'!$C$27)*Assumptions!$C$70</f>
-        <v>46377.1728</v>
+        <f aca="false">(Rollout!$C$5*'Unit Economics'!$E$27+Rollout!$D$5*'Unit Economics'!$D$27+Rollout!$E$5*'Unit Economics'!$C$27)*Assumptions!$C$75</f>
+        <v>835918.54524</v>
       </c>
       <c r="F16" s="37" t="n">
-        <f aca="false">(Rollout!$C$5*'Unit Economics'!$F$27+Rollout!$D$5*'Unit Economics'!$E$27+Rollout!$E$5*'Unit Economics'!$D$27+Rollout!$F$5*'Unit Economics'!$C$27)*Assumptions!$C$70</f>
-        <v>152830.5576</v>
+        <f aca="false">(Rollout!$C$5*'Unit Economics'!$F$27+Rollout!$D$5*'Unit Economics'!$E$27+Rollout!$E$5*'Unit Economics'!$D$27+Rollout!$F$5*'Unit Economics'!$C$27)*Assumptions!$C$75</f>
+        <v>1313462.26035</v>
       </c>
       <c r="G16" s="37" t="n">
-        <f aca="false">(Rollout!$C$5*'Unit Economics'!$G$27+Rollout!$D$5*'Unit Economics'!$F$27+Rollout!$E$5*'Unit Economics'!$E$27+Rollout!$F$5*'Unit Economics'!$D$27+Rollout!$G$5*'Unit Economics'!$C$27)*Assumptions!$C$70</f>
-        <v>392084.7504</v>
+        <f aca="false">(Rollout!$C$5*'Unit Economics'!$G$27+Rollout!$D$5*'Unit Economics'!$F$27+Rollout!$E$5*'Unit Economics'!$E$27+Rollout!$F$5*'Unit Economics'!$D$27+Rollout!$G$5*'Unit Economics'!$C$27)*Assumptions!$C$75</f>
+        <v>1656197.090865</v>
       </c>
       <c r="H16" s="2"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>283</v>
+        <v>297</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="9" t="n">
-        <f aca="false">Headcount!C21</f>
-        <v>51562.5</v>
+        <f aca="false">Headcount!C22</f>
+        <v>515625</v>
       </c>
       <c r="D17" s="9" t="n">
-        <f aca="false">Headcount!D21</f>
-        <v>70812.5</v>
+        <f aca="false">Headcount!D22</f>
+        <v>885156.25</v>
       </c>
       <c r="E17" s="9" t="n">
-        <f aca="false">Headcount!E21</f>
-        <v>145873.75</v>
+        <f aca="false">Headcount!E22</f>
+        <v>1094053.125</v>
       </c>
       <c r="F17" s="9" t="n">
-        <f aca="false">Headcount!F21</f>
-        <v>338062.415625</v>
+        <f aca="false">Headcount!F22</f>
+        <v>1126874.71875</v>
       </c>
       <c r="G17" s="9" t="n">
-        <f aca="false">Headcount!G21</f>
-        <v>696408.5761875</v>
+        <f aca="false">Headcount!G22</f>
+        <v>1160680.9603125</v>
       </c>
       <c r="H17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>284</v>
+        <v>298</v>
       </c>
       <c r="B18" s="2"/>
-      <c r="C18" s="37" t="n">
-        <f aca="false">Rollout!C5*(Assumptions!$C$63+Assumptions!$C$61)*Assumptions!$F$10</f>
-        <v>30500</v>
-      </c>
-      <c r="D18" s="37" t="n">
-        <f aca="false">Rollout!D5*(Assumptions!$C$63+Assumptions!$C$61)*Assumptions!$F$10</f>
-        <v>122000</v>
-      </c>
-      <c r="E18" s="37" t="n">
-        <f aca="false">Rollout!E5*(Assumptions!$C$63+Assumptions!$C$61)*Assumptions!$F$10</f>
-        <v>305000</v>
-      </c>
-      <c r="F18" s="37" t="n">
-        <f aca="false">Rollout!F5*(Assumptions!$C$63+Assumptions!$C$61)*Assumptions!$F$10</f>
-        <v>610000</v>
-      </c>
-      <c r="G18" s="37" t="n">
-        <f aca="false">Rollout!G5*(Assumptions!$C$63+Assumptions!$C$61)*Assumptions!$F$10</f>
-        <v>1067500</v>
+      <c r="C18" s="9" t="n">
+        <f aca="false">Headcount!C23</f>
+        <v>196875</v>
+      </c>
+      <c r="D18" s="9" t="n">
+        <f aca="false">Headcount!D23</f>
+        <v>225312.5</v>
+      </c>
+      <c r="E18" s="9" t="n">
+        <f aca="false">Headcount!E23</f>
+        <v>92828.75</v>
+      </c>
+      <c r="F18" s="9" t="n">
+        <f aca="false">Headcount!F23</f>
+        <v>0</v>
+      </c>
+      <c r="G18" s="9" t="n">
+        <f aca="false">Headcount!G23</f>
+        <v>0</v>
       </c>
       <c r="H18" s="2"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>247</v>
+        <v>299</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="37" t="n">
-        <f aca="false">Rollout!$C$5*'Unit Economics'!$C$41</f>
-        <v>3360</v>
+        <f aca="false">Rollout!C5*(Assumptions!$C$68+Assumptions!$C$66)*Assumptions!$F$10</f>
+        <v>1830000</v>
       </c>
       <c r="D19" s="37" t="n">
-        <f aca="false">Rollout!$C$5*'Unit Economics'!$D$41+Rollout!$D$5*'Unit Economics'!$C$41</f>
-        <v>18771.2</v>
+        <f aca="false">Rollout!D5*(Assumptions!$C$68+Assumptions!$C$66)*Assumptions!$F$10</f>
+        <v>934825</v>
       </c>
       <c r="E19" s="37" t="n">
-        <f aca="false">Rollout!$C$5*'Unit Economics'!$E$41+Rollout!$D$5*'Unit Economics'!$D$41+Rollout!$E$5*'Unit Economics'!$C$41</f>
-        <v>59001.6</v>
+        <f aca="false">Rollout!E5*(Assumptions!$C$68+Assumptions!$C$66)*Assumptions!$F$10</f>
+        <v>0</v>
       </c>
       <c r="F19" s="37" t="n">
-        <f aca="false">Rollout!$C$5*'Unit Economics'!$F$41+Rollout!$D$5*'Unit Economics'!$E$41+Rollout!$E$5*'Unit Economics'!$D$41+Rollout!$F$5*'Unit Economics'!$C$41</f>
-        <v>139843.2</v>
+        <f aca="false">Rollout!F5*(Assumptions!$C$68+Assumptions!$C$66)*Assumptions!$F$10</f>
+        <v>0</v>
       </c>
       <c r="G19" s="37" t="n">
-        <f aca="false">Rollout!$C$5*'Unit Economics'!$G$41+Rollout!$D$5*'Unit Economics'!$F$41+Rollout!$E$5*'Unit Economics'!$E$41+Rollout!$F$5*'Unit Economics'!$D$41+Rollout!$G$5*'Unit Economics'!$C$41</f>
-        <v>279003.2</v>
+        <f aca="false">Rollout!G5*(Assumptions!$C$68+Assumptions!$C$66)*Assumptions!$F$10</f>
+        <v>0</v>
       </c>
       <c r="H19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
-        <v>176</v>
+        <v>260</v>
       </c>
       <c r="B20" s="2"/>
-      <c r="C20" s="9" t="n">
-        <f aca="false">Assumptions!C$91</f>
-        <v>50000</v>
-      </c>
-      <c r="D20" s="9" t="n">
-        <f aca="false">Assumptions!D$91</f>
-        <v>150000</v>
-      </c>
-      <c r="E20" s="9" t="n">
-        <f aca="false">Assumptions!E$91</f>
-        <v>300000</v>
-      </c>
-      <c r="F20" s="9" t="n">
-        <f aca="false">Assumptions!F$91</f>
-        <v>500000</v>
-      </c>
-      <c r="G20" s="9" t="n">
-        <f aca="false">Assumptions!G$91</f>
-        <v>700000</v>
+      <c r="C20" s="37" t="n">
+        <f aca="false">Rollout!$C$5*'Unit Economics'!$C$41</f>
+        <v>159408</v>
+      </c>
+      <c r="D20" s="37" t="n">
+        <f aca="false">Rollout!$C$5*'Unit Economics'!$D$41+Rollout!$D$5*'Unit Economics'!$C$41</f>
+        <v>334358.28</v>
+      </c>
+      <c r="E20" s="37" t="n">
+        <f aca="false">Rollout!$C$5*'Unit Economics'!$E$41+Rollout!$D$5*'Unit Economics'!$D$41+Rollout!$E$5*'Unit Economics'!$C$41</f>
+        <v>322618.7664</v>
+      </c>
+      <c r="F20" s="37" t="n">
+        <f aca="false">Rollout!$C$5*'Unit Economics'!$F$41+Rollout!$D$5*'Unit Economics'!$E$41+Rollout!$E$5*'Unit Economics'!$D$41+Rollout!$F$5*'Unit Economics'!$C$41</f>
+        <v>242270.0496</v>
+      </c>
+      <c r="G20" s="37" t="n">
+        <f aca="false">Rollout!$C$5*'Unit Economics'!$G$41+Rollout!$D$5*'Unit Economics'!$F$41+Rollout!$E$5*'Unit Economics'!$E$41+Rollout!$F$5*'Unit Economics'!$D$41+Rollout!$G$5*'Unit Economics'!$C$41</f>
+        <v>164150.388</v>
       </c>
       <c r="H20" s="2"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>285</v>
+        <v>185</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" s="9" t="n">
-        <f aca="false">Headcount!C17</f>
-        <v>478125</v>
+        <f aca="false">Assumptions!C$96</f>
+        <v>50000</v>
       </c>
       <c r="D21" s="9" t="n">
-        <f aca="false">Headcount!D17</f>
-        <v>875500</v>
+        <f aca="false">Assumptions!D$96</f>
+        <v>150000</v>
       </c>
       <c r="E21" s="9" t="n">
-        <f aca="false">Headcount!E17</f>
-        <v>1465368.125</v>
+        <f aca="false">Assumptions!E$96</f>
+        <v>300000</v>
       </c>
       <c r="F21" s="9" t="n">
-        <f aca="false">Headcount!F17</f>
-        <v>2205942.63125</v>
+        <f aca="false">Assumptions!F$96</f>
+        <v>500000</v>
       </c>
       <c r="G21" s="9" t="n">
-        <f aca="false">Headcount!G17</f>
-        <v>2989632.7765625</v>
+        <f aca="false">Assumptions!G$96</f>
+        <v>700000</v>
       </c>
       <c r="H21" s="2"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="11" t="s">
-        <v>286</v>
+        <v>300</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="9" t="n">
-        <f aca="false">Headcount!C16</f>
-        <v>300000</v>
+        <f aca="false">Headcount!C18</f>
+        <v>478125</v>
       </c>
       <c r="D22" s="9" t="n">
-        <f aca="false">Headcount!D16</f>
-        <v>412000</v>
+        <f aca="false">Headcount!D18</f>
+        <v>875500</v>
       </c>
       <c r="E22" s="9" t="n">
-        <f aca="false">Headcount!E16</f>
-        <v>530450</v>
+        <f aca="false">Headcount!E18</f>
+        <v>1465368.125</v>
       </c>
       <c r="F22" s="9" t="n">
-        <f aca="false">Headcount!F16</f>
-        <v>764908.9</v>
+        <f aca="false">Headcount!F18</f>
+        <v>2205942.63125</v>
       </c>
       <c r="G22" s="9" t="n">
-        <f aca="false">Headcount!G16</f>
-        <v>1012957.929</v>
+        <f aca="false">Headcount!G18</f>
+        <v>2989632.7765625</v>
       </c>
       <c r="H22" s="2"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>287</v>
+        <v>301</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" s="9" t="n">
-        <f aca="false">Headcount!C18</f>
-        <v>103125</v>
+        <f aca="false">Headcount!C17</f>
+        <v>300000</v>
       </c>
       <c r="D23" s="9" t="n">
-        <f aca="false">Headcount!D18</f>
-        <v>141625</v>
+        <f aca="false">Headcount!D17</f>
+        <v>412000</v>
       </c>
       <c r="E23" s="9" t="n">
-        <f aca="false">Headcount!E18</f>
-        <v>218810.625</v>
+        <f aca="false">Headcount!E17</f>
+        <v>530450</v>
       </c>
       <c r="F23" s="9" t="n">
-        <f aca="false">Headcount!F18</f>
-        <v>375624.90625</v>
+        <f aca="false">Headcount!F17</f>
+        <v>764908.9</v>
       </c>
       <c r="G23" s="9" t="n">
-        <f aca="false">Headcount!G18</f>
-        <v>541651.1148125</v>
+        <f aca="false">Headcount!G17</f>
+        <v>1012957.929</v>
       </c>
       <c r="H23" s="2"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
-        <v>288</v>
+        <v>302</v>
       </c>
       <c r="B24" s="2"/>
-      <c r="C24" s="37" t="n">
-        <f aca="false">Assumptions!C$92+Rollout!C8*Assumptions!$C$93</f>
-        <v>61000</v>
-      </c>
-      <c r="D24" s="37" t="n">
-        <f aca="false">Assumptions!D$92+Rollout!D8*Assumptions!$C$93</f>
-        <v>95970</v>
-      </c>
-      <c r="E24" s="37" t="n">
-        <f aca="false">Assumptions!E$92+Rollout!E8*Assumptions!$C$93</f>
-        <v>159800</v>
-      </c>
-      <c r="F24" s="37" t="n">
-        <f aca="false">Assumptions!F$92+Rollout!F8*Assumptions!$C$93</f>
-        <v>249270</v>
-      </c>
-      <c r="G24" s="37" t="n">
-        <f aca="false">Assumptions!G$92+Rollout!G8*Assumptions!$C$93</f>
-        <v>363030</v>
+      <c r="C24" s="9" t="n">
+        <f aca="false">Headcount!C19</f>
+        <v>103125</v>
+      </c>
+      <c r="D24" s="9" t="n">
+        <f aca="false">Headcount!D19</f>
+        <v>141625</v>
+      </c>
+      <c r="E24" s="9" t="n">
+        <f aca="false">Headcount!E19</f>
+        <v>218810.625</v>
+      </c>
+      <c r="F24" s="9" t="n">
+        <f aca="false">Headcount!F19</f>
+        <v>375624.90625</v>
+      </c>
+      <c r="G24" s="9" t="n">
+        <f aca="false">Headcount!G19</f>
+        <v>541651.1148125</v>
       </c>
       <c r="H24" s="2"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>289</v>
+        <v>303</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" s="37" t="n">
-        <f aca="false">Headcount!C12*Assumptions!$C$94</f>
-        <v>27000</v>
+        <f aca="false">Assumptions!C$97+Rollout!C8*Assumptions!$C$98</f>
+        <v>120000</v>
       </c>
       <c r="D25" s="37" t="n">
-        <f aca="false">Headcount!D12*Assumptions!$C$94</f>
-        <v>48000</v>
+        <f aca="false">Assumptions!D$97+Rollout!D8*Assumptions!$C$98</f>
+        <v>238850</v>
       </c>
       <c r="E25" s="37" t="n">
-        <f aca="false">Headcount!E12*Assumptions!$C$94</f>
-        <v>102000</v>
+        <f aca="false">Assumptions!E$97+Rollout!E8*Assumptions!$C$98</f>
+        <v>315580.5</v>
       </c>
       <c r="F25" s="37" t="n">
-        <f aca="false">Headcount!F12*Assumptions!$C$94</f>
-        <v>195000</v>
+        <f aca="false">Assumptions!F$97+Rollout!F8*Assumptions!$C$98</f>
+        <v>372248</v>
       </c>
       <c r="G25" s="37" t="n">
-        <f aca="false">Headcount!G12*Assumptions!$C$94</f>
-        <v>348000</v>
+        <f aca="false">Assumptions!G$97+Rollout!G8*Assumptions!$C$98</f>
+        <v>430128.5</v>
       </c>
       <c r="H25" s="2"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="4" t="s">
-        <v>290</v>
+      <c r="A26" s="11" t="s">
+        <v>304</v>
       </c>
       <c r="B26" s="2"/>
-      <c r="C26" s="38" t="n">
-        <f aca="false">SUM(C14:C25)</f>
-        <v>1231844</v>
-      </c>
-      <c r="D26" s="38" t="n">
-        <f aca="false">SUM(D14:D25)</f>
-        <v>2333251.7732</v>
-      </c>
-      <c r="E26" s="38" t="n">
-        <f aca="false">SUM(E14:E25)</f>
-        <v>4446626.2728</v>
-      </c>
-      <c r="F26" s="38" t="n">
-        <f aca="false">SUM(F14:F25)</f>
-        <v>8239396.7076</v>
-      </c>
-      <c r="G26" s="38" t="n">
-        <f aca="false">SUM(G14:G25)</f>
-        <v>14154983.7831813</v>
+      <c r="C26" s="37" t="n">
+        <f aca="false">Headcount!C13*Assumptions!$C$99</f>
+        <v>267000</v>
+      </c>
+      <c r="D26" s="37" t="n">
+        <f aca="false">Headcount!D13*Assumptions!$C$99</f>
+        <v>390000</v>
+      </c>
+      <c r="E26" s="37" t="n">
+        <f aca="false">Headcount!E13*Assumptions!$C$99</f>
+        <v>390000</v>
+      </c>
+      <c r="F26" s="37" t="n">
+        <f aca="false">Headcount!F13*Assumptions!$C$99</f>
+        <v>402000</v>
+      </c>
+      <c r="G26" s="37" t="n">
+        <f aca="false">Headcount!G13*Assumptions!$C$99</f>
+        <v>414000</v>
       </c>
       <c r="H26" s="2"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="B27" s="2"/>
+      <c r="C27" s="38" t="n">
+        <f aca="false">SUM(C14:C26)</f>
+        <v>8453734.7</v>
+      </c>
+      <c r="D27" s="38" t="n">
+        <f aca="false">SUM(D14:D26)</f>
+        <v>12489105.89525</v>
+      </c>
+      <c r="E27" s="38" t="n">
+        <f aca="false">SUM(E14:E26)</f>
+        <v>14782197.18664</v>
+      </c>
+      <c r="F27" s="38" t="n">
+        <f aca="false">SUM(F14:F26)</f>
+        <v>16611999.59745</v>
+      </c>
+      <c r="G27" s="38" t="n">
+        <f aca="false">SUM(G14:G26)</f>
+        <v>18562362.1288963</v>
+      </c>
+      <c r="H27" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -7720,7 +7980,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>291</v>
+        <v>306</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -7732,7 +7992,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>292</v>
+        <v>307</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -7754,7 +8014,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="7" t="s">
@@ -7776,82 +8036,82 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>293</v>
+        <v>308</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="27" t="n">
         <f aca="false">Revenue!C11</f>
-        <v>18028.56</v>
+        <v>879057.72</v>
       </c>
       <c r="D5" s="27" t="n">
         <f aca="false">Revenue!D11</f>
-        <v>217104.8736</v>
+        <v>7578011.8893</v>
       </c>
       <c r="E5" s="27" t="n">
         <f aca="false">Revenue!E11</f>
-        <v>1084578.1344</v>
+        <v>19487904.15096</v>
       </c>
       <c r="F5" s="27" t="n">
         <f aca="false">Revenue!F11</f>
-        <v>3547797.98496</v>
+        <v>29622252.2451</v>
       </c>
       <c r="G5" s="27" t="n">
         <f aca="false">Revenue!G11</f>
-        <v>9061606.73472</v>
+        <v>36790077.802794</v>
       </c>
       <c r="H5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>276</v>
+        <v>290</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="9" t="n">
         <f aca="false">Costs!C11</f>
-        <v>7965.87424</v>
+        <v>447351.61488</v>
       </c>
       <c r="D6" s="9" t="n">
         <f aca="false">Costs!D11</f>
-        <v>49761.8100064</v>
+        <v>1218862.1443772</v>
       </c>
       <c r="E6" s="9" t="n">
         <f aca="false">Costs!E11</f>
-        <v>171748.3281856</v>
+        <v>1622944.40536224</v>
       </c>
       <c r="F6" s="9" t="n">
         <f aca="false">Costs!F11</f>
-        <v>442838.70257984</v>
+        <v>1786929.33846</v>
       </c>
       <c r="G6" s="9" t="n">
         <f aca="false">Costs!G11</f>
-        <v>956244.88249088</v>
+        <v>1921178.79383362</v>
       </c>
       <c r="H6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>294</v>
+        <v>309</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="38" t="n">
         <f aca="false">C5-C6</f>
-        <v>10062.68576</v>
+        <v>431706.10512</v>
       </c>
       <c r="D7" s="38" t="n">
         <f aca="false">D5-D6</f>
-        <v>167343.0635936</v>
+        <v>6359149.7449228</v>
       </c>
       <c r="E7" s="38" t="n">
         <f aca="false">E5-E6</f>
-        <v>912829.8062144</v>
+        <v>17864959.7455978</v>
       </c>
       <c r="F7" s="38" t="n">
         <f aca="false">F5-F6</f>
-        <v>3104959.28238016</v>
+        <v>27835322.90664</v>
       </c>
       <c r="G7" s="38" t="n">
         <f aca="false">G5-G6</f>
-        <v>8105361.85222912</v>
+        <v>34868899.0089604</v>
       </c>
       <c r="H7" s="2"/>
     </row>
@@ -7862,23 +8122,23 @@
       <c r="B8" s="2"/>
       <c r="C8" s="34" t="n">
         <f aca="false">IF(C5=0,0,C7/C5)</f>
-        <v>0.558152495817747</v>
+        <v>0.49110097698704</v>
       </c>
       <c r="D8" s="34" t="n">
         <f aca="false">IF(D5=0,0,D7/D5)</f>
-        <v>0.77079367597209</v>
+        <v>0.839158058580218</v>
       </c>
       <c r="E8" s="34" t="n">
         <f aca="false">IF(E5=0,0,E7/E5)</f>
-        <v>0.841645038989641</v>
+        <v>0.916720423459067</v>
       </c>
       <c r="F8" s="34" t="n">
         <f aca="false">IF(F5=0,0,F7/F5)</f>
-        <v>0.875179278962009</v>
+        <v>0.939676114980231</v>
       </c>
       <c r="G8" s="34" t="n">
         <f aca="false">IF(G5=0,0,G7/G5)</f>
-        <v>0.89447292180238</v>
+        <v>0.947779974695033</v>
       </c>
       <c r="H8" s="2"/>
     </row>
@@ -7894,136 +8154,136 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>295</v>
+        <v>310</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="9" t="n">
         <f aca="false">Costs!C14</f>
-        <v>65625</v>
+        <v>1968750</v>
       </c>
       <c r="D10" s="9" t="n">
         <f aca="false">Costs!D14</f>
-        <v>180250</v>
+        <v>3379687.5</v>
       </c>
       <c r="E10" s="9" t="n">
         <f aca="false">Costs!E14</f>
-        <v>510558.125</v>
+        <v>4130879.375</v>
       </c>
       <c r="F10" s="9" t="n">
         <f aca="false">Costs!F14</f>
-        <v>1242976.9625</v>
+        <v>4159192.14375</v>
       </c>
       <c r="G10" s="9" t="n">
         <f aca="false">Costs!G14</f>
-        <v>2609773.5531875</v>
+        <v>4234726.897625</v>
       </c>
       <c r="H10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="9" t="n">
-        <f aca="false">Costs!C15+Costs!C16+Costs!C17+Costs!C18+Costs!C19+Costs!C20</f>
-        <v>196969</v>
+        <f aca="false">Costs!C15+Costs!C16+Costs!C17+Costs!C18+Costs!C19+Costs!C20+Costs!C21</f>
+        <v>5216734.7</v>
       </c>
       <c r="D11" s="9" t="n">
-        <f aca="false">Costs!D15+Costs!D16+Costs!D17+Costs!D18+Costs!D19+Costs!D20</f>
-        <v>579906.7732</v>
+        <f aca="false">Costs!D15+Costs!D16+Costs!D17+Costs!D18+Costs!D19+Costs!D20+Costs!D21</f>
+        <v>7051443.39525</v>
       </c>
       <c r="E11" s="9" t="n">
-        <f aca="false">Costs!E15+Costs!E16+Costs!E17+Costs!E18+Costs!E19+Costs!E20</f>
-        <v>1459639.3978</v>
+        <f aca="false">Costs!E15+Costs!E16+Costs!E17+Costs!E18+Costs!E19+Costs!E20+Costs!E21</f>
+        <v>7731108.56164</v>
       </c>
       <c r="F11" s="9" t="n">
-        <f aca="false">Costs!F15+Costs!F16+Costs!F17+Costs!F18+Costs!F19+Costs!F20</f>
-        <v>3205673.3076</v>
+        <f aca="false">Costs!F15+Costs!F16+Costs!F17+Costs!F18+Costs!F19+Costs!F20+Costs!F21</f>
+        <v>8332083.0162</v>
       </c>
       <c r="G11" s="9" t="n">
-        <f aca="false">Costs!G15+Costs!G16+Costs!G17+Costs!G18+Costs!G19+Costs!G20</f>
-        <v>6289938.40961875</v>
+        <f aca="false">Costs!G15+Costs!G16+Costs!G17+Costs!G18+Costs!G19+Costs!G20+Costs!G21</f>
+        <v>8939264.91089625</v>
       </c>
       <c r="H11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="9" t="n">
-        <f aca="false">Costs!C21</f>
+        <f aca="false">Costs!C22</f>
         <v>478125</v>
       </c>
       <c r="D12" s="9" t="n">
-        <f aca="false">Costs!D21</f>
+        <f aca="false">Costs!D22</f>
         <v>875500</v>
       </c>
       <c r="E12" s="9" t="n">
-        <f aca="false">Costs!E21</f>
+        <f aca="false">Costs!E22</f>
         <v>1465368.125</v>
       </c>
       <c r="F12" s="9" t="n">
-        <f aca="false">Costs!F21</f>
+        <f aca="false">Costs!F22</f>
         <v>2205942.63125</v>
       </c>
       <c r="G12" s="9" t="n">
-        <f aca="false">Costs!G21</f>
+        <f aca="false">Costs!G22</f>
         <v>2989632.7765625</v>
       </c>
       <c r="H12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>297</v>
+        <v>312</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="9" t="n">
-        <f aca="false">Costs!C22+Costs!C23+Costs!C24+Costs!C25</f>
-        <v>491125</v>
+        <f aca="false">Costs!C23+Costs!C24+Costs!C25+Costs!C26</f>
+        <v>790125</v>
       </c>
       <c r="D13" s="9" t="n">
-        <f aca="false">Costs!D22+Costs!D23+Costs!D24+Costs!D25</f>
-        <v>697595</v>
+        <f aca="false">Costs!D23+Costs!D24+Costs!D25+Costs!D26</f>
+        <v>1182475</v>
       </c>
       <c r="E13" s="9" t="n">
-        <f aca="false">Costs!E22+Costs!E23+Costs!E24+Costs!E25</f>
-        <v>1011060.625</v>
+        <f aca="false">Costs!E23+Costs!E24+Costs!E25+Costs!E26</f>
+        <v>1454841.125</v>
       </c>
       <c r="F13" s="9" t="n">
-        <f aca="false">Costs!F22+Costs!F23+Costs!F24+Costs!F25</f>
-        <v>1584803.80625</v>
+        <f aca="false">Costs!F23+Costs!F24+Costs!F25+Costs!F26</f>
+        <v>1914781.80625</v>
       </c>
       <c r="G13" s="9" t="n">
-        <f aca="false">Costs!G22+Costs!G23+Costs!G24+Costs!G25</f>
-        <v>2265639.0438125</v>
+        <f aca="false">Costs!G23+Costs!G24+Costs!G25+Costs!G26</f>
+        <v>2398737.5438125</v>
       </c>
       <c r="H13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="40" t="n">
         <f aca="false">SUM(C10:C13)</f>
-        <v>1231844</v>
+        <v>8453734.7</v>
       </c>
       <c r="D14" s="40" t="n">
         <f aca="false">SUM(D10:D13)</f>
-        <v>2333251.7732</v>
+        <v>12489105.89525</v>
       </c>
       <c r="E14" s="40" t="n">
         <f aca="false">SUM(E10:E13)</f>
-        <v>4446626.2728</v>
+        <v>14782197.18664</v>
       </c>
       <c r="F14" s="40" t="n">
         <f aca="false">SUM(F10:F13)</f>
-        <v>8239396.7076</v>
+        <v>16611999.59745</v>
       </c>
       <c r="G14" s="40" t="n">
         <f aca="false">SUM(G10:G13)</f>
-        <v>14154983.7831813</v>
+        <v>18562362.1288963</v>
       </c>
       <c r="H14" s="2"/>
     </row>
@@ -8039,28 +8299,28 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>298</v>
+        <v>313</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="27" t="n">
         <f aca="false">C7-C14</f>
-        <v>-1221781.31424</v>
+        <v>-8022028.59488</v>
       </c>
       <c r="D16" s="27" t="n">
         <f aca="false">D7-D14</f>
-        <v>-2165908.7096064</v>
+        <v>-6129956.1503272</v>
       </c>
       <c r="E16" s="27" t="n">
         <f aca="false">E7-E14</f>
-        <v>-3533796.4665856</v>
+        <v>3082762.55895776</v>
       </c>
       <c r="F16" s="27" t="n">
         <f aca="false">F7-F14</f>
-        <v>-5134437.42521984</v>
+        <v>11223323.30919</v>
       </c>
       <c r="G16" s="27" t="n">
         <f aca="false">G7-G14</f>
-        <v>-6049621.93095213</v>
+        <v>16306536.8800641</v>
       </c>
       <c r="H16" s="2"/>
     </row>
@@ -8071,110 +8331,110 @@
       <c r="B17" s="2"/>
       <c r="C17" s="34" t="n">
         <f aca="false">IF(C5=0,0,C16/C5)</f>
-        <v>-67.7692125294533</v>
+        <v>-9.12571314984868</v>
       </c>
       <c r="D17" s="34" t="n">
         <f aca="false">IF(D5=0,0,D16/D5)</f>
-        <v>-9.97632468443306</v>
+        <v>-0.8089135039472</v>
       </c>
       <c r="E17" s="34" t="n">
         <f aca="false">IF(E5=0,0,E16/E5)</f>
-        <v>-3.25822211835437</v>
+        <v>0.158188511965044</v>
       </c>
       <c r="F17" s="34" t="n">
         <f aca="false">IF(F5=0,0,F16/F5)</f>
-        <v>-1.44721809048486</v>
+        <v>0.378881498149639</v>
       </c>
       <c r="G17" s="34" t="n">
         <f aca="false">IF(G5=0,0,G16/G5)</f>
-        <v>-0.667610293412172</v>
+        <v>0.443231921592342</v>
       </c>
       <c r="H17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>299</v>
+        <v>314</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="37" t="n">
-        <f aca="false">Headcount!C13*Assumptions!$C$95</f>
-        <v>22500</v>
+        <f aca="false">Headcount!C14*Assumptions!$C$100</f>
+        <v>222500</v>
       </c>
       <c r="D18" s="37" t="n">
-        <f aca="false">Headcount!D13*Assumptions!$C$95</f>
-        <v>17500</v>
+        <f aca="false">Headcount!D14*Assumptions!$C$100</f>
+        <v>102500</v>
       </c>
       <c r="E18" s="37" t="n">
-        <f aca="false">Headcount!E13*Assumptions!$C$95</f>
-        <v>45000</v>
+        <f aca="false">Headcount!E14*Assumptions!$C$100</f>
+        <v>0</v>
       </c>
       <c r="F18" s="37" t="n">
-        <f aca="false">Headcount!F13*Assumptions!$C$95</f>
-        <v>77500</v>
+        <f aca="false">Headcount!F14*Assumptions!$C$100</f>
+        <v>10000</v>
       </c>
       <c r="G18" s="37" t="n">
-        <f aca="false">Headcount!G13*Assumptions!$C$95</f>
-        <v>127500</v>
+        <f aca="false">Headcount!G14*Assumptions!$C$100</f>
+        <v>10000</v>
       </c>
       <c r="H18" s="2"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>300</v>
+        <v>315</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="37" t="n">
-        <f aca="false">(C18)/Assumptions!$C$96</f>
-        <v>7500</v>
+        <f aca="false">(C18)/Assumptions!$C$101</f>
+        <v>74166.6666666667</v>
       </c>
       <c r="D19" s="37" t="n">
-        <f aca="false">(C18+D18)/Assumptions!$C$96</f>
-        <v>13333.3333333333</v>
+        <f aca="false">(C18+D18)/Assumptions!$C$101</f>
+        <v>108333.333333333</v>
       </c>
       <c r="E19" s="37" t="n">
-        <f aca="false">(C18+D18+E18)/Assumptions!$C$96</f>
-        <v>28333.3333333333</v>
+        <f aca="false">(C18+D18+E18)/Assumptions!$C$101</f>
+        <v>108333.333333333</v>
       </c>
       <c r="F19" s="37" t="n">
-        <f aca="false">(D18+E18+F18)/Assumptions!$C$96</f>
-        <v>46666.6666666667</v>
+        <f aca="false">(D18+E18+F18)/Assumptions!$C$101</f>
+        <v>37500</v>
       </c>
       <c r="G19" s="37" t="n">
-        <f aca="false">(E18+F18+G18)/Assumptions!$C$96</f>
-        <v>83333.3333333333</v>
+        <f aca="false">(E18+F18+G18)/Assumptions!$C$101</f>
+        <v>6666.66666666667</v>
       </c>
       <c r="H19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>301</v>
+        <v>316</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="27" t="n">
         <f aca="false">C16-C19</f>
-        <v>-1229281.31424</v>
+        <v>-8096195.26154667</v>
       </c>
       <c r="D20" s="27" t="n">
         <f aca="false">D16-D19</f>
-        <v>-2179242.04293973</v>
+        <v>-6238289.48366053</v>
       </c>
       <c r="E20" s="27" t="n">
         <f aca="false">E16-E19</f>
-        <v>-3562129.79991893</v>
+        <v>2974429.22562442</v>
       </c>
       <c r="F20" s="27" t="n">
         <f aca="false">F16-F19</f>
-        <v>-5181104.09188651</v>
+        <v>11185823.30919</v>
       </c>
       <c r="G20" s="27" t="n">
         <f aca="false">G16-G19</f>
-        <v>-6132955.26428547</v>
+        <v>16299870.2133975</v>
       </c>
       <c r="H20" s="2"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>302</v>
+        <v>317</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" s="37" t="n">
@@ -8183,25 +8443,25 @@
       </c>
       <c r="D21" s="37" t="n">
         <f aca="false">C23</f>
-        <v>1229281.31424</v>
+        <v>8096195.26154667</v>
       </c>
       <c r="E21" s="37" t="n">
         <f aca="false">D23</f>
-        <v>3408523.35717973</v>
+        <v>14334484.7452072</v>
       </c>
       <c r="F21" s="37" t="n">
         <f aca="false">E23</f>
-        <v>6970653.15709867</v>
+        <v>11360055.5195828</v>
       </c>
       <c r="G21" s="37" t="n">
         <f aca="false">F23</f>
-        <v>12151757.2489852</v>
+        <v>174232.210392773</v>
       </c>
       <c r="H21" s="2"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="11" t="s">
-        <v>303</v>
+        <v>318</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="37" t="n">
@@ -8222,88 +8482,88 @@
       </c>
       <c r="G22" s="37" t="n">
         <f aca="false">MAX(0,G20-G21)</f>
-        <v>0</v>
+        <v>16125638.0030047</v>
       </c>
       <c r="H22" s="2"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>304</v>
+        <v>319</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" s="37" t="n">
         <f aca="false">MAX(0,C21-MAX(0,C20))+MAX(0,-C20)</f>
-        <v>1229281.31424</v>
+        <v>8096195.26154667</v>
       </c>
       <c r="D23" s="37" t="n">
         <f aca="false">MAX(0,D21-MAX(0,D20))+MAX(0,-D20)</f>
-        <v>3408523.35717973</v>
+        <v>14334484.7452072</v>
       </c>
       <c r="E23" s="37" t="n">
         <f aca="false">MAX(0,E21-MAX(0,E20))+MAX(0,-E20)</f>
-        <v>6970653.15709867</v>
+        <v>11360055.5195828</v>
       </c>
       <c r="F23" s="37" t="n">
         <f aca="false">MAX(0,F21-MAX(0,F20))+MAX(0,-F20)</f>
-        <v>12151757.2489852</v>
+        <v>174232.210392773</v>
       </c>
       <c r="G23" s="37" t="n">
         <f aca="false">MAX(0,G21-MAX(0,G20))+MAX(0,-G20)</f>
-        <v>18284712.5132706</v>
+        <v>0</v>
       </c>
       <c r="H23" s="2"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
-        <v>305</v>
+        <v>320</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" s="37" t="n">
-        <f aca="false">C22*Assumptions!$C$99</f>
+        <f aca="false">C22*Assumptions!$C$104</f>
         <v>0</v>
       </c>
       <c r="D24" s="37" t="n">
-        <f aca="false">D22*Assumptions!$C$99</f>
+        <f aca="false">D22*Assumptions!$C$104</f>
         <v>0</v>
       </c>
       <c r="E24" s="37" t="n">
-        <f aca="false">E22*Assumptions!$C$99</f>
+        <f aca="false">E22*Assumptions!$C$104</f>
         <v>0</v>
       </c>
       <c r="F24" s="37" t="n">
-        <f aca="false">F22*Assumptions!$C$99</f>
+        <f aca="false">F22*Assumptions!$C$104</f>
         <v>0</v>
       </c>
       <c r="G24" s="37" t="n">
-        <f aca="false">G22*Assumptions!$C$99</f>
-        <v>0</v>
+        <f aca="false">G22*Assumptions!$C$104</f>
+        <v>4031409.50075117</v>
       </c>
       <c r="H24" s="2"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>306</v>
+        <v>321</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" s="38" t="n">
         <f aca="false">C20-C24</f>
-        <v>-1229281.31424</v>
+        <v>-8096195.26154667</v>
       </c>
       <c r="D25" s="38" t="n">
         <f aca="false">D20-D24</f>
-        <v>-2179242.04293973</v>
+        <v>-6238289.48366053</v>
       </c>
       <c r="E25" s="38" t="n">
         <f aca="false">E20-E24</f>
-        <v>-3562129.79991893</v>
+        <v>2974429.22562442</v>
       </c>
       <c r="F25" s="38" t="n">
         <f aca="false">F20-F24</f>
-        <v>-5181104.09188651</v>
+        <v>11185823.30919</v>
       </c>
       <c r="G25" s="38" t="n">
         <f aca="false">G20-G24</f>
-        <v>-6132955.26428547</v>
+        <v>12268460.7126463</v>
       </c>
       <c r="H25" s="2"/>
     </row>
@@ -8334,7 +8594,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>307</v>
+        <v>322</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -8346,7 +8606,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>308</v>
+        <v>323</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -8368,7 +8628,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="7" t="s">
@@ -8390,34 +8650,34 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>298</v>
+        <v>313</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="9" t="n">
         <f aca="false">'P&amp;L'!C16</f>
-        <v>-1221781.31424</v>
+        <v>-8022028.59488</v>
       </c>
       <c r="D5" s="9" t="n">
         <f aca="false">'P&amp;L'!D16</f>
-        <v>-2165908.7096064</v>
+        <v>-6129956.1503272</v>
       </c>
       <c r="E5" s="9" t="n">
         <f aca="false">'P&amp;L'!E16</f>
-        <v>-3533796.4665856</v>
+        <v>3082762.55895776</v>
       </c>
       <c r="F5" s="9" t="n">
         <f aca="false">'P&amp;L'!F16</f>
-        <v>-5134437.42521984</v>
+        <v>11223323.30919</v>
       </c>
       <c r="G5" s="9" t="n">
         <f aca="false">'P&amp;L'!G16</f>
-        <v>-6049621.93095213</v>
+        <v>16306536.8800641</v>
       </c>
       <c r="H5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>309</v>
+        <v>324</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="9" t="n">
@@ -8438,202 +8698,202 @@
       </c>
       <c r="G6" s="9" t="n">
         <f aca="false">-'P&amp;L'!G24</f>
-        <v>-0</v>
+        <v>-4031409.50075117</v>
       </c>
       <c r="H6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>310</v>
+        <v>325</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="9" t="n">
         <f aca="false">-'P&amp;L'!C18</f>
-        <v>-22500</v>
+        <v>-222500</v>
       </c>
       <c r="D7" s="9" t="n">
         <f aca="false">-'P&amp;L'!D18</f>
-        <v>-17500</v>
+        <v>-102500</v>
       </c>
       <c r="E7" s="9" t="n">
         <f aca="false">-'P&amp;L'!E18</f>
-        <v>-45000</v>
+        <v>-0</v>
       </c>
       <c r="F7" s="9" t="n">
         <f aca="false">-'P&amp;L'!F18</f>
-        <v>-77500</v>
+        <v>-10000</v>
       </c>
       <c r="G7" s="9" t="n">
         <f aca="false">-'P&amp;L'!G18</f>
-        <v>-127500</v>
+        <v>-10000</v>
       </c>
       <c r="H7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>311</v>
+        <v>326</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="37" t="n">
-        <f aca="false">-'P&amp;L'!C5*Assumptions!$C$100</f>
-        <v>-540.8568</v>
+        <f aca="false">-'P&amp;L'!C5*Assumptions!$C$105</f>
+        <v>-26371.7316</v>
       </c>
       <c r="D8" s="37" t="n">
-        <f aca="false">-('P&amp;L'!D5-'P&amp;L'!C5)*Assumptions!$C$100</f>
-        <v>-5972.289408</v>
+        <f aca="false">-('P&amp;L'!D5-'P&amp;L'!C5)*Assumptions!$C$105</f>
+        <v>-200968.625079</v>
       </c>
       <c r="E8" s="37" t="n">
-        <f aca="false">-('P&amp;L'!E5-'P&amp;L'!D5)*Assumptions!$C$100</f>
-        <v>-26024.197824</v>
+        <f aca="false">-('P&amp;L'!E5-'P&amp;L'!D5)*Assumptions!$C$105</f>
+        <v>-357296.7678498</v>
       </c>
       <c r="F8" s="37" t="n">
-        <f aca="false">-('P&amp;L'!F5-'P&amp;L'!E5)*Assumptions!$C$100</f>
-        <v>-73896.5955168</v>
+        <f aca="false">-('P&amp;L'!F5-'P&amp;L'!E5)*Assumptions!$C$105</f>
+        <v>-304030.4428242</v>
       </c>
       <c r="G8" s="37" t="n">
-        <f aca="false">-('P&amp;L'!G5-'P&amp;L'!F5)*Assumptions!$C$100</f>
-        <v>-165414.2624928</v>
+        <f aca="false">-('P&amp;L'!G5-'P&amp;L'!F5)*Assumptions!$C$105</f>
+        <v>-215034.76673082</v>
       </c>
       <c r="H8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>312</v>
+        <v>327</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="38" t="n">
         <f aca="false">SUM(C5:C8)</f>
-        <v>-1244822.17104</v>
+        <v>-8270900.32648</v>
       </c>
       <c r="D9" s="38" t="n">
         <f aca="false">SUM(D5:D8)</f>
-        <v>-2189380.9990144</v>
+        <v>-6433424.7754062</v>
       </c>
       <c r="E9" s="38" t="n">
         <f aca="false">SUM(E5:E8)</f>
-        <v>-3604820.6644096</v>
+        <v>2725465.79110796</v>
       </c>
       <c r="F9" s="38" t="n">
         <f aca="false">SUM(F5:F8)</f>
-        <v>-5285834.02073664</v>
+        <v>10909292.8663658</v>
       </c>
       <c r="G9" s="38" t="n">
         <f aca="false">SUM(G5:G8)</f>
-        <v>-6342536.19344493</v>
+        <v>12050092.6125821</v>
       </c>
       <c r="H9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="9" t="n">
-        <f aca="false">Assumptions!C$104</f>
-        <v>2000000</v>
+        <f aca="false">Assumptions!C$109</f>
+        <v>10000000</v>
       </c>
       <c r="D10" s="9" t="n">
-        <f aca="false">Assumptions!D$104</f>
-        <v>8000000</v>
+        <f aca="false">Assumptions!D$109</f>
+        <v>6000000</v>
       </c>
       <c r="E10" s="9" t="n">
-        <f aca="false">Assumptions!E$104</f>
+        <f aca="false">Assumptions!E$109</f>
         <v>0</v>
       </c>
       <c r="F10" s="9" t="n">
-        <f aca="false">Assumptions!F$104</f>
-        <v>15000000</v>
+        <f aca="false">Assumptions!F$109</f>
+        <v>0</v>
       </c>
       <c r="G10" s="9" t="n">
-        <f aca="false">Assumptions!G$104</f>
+        <f aca="false">Assumptions!G$109</f>
         <v>0</v>
       </c>
       <c r="H10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>313</v>
+        <v>328</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="37" t="n">
         <f aca="false">C9+C10</f>
-        <v>755177.82896</v>
+        <v>1729099.67352</v>
       </c>
       <c r="D11" s="37" t="n">
         <f aca="false">D9+D10</f>
-        <v>5810619.0009856</v>
+        <v>-433424.7754062</v>
       </c>
       <c r="E11" s="37" t="n">
         <f aca="false">E9+E10</f>
-        <v>-3604820.6644096</v>
+        <v>2725465.79110796</v>
       </c>
       <c r="F11" s="37" t="n">
         <f aca="false">F9+F10</f>
-        <v>9714165.97926336</v>
+        <v>10909292.8663658</v>
       </c>
       <c r="G11" s="37" t="n">
         <f aca="false">G9+G10</f>
-        <v>-6342536.19344493</v>
+        <v>12050092.6125821</v>
       </c>
       <c r="H11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>314</v>
+        <v>329</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="37" t="n">
-        <f aca="false">Assumptions!$C$101</f>
+        <f aca="false">Assumptions!$C$106</f>
         <v>250000</v>
       </c>
       <c r="D12" s="37" t="n">
         <f aca="false">C13</f>
-        <v>1005177.82896</v>
+        <v>1979099.67352</v>
       </c>
       <c r="E12" s="37" t="n">
         <f aca="false">D13</f>
-        <v>6815796.8299456</v>
+        <v>1545674.8981138</v>
       </c>
       <c r="F12" s="37" t="n">
         <f aca="false">E13</f>
-        <v>3210976.165536</v>
+        <v>4271140.68922176</v>
       </c>
       <c r="G12" s="37" t="n">
         <f aca="false">F13</f>
-        <v>12925142.1447994</v>
+        <v>15180433.5555876</v>
       </c>
       <c r="H12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>315</v>
+        <v>330</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="38" t="n">
         <f aca="false">C12+C11</f>
-        <v>1005177.82896</v>
+        <v>1979099.67352</v>
       </c>
       <c r="D13" s="38" t="n">
         <f aca="false">D12+D11</f>
-        <v>6815796.8299456</v>
+        <v>1545674.8981138</v>
       </c>
       <c r="E13" s="38" t="n">
         <f aca="false">E12+E11</f>
-        <v>3210976.165536</v>
+        <v>4271140.68922176</v>
       </c>
       <c r="F13" s="38" t="n">
         <f aca="false">F12+F11</f>
-        <v>12925142.1447994</v>
+        <v>15180433.5555876</v>
       </c>
       <c r="G13" s="38" t="n">
         <f aca="false">G12+G11</f>
-        <v>6582605.95135443</v>
+        <v>27230526.1681697</v>
       </c>
       <c r="H13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>316</v>
+        <v>331</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="41" t="n">
@@ -8670,12 +8930,12 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>317</v>
+        <v>332</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="27" t="n">
         <f aca="false">MIN(C13:G13)</f>
-        <v>1005177.82896</v>
+        <v>1545674.8981138</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
@@ -8685,19 +8945,19 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>318</v>
+        <v>333</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="27" t="n">
         <f aca="false">-MIN(0,C9,C9+D9,C9+D9+E9,C9+D9+E9+F9,C9+D9+E9+F9+G9)</f>
-        <v>18667394.0486456</v>
+        <v>14704325.1018862</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
       <c r="H17" s="17" t="s">
-        <v>319</v>
+        <v>334</v>
       </c>
     </row>
   </sheetData>

--- a/docs/finance/TownCore-LRP.xlsx
+++ b/docs/finance/TownCore-LRP.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="359">
   <si>
     <t xml:space="preserve">TownCore long-range plan, FY2027-FY2031</t>
   </si>
@@ -175,25 +175,25 @@
     <t xml:space="preserve">Launch capacity: how many towns can launch, and how fast</t>
   </si>
   <si>
-    <t xml:space="preserve">US incorporated places with 5,000+ people</t>
-  </si>
-  <si>
-    <t xml:space="preserve">places</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Census Vintage 2025 city estimates (sub-est2025.csv, SUMLEV 162). Florida: 229. The §10a floor is 5,000 people. New England towns (county subdivisions) are not counted.</t>
+    <t xml:space="preserve">US towns with more than 2,000 people</t>
+  </si>
+  <si>
+    <t xml:space="preserve">towns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owner plan (2026-10-17): every US town over 2,000 people. Census Vintage 2025 (sub-est2025.csv): 7,683 incorporated places (SUMLEV 162; Florida 295) plus 750 New England towns (active county subdivisions with no place of their own).</t>
   </si>
   <si>
     <t xml:space="preserve">Share that pass readiness (Rule 7)</t>
   </si>
   <si>
-    <t xml:space="preserve">Estimate, and the biggest unknown. Today almost none pass: Boca makes about 0.8 real items a day against a bar of 10, Delray 0.53 against 3. Getting here needs more sources per town (permits, police and fire feeds, property sales, schools, sports) or a lower bar (owner call).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Share allowed by the naming neighbor rule</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Towns within 50 miles must use different name patterns (§10b). Computed on the Census gazetteer, largest towns first: the original 6 patterns allowed 41% (2,021 places); the 22 patterns adopted 2026-10-17 allow 74% (3,636; Florida 185 of 229). The rest sit in metros with more than 22 towns within 50 miles of each other.</t>
+    <t xml:space="preserve">Owner plan: every town. Rule 7 still stops a town below 3 real items a day (10 for large), and today almost none pass: Boca makes about 0.8 a day, Delray 0.53. Reaching 100% needs many more sources per town or a lower bar. Set lower to see the plan without that work.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share allowed by the naming rule</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owner, 2026-10-17: naming never stops a launch. 22 patterns; a neighbor's pattern is used only when nothing else is left.</t>
   </si>
   <si>
     <t xml:space="preserve">Fiscal year</t>
@@ -202,10 +202,7 @@
     <t xml:space="preserve">Launches the team can do in a year</t>
   </si>
   <si>
-    <t xml:space="preserve">towns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">About 100 a month: the launcher is automated, each launch needs ~45 minutes of people (approval, Facebook page, Google Publisher Center). A pacing choice too: launching hundreds of AI-written sites at once invites Google's scaled-content review. Scaled by the launch multiplier.</t>
+    <t xml:space="preserve">About 250 a month: the launcher is automated, each launch needs ~45 minutes of people (approval, Facebook page, Google Publisher Center). A pacing choice too: launching hundreds of AI-written sites at once invites Google's scaled-content review. Scaled by the launch multiplier.</t>
   </si>
   <si>
     <t xml:space="preserve">Launches per launch operator per year</t>
@@ -232,13 +229,13 @@
     <t xml:space="preserve">Share of launches</t>
   </si>
   <si>
-    <t xml:space="preserve">Census 2025, places of 5,000+: 3,535 under 30,000 (small), 1,023 of 30,000-100,000 (mid), 343 of 100,000+ (large); tiers from packages/config/src/launch.ts.</t>
+    <t xml:space="preserve">Census 2025, towns over 2,000: 7,067 under 30,000 (small, incl. the 750 New England towns), 1,023 of 30,000-100,000 (mid), 343 of 100,000+ (large); tiers from packages/config/src/launch.ts.</t>
   </si>
   <si>
     <t xml:space="preserve">Households per town</t>
   </si>
   <si>
-    <t xml:space="preserve">Median town population by tier (10,371 / 48,420 / 157,113, Census 2025) / ~2.5 people a household.</t>
+    <t xml:space="preserve">Mean town population by tier (8,397 / 53,365 / 185,762, Census 2025, each town capped at 300,000) / ~2.5 people a household. Revenue scales with households, so the mean is used.</t>
   </si>
   <si>
     <t xml:space="preserve">Directory listings per town</t>
@@ -649,7 +646,7 @@
     <t xml:space="preserve">Equity raised</t>
   </si>
   <si>
-    <t xml:space="preserve">Plan: $10M in FY2027 and $6M in FY2028, sized to the launch pace. Adjust to keep cash above zero.</t>
+    <t xml:space="preserve">Plan: $25M in FY2027 and $35M in FY2028, sized to the every-town launch pace with a buffer. Adjust to keep cash above zero.</t>
   </si>
   <si>
     <t xml:space="preserve">Town rollout</t>
@@ -1376,6 +1373,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="165" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1397,10 +1398,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="169" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1805,23 +1802,23 @@
       <c r="B7" s="2"/>
       <c r="C7" s="8" t="n">
         <f aca="false">Rollout!C7</f>
-        <v>1200</v>
+        <v>3000</v>
       </c>
       <c r="D7" s="8" t="n">
         <f aca="false">Rollout!D7</f>
-        <v>1777</v>
+        <v>5910</v>
       </c>
       <c r="E7" s="8" t="n">
         <f aca="false">Rollout!E7</f>
-        <v>1734.61</v>
+        <v>8193</v>
       </c>
       <c r="F7" s="8" t="n">
         <f aca="false">Rollout!F7</f>
-        <v>1710.35</v>
+        <v>8030.01</v>
       </c>
       <c r="G7" s="8" t="n">
         <f aca="false">Rollout!G7</f>
-        <v>1692.22</v>
+        <v>7921.35</v>
       </c>
       <c r="H7" s="2"/>
     </row>
@@ -1832,23 +1829,23 @@
       <c r="B8" s="2"/>
       <c r="C8" s="8" t="n">
         <f aca="false">KPIs!C8</f>
-        <v>199260</v>
+        <v>364140</v>
       </c>
       <c r="D8" s="8" t="n">
         <f aca="false">KPIs!D8</f>
-        <v>617207.85</v>
+        <v>1306048.8</v>
       </c>
       <c r="E8" s="8" t="n">
         <f aca="false">KPIs!E8</f>
-        <v>1020481.308</v>
+        <v>2620958.34</v>
       </c>
       <c r="F8" s="8" t="n">
         <f aca="false">KPIs!F8</f>
-        <v>1323318.87</v>
+        <v>3859078.0368</v>
       </c>
       <c r="G8" s="8" t="n">
         <f aca="false">KPIs!G8</f>
-        <v>1528506.855</v>
+        <v>4752682.452</v>
       </c>
       <c r="H8" s="2"/>
     </row>
@@ -1859,23 +1856,23 @@
       <c r="B9" s="2"/>
       <c r="C9" s="9" t="n">
         <f aca="false">'P&amp;L'!C5</f>
-        <v>879057.72</v>
+        <v>1898193.24</v>
       </c>
       <c r="D9" s="9" t="n">
         <f aca="false">'P&amp;L'!D5</f>
-        <v>7578011.8893</v>
+        <v>17162730.936</v>
       </c>
       <c r="E9" s="9" t="n">
         <f aca="false">'P&amp;L'!E5</f>
-        <v>19487904.15096</v>
+        <v>49867349.09364</v>
       </c>
       <c r="F9" s="9" t="n">
         <f aca="false">'P&amp;L'!F5</f>
-        <v>29622252.2451</v>
+        <v>90378208.443456</v>
       </c>
       <c r="G9" s="9" t="n">
         <f aca="false">'P&amp;L'!G5</f>
-        <v>36790077.802794</v>
+        <v>125554175.48988</v>
       </c>
       <c r="H9" s="2"/>
     </row>
@@ -1886,23 +1883,23 @@
       <c r="B10" s="2"/>
       <c r="C10" s="10" t="n">
         <f aca="false">'P&amp;L'!C8</f>
-        <v>0.49110097698704</v>
+        <v>0.431548852760639</v>
       </c>
       <c r="D10" s="10" t="n">
         <f aca="false">'P&amp;L'!D8</f>
-        <v>0.839158058580218</v>
+        <v>0.799502416256723</v>
       </c>
       <c r="E10" s="10" t="n">
         <f aca="false">'P&amp;L'!E8</f>
-        <v>0.916720423459067</v>
+        <v>0.88225003205724</v>
       </c>
       <c r="F10" s="10" t="n">
         <f aca="false">'P&amp;L'!F8</f>
-        <v>0.939676114980231</v>
+        <v>0.918154757640337</v>
       </c>
       <c r="G10" s="10" t="n">
         <f aca="false">'P&amp;L'!G8</f>
-        <v>0.947779974695033</v>
+        <v>0.936222688325491</v>
       </c>
       <c r="H10" s="2"/>
     </row>
@@ -1913,23 +1910,23 @@
       <c r="B11" s="2"/>
       <c r="C11" s="9" t="n">
         <f aca="false">'P&amp;L'!C16</f>
-        <v>-8022028.59488</v>
+        <v>-18714272.68496</v>
       </c>
       <c r="D11" s="9" t="n">
         <f aca="false">'P&amp;L'!D16</f>
-        <v>-6129956.1503272</v>
+        <v>-21529601.343104</v>
       </c>
       <c r="E11" s="9" t="n">
         <f aca="false">'P&amp;L'!E16</f>
-        <v>3082762.55895776</v>
+        <v>-9655829.95082656</v>
       </c>
       <c r="F11" s="9" t="n">
         <f aca="false">'P&amp;L'!F16</f>
-        <v>11223323.30919</v>
+        <v>22598678.7557132</v>
       </c>
       <c r="G11" s="9" t="n">
         <f aca="false">'P&amp;L'!G16</f>
-        <v>16306536.8800641</v>
+        <v>54040935.9844372</v>
       </c>
       <c r="H11" s="2"/>
     </row>
@@ -1940,23 +1937,23 @@
       <c r="B12" s="2"/>
       <c r="C12" s="10" t="n">
         <f aca="false">'P&amp;L'!C17</f>
-        <v>-9.12571314984868</v>
+        <v>-9.85899237790985</v>
       </c>
       <c r="D12" s="10" t="n">
         <f aca="false">'P&amp;L'!D17</f>
-        <v>-0.8089135039472</v>
+        <v>-1.25443913462188</v>
       </c>
       <c r="E12" s="10" t="n">
         <f aca="false">'P&amp;L'!E17</f>
-        <v>0.158188511965044</v>
+        <v>-0.193630303722282</v>
       </c>
       <c r="F12" s="10" t="n">
         <f aca="false">'P&amp;L'!F17</f>
-        <v>0.378881498149639</v>
+        <v>0.250045659732808</v>
       </c>
       <c r="G12" s="10" t="n">
         <f aca="false">'P&amp;L'!G17</f>
-        <v>0.443231921592342</v>
+        <v>0.430419265417366</v>
       </c>
       <c r="H12" s="2"/>
     </row>
@@ -1967,23 +1964,23 @@
       <c r="B13" s="2"/>
       <c r="C13" s="9" t="n">
         <f aca="false">'P&amp;L'!C25</f>
-        <v>-8096195.26154667</v>
+        <v>-18892606.0182933</v>
       </c>
       <c r="D13" s="9" t="n">
         <f aca="false">'P&amp;L'!D25</f>
-        <v>-6238289.48366053</v>
+        <v>-21872101.343104</v>
       </c>
       <c r="E13" s="9" t="n">
         <f aca="false">'P&amp;L'!E25</f>
-        <v>2974429.22562442</v>
+        <v>-10129163.2841599</v>
       </c>
       <c r="F13" s="9" t="n">
         <f aca="false">'P&amp;L'!F25</f>
-        <v>11185823.30919</v>
+        <v>22303678.7557132</v>
       </c>
       <c r="G13" s="9" t="n">
         <f aca="false">'P&amp;L'!G25</f>
-        <v>12268460.7126463</v>
+        <v>47580124.9607889</v>
       </c>
       <c r="H13" s="2"/>
     </row>
@@ -1994,23 +1991,23 @@
       <c r="B14" s="2"/>
       <c r="C14" s="9" t="n">
         <f aca="false">'Cash Flow'!C13</f>
-        <v>1979099.67352</v>
+        <v>5943781.51784</v>
       </c>
       <c r="D14" s="9" t="n">
         <f aca="false">'Cash Flow'!D13</f>
-        <v>1545674.8981138</v>
+        <v>18463744.043856</v>
       </c>
       <c r="E14" s="9" t="n">
         <f aca="false">'Cash Flow'!E13</f>
-        <v>4271140.68922176</v>
+        <v>7434275.54830025</v>
       </c>
       <c r="F14" s="9" t="n">
         <f aca="false">'Cash Flow'!F13</f>
-        <v>15180433.5555876</v>
+        <v>28817628.523519</v>
       </c>
       <c r="G14" s="9" t="n">
         <f aca="false">'Cash Flow'!G13</f>
-        <v>27230526.1681697</v>
+        <v>75473307.8062485</v>
       </c>
       <c r="H14" s="2"/>
     </row>
@@ -2021,23 +2018,23 @@
       <c r="B15" s="2"/>
       <c r="C15" s="9" t="n">
         <f aca="false">KPIs!C22</f>
-        <v>17170813.8057806</v>
+        <v>33780959.8039639</v>
       </c>
       <c r="D15" s="9" t="n">
         <f aca="false">KPIs!D22</f>
-        <v>25231246.9857268</v>
+        <v>66863868.3138088</v>
       </c>
       <c r="E15" s="9" t="n">
         <f aca="false">KPIs!E22</f>
-        <v>23594736.5567876</v>
+        <v>92357578.2246254</v>
       </c>
       <c r="F15" s="9" t="n">
         <f aca="false">KPIs!F22</f>
-        <v>21818314.6293474</v>
+        <v>89083676.518476</v>
       </c>
       <c r="G15" s="9" t="n">
         <f aca="false">KPIs!G22</f>
-        <v>20070116.8074734</v>
+        <v>86343208.4565014</v>
       </c>
       <c r="H15" s="2"/>
     </row>
@@ -2232,7 +2229,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2244,7 +2241,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2288,7 +2285,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B5" s="16"/>
       <c r="C5" s="16"/>
@@ -2300,20 +2297,20 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="33" t="n">
         <f aca="false">Rollout!C5</f>
-        <v>1200</v>
+        <v>3000</v>
       </c>
       <c r="D6" s="33" t="n">
         <f aca="false">Rollout!D5</f>
-        <v>613</v>
+        <v>3000</v>
       </c>
       <c r="E6" s="33" t="n">
         <f aca="false">Rollout!E5</f>
-        <v>0</v>
+        <v>2433</v>
       </c>
       <c r="F6" s="33" t="n">
         <f aca="false">Rollout!F5</f>
@@ -2332,83 +2329,83 @@
       <c r="B7" s="2"/>
       <c r="C7" s="33" t="n">
         <f aca="false">Rollout!C7</f>
-        <v>1200</v>
+        <v>3000</v>
       </c>
       <c r="D7" s="33" t="n">
         <f aca="false">Rollout!D7</f>
-        <v>1777</v>
+        <v>5910</v>
       </c>
       <c r="E7" s="33" t="n">
         <f aca="false">Rollout!E7</f>
-        <v>1734.61</v>
+        <v>8193</v>
       </c>
       <c r="F7" s="33" t="n">
         <f aca="false">Rollout!F7</f>
-        <v>1710.35</v>
+        <v>8030.01</v>
       </c>
       <c r="G7" s="33" t="n">
         <f aca="false">Rollout!G7</f>
-        <v>1692.22</v>
+        <v>7921.35</v>
       </c>
       <c r="H7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="33" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$C$10</f>
-        <v>199260</v>
+        <v>364140</v>
       </c>
       <c r="D8" s="33" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$D$10+Rollout!$D$5*'Unit Economics'!$C$10</f>
-        <v>617207.85</v>
+        <v>1306048.8</v>
       </c>
       <c r="E8" s="33" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$E$10+Rollout!$D$5*'Unit Economics'!$D$10+Rollout!$E$5*'Unit Economics'!$C$10</f>
-        <v>1020481.308</v>
+        <v>2620958.34</v>
       </c>
       <c r="F8" s="33" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$F$10+Rollout!$D$5*'Unit Economics'!$E$10+Rollout!$E$5*'Unit Economics'!$D$10+Rollout!$F$5*'Unit Economics'!$C$10</f>
-        <v>1323318.87</v>
+        <v>3859078.0368</v>
       </c>
       <c r="G8" s="33" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$G$10+Rollout!$D$5*'Unit Economics'!$F$10+Rollout!$E$5*'Unit Economics'!$E$10+Rollout!$F$5*'Unit Economics'!$D$10+Rollout!$G$5*'Unit Economics'!$C$10</f>
-        <v>1528506.855</v>
+        <v>4752682.452</v>
       </c>
       <c r="H8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="33" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$C$12</f>
-        <v>79704000</v>
+        <v>145656000</v>
       </c>
       <c r="D9" s="33" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$D$12+Rollout!$D$5*'Unit Economics'!$C$12</f>
-        <v>349966980</v>
+        <v>710801280</v>
       </c>
       <c r="E9" s="33" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$E$12+Rollout!$D$5*'Unit Economics'!$D$12+Rollout!$E$5*'Unit Economics'!$C$12</f>
-        <v>612288784.8</v>
+        <v>1513511496</v>
       </c>
       <c r="F9" s="33" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$F$12+Rollout!$D$5*'Unit Economics'!$E$12+Rollout!$E$5*'Unit Economics'!$D$12+Rollout!$F$5*'Unit Economics'!$C$12</f>
-        <v>756530442</v>
+        <v>2246988502.08</v>
       </c>
       <c r="G9" s="33" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$G$12+Rollout!$D$5*'Unit Economics'!$F$12+Rollout!$E$5*'Unit Economics'!$E$12+Rollout!$F$5*'Unit Economics'!$D$12+Rollout!$G$5*'Unit Economics'!$C$12</f>
-        <v>860905486.8</v>
+        <v>2715421111.2</v>
       </c>
       <c r="H9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B10" s="16"/>
       <c r="C10" s="16"/>
@@ -2420,61 +2417,61 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="33" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$C$17</f>
-        <v>6122.88</v>
+        <v>14631.36</v>
       </c>
       <c r="D11" s="33" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$D$17+Rollout!$D$5*'Unit Economics'!$C$17</f>
-        <v>22384.9872</v>
+        <v>60316.032</v>
       </c>
       <c r="E11" s="33" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$E$17+Rollout!$D$5*'Unit Economics'!$D$17+Rollout!$E$5*'Unit Economics'!$C$17</f>
-        <v>43088.74784</v>
+        <v>135864.14496</v>
       </c>
       <c r="F11" s="33" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$F$17+Rollout!$D$5*'Unit Economics'!$E$17+Rollout!$E$5*'Unit Economics'!$D$17+Rollout!$F$5*'Unit Economics'!$C$17</f>
-        <v>60648.6088</v>
+        <v>217770.316992</v>
       </c>
       <c r="G11" s="33" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$G$17+Rollout!$D$5*'Unit Economics'!$F$17+Rollout!$E$5*'Unit Economics'!$E$17+Rollout!$F$5*'Unit Economics'!$D$17+Rollout!$G$5*'Unit Economics'!$C$17</f>
-        <v>74647.40216</v>
+        <v>288291.33264</v>
       </c>
       <c r="H11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="42" t="n">
         <f aca="false">IF(C11=0,0,(Revenue!C5+Revenue!C6+Revenue!C7)/C11/12)</f>
-        <v>8.24490435873315</v>
+        <v>7.72501804343547</v>
       </c>
       <c r="D12" s="42" t="n">
         <f aca="false">IF(D11=0,0,(Revenue!D5+Revenue!D6+Revenue!D7)/D11/12)</f>
-        <v>18.5326371953431</v>
+        <v>16.410443710886</v>
       </c>
       <c r="E12" s="42" t="n">
         <f aca="false">IF(E11=0,0,(Revenue!E5+Revenue!E6+Revenue!E7)/E11/12)</f>
-        <v>21.7373985142939</v>
+        <v>19.3235441734311</v>
       </c>
       <c r="F12" s="42" t="n">
         <f aca="false">IF(F11=0,0,(Revenue!F5+Revenue!F6+Revenue!F7)/F11/12)</f>
-        <v>23.1203316571377</v>
+        <v>21.4351696295666</v>
       </c>
       <c r="G12" s="42" t="n">
         <f aca="false">IF(G11=0,0,(Revenue!G5+Revenue!G6+Revenue!G7)/G11/12)</f>
-        <v>23.8246888107378</v>
+        <v>22.3716527441142</v>
       </c>
       <c r="H12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B13" s="16"/>
       <c r="C13" s="16"/>
@@ -2491,50 +2488,50 @@
       <c r="B14" s="2"/>
       <c r="C14" s="37" t="n">
         <f aca="false">'P&amp;L'!C5</f>
-        <v>879057.72</v>
+        <v>1898193.24</v>
       </c>
       <c r="D14" s="37" t="n">
         <f aca="false">'P&amp;L'!D5</f>
-        <v>7578011.8893</v>
+        <v>17162730.936</v>
       </c>
       <c r="E14" s="37" t="n">
         <f aca="false">'P&amp;L'!E5</f>
-        <v>19487904.15096</v>
+        <v>49867349.09364</v>
       </c>
       <c r="F14" s="37" t="n">
         <f aca="false">'P&amp;L'!F5</f>
-        <v>29622252.2451</v>
+        <v>90378208.443456</v>
       </c>
       <c r="G14" s="37" t="n">
         <f aca="false">'P&amp;L'!G5</f>
-        <v>36790077.802794</v>
+        <v>125554175.48988</v>
       </c>
       <c r="H14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="37" t="n">
         <f aca="false">IF(Rollout!C8=0,0,'P&amp;L'!C5/Rollout!C8)</f>
-        <v>1465.0962</v>
+        <v>1265.46216</v>
       </c>
       <c r="D15" s="37" t="n">
         <f aca="false">IF(Rollout!D8=0,0,'P&amp;L'!D5/Rollout!D8)</f>
-        <v>5091.03922693987</v>
+        <v>3852.46485656566</v>
       </c>
       <c r="E15" s="37" t="n">
         <f aca="false">IF(Rollout!E8=0,0,'P&amp;L'!E5/Rollout!E8)</f>
-        <v>11099.1278364967</v>
+        <v>7071.87819522655</v>
       </c>
       <c r="F15" s="37" t="n">
         <f aca="false">IF(Rollout!F8=0,0,'P&amp;L'!F5/Rollout!F8)</f>
-        <v>17197.4433636965</v>
+        <v>11141.9777764368</v>
       </c>
       <c r="G15" s="37" t="n">
         <f aca="false">IF(Rollout!G8=0,0,'P&amp;L'!G5/Rollout!G8)</f>
-        <v>21624.8763745016</v>
+        <v>15742.1280053713</v>
       </c>
       <c r="H15" s="2"/>
     </row>
@@ -2545,23 +2542,23 @@
       <c r="B16" s="2"/>
       <c r="C16" s="34" t="n">
         <f aca="false">'P&amp;L'!C8</f>
-        <v>0.49110097698704</v>
+        <v>0.431548852760639</v>
       </c>
       <c r="D16" s="34" t="n">
         <f aca="false">'P&amp;L'!D8</f>
-        <v>0.839158058580218</v>
+        <v>0.799502416256723</v>
       </c>
       <c r="E16" s="34" t="n">
         <f aca="false">'P&amp;L'!E8</f>
-        <v>0.916720423459067</v>
+        <v>0.88225003205724</v>
       </c>
       <c r="F16" s="34" t="n">
         <f aca="false">'P&amp;L'!F8</f>
-        <v>0.939676114980231</v>
+        <v>0.918154757640337</v>
       </c>
       <c r="G16" s="34" t="n">
         <f aca="false">'P&amp;L'!G8</f>
-        <v>0.947779974695033</v>
+        <v>0.936222688325491</v>
       </c>
       <c r="H16" s="2"/>
     </row>
@@ -2572,23 +2569,23 @@
       <c r="B17" s="2"/>
       <c r="C17" s="37" t="n">
         <f aca="false">'P&amp;L'!C16</f>
-        <v>-8022028.59488</v>
+        <v>-18714272.68496</v>
       </c>
       <c r="D17" s="37" t="n">
         <f aca="false">'P&amp;L'!D16</f>
-        <v>-6129956.1503272</v>
+        <v>-21529601.343104</v>
       </c>
       <c r="E17" s="37" t="n">
         <f aca="false">'P&amp;L'!E16</f>
-        <v>3082762.55895776</v>
+        <v>-9655829.95082656</v>
       </c>
       <c r="F17" s="37" t="n">
         <f aca="false">'P&amp;L'!F16</f>
-        <v>11223323.30919</v>
+        <v>22598678.7557132</v>
       </c>
       <c r="G17" s="37" t="n">
         <f aca="false">'P&amp;L'!G16</f>
-        <v>16306536.8800641</v>
+        <v>54040935.9844372</v>
       </c>
       <c r="H17" s="2"/>
     </row>
@@ -2599,23 +2596,23 @@
       <c r="B18" s="2"/>
       <c r="C18" s="34" t="n">
         <f aca="false">'P&amp;L'!C17</f>
-        <v>-9.12571314984868</v>
+        <v>-9.85899237790985</v>
       </c>
       <c r="D18" s="34" t="n">
         <f aca="false">'P&amp;L'!D17</f>
-        <v>-0.8089135039472</v>
+        <v>-1.25443913462188</v>
       </c>
       <c r="E18" s="34" t="n">
         <f aca="false">'P&amp;L'!E17</f>
-        <v>0.158188511965044</v>
+        <v>-0.193630303722282</v>
       </c>
       <c r="F18" s="34" t="n">
         <f aca="false">'P&amp;L'!F17</f>
-        <v>0.378881498149639</v>
+        <v>0.250045659732808</v>
       </c>
       <c r="G18" s="34" t="n">
         <f aca="false">'P&amp;L'!G17</f>
-        <v>0.443231921592342</v>
+        <v>0.430419265417366</v>
       </c>
       <c r="H18" s="2"/>
     </row>
@@ -2626,135 +2623,135 @@
       <c r="B19" s="2"/>
       <c r="C19" s="37" t="n">
         <f aca="false">'Cash Flow'!C13</f>
-        <v>1979099.67352</v>
+        <v>5943781.51784</v>
       </c>
       <c r="D19" s="37" t="n">
         <f aca="false">'Cash Flow'!D13</f>
-        <v>1545674.8981138</v>
+        <v>18463744.043856</v>
       </c>
       <c r="E19" s="37" t="n">
         <f aca="false">'Cash Flow'!E13</f>
-        <v>4271140.68922176</v>
+        <v>7434275.54830025</v>
       </c>
       <c r="F19" s="37" t="n">
         <f aca="false">'Cash Flow'!F13</f>
-        <v>15180433.5555876</v>
+        <v>28817628.523519</v>
       </c>
       <c r="G19" s="37" t="n">
         <f aca="false">'Cash Flow'!G13</f>
-        <v>27230526.1681697</v>
+        <v>75473307.8062485</v>
       </c>
       <c r="H19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="34" t="n">
         <f aca="false">IF('P&amp;L'!C5=0,0,Costs!C6/'P&amp;L'!C5)</f>
-        <v>0.247735268168739</v>
+        <v>0.270203259179239</v>
       </c>
       <c r="D20" s="34" t="n">
         <f aca="false">IF('P&amp;L'!D5=0,0,Costs!D6/'P&amp;L'!D5)</f>
-        <v>0.0704309792326417</v>
+        <v>0.0878601503235732</v>
       </c>
       <c r="E20" s="34" t="n">
         <f aca="false">IF('P&amp;L'!E5=0,0,Costs!E6/'P&amp;L'!E5)</f>
-        <v>0.0323065580722792</v>
+        <v>0.0478366835485996</v>
       </c>
       <c r="F20" s="34" t="n">
         <f aca="false">IF('P&amp;L'!F5=0,0,Costs!F6/'P&amp;L'!F5)</f>
-        <v>0.0209566034838788</v>
+        <v>0.0303803032457523</v>
       </c>
       <c r="G20" s="34" t="n">
         <f aca="false">IF('P&amp;L'!G5=0,0,Costs!G6/'P&amp;L'!G5)</f>
-        <v>0.0166947568203662</v>
+        <v>0.0215728631694795</v>
       </c>
       <c r="H20" s="17" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" s="37" t="n">
         <f aca="false">Costs!C22+Costs!C23+Costs!C24+Costs!C21+Assumptions!C$97+Costs!C26</f>
-        <v>1258250</v>
+        <v>1633250</v>
       </c>
       <c r="D21" s="37" t="n">
         <f aca="false">Costs!D22+Costs!D23+Costs!D24+Costs!D21+Assumptions!D$97+Costs!D26</f>
-        <v>2059125</v>
+        <v>2902125</v>
       </c>
       <c r="E21" s="37" t="n">
         <f aca="false">Costs!E22+Costs!E23+Costs!E24+Costs!E21+Assumptions!E$97+Costs!E26</f>
-        <v>3044628.75</v>
+        <v>4358628.75</v>
       </c>
       <c r="F21" s="37" t="n">
         <f aca="false">Costs!F22+Costs!F23+Costs!F24+Costs!F21+Assumptions!F$97+Costs!F26</f>
-        <v>4448476.4375</v>
+        <v>5708476.4375</v>
       </c>
       <c r="G21" s="37" t="n">
         <f aca="false">Costs!G22+Costs!G23+Costs!G24+Costs!G21+Assumptions!G$97+Costs!G26</f>
-        <v>5918241.820375</v>
+        <v>7166241.820375</v>
       </c>
       <c r="H21" s="2"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="37" t="n">
         <f aca="false">Rollout!C7/'Unit Economics'!$G$7*'Unit Economics'!$G$42-C21</f>
-        <v>17170813.8057806</v>
+        <v>33780959.8039639</v>
       </c>
       <c r="D22" s="37" t="n">
         <f aca="false">Rollout!D7/'Unit Economics'!$G$7*'Unit Economics'!$G$42-D21</f>
-        <v>25231246.9857268</v>
+        <v>66863868.3138088</v>
       </c>
       <c r="E22" s="37" t="n">
         <f aca="false">Rollout!E7/'Unit Economics'!$G$7*'Unit Economics'!$G$42-E21</f>
-        <v>23594736.5567876</v>
+        <v>92357578.2246254</v>
       </c>
       <c r="F22" s="37" t="n">
         <f aca="false">Rollout!F7/'Unit Economics'!$G$7*'Unit Economics'!$G$42-F21</f>
-        <v>21818314.6293474</v>
+        <v>89083676.518476</v>
       </c>
       <c r="G22" s="37" t="n">
         <f aca="false">Rollout!G7/'Unit Economics'!$G$7*'Unit Economics'!$G$42-G21</f>
-        <v>20070116.8074734</v>
+        <v>86343208.4565014</v>
       </c>
       <c r="H22" s="17" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" s="33" t="n">
         <f aca="false">IF('Unit Economics'!$G$42&lt;=0,0,C21/('Unit Economics'!$G$42/'Unit Economics'!$G$7))</f>
-        <v>81.9303691122058</v>
+        <v>138.355480105943</v>
       </c>
       <c r="D23" s="33" t="n">
         <f aca="false">IF('Unit Economics'!$G$42&lt;=0,0,D21/('Unit Economics'!$G$42/'Unit Economics'!$G$7))</f>
-        <v>134.078975798268</v>
+        <v>245.844113088908</v>
       </c>
       <c r="E23" s="33" t="n">
         <f aca="false">IF('Unit Economics'!$G$42&lt;=0,0,E21/('Unit Economics'!$G$42/'Unit Economics'!$G$7))</f>
-        <v>198.249598487688</v>
+        <v>369.227107491085</v>
       </c>
       <c r="F23" s="33" t="n">
         <f aca="false">IF('Unit Economics'!$G$42&lt;=0,0,F21/('Unit Economics'!$G$42/'Unit Economics'!$G$7))</f>
-        <v>289.660493948997</v>
+        <v>483.575079249211</v>
       </c>
       <c r="G23" s="33" t="n">
         <f aca="false">IF('Unit Economics'!$G$42&lt;=0,0,G21/('Unit Economics'!$G$42/'Unit Economics'!$G$7))</f>
-        <v>385.363589778356</v>
+        <v>607.064948791224</v>
       </c>
       <c r="H23" s="2"/>
     </row>
@@ -2770,7 +2767,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="15" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B25" s="16"/>
       <c r="C25" s="16"/>
@@ -2782,12 +2779,12 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" s="9" t="n">
         <f aca="false">'Unit Economics'!G25</f>
-        <v>21494.26602</v>
+        <v>17934.8284368</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
@@ -2797,12 +2794,12 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" s="9" t="n">
         <f aca="false">'Unit Economics'!G42</f>
-        <v>14282.52444948</v>
+        <v>10978.4050392288</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
@@ -2812,12 +2809,12 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" s="10" t="n">
         <f aca="false">'Unit Economics'!G43</f>
-        <v>0.664480677599802</v>
+        <v>0.612127686524311</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
@@ -2827,7 +2824,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" s="9" t="n">
@@ -2842,29 +2839,29 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="41" t="n">
         <f aca="false">IFERROR(MATCH(TRUE(),INDEX('Unit Economics'!C45:G45&gt;0,0),0),"After Age 5")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
       <c r="H30" s="17" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" s="2" t="str">
         <f aca="false">IFERROR(INDEX(C4:G4,MATCH(TRUE(),INDEX(C17:G17&gt;0,0),0)),"Not by FY2031")</f>
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>
@@ -2874,12 +2871,12 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" s="9" t="n">
         <f aca="false">'Cash Flow'!C17</f>
-        <v>14704325.1018862</v>
+        <v>52815724.4516998</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" s="2"/>
@@ -3113,7 +3110,7 @@
         <v>49</v>
       </c>
       <c r="C13" s="21" t="n">
-        <v>4901</v>
+        <v>8433</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
@@ -3129,7 +3126,7 @@
       </c>
       <c r="B14" s="17"/>
       <c r="C14" s="22" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
@@ -3144,8 +3141,8 @@
         <v>53</v>
       </c>
       <c r="B15" s="17"/>
-      <c r="C15" s="22" t="n">
-        <v>0.74</v>
+      <c r="C15" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
@@ -3192,33 +3189,33 @@
         <v>56</v>
       </c>
       <c r="B18" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="C18" s="24" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D18" s="24" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E18" s="24" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F18" s="24" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G18" s="24" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H18" s="17" t="s">
         <v>57</v>
-      </c>
-      <c r="C18" s="23" t="n">
-        <v>1200</v>
-      </c>
-      <c r="D18" s="23" t="n">
-        <v>1200</v>
-      </c>
-      <c r="E18" s="23" t="n">
-        <v>1200</v>
-      </c>
-      <c r="F18" s="23" t="n">
-        <v>1200</v>
-      </c>
-      <c r="G18" s="23" t="n">
-        <v>1200</v>
-      </c>
-      <c r="H18" s="17" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="C19" s="21" t="n">
         <v>400</v>
@@ -3228,7 +3225,7 @@
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
       <c r="H19" s="17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3243,7 +3240,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B21" s="16"/>
       <c r="C21" s="16"/>
@@ -3257,92 +3254,92 @@
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="D22" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="D22" s="18" t="s">
+      <c r="E22" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="E22" s="18" t="s">
+      <c r="F22" s="18" t="s">
         <v>64</v>
-      </c>
-      <c r="F22" s="18" t="s">
-        <v>65</v>
       </c>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" s="22" t="n">
-        <v>0.72</v>
+        <v>0.84</v>
       </c>
       <c r="D23" s="22" t="n">
-        <v>0.21</v>
+        <v>0.12</v>
       </c>
       <c r="E23" s="22" t="n">
-        <v>0.07</v>
-      </c>
-      <c r="F23" s="24" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F23" s="25" t="n">
         <f aca="false">SUM(C23:E23)</f>
         <v>1</v>
       </c>
       <c r="G23" s="2"/>
       <c r="H23" s="17" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" s="21" t="n">
-        <v>4000</v>
+        <v>3300</v>
       </c>
       <c r="D24" s="21" t="n">
-        <v>19000</v>
+        <v>21000</v>
       </c>
       <c r="E24" s="21" t="n">
-        <v>60000</v>
-      </c>
-      <c r="F24" s="25" t="n">
+        <v>70000</v>
+      </c>
+      <c r="F24" s="26" t="n">
         <f aca="false">SUMPRODUCT(C24:E24,$C$23:$E$23)</f>
-        <v>11070</v>
+        <v>8092</v>
       </c>
       <c r="G24" s="2"/>
       <c r="H24" s="17" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" s="21" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="D25" s="21" t="n">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="E25" s="21" t="n">
-        <v>3000</v>
-      </c>
-      <c r="F25" s="25" t="n">
+        <v>3500</v>
+      </c>
+      <c r="F25" s="26" t="n">
         <f aca="false">SUMPRODUCT(C25:E25,$C$23:$E$23)</f>
-        <v>564</v>
+        <v>423.2</v>
       </c>
       <c r="G25" s="2"/>
       <c r="H25" s="17" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" s="21" t="n">
@@ -3354,36 +3351,36 @@
       <c r="E26" s="21" t="n">
         <v>10</v>
       </c>
-      <c r="F26" s="25" t="n">
+      <c r="F26" s="26" t="n">
         <f aca="false">SUMPRODUCT(C26:E26,$C$23:$E$23)</f>
-        <v>4.12</v>
+        <v>3.64</v>
       </c>
       <c r="G26" s="2"/>
       <c r="H26" s="17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B27" s="2"/>
-      <c r="C27" s="26" t="n">
+      <c r="C27" s="27" t="n">
         <v>150</v>
       </c>
-      <c r="D27" s="26" t="n">
+      <c r="D27" s="27" t="n">
         <v>400</v>
       </c>
-      <c r="E27" s="26" t="n">
+      <c r="E27" s="27" t="n">
         <v>900</v>
       </c>
-      <c r="F27" s="27" t="n">
+      <c r="F27" s="28" t="n">
         <f aca="false">SUMPRODUCT(C27:E27,$C$23:$E$23)</f>
-        <v>255</v>
+        <v>210</v>
       </c>
       <c r="G27" s="2"/>
       <c r="H27" s="17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3398,7 +3395,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B29" s="16"/>
       <c r="C29" s="16"/>
@@ -3410,29 +3407,29 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B30" s="6"/>
       <c r="C30" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D30" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="D30" s="7" t="s">
+      <c r="E30" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="E30" s="7" t="s">
+      <c r="F30" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="F30" s="7" t="s">
+      <c r="G30" s="7" t="s">
         <v>81</v>
-      </c>
-      <c r="G30" s="7" t="s">
-        <v>82</v>
       </c>
       <c r="H30" s="6"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B31" s="17"/>
       <c r="C31" s="22" t="n">
@@ -3451,55 +3448,55 @@
         <v>0.085</v>
       </c>
       <c r="H31" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="B32" s="17"/>
+      <c r="C32" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="E32" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="F32" s="29" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G32" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="H32" s="17" t="s">
         <v>85</v>
-      </c>
-      <c r="B32" s="17"/>
-      <c r="C32" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="D32" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="E32" s="28" t="n">
-        <v>3</v>
-      </c>
-      <c r="F32" s="28" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="G32" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="H32" s="17" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="B33" s="17"/>
+      <c r="C33" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" s="23" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="E33" s="23" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F33" s="23" t="n">
+        <v>0.94</v>
+      </c>
+      <c r="G33" s="23" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="H33" s="17" t="s">
         <v>87</v>
-      </c>
-      <c r="B33" s="17"/>
-      <c r="C33" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="D33" s="29" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="E33" s="29" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F33" s="29" t="n">
-        <v>0.94</v>
-      </c>
-      <c r="G33" s="29" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="H33" s="17" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3514,7 +3511,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="15" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B35" s="16"/>
       <c r="C35" s="16"/>
@@ -3526,29 +3523,29 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B36" s="6"/>
       <c r="C36" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D36" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="D36" s="7" t="s">
+      <c r="E36" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="E36" s="7" t="s">
+      <c r="F36" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="F36" s="7" t="s">
+      <c r="G36" s="7" t="s">
         <v>81</v>
-      </c>
-      <c r="G36" s="7" t="s">
-        <v>82</v>
       </c>
       <c r="H36" s="6"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B37" s="17"/>
       <c r="C37" s="22" t="n">
@@ -3567,36 +3564,36 @@
         <v>0.38</v>
       </c>
       <c r="H37" s="17" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="B38" s="17"/>
+      <c r="C38" s="23" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D38" s="23" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E38" s="23" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="F38" s="23" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G38" s="23" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H38" s="17" t="s">
         <v>92</v>
-      </c>
-      <c r="B38" s="17"/>
-      <c r="C38" s="29" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="D38" s="29" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E38" s="29" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="F38" s="29" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G38" s="29" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="H38" s="17" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B39" s="17"/>
       <c r="C39" s="22" t="n">
@@ -3615,84 +3612,84 @@
         <v>0.18</v>
       </c>
       <c r="H39" s="17" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="B40" s="17"/>
+      <c r="C40" s="23" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D40" s="23" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E40" s="23" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F40" s="23" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G40" s="23" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H40" s="17" t="s">
         <v>96</v>
-      </c>
-      <c r="B40" s="17"/>
-      <c r="C40" s="29" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D40" s="29" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E40" s="29" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="F40" s="29" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="G40" s="29" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H40" s="17" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="B41" s="17"/>
+      <c r="C41" s="23" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D41" s="23" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E41" s="23" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F41" s="23" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G41" s="23" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="H41" s="17" t="s">
         <v>98</v>
-      </c>
-      <c r="B41" s="17"/>
-      <c r="C41" s="29" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D41" s="29" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E41" s="29" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F41" s="29" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="G41" s="29" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="H41" s="17" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="B42" s="17"/>
+      <c r="C42" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="23" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E42" s="23" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F42" s="23" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G42" s="23" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H42" s="17" t="s">
         <v>100</v>
-      </c>
-      <c r="B42" s="17"/>
-      <c r="C42" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D42" s="29" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="E42" s="29" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F42" s="29" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="G42" s="29" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H42" s="17" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B43" s="17"/>
       <c r="C43" s="21" t="n">
@@ -3711,7 +3708,7 @@
         <v>1</v>
       </c>
       <c r="H43" s="17" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3726,7 +3723,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="15" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B45" s="16"/>
       <c r="C45" s="16"/>
@@ -3738,10 +3735,10 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="B46" s="17" t="s">
         <v>105</v>
-      </c>
-      <c r="B46" s="17" t="s">
-        <v>106</v>
       </c>
       <c r="C46" s="21" t="n">
         <v>28</v>
@@ -3751,17 +3748,17 @@
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
       <c r="H46" s="17" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="B47" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="B47" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="C47" s="26" t="n">
+      <c r="C47" s="27" t="n">
         <v>38</v>
       </c>
       <c r="D47" s="2"/>
@@ -3769,15 +3766,15 @@
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
       <c r="H47" s="17" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="B48" s="17" t="s">
         <v>111</v>
-      </c>
-      <c r="B48" s="17" t="s">
-        <v>112</v>
       </c>
       <c r="C48" s="21" t="n">
         <v>30</v>
@@ -3787,15 +3784,15 @@
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
       <c r="H48" s="17" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="11" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B49" s="17"/>
-      <c r="C49" s="29" t="n">
+      <c r="C49" s="23" t="n">
         <v>0.08</v>
       </c>
       <c r="D49" s="2"/>
@@ -3803,17 +3800,17 @@
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
       <c r="H49" s="17" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="11" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B50" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="C50" s="26" t="n">
+        <v>108</v>
+      </c>
+      <c r="C50" s="27" t="n">
         <v>39</v>
       </c>
       <c r="D50" s="2"/>
@@ -3821,17 +3818,17 @@
       <c r="F50" s="2"/>
       <c r="G50" s="2"/>
       <c r="H50" s="17" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B51" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="C51" s="26" t="n">
+        <v>108</v>
+      </c>
+      <c r="C51" s="27" t="n">
         <v>99</v>
       </c>
       <c r="D51" s="2"/>
@@ -3839,15 +3836,15 @@
       <c r="F51" s="2"/>
       <c r="G51" s="2"/>
       <c r="H51" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="B52" s="17" t="s">
         <v>120</v>
-      </c>
-      <c r="B52" s="17" t="s">
-        <v>121</v>
       </c>
       <c r="C52" s="21" t="n">
         <v>300</v>
@@ -3857,17 +3854,17 @@
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
       <c r="H52" s="17" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="B53" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="B53" s="17" t="s">
-        <v>124</v>
-      </c>
-      <c r="C53" s="26" t="n">
+      <c r="C53" s="27" t="n">
         <v>30</v>
       </c>
       <c r="D53" s="2"/>
@@ -3875,15 +3872,15 @@
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
       <c r="H53" s="17" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="B54" s="17" t="s">
         <v>126</v>
-      </c>
-      <c r="B54" s="17" t="s">
-        <v>127</v>
       </c>
       <c r="C54" s="30" t="n">
         <v>6</v>
@@ -3893,15 +3890,15 @@
       <c r="F54" s="2"/>
       <c r="G54" s="2"/>
       <c r="H54" s="17" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="11" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B55" s="17"/>
-      <c r="C55" s="29" t="n">
+      <c r="C55" s="23" t="n">
         <v>0.8</v>
       </c>
       <c r="D55" s="2"/>
@@ -3909,7 +3906,7 @@
       <c r="F55" s="2"/>
       <c r="G55" s="2"/>
       <c r="H55" s="17" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3924,7 +3921,7 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="15" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B57" s="16"/>
       <c r="C57" s="16"/>
@@ -3936,10 +3933,10 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="B58" s="17" t="s">
         <v>132</v>
-      </c>
-      <c r="B58" s="17" t="s">
-        <v>133</v>
       </c>
       <c r="C58" s="31" t="n">
         <v>0.12</v>
@@ -3949,15 +3946,15 @@
       <c r="F58" s="2"/>
       <c r="G58" s="2"/>
       <c r="H58" s="17" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="B59" s="17" t="s">
         <v>135</v>
-      </c>
-      <c r="B59" s="17" t="s">
-        <v>136</v>
       </c>
       <c r="C59" s="30" t="n">
         <v>0.5</v>
@@ -3967,15 +3964,15 @@
       <c r="F59" s="2"/>
       <c r="G59" s="2"/>
       <c r="H59" s="17" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="11" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B60" s="17" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C60" s="30" t="n">
         <v>5</v>
@@ -3985,17 +3982,17 @@
       <c r="F60" s="2"/>
       <c r="G60" s="2"/>
       <c r="H60" s="17" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="11" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B61" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="C61" s="26" t="n">
+        <v>108</v>
+      </c>
+      <c r="C61" s="27" t="n">
         <v>25</v>
       </c>
       <c r="D61" s="2"/>
@@ -4003,15 +4000,15 @@
       <c r="F61" s="2"/>
       <c r="G61" s="2"/>
       <c r="H61" s="17" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="B62" s="17" t="s">
         <v>142</v>
-      </c>
-      <c r="B62" s="17" t="s">
-        <v>143</v>
       </c>
       <c r="C62" s="30" t="n">
         <v>0.1</v>
@@ -4021,15 +4018,15 @@
       <c r="F62" s="2"/>
       <c r="G62" s="2"/>
       <c r="H62" s="17" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="11" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B63" s="17"/>
-      <c r="C63" s="29" t="n">
+      <c r="C63" s="23" t="n">
         <v>0.029</v>
       </c>
       <c r="D63" s="2"/>
@@ -4037,15 +4034,15 @@
       <c r="F63" s="2"/>
       <c r="G63" s="2"/>
       <c r="H63" s="17" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="B64" s="17" t="s">
         <v>147</v>
-      </c>
-      <c r="B64" s="17" t="s">
-        <v>148</v>
       </c>
       <c r="C64" s="30" t="n">
         <v>0.3</v>
@@ -4055,17 +4052,17 @@
       <c r="F64" s="2"/>
       <c r="G64" s="2"/>
       <c r="H64" s="17" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="B65" s="17" t="s">
         <v>150</v>
       </c>
-      <c r="B65" s="17" t="s">
-        <v>151</v>
-      </c>
-      <c r="C65" s="26" t="n">
+      <c r="C65" s="27" t="n">
         <v>20</v>
       </c>
       <c r="D65" s="2"/>
@@ -4073,17 +4070,17 @@
       <c r="F65" s="2"/>
       <c r="G65" s="2"/>
       <c r="H65" s="17" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="B66" s="17" t="s">
         <v>153</v>
       </c>
-      <c r="B66" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="C66" s="26" t="n">
+      <c r="C66" s="27" t="n">
         <v>25</v>
       </c>
       <c r="D66" s="2"/>
@@ -4091,17 +4088,17 @@
       <c r="F66" s="2"/>
       <c r="G66" s="2"/>
       <c r="H66" s="17" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="11" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B67" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="C67" s="26" t="n">
+        <v>153</v>
+      </c>
+      <c r="C67" s="27" t="n">
         <v>15</v>
       </c>
       <c r="D67" s="2"/>
@@ -4109,15 +4106,15 @@
       <c r="F67" s="2"/>
       <c r="G67" s="2"/>
       <c r="H67" s="17" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="11" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B68" s="17" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C68" s="32" t="n">
         <v>1500</v>
@@ -4127,15 +4124,15 @@
       <c r="F68" s="2"/>
       <c r="G68" s="2"/>
       <c r="H68" s="17" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="B69" s="17" t="s">
         <v>159</v>
-      </c>
-      <c r="B69" s="17" t="s">
-        <v>160</v>
       </c>
       <c r="C69" s="30" t="n">
         <v>2</v>
@@ -4145,15 +4142,15 @@
       <c r="F69" s="2"/>
       <c r="G69" s="2"/>
       <c r="H69" s="17" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="11" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B70" s="17"/>
-      <c r="C70" s="29" t="n">
+      <c r="C70" s="23" t="n">
         <v>0.4</v>
       </c>
       <c r="D70" s="2"/>
@@ -4161,7 +4158,7 @@
       <c r="F70" s="2"/>
       <c r="G70" s="2"/>
       <c r="H70" s="17" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4176,7 +4173,7 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="15" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B72" s="16"/>
       <c r="C72" s="16"/>
@@ -4188,10 +4185,10 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="11" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B73" s="17"/>
-      <c r="C73" s="29" t="n">
+      <c r="C73" s="23" t="n">
         <v>0.25</v>
       </c>
       <c r="D73" s="2"/>
@@ -4199,15 +4196,15 @@
       <c r="F73" s="2"/>
       <c r="G73" s="2"/>
       <c r="H73" s="17" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="11" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B74" s="17"/>
-      <c r="C74" s="29" t="n">
+      <c r="C74" s="23" t="n">
         <v>0.03</v>
       </c>
       <c r="D74" s="2"/>
@@ -4215,15 +4212,15 @@
       <c r="F74" s="2"/>
       <c r="G74" s="2"/>
       <c r="H74" s="17" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="11" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B75" s="17"/>
-      <c r="C75" s="29" t="n">
+      <c r="C75" s="23" t="n">
         <v>0.1</v>
       </c>
       <c r="D75" s="2"/>
@@ -4231,17 +4228,17 @@
       <c r="F75" s="2"/>
       <c r="G75" s="2"/>
       <c r="H75" s="17" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="11" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B76" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="C76" s="23" t="n">
+        <v>49</v>
+      </c>
+      <c r="C76" s="24" t="n">
         <v>40</v>
       </c>
       <c r="D76" s="2"/>
@@ -4249,17 +4246,17 @@
       <c r="F76" s="2"/>
       <c r="G76" s="2"/>
       <c r="H76" s="17" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="11" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B77" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="C77" s="23" t="n">
+        <v>49</v>
+      </c>
+      <c r="C77" s="24" t="n">
         <v>30</v>
       </c>
       <c r="D77" s="2"/>
@@ -4267,15 +4264,15 @@
       <c r="F77" s="2"/>
       <c r="G77" s="2"/>
       <c r="H77" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B78" s="17" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="C78" s="21" t="n">
         <v>120</v>
@@ -4285,7 +4282,7 @@
       <c r="F78" s="2"/>
       <c r="G78" s="2"/>
       <c r="H78" s="17" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4300,7 +4297,7 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="15" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B80" s="16"/>
       <c r="C80" s="16"/>
@@ -4312,12 +4309,12 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="11" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B81" s="17" t="s">
-        <v>151</v>
-      </c>
-      <c r="C81" s="26" t="n">
+        <v>150</v>
+      </c>
+      <c r="C81" s="27" t="n">
         <v>160000</v>
       </c>
       <c r="D81" s="2"/>
@@ -4325,17 +4322,17 @@
       <c r="F81" s="2"/>
       <c r="G81" s="2"/>
       <c r="H81" s="17" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="11" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B82" s="17" t="s">
-        <v>151</v>
-      </c>
-      <c r="C82" s="26" t="n">
+        <v>150</v>
+      </c>
+      <c r="C82" s="27" t="n">
         <v>170000</v>
       </c>
       <c r="D82" s="2"/>
@@ -4343,17 +4340,17 @@
       <c r="F82" s="2"/>
       <c r="G82" s="2"/>
       <c r="H82" s="17" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="11" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B83" s="17" t="s">
-        <v>151</v>
-      </c>
-      <c r="C83" s="26" t="n">
+        <v>150</v>
+      </c>
+      <c r="C83" s="27" t="n">
         <v>70000</v>
       </c>
       <c r="D83" s="2"/>
@@ -4361,17 +4358,17 @@
       <c r="F83" s="2"/>
       <c r="G83" s="2"/>
       <c r="H83" s="17" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="11" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B84" s="17" t="s">
-        <v>151</v>
-      </c>
-      <c r="C84" s="26" t="n">
+        <v>150</v>
+      </c>
+      <c r="C84" s="27" t="n">
         <v>65000</v>
       </c>
       <c r="D84" s="2"/>
@@ -4379,17 +4376,17 @@
       <c r="F84" s="2"/>
       <c r="G84" s="2"/>
       <c r="H84" s="17" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="11" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B85" s="17" t="s">
-        <v>151</v>
-      </c>
-      <c r="C85" s="26" t="n">
+        <v>150</v>
+      </c>
+      <c r="C85" s="27" t="n">
         <v>55000</v>
       </c>
       <c r="D85" s="2"/>
@@ -4397,17 +4394,17 @@
       <c r="F85" s="2"/>
       <c r="G85" s="2"/>
       <c r="H85" s="17" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="11" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B86" s="17" t="s">
-        <v>151</v>
-      </c>
-      <c r="C86" s="26" t="n">
+        <v>150</v>
+      </c>
+      <c r="C86" s="27" t="n">
         <v>110000</v>
       </c>
       <c r="D86" s="2"/>
@@ -4415,7 +4412,7 @@
       <c r="F86" s="2"/>
       <c r="G86" s="2"/>
       <c r="H86" s="17" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4430,7 +4427,7 @@
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="15" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B88" s="16"/>
       <c r="C88" s="16"/>
@@ -4464,10 +4461,10 @@
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="11" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B90" s="17" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C90" s="21" t="n">
         <v>2</v>
@@ -4485,15 +4482,15 @@
         <v>5</v>
       </c>
       <c r="H90" s="17" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="11" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B91" s="17" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C91" s="21" t="n">
         <v>3</v>
@@ -4511,15 +4508,15 @@
         <v>14</v>
       </c>
       <c r="H91" s="17" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="11" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B92" s="17" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C92" s="21" t="n">
         <v>1</v>
@@ -4537,7 +4534,7 @@
         <v>4</v>
       </c>
       <c r="H92" s="17" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4552,7 +4549,7 @@
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="15" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B94" s="16"/>
       <c r="C94" s="16"/>
@@ -4586,64 +4583,64 @@
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="B96" s="17" t="s">
         <v>185</v>
       </c>
-      <c r="B96" s="17" t="s">
+      <c r="C96" s="27" t="n">
+        <v>50000</v>
+      </c>
+      <c r="D96" s="27" t="n">
+        <v>150000</v>
+      </c>
+      <c r="E96" s="27" t="n">
+        <v>300000</v>
+      </c>
+      <c r="F96" s="27" t="n">
+        <v>500000</v>
+      </c>
+      <c r="G96" s="27" t="n">
+        <v>700000</v>
+      </c>
+      <c r="H96" s="17" t="s">
         <v>186</v>
-      </c>
-      <c r="C96" s="26" t="n">
-        <v>50000</v>
-      </c>
-      <c r="D96" s="26" t="n">
-        <v>150000</v>
-      </c>
-      <c r="E96" s="26" t="n">
-        <v>300000</v>
-      </c>
-      <c r="F96" s="26" t="n">
-        <v>500000</v>
-      </c>
-      <c r="G96" s="26" t="n">
-        <v>700000</v>
-      </c>
-      <c r="H96" s="17" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B97" s="17" t="s">
+        <v>185</v>
+      </c>
+      <c r="C97" s="27" t="n">
+        <v>60000</v>
+      </c>
+      <c r="D97" s="27" t="n">
+        <v>90000</v>
+      </c>
+      <c r="E97" s="27" t="n">
+        <v>140000</v>
+      </c>
+      <c r="F97" s="27" t="n">
+        <v>200000</v>
+      </c>
+      <c r="G97" s="27" t="n">
+        <v>260000</v>
+      </c>
+      <c r="H97" s="17" t="s">
         <v>188</v>
-      </c>
-      <c r="B97" s="17" t="s">
-        <v>186</v>
-      </c>
-      <c r="C97" s="26" t="n">
-        <v>60000</v>
-      </c>
-      <c r="D97" s="26" t="n">
-        <v>90000</v>
-      </c>
-      <c r="E97" s="26" t="n">
-        <v>140000</v>
-      </c>
-      <c r="F97" s="26" t="n">
-        <v>200000</v>
-      </c>
-      <c r="G97" s="26" t="n">
-        <v>260000</v>
-      </c>
-      <c r="H97" s="17" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="B98" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="B98" s="17" t="s">
-        <v>191</v>
-      </c>
-      <c r="C98" s="26" t="n">
+      <c r="C98" s="27" t="n">
         <v>100</v>
       </c>
       <c r="D98" s="2"/>
@@ -4651,17 +4648,17 @@
       <c r="F98" s="2"/>
       <c r="G98" s="2"/>
       <c r="H98" s="17" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B99" s="17" t="s">
-        <v>151</v>
-      </c>
-      <c r="C99" s="26" t="n">
+        <v>150</v>
+      </c>
+      <c r="C99" s="27" t="n">
         <v>3000</v>
       </c>
       <c r="D99" s="2"/>
@@ -4669,17 +4666,17 @@
       <c r="F99" s="2"/>
       <c r="G99" s="2"/>
       <c r="H99" s="17" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="B100" s="17" t="s">
         <v>193</v>
       </c>
-      <c r="B100" s="17" t="s">
-        <v>194</v>
-      </c>
-      <c r="C100" s="26" t="n">
+      <c r="C100" s="27" t="n">
         <v>2500</v>
       </c>
       <c r="D100" s="2"/>
@@ -4687,15 +4684,15 @@
       <c r="F100" s="2"/>
       <c r="G100" s="2"/>
       <c r="H100" s="17" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="B101" s="17" t="s">
         <v>195</v>
-      </c>
-      <c r="B101" s="17" t="s">
-        <v>196</v>
       </c>
       <c r="C101" s="21" t="n">
         <v>3</v>
@@ -4705,7 +4702,7 @@
       <c r="F101" s="2"/>
       <c r="G101" s="2"/>
       <c r="H101" s="17" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4720,7 +4717,7 @@
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="15" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B103" s="16"/>
       <c r="C103" s="16"/>
@@ -4732,10 +4729,10 @@
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="11" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B104" s="17"/>
-      <c r="C104" s="29" t="n">
+      <c r="C104" s="23" t="n">
         <v>0.25</v>
       </c>
       <c r="D104" s="2"/>
@@ -4743,15 +4740,15 @@
       <c r="F104" s="2"/>
       <c r="G104" s="2"/>
       <c r="H104" s="17" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="11" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B105" s="17"/>
-      <c r="C105" s="29" t="n">
+      <c r="C105" s="23" t="n">
         <v>0.03</v>
       </c>
       <c r="D105" s="2"/>
@@ -4759,15 +4756,15 @@
       <c r="F105" s="2"/>
       <c r="G105" s="2"/>
       <c r="H105" s="17" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="11" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B106" s="17" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C106" s="32" t="n">
         <v>250000</v>
@@ -4777,7 +4774,7 @@
       <c r="F106" s="2"/>
       <c r="G106" s="2"/>
       <c r="H106" s="17" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4814,16 +4811,16 @@
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="11" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B109" s="17" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C109" s="32" t="n">
-        <v>10000000</v>
+        <v>25000000</v>
       </c>
       <c r="D109" s="32" t="n">
-        <v>6000000</v>
+        <v>35000000</v>
       </c>
       <c r="E109" s="32" t="n">
         <v>0</v>
@@ -4835,7 +4832,7 @@
         <v>0</v>
       </c>
       <c r="H109" s="17" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
   </sheetData>
@@ -4865,7 +4862,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -4877,7 +4874,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4921,20 +4918,20 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="33" t="n">
         <f aca="false">MAX(0,MIN(ROUND(Assumptions!C$18*Assumptions!$F$7,0),$C$10))</f>
-        <v>1200</v>
+        <v>3000</v>
       </c>
       <c r="D5" s="33" t="n">
         <f aca="false">MAX(0,MIN(ROUND(Assumptions!D$18*Assumptions!$F$7,0),$C$10-C6))</f>
-        <v>613</v>
+        <v>3000</v>
       </c>
       <c r="E5" s="33" t="n">
         <f aca="false">MAX(0,MIN(ROUND(Assumptions!E$18*Assumptions!$F$7,0),$C$10-D6))</f>
-        <v>0</v>
+        <v>2433</v>
       </c>
       <c r="F5" s="33" t="n">
         <f aca="false">MAX(0,MIN(ROUND(Assumptions!F$18*Assumptions!$F$7,0),$C$10-E6))</f>
@@ -4945,33 +4942,33 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="33" t="n">
         <f aca="false">C5</f>
-        <v>1200</v>
+        <v>3000</v>
       </c>
       <c r="D6" s="33" t="n">
         <f aca="false">C6+D5</f>
-        <v>1813</v>
+        <v>6000</v>
       </c>
       <c r="E6" s="33" t="n">
         <f aca="false">D6+E5</f>
-        <v>1813</v>
+        <v>8433</v>
       </c>
       <c r="F6" s="33" t="n">
         <f aca="false">E6+F5</f>
-        <v>1813</v>
+        <v>8433</v>
       </c>
       <c r="G6" s="33" t="n">
         <f aca="false">F6+G5</f>
-        <v>1813</v>
+        <v>8433</v>
       </c>
       <c r="H6" s="2"/>
     </row>
@@ -4982,55 +4979,55 @@
       <c r="B7" s="2"/>
       <c r="C7" s="33" t="n">
         <f aca="false">C$5*Assumptions!$C$33</f>
-        <v>1200</v>
+        <v>3000</v>
       </c>
       <c r="D7" s="33" t="n">
         <f aca="false">C$5*Assumptions!$D$33+D$5*Assumptions!$C$33</f>
-        <v>1777</v>
+        <v>5910</v>
       </c>
       <c r="E7" s="33" t="n">
         <f aca="false">C$5*Assumptions!$E$33+D$5*Assumptions!$D$33+E$5*Assumptions!$C$33</f>
-        <v>1734.61</v>
+        <v>8193</v>
       </c>
       <c r="F7" s="33" t="n">
         <f aca="false">C$5*Assumptions!$F$33+D$5*Assumptions!$E$33+E$5*Assumptions!$D$33+F$5*Assumptions!$C$33</f>
-        <v>1710.35</v>
+        <v>8030.01</v>
       </c>
       <c r="G7" s="33" t="n">
         <f aca="false">C$5*Assumptions!$G$33+D$5*Assumptions!$F$33+E$5*Assumptions!$E$33+F$5*Assumptions!$D$33+G$5*Assumptions!$C$33</f>
-        <v>1692.22</v>
+        <v>7921.35</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="33" t="n">
         <f aca="false">C7/2</f>
-        <v>600</v>
+        <v>1500</v>
       </c>
       <c r="D8" s="33" t="n">
         <f aca="false">(C7+D7)/2</f>
-        <v>1488.5</v>
+        <v>4455</v>
       </c>
       <c r="E8" s="33" t="n">
         <f aca="false">(D7+E7)/2</f>
-        <v>1755.805</v>
+        <v>7051.5</v>
       </c>
       <c r="F8" s="33" t="n">
         <f aca="false">(E7+F7)/2</f>
-        <v>1722.48</v>
+        <v>8111.505</v>
       </c>
       <c r="G8" s="33" t="n">
         <f aca="false">(F7+G7)/2</f>
-        <v>1701.285</v>
+        <v>7975.68</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5045,33 +5042,33 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B10" s="2"/>
-      <c r="C10" s="25" t="n">
+      <c r="C10" s="26" t="n">
         <f aca="false">ROUND(MIN(Assumptions!$C$13,Assumptions!$C$13*Assumptions!$C$14*Assumptions!$C$15*Assumptions!$F$7),0)</f>
-        <v>1813</v>
+        <v>8433</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
       <c r="H10" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="33" t="n">
         <f aca="false">$C$10-C6</f>
-        <v>613</v>
+        <v>5433</v>
       </c>
       <c r="D11" s="33" t="n">
         <f aca="false">$C$10-D6</f>
-        <v>0</v>
+        <v>2433</v>
       </c>
       <c r="E11" s="33" t="n">
         <f aca="false">$C$10-E6</f>
@@ -5114,7 +5111,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -5126,7 +5123,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -5148,29 +5145,29 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="E4" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="F4" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="G4" s="7" t="s">
         <v>81</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>82</v>
       </c>
       <c r="H4" s="6"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B5" s="16"/>
       <c r="C5" s="16"/>
@@ -5182,7 +5179,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="34" t="n">
@@ -5206,12 +5203,12 @@
         <v>1</v>
       </c>
       <c r="H6" s="17" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="34" t="n">
@@ -5238,7 +5235,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="35" t="n">
@@ -5265,7 +5262,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B9" s="16"/>
       <c r="C9" s="16"/>
@@ -5277,88 +5274,88 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="33" t="n">
         <f aca="false">Assumptions!$F$24*Assumptions!C$31*Assumptions!$F$8*C7</f>
-        <v>166.05</v>
+        <v>121.38</v>
       </c>
       <c r="D10" s="33" t="n">
         <f aca="false">Assumptions!$F$24*Assumptions!D$31*Assumptions!$F$8*D7</f>
-        <v>429.516</v>
+        <v>313.9696</v>
       </c>
       <c r="E10" s="33" t="n">
         <f aca="false">Assumptions!$F$24*Assumptions!E$31*Assumptions!$F$8*E7</f>
-        <v>630.99</v>
+        <v>461.244</v>
       </c>
       <c r="F10" s="33" t="n">
         <f aca="false">Assumptions!$F$24*Assumptions!F$31*Assumptions!$F$8*F7</f>
-        <v>780.435</v>
+        <v>570.486</v>
       </c>
       <c r="G10" s="33" t="n">
         <f aca="false">Assumptions!$F$24*Assumptions!G$31*Assumptions!$F$8*G7</f>
-        <v>875.0835</v>
+        <v>639.6726</v>
       </c>
       <c r="H10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="33" t="n">
         <f aca="false">C10</f>
-        <v>166.05</v>
+        <v>121.38</v>
       </c>
       <c r="D11" s="33" t="n">
         <f aca="false">MAX(0,D10-C10)</f>
-        <v>263.466</v>
+        <v>192.5896</v>
       </c>
       <c r="E11" s="33" t="n">
         <f aca="false">MAX(0,E10-D10)</f>
-        <v>201.474</v>
+        <v>147.2744</v>
       </c>
       <c r="F11" s="33" t="n">
         <f aca="false">MAX(0,F10-E10)</f>
-        <v>149.445</v>
+        <v>109.242</v>
       </c>
       <c r="G11" s="33" t="n">
         <f aca="false">MAX(0,G10-F10)</f>
-        <v>94.6485000000001</v>
+        <v>69.1866000000001</v>
       </c>
       <c r="H11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="33" t="n">
         <f aca="false">Assumptions!$F$24*Assumptions!C$32*Assumptions!$F$8*12*C8</f>
-        <v>66420</v>
+        <v>48552</v>
       </c>
       <c r="D12" s="33" t="n">
         <f aca="false">Assumptions!$F$24*Assumptions!D$32*Assumptions!$F$8*12*D8</f>
-        <v>257709.6</v>
+        <v>188381.76</v>
       </c>
       <c r="E12" s="33" t="n">
         <f aca="false">Assumptions!$F$24*Assumptions!E$32*Assumptions!$F$8*12*E8</f>
-        <v>378594</v>
+        <v>276746.4</v>
       </c>
       <c r="F12" s="33" t="n">
         <f aca="false">Assumptions!$F$24*Assumptions!F$32*Assumptions!$F$8*12*F8</f>
-        <v>437043.6</v>
+        <v>319472.16</v>
       </c>
       <c r="G12" s="33" t="n">
         <f aca="false">Assumptions!$F$24*Assumptions!G$32*Assumptions!$F$8*12*G8</f>
-        <v>494164.8</v>
+        <v>361226.88</v>
       </c>
       <c r="H12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B13" s="16"/>
       <c r="C13" s="16"/>
@@ -5370,7 +5367,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="36" t="n">
@@ -5397,34 +5394,34 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="36" t="n">
         <f aca="false">Assumptions!$F$25*Assumptions!C$38*MIN(1,Assumptions!C$39*Assumptions!$F$9)*C7</f>
-        <v>0.9024</v>
+        <v>0.67712</v>
       </c>
       <c r="D15" s="36" t="n">
         <f aca="false">Assumptions!$F$25*Assumptions!D$38*MIN(1,Assumptions!D$39*Assumptions!$F$9)*D7</f>
-        <v>3.28248</v>
+        <v>2.463024</v>
       </c>
       <c r="E15" s="36" t="n">
         <f aca="false">Assumptions!$F$25*Assumptions!E$38*MIN(1,Assumptions!E$39*Assumptions!$F$9)*E7</f>
-        <v>6.4296</v>
+        <v>4.82448</v>
       </c>
       <c r="F15" s="36" t="n">
         <f aca="false">Assumptions!$F$25*Assumptions!F$38*MIN(1,Assumptions!F$39*Assumptions!$F$9)*F7</f>
-        <v>9.01272</v>
+        <v>6.762736</v>
       </c>
       <c r="G15" s="36" t="n">
         <f aca="false">Assumptions!$F$25*Assumptions!G$38*MIN(1,Assumptions!G$39*Assumptions!$F$9)*G7</f>
-        <v>11.329632</v>
+        <v>8.5012416</v>
       </c>
       <c r="H15" s="2"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="36" t="n">
@@ -5451,36 +5448,36 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="36" t="n">
         <f aca="false">C14+C15+C16</f>
-        <v>5.1024</v>
+        <v>4.87712</v>
       </c>
       <c r="D17" s="36" t="n">
         <f aca="false">D14+D15+D16</f>
-        <v>16.04768</v>
+        <v>15.228224</v>
       </c>
       <c r="E17" s="36" t="n">
         <f aca="false">E14+E15+E16</f>
-        <v>27.7096</v>
+        <v>26.10448</v>
       </c>
       <c r="F17" s="36" t="n">
         <f aca="false">F14+F15+F16</f>
-        <v>36.38552</v>
+        <v>34.135536</v>
       </c>
       <c r="G17" s="36" t="n">
         <f aca="false">G14+G15+G16</f>
-        <v>43.619232</v>
+        <v>40.7908416</v>
       </c>
       <c r="H17" s="17" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="15" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B18" s="16"/>
       <c r="C18" s="16"/>
@@ -5492,7 +5489,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="37" t="n">
@@ -5516,39 +5513,39 @@
         <v>4151.234304</v>
       </c>
       <c r="H19" s="17" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="37" t="n">
         <f aca="false">C15*Assumptions!$C$50*12*C6</f>
-        <v>211.1616</v>
+        <v>158.44608</v>
       </c>
       <c r="D20" s="37" t="n">
         <f aca="false">D15*Assumptions!$C$50*12*D6</f>
-        <v>1536.20064</v>
+        <v>1152.695232</v>
       </c>
       <c r="E20" s="37" t="n">
         <f aca="false">E15*Assumptions!$C$50*12*E6</f>
-        <v>3009.0528</v>
+        <v>2257.85664</v>
       </c>
       <c r="F20" s="37" t="n">
         <f aca="false">F15*Assumptions!$C$50*12*F6</f>
-        <v>4217.95296</v>
+        <v>3164.960448</v>
       </c>
       <c r="G20" s="37" t="n">
         <f aca="false">G15*Assumptions!$C$50*12*G6</f>
-        <v>5302.267776</v>
+        <v>3978.5810688</v>
       </c>
       <c r="H20" s="2"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" s="37" t="n">
@@ -5575,63 +5572,63 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="11" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="37" t="n">
         <f aca="false">C10/1000*Assumptions!$C$53*Assumptions!$C$52*MIN(1,Assumptions!C$40*Assumptions!$F$9)*C6</f>
-        <v>74.7225</v>
+        <v>54.621</v>
       </c>
       <c r="D22" s="37" t="n">
         <f aca="false">D10/1000*Assumptions!$C$53*Assumptions!$C$52*MIN(1,Assumptions!D$40*Assumptions!$F$9)*D6</f>
-        <v>1159.6932</v>
+        <v>847.71792</v>
       </c>
       <c r="E22" s="37" t="n">
         <f aca="false">E10/1000*Assumptions!$C$53*Assumptions!$C$52*MIN(1,Assumptions!E$40*Assumptions!$F$9)*E6</f>
-        <v>2555.5095</v>
+        <v>1868.0382</v>
       </c>
       <c r="F22" s="37" t="n">
         <f aca="false">F10/1000*Assumptions!$C$53*Assumptions!$C$52*MIN(1,Assumptions!F$40*Assumptions!$F$9)*F6</f>
-        <v>3863.15325</v>
+        <v>2823.9057</v>
       </c>
       <c r="G22" s="37" t="n">
         <f aca="false">G10/1000*Assumptions!$C$53*Assumptions!$C$52*MIN(1,Assumptions!G$40*Assumptions!$F$9)*G6</f>
-        <v>4725.4509</v>
+        <v>3454.23204</v>
       </c>
       <c r="H22" s="17" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" s="37" t="n">
         <f aca="false">Assumptions!$F$27*12*MIN(1,Assumptions!C$41*Assumptions!$F$9)*C8</f>
-        <v>153</v>
+        <v>126</v>
       </c>
       <c r="D23" s="37" t="n">
         <f aca="false">Assumptions!$F$27*12*MIN(1,Assumptions!D$41*Assumptions!$F$9)*D8</f>
-        <v>890.46</v>
+        <v>733.32</v>
       </c>
       <c r="E23" s="37" t="n">
         <f aca="false">Assumptions!$F$27*12*MIN(1,Assumptions!E$41*Assumptions!$F$9)*E8</f>
-        <v>1453.5</v>
+        <v>1197</v>
       </c>
       <c r="F23" s="37" t="n">
         <f aca="false">Assumptions!$F$27*12*MIN(1,Assumptions!F$41*Assumptions!$F$9)*F8</f>
-        <v>1725.84</v>
+        <v>1421.28</v>
       </c>
       <c r="G23" s="37" t="n">
         <f aca="false">Assumptions!$F$27*12*MIN(1,Assumptions!G$41*Assumptions!$F$9)*G8</f>
-        <v>1849.77</v>
+        <v>1523.34</v>
       </c>
       <c r="H23" s="2"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" s="37" t="n">
@@ -5644,102 +5641,102 @@
       </c>
       <c r="E24" s="37" t="n">
         <f aca="false">E12/1000*Assumptions!$C$54*Assumptions!$C$55*Assumptions!E$43</f>
-        <v>1817.2512</v>
+        <v>1328.38272</v>
       </c>
       <c r="F24" s="37" t="n">
         <f aca="false">F12/1000*Assumptions!$C$54*Assumptions!$C$55*Assumptions!F$43</f>
-        <v>2097.80928</v>
+        <v>1533.466368</v>
       </c>
       <c r="G24" s="37" t="n">
         <f aca="false">G12/1000*Assumptions!$C$54*Assumptions!$C$55*Assumptions!G$43</f>
-        <v>2371.99104</v>
+        <v>1733.889024</v>
       </c>
       <c r="H24" s="2"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" s="38" t="n">
         <f aca="false">SUM(C19:C24)</f>
-        <v>732.5481</v>
+        <v>632.73108</v>
       </c>
       <c r="D25" s="38" t="n">
         <f aca="false">SUM(D19:D24)</f>
-        <v>5940.79992</v>
+        <v>5088.179232</v>
       </c>
       <c r="E25" s="38" t="n">
         <f aca="false">SUM(E19:E24)</f>
-        <v>13205.1615</v>
+        <v>11021.12556</v>
       </c>
       <c r="F25" s="38" t="n">
         <f aca="false">SUM(F19:F24)</f>
-        <v>17939.573538</v>
+        <v>14978.430564</v>
       </c>
       <c r="G25" s="38" t="n">
         <f aca="false">SUM(G19:G24)</f>
-        <v>21494.26602</v>
+        <v>17934.8284368</v>
       </c>
       <c r="H25" s="2"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" s="37" t="n">
         <f aca="false">C19+C20</f>
-        <v>504.8256</v>
+        <v>452.11008</v>
       </c>
       <c r="D26" s="37" t="n">
         <f aca="false">D19+D20</f>
-        <v>3245.32512</v>
+        <v>2861.819712</v>
       </c>
       <c r="E26" s="37" t="n">
         <f aca="false">E19+E20</f>
-        <v>5798.8608</v>
+        <v>5047.66464</v>
       </c>
       <c r="F26" s="37" t="n">
         <f aca="false">F19+F20</f>
-        <v>7751.318208</v>
+        <v>6698.325696</v>
       </c>
       <c r="G26" s="37" t="n">
         <f aca="false">G19+G20</f>
-        <v>9453.50208</v>
+        <v>8129.8153728</v>
       </c>
       <c r="H26" s="2"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" s="37" t="n">
         <f aca="false">C21+C22+C23</f>
-        <v>227.7225</v>
+        <v>180.621</v>
       </c>
       <c r="D27" s="37" t="n">
         <f aca="false">D21+D22+D23</f>
-        <v>2695.4748</v>
+        <v>2226.35952</v>
       </c>
       <c r="E27" s="37" t="n">
         <f aca="false">E21+E22+E23</f>
-        <v>5589.0495</v>
+        <v>4645.0782</v>
       </c>
       <c r="F27" s="37" t="n">
         <f aca="false">F21+F22+F23</f>
-        <v>8090.44605</v>
+        <v>6746.6385</v>
       </c>
       <c r="G27" s="37" t="n">
         <f aca="false">G21+G22+G23</f>
-        <v>9668.7729</v>
+        <v>8071.12404</v>
       </c>
       <c r="H27" s="2"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="15" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B28" s="16"/>
       <c r="C28" s="16"/>
@@ -5751,36 +5748,36 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="11" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" s="37" t="n">
         <f aca="false">MIN(Assumptions!$C$60,Assumptions!$F$26*Assumptions!$C$58+Assumptions!$C$59)*Assumptions!$F$10*365*C8</f>
-        <v>181.478</v>
+        <v>170.966</v>
       </c>
       <c r="D29" s="37" t="n">
         <f aca="false">MIN(Assumptions!$C$60,Assumptions!$F$26*Assumptions!$C$58+Assumptions!$C$59)*Assumptions!$F$10*365*D8</f>
-        <v>352.06732</v>
+        <v>331.67404</v>
       </c>
       <c r="E29" s="37" t="n">
         <f aca="false">MIN(Assumptions!$C$60,Assumptions!$F$26*Assumptions!$C$58+Assumptions!$C$59)*Assumptions!$F$10*365*E8</f>
-        <v>344.8082</v>
+        <v>324.8354</v>
       </c>
       <c r="F29" s="37" t="n">
         <f aca="false">MIN(Assumptions!$C$60,Assumptions!$F$26*Assumptions!$C$58+Assumptions!$C$59)*Assumptions!$F$10*365*F8</f>
-        <v>341.17864</v>
+        <v>321.41608</v>
       </c>
       <c r="G29" s="37" t="n">
         <f aca="false">MIN(Assumptions!$C$60,Assumptions!$F$26*Assumptions!$C$58+Assumptions!$C$59)*Assumptions!$F$10*365*G8</f>
-        <v>337.54908</v>
+        <v>317.99676</v>
       </c>
       <c r="H29" s="17" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="11" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="37" t="n">
@@ -5807,61 +5804,61 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="11" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" s="37" t="n">
         <f aca="false">C10*Assumptions!$C$52/1000*Assumptions!$C$62*C6</f>
-        <v>2.49075</v>
+        <v>1.8207</v>
       </c>
       <c r="D31" s="37" t="n">
         <f aca="false">D10*Assumptions!$C$52/1000*Assumptions!$C$62*D6</f>
-        <v>12.88548</v>
+        <v>9.419088</v>
       </c>
       <c r="E31" s="37" t="n">
         <f aca="false">E10*Assumptions!$C$52/1000*Assumptions!$C$62*E6</f>
-        <v>18.9297</v>
+        <v>13.83732</v>
       </c>
       <c r="F31" s="37" t="n">
         <f aca="false">F10*Assumptions!$C$52/1000*Assumptions!$C$62*F6</f>
-        <v>23.41305</v>
+        <v>17.11458</v>
       </c>
       <c r="G31" s="37" t="n">
         <f aca="false">G10*Assumptions!$C$52/1000*Assumptions!$C$62*G6</f>
-        <v>26.252505</v>
+        <v>19.190178</v>
       </c>
       <c r="H31" s="2"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="11" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" s="37" t="n">
         <f aca="false">C26*Assumptions!$C$63+(C14+C15)*12*Assumptions!$C$64*C6</f>
-        <v>23.8242624</v>
+        <v>21.89000832</v>
       </c>
       <c r="D32" s="37" t="n">
         <f aca="false">D26*Assumptions!$C$63+(D14+D15)*12*Assumptions!$C$64*D6</f>
-        <v>149.93055648</v>
+        <v>135.858858048</v>
       </c>
       <c r="E32" s="37" t="n">
         <f aca="false">E26*Assumptions!$C$63+(E14+E15)*12*Assumptions!$C$64*E6</f>
-        <v>263.1335232</v>
+        <v>235.57040256</v>
       </c>
       <c r="F32" s="37" t="n">
         <f aca="false">F26*Assumptions!$C$63+(F14+F15)*12*Assumptions!$C$64*F6</f>
-        <v>348.195940032</v>
+        <v>309.559214784</v>
       </c>
       <c r="G32" s="37" t="n">
         <f aca="false">G26*Assumptions!$C$63+(G14+G15)*12*Assumptions!$C$64*G6</f>
-        <v>421.80639552</v>
+        <v>373.2372755712</v>
       </c>
       <c r="H32" s="2"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="11" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" s="37" t="n">
@@ -5885,60 +5882,60 @@
         <v>18.6</v>
       </c>
       <c r="H33" s="17" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" s="38" t="n">
         <f aca="false">SUM(C29:C33)</f>
-        <v>357.7930124</v>
+        <v>344.67670832</v>
       </c>
       <c r="D34" s="38" t="n">
         <f aca="false">SUM(D29:D33)</f>
-        <v>825.28335648</v>
+        <v>787.351986048</v>
       </c>
       <c r="E34" s="38" t="n">
         <f aca="false">SUM(E29:E33)</f>
-        <v>930.8714232</v>
+        <v>878.24312256</v>
       </c>
       <c r="F34" s="38" t="n">
         <f aca="false">SUM(F29:F33)</f>
-        <v>1013.587630032</v>
+        <v>948.889874784</v>
       </c>
       <c r="G34" s="38" t="n">
         <f aca="false">SUM(G29:G33)</f>
-        <v>1083.20798052</v>
+        <v>1008.0242135712</v>
       </c>
       <c r="H34" s="2"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B35" s="2"/>
-      <c r="C35" s="27" t="n">
+      <c r="C35" s="28" t="n">
         <f aca="false">C25-C34</f>
-        <v>374.7550876</v>
-      </c>
-      <c r="D35" s="27" t="n">
+        <v>288.05437168</v>
+      </c>
+      <c r="D35" s="28" t="n">
         <f aca="false">D25-D34</f>
-        <v>5115.51656352</v>
-      </c>
-      <c r="E35" s="27" t="n">
+        <v>4300.827245952</v>
+      </c>
+      <c r="E35" s="28" t="n">
         <f aca="false">E25-E34</f>
-        <v>12274.2900768</v>
-      </c>
-      <c r="F35" s="27" t="n">
+        <v>10142.88243744</v>
+      </c>
+      <c r="F35" s="28" t="n">
         <f aca="false">F25-F34</f>
-        <v>16925.985907968</v>
-      </c>
-      <c r="G35" s="27" t="n">
+        <v>14029.540689216</v>
+      </c>
+      <c r="G35" s="28" t="n">
         <f aca="false">G25-G34</f>
-        <v>20411.05803948</v>
+        <v>16926.8042232288</v>
       </c>
       <c r="H35" s="2"/>
     </row>
@@ -5949,29 +5946,29 @@
       <c r="B36" s="2"/>
       <c r="C36" s="34" t="n">
         <f aca="false">IF(C25=0,0,C35/C25)</f>
-        <v>0.511577448088392</v>
+        <v>0.455255606663103</v>
       </c>
       <c r="D36" s="34" t="n">
         <f aca="false">IF(D25=0,0,D35/D25)</f>
-        <v>0.861082115608431</v>
+        <v>0.845258598381072</v>
       </c>
       <c r="E36" s="34" t="n">
         <f aca="false">IF(E25=0,0,E35/E25)</f>
-        <v>0.929507002000695</v>
+        <v>0.920312755917827</v>
       </c>
       <c r="F36" s="34" t="n">
         <f aca="false">IF(F25=0,0,F35/F25)</f>
-        <v>0.943499903836343</v>
+        <v>0.936649579491685</v>
       </c>
       <c r="G36" s="34" t="n">
         <f aca="false">IF(G25=0,0,G35/G25)</f>
-        <v>0.949604793226617</v>
+        <v>0.943795157164545</v>
       </c>
       <c r="H36" s="2"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="15" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B37" s="16"/>
       <c r="C37" s="16"/>
@@ -5983,7 +5980,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="11" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" s="37" t="n">
@@ -6010,34 +6007,34 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="11" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" s="37" t="n">
         <f aca="false">Assumptions!$C$84*(1+Assumptions!$C$73)/Assumptions!$C$77*C8+C27*Assumptions!$C$75</f>
-        <v>1376.93891666667</v>
+        <v>1372.22876666667</v>
       </c>
       <c r="D39" s="37" t="n">
         <f aca="false">Assumptions!$C$84*(1+Assumptions!$C$73)/Assumptions!$C$77*D8+D27*Assumptions!$C$75</f>
-        <v>2896.63081333333</v>
+        <v>2849.71928533333</v>
       </c>
       <c r="E39" s="37" t="n">
         <f aca="false">Assumptions!$C$84*(1+Assumptions!$C$73)/Assumptions!$C$77*E8+E27*Assumptions!$C$75</f>
-        <v>3131.82161666667</v>
+        <v>3037.42448666667</v>
       </c>
       <c r="F39" s="37" t="n">
         <f aca="false">Assumptions!$C$84*(1+Assumptions!$C$73)/Assumptions!$C$77*F8+F27*Assumptions!$C$75</f>
-        <v>3354.87793833333</v>
+        <v>3220.49718333333</v>
       </c>
       <c r="G39" s="37" t="n">
         <f aca="false">Assumptions!$C$84*(1+Assumptions!$C$73)/Assumptions!$C$77*G8+G27*Assumptions!$C$75</f>
-        <v>3485.62729</v>
+        <v>3325.862404</v>
       </c>
       <c r="H39" s="2"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="11" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" s="37" t="n">
@@ -6064,88 +6061,88 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="11" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B41" s="2"/>
       <c r="C41" s="37" t="n">
         <f aca="false">C11*Assumptions!$C$70*Assumptions!$C$69</f>
-        <v>132.84</v>
+        <v>97.104</v>
       </c>
       <c r="D41" s="37" t="n">
         <f aca="false">D11*Assumptions!$C$70*Assumptions!$C$69</f>
-        <v>210.7728</v>
+        <v>154.07168</v>
       </c>
       <c r="E41" s="37" t="n">
         <f aca="false">E11*Assumptions!$C$70*Assumptions!$C$69</f>
-        <v>161.1792</v>
+        <v>117.81952</v>
       </c>
       <c r="F41" s="37" t="n">
         <f aca="false">F11*Assumptions!$C$70*Assumptions!$C$69</f>
-        <v>119.556</v>
+        <v>87.3936</v>
       </c>
       <c r="G41" s="37" t="n">
         <f aca="false">G11*Assumptions!$C$70*Assumptions!$C$69</f>
-        <v>75.7188000000001</v>
+        <v>55.3492800000001</v>
       </c>
       <c r="H41" s="2"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" s="38" t="n">
         <f aca="false">C35-SUM(C38:C41)</f>
-        <v>-2515.2321624</v>
+        <v>-2561.48672832</v>
       </c>
       <c r="D42" s="38" t="n">
         <f aca="false">D35-SUM(D38:D41)</f>
-        <v>-669.491216480001</v>
+        <v>-1380.567886048</v>
       </c>
       <c r="E42" s="38" t="n">
         <f aca="false">E35-SUM(E38:E41)</f>
-        <v>6358.8934268</v>
+        <v>4365.24259744</v>
       </c>
       <c r="F42" s="38" t="n">
         <f aca="false">F35-SUM(F38:F41)</f>
-        <v>10856.760302968</v>
+        <v>8126.858239216</v>
       </c>
       <c r="G42" s="38" t="n">
         <f aca="false">G35-SUM(G38:G41)</f>
-        <v>14282.52444948</v>
+        <v>10978.4050392288</v>
       </c>
       <c r="H42" s="2"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="11" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B43" s="2"/>
       <c r="C43" s="34" t="n">
         <f aca="false">IF(C25=0,0,C42/C25)</f>
-        <v>-3.43353857910491</v>
+        <v>-4.04830236618059</v>
       </c>
       <c r="D43" s="34" t="n">
         <f aca="false">IF(D25=0,0,D42/D25)</f>
-        <v>-0.112693782907269</v>
+        <v>-0.271328469988929</v>
       </c>
       <c r="E43" s="34" t="n">
         <f aca="false">IF(E25=0,0,E42/E25)</f>
-        <v>0.481546055063393</v>
+        <v>0.396079563169408</v>
       </c>
       <c r="F43" s="34" t="n">
         <f aca="false">IF(F25=0,0,F42/F25)</f>
-        <v>0.605184971647791</v>
+        <v>0.542570745612598</v>
       </c>
       <c r="G43" s="34" t="n">
         <f aca="false">IF(G25=0,0,G42/G25)</f>
-        <v>0.664480677599802</v>
+        <v>0.612127686524311</v>
       </c>
       <c r="H43" s="2"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="11" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B44" s="2"/>
       <c r="C44" s="37" t="n">
@@ -6172,31 +6169,31 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="B45" s="2"/>
+      <c r="C45" s="28" t="n">
+        <f aca="false">C42-C44</f>
+        <v>-4101.48672832</v>
+      </c>
+      <c r="D45" s="28" t="n">
+        <f aca="false">C45+D42-D44</f>
+        <v>-5482.054614368</v>
+      </c>
+      <c r="E45" s="28" t="n">
+        <f aca="false">D45+E42-E44</f>
+        <v>-1116.812016928</v>
+      </c>
+      <c r="F45" s="28" t="n">
+        <f aca="false">E45+F42-F44</f>
+        <v>7010.046222288</v>
+      </c>
+      <c r="G45" s="28" t="n">
+        <f aca="false">F45+G42-G44</f>
+        <v>17988.4512615168</v>
+      </c>
+      <c r="H45" s="17" t="s">
         <v>264</v>
-      </c>
-      <c r="B45" s="2"/>
-      <c r="C45" s="27" t="n">
-        <f aca="false">C42-C44</f>
-        <v>-4055.2321624</v>
-      </c>
-      <c r="D45" s="27" t="n">
-        <f aca="false">C45+D42-D44</f>
-        <v>-4724.72337888</v>
-      </c>
-      <c r="E45" s="27" t="n">
-        <f aca="false">D45+E42-E44</f>
-        <v>1634.17004792</v>
-      </c>
-      <c r="F45" s="27" t="n">
-        <f aca="false">E45+F42-F44</f>
-        <v>12490.930350888</v>
-      </c>
-      <c r="G45" s="27" t="n">
-        <f aca="false">F45+G42-G44</f>
-        <v>26773.454800368</v>
-      </c>
-      <c r="H45" s="17" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6211,7 +6208,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="17" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -6248,7 +6245,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -6260,7 +6257,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -6304,61 +6301,61 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$C$19</f>
-        <v>352396.8</v>
+        <v>880992</v>
       </c>
       <c r="D5" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$D$19+Rollout!$D$5*'Unit Economics'!$C$19</f>
-        <v>2230965.408</v>
+        <v>6008365.44</v>
       </c>
       <c r="E5" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$E$19+Rollout!$D$5*'Unit Economics'!$D$19+Rollout!$E$5*'Unit Economics'!$C$19</f>
-        <v>4395462.90624</v>
+        <v>14211281.952</v>
       </c>
       <c r="F5" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$F$19+Rollout!$D$5*'Unit Economics'!$E$19+Rollout!$E$5*'Unit Economics'!$D$19+Rollout!$F$5*'Unit Economics'!$C$19</f>
-        <v>5950190.6016</v>
+        <v>23127819.60384</v>
       </c>
       <c r="G5" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$G$19+Rollout!$D$5*'Unit Economics'!$F$19+Rollout!$E$5*'Unit Economics'!$E$19+Rollout!$F$5*'Unit Economics'!$D$19+Rollout!$G$5*'Unit Economics'!$C$19</f>
-        <v>7147434.061824</v>
+        <v>29841401.52</v>
       </c>
       <c r="H5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$C$20</f>
-        <v>253393.92</v>
+        <v>475338.24</v>
       </c>
       <c r="D6" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$D$20+Rollout!$D$5*'Unit Economics'!$C$20</f>
-        <v>1972882.8288</v>
+        <v>3933423.936</v>
       </c>
       <c r="E6" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$E$20+Rollout!$D$5*'Unit Economics'!$D$20+Rollout!$E$5*'Unit Economics'!$C$20</f>
-        <v>4552554.35232</v>
+        <v>10617154.92864</v>
       </c>
       <c r="F6" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$F$20+Rollout!$D$5*'Unit Economics'!$E$20+Rollout!$E$5*'Unit Economics'!$D$20+Rollout!$F$5*'Unit Economics'!$C$20</f>
-        <v>6906092.9184</v>
+        <v>19072958.763456</v>
       </c>
       <c r="G6" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$G$20+Rollout!$D$5*'Unit Economics'!$F$20+Rollout!$E$5*'Unit Economics'!$E$20+Rollout!$F$5*'Unit Economics'!$D$20+Rollout!$G$5*'Unit Economics'!$C$20</f>
-        <v>8948326.49568</v>
+        <v>26923989.75552</v>
       </c>
       <c r="H6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="37" t="n">
@@ -6367,79 +6364,79 @@
       </c>
       <c r="D7" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$D$21+Rollout!$D$5*'Unit Economics'!$C$21</f>
-        <v>774385.92</v>
+        <v>1935964.8</v>
       </c>
       <c r="E7" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$E$21+Rollout!$D$5*'Unit Economics'!$D$21+Rollout!$E$5*'Unit Economics'!$C$21</f>
-        <v>2291630.1408</v>
+        <v>6676084.8</v>
       </c>
       <c r="F7" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$F$21+Rollout!$D$5*'Unit Economics'!$E$21+Rollout!$E$5*'Unit Economics'!$D$21+Rollout!$F$5*'Unit Economics'!$C$21</f>
-        <v>3970307.88</v>
+        <v>13814545.8528</v>
       </c>
       <c r="G7" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$G$21+Rollout!$D$5*'Unit Economics'!$F$21+Rollout!$E$5*'Unit Economics'!$E$21+Rollout!$F$5*'Unit Economics'!$D$21+Rollout!$G$5*'Unit Economics'!$C$21</f>
-        <v>5245652.9664</v>
+        <v>20629251.72</v>
       </c>
       <c r="H7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$C$22</f>
-        <v>89667</v>
+        <v>163863</v>
       </c>
       <c r="D8" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$D$22+Rollout!$D$5*'Unit Economics'!$C$22</f>
-        <v>1437436.7325</v>
+        <v>2707016.76</v>
       </c>
       <c r="E8" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$E$22+Rollout!$D$5*'Unit Economics'!$D$22+Rollout!$E$5*'Unit Economics'!$C$22</f>
-        <v>3777503.3316</v>
+        <v>8280161.253</v>
       </c>
       <c r="F8" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$F$22+Rollout!$D$5*'Unit Economics'!$E$22+Rollout!$E$5*'Unit Economics'!$D$22+Rollout!$F$5*'Unit Economics'!$C$22</f>
-        <v>6202311.2235</v>
+        <v>16138329.39936</v>
       </c>
       <c r="G8" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$G$22+Rollout!$D$5*'Unit Economics'!$F$22+Rollout!$E$5*'Unit Economics'!$E$22+Rollout!$F$5*'Unit Economics'!$D$22+Rollout!$G$5*'Unit Economics'!$C$22</f>
-        <v>8038654.02225</v>
+        <v>23379350.1606</v>
       </c>
       <c r="H8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$C$23</f>
-        <v>183600</v>
+        <v>378000</v>
       </c>
       <c r="D9" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$D$23+Rollout!$D$5*'Unit Economics'!$C$23</f>
-        <v>1162341</v>
+        <v>2577960</v>
       </c>
       <c r="E9" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$E$23+Rollout!$D$5*'Unit Economics'!$D$23+Rollout!$E$5*'Unit Economics'!$C$23</f>
-        <v>2290051.98</v>
+        <v>6097518</v>
       </c>
       <c r="F9" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$F$23+Rollout!$D$5*'Unit Economics'!$E$23+Rollout!$E$5*'Unit Economics'!$D$23+Rollout!$F$5*'Unit Economics'!$C$23</f>
-        <v>2962003.5</v>
+        <v>9639007.56</v>
       </c>
       <c r="G9" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$G$23+Rollout!$D$5*'Unit Economics'!$F$23+Rollout!$E$5*'Unit Economics'!$E$23+Rollout!$F$5*'Unit Economics'!$D$23+Rollout!$G$5*'Unit Economics'!$C$23</f>
-        <v>3277663.92</v>
+        <v>11746161</v>
       </c>
       <c r="H9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="37" t="n">
@@ -6452,48 +6449,48 @@
       </c>
       <c r="E10" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$E$24+Rollout!$D$5*'Unit Economics'!$D$24+Rollout!$E$5*'Unit Economics'!$C$24</f>
-        <v>2180701.44</v>
+        <v>3985148.16</v>
       </c>
       <c r="F10" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$F$24+Rollout!$D$5*'Unit Economics'!$E$24+Rollout!$E$5*'Unit Economics'!$D$24+Rollout!$F$5*'Unit Economics'!$C$24</f>
-        <v>3631346.1216</v>
+        <v>8585547.264</v>
       </c>
       <c r="G10" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$G$24+Rollout!$D$5*'Unit Economics'!$F$24+Rollout!$E$5*'Unit Economics'!$E$24+Rollout!$F$5*'Unit Economics'!$D$24+Rollout!$G$5*'Unit Economics'!$C$24</f>
-        <v>4132346.33664</v>
+        <v>13034021.33376</v>
       </c>
       <c r="H10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="38" t="n">
         <f aca="false">SUM(C5:C10)</f>
-        <v>879057.72</v>
+        <v>1898193.24</v>
       </c>
       <c r="D11" s="38" t="n">
         <f aca="false">SUM(D5:D10)</f>
-        <v>7578011.8893</v>
+        <v>17162730.936</v>
       </c>
       <c r="E11" s="38" t="n">
         <f aca="false">SUM(E5:E10)</f>
-        <v>19487904.15096</v>
+        <v>49867349.09364</v>
       </c>
       <c r="F11" s="38" t="n">
         <f aca="false">SUM(F5:F10)</f>
-        <v>29622252.2451</v>
+        <v>90378208.443456</v>
       </c>
       <c r="G11" s="38" t="n">
         <f aca="false">SUM(G5:G10)</f>
-        <v>36790077.802794</v>
+        <v>125554175.48988</v>
       </c>
       <c r="H11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="34" t="n">
@@ -6502,19 +6499,19 @@
       </c>
       <c r="D12" s="34" t="n">
         <f aca="false">IF(C11=0,0,D11/C11-1)</f>
-        <v>7.62060785871945</v>
+        <v>8.04161419097668</v>
       </c>
       <c r="E12" s="34" t="n">
         <f aca="false">IF(D11=0,0,E11/D11-1)</f>
-        <v>1.57163810715005</v>
+        <v>1.90556026774503</v>
       </c>
       <c r="F12" s="34" t="n">
         <f aca="false">IF(E11=0,0,F11/E11-1)</f>
-        <v>0.520032734953736</v>
+        <v>0.81237242576792</v>
       </c>
       <c r="G12" s="34" t="n">
         <f aca="false">IF(F11=0,0,G11/F11-1)</f>
-        <v>0.241974360976542</v>
+        <v>0.389208501166865</v>
       </c>
       <c r="H12" s="2"/>
     </row>
@@ -6530,7 +6527,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -6542,61 +6539,61 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="34" t="n">
         <f aca="false">IF(C$11=0,0,C5/C$11)</f>
-        <v>0.400880160633821</v>
+        <v>0.464121345200871</v>
       </c>
       <c r="D15" s="34" t="n">
         <f aca="false">IF(D$11=0,0,D5/D$11)</f>
-        <v>0.294399829479032</v>
+        <v>0.350082132173793</v>
       </c>
       <c r="E15" s="34" t="n">
         <f aca="false">IF(E$11=0,0,E5/E$11)</f>
-        <v>0.225548261741808</v>
+        <v>0.284981700657765</v>
       </c>
       <c r="F15" s="34" t="n">
         <f aca="false">IF(F$11=0,0,F5/F$11)</f>
-        <v>0.200868946505722</v>
+        <v>0.255900399024945</v>
       </c>
       <c r="G15" s="34" t="n">
         <f aca="false">IF(G$11=0,0,G5/G$11)</f>
-        <v>0.194276133367709</v>
+        <v>0.237677491836226</v>
       </c>
       <c r="H15" s="2"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="34" t="n">
         <f aca="false">IF(C$11=0,0,C6/C$11)</f>
-        <v>0.288256293341011</v>
+        <v>0.250416148358004</v>
       </c>
       <c r="D16" s="34" t="n">
         <f aca="false">IF(D$11=0,0,D6/D$11)</f>
-        <v>0.260343063275695</v>
+        <v>0.229184035493406</v>
       </c>
       <c r="E16" s="34" t="n">
         <f aca="false">IF(E$11=0,0,E6/E$11)</f>
-        <v>0.233609233556074</v>
+        <v>0.21290794721619</v>
       </c>
       <c r="F16" s="34" t="n">
         <f aca="false">IF(F$11=0,0,F6/F$11)</f>
-        <v>0.233138684434178</v>
+        <v>0.211034928573393</v>
       </c>
       <c r="G16" s="34" t="n">
         <f aca="false">IF(G$11=0,0,G6/G$11)</f>
-        <v>0.24322662603884</v>
+        <v>0.214441213527703</v>
       </c>
       <c r="H16" s="2"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="34" t="n">
@@ -6605,79 +6602,79 @@
       </c>
       <c r="D17" s="34" t="n">
         <f aca="false">IF(D$11=0,0,D7/D$11)</f>
-        <v>0.102188533260738</v>
+        <v>0.112800509850049</v>
       </c>
       <c r="E17" s="34" t="n">
         <f aca="false">IF(E$11=0,0,E7/E$11)</f>
-        <v>0.117592436982871</v>
+        <v>0.133876873772932</v>
       </c>
       <c r="F17" s="34" t="n">
         <f aca="false">IF(F$11=0,0,F7/F$11)</f>
-        <v>0.134031262955596</v>
+        <v>0.152852618908051</v>
       </c>
       <c r="G17" s="34" t="n">
         <f aca="false">IF(G$11=0,0,G7/G$11)</f>
-        <v>0.142583361593262</v>
+        <v>0.164305580754364</v>
       </c>
       <c r="H17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="34" t="n">
         <f aca="false">IF(C$11=0,0,C8/C$11)</f>
-        <v>0.102003540791383</v>
+        <v>0.0863257736604309</v>
       </c>
       <c r="D18" s="34" t="n">
         <f aca="false">IF(D$11=0,0,D8/D$11)</f>
-        <v>0.189685204179955</v>
+        <v>0.157726457991709</v>
       </c>
       <c r="E18" s="34" t="n">
         <f aca="false">IF(E$11=0,0,E8/E$11)</f>
-        <v>0.193838357492841</v>
+        <v>0.166043742117747</v>
       </c>
       <c r="F18" s="34" t="n">
         <f aca="false">IF(F$11=0,0,F8/F$11)</f>
-        <v>0.209380136668236</v>
+        <v>0.178564387116135</v>
       </c>
       <c r="G18" s="34" t="n">
         <f aca="false">IF(G$11=0,0,G8/G$11)</f>
-        <v>0.218500598594535</v>
+        <v>0.186209260419893</v>
       </c>
       <c r="H18" s="2"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="34" t="n">
         <f aca="false">IF(C$11=0,0,C9/C$11)</f>
-        <v>0.208860005233786</v>
+        <v>0.199136732780694</v>
       </c>
       <c r="D19" s="34" t="n">
         <f aca="false">IF(D$11=0,0,D9/D$11)</f>
-        <v>0.153383369804579</v>
+        <v>0.150206864491044</v>
       </c>
       <c r="E19" s="34" t="n">
         <f aca="false">IF(E$11=0,0,E9/E$11)</f>
-        <v>0.117511455426939</v>
+        <v>0.122274757147211</v>
       </c>
       <c r="F19" s="34" t="n">
         <f aca="false">IF(F$11=0,0,F9/F$11)</f>
-        <v>0.0999925149341054</v>
+        <v>0.106651899014247</v>
       </c>
       <c r="G19" s="34" t="n">
         <f aca="false">IF(G$11=0,0,G9/G$11)</f>
-        <v>0.0890909754953299</v>
+        <v>0.093554523011039</v>
       </c>
       <c r="H19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="34" t="n">
@@ -6690,15 +6687,15 @@
       </c>
       <c r="E20" s="34" t="n">
         <f aca="false">IF(E$11=0,0,E10/E$11)</f>
-        <v>0.111900254799466</v>
+        <v>0.0799149790881557</v>
       </c>
       <c r="F20" s="34" t="n">
         <f aca="false">IF(F$11=0,0,F10/F$11)</f>
-        <v>0.122588454502162</v>
+        <v>0.0949957673632294</v>
       </c>
       <c r="G20" s="34" t="n">
         <f aca="false">IF(G$11=0,0,G10/G$11)</f>
-        <v>0.112322304910325</v>
+        <v>0.103811930450776</v>
       </c>
       <c r="H20" s="2"/>
     </row>
@@ -6729,7 +6726,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -6741,7 +6738,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -6785,7 +6782,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -6797,7 +6794,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="8" t="n">
@@ -6824,7 +6821,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="8" t="n">
@@ -6851,7 +6848,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="8" t="n">
@@ -6878,101 +6875,101 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="33" t="n">
         <f aca="false">IF(Rollout!C$7=0,0,MAX(1,ROUNDUP(Rollout!C$7/Assumptions!$C$76,0)))</f>
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="D9" s="33" t="n">
         <f aca="false">IF(Rollout!D$7=0,0,MAX(1,ROUNDUP(Rollout!D$7/Assumptions!$C$76,0)))</f>
-        <v>45</v>
+        <v>148</v>
       </c>
       <c r="E9" s="33" t="n">
         <f aca="false">IF(Rollout!E$7=0,0,MAX(1,ROUNDUP(Rollout!E$7/Assumptions!$C$76,0)))</f>
-        <v>44</v>
+        <v>205</v>
       </c>
       <c r="F9" s="33" t="n">
         <f aca="false">IF(Rollout!F$7=0,0,MAX(1,ROUNDUP(Rollout!F$7/Assumptions!$C$76,0)))</f>
-        <v>43</v>
+        <v>201</v>
       </c>
       <c r="G9" s="33" t="n">
         <f aca="false">IF(Rollout!G$7=0,0,MAX(1,ROUNDUP(Rollout!G$7/Assumptions!$C$76,0)))</f>
-        <v>43</v>
+        <v>199</v>
       </c>
       <c r="H9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="33" t="n">
         <f aca="false">IF(Rollout!C$7=0,0,MAX(1,ROUNDUP(Rollout!C$7/Assumptions!$C$77,0)))</f>
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="D10" s="33" t="n">
         <f aca="false">IF(Rollout!D$7=0,0,MAX(1,ROUNDUP(Rollout!D$7/Assumptions!$C$77,0)))</f>
-        <v>60</v>
+        <v>197</v>
       </c>
       <c r="E10" s="33" t="n">
         <f aca="false">IF(Rollout!E$7=0,0,MAX(1,ROUNDUP(Rollout!E$7/Assumptions!$C$77,0)))</f>
-        <v>58</v>
+        <v>274</v>
       </c>
       <c r="F10" s="33" t="n">
         <f aca="false">IF(Rollout!F$7=0,0,MAX(1,ROUNDUP(Rollout!F$7/Assumptions!$C$77,0)))</f>
-        <v>58</v>
+        <v>268</v>
       </c>
       <c r="G10" s="33" t="n">
         <f aca="false">IF(Rollout!G$7=0,0,MAX(1,ROUNDUP(Rollout!G$7/Assumptions!$C$77,0)))</f>
-        <v>57</v>
+        <v>265</v>
       </c>
       <c r="H10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="33" t="n">
         <f aca="false">IF(Rollout!C$7=0,0,MAX(1,ROUNDUP(Rollout!C$7/Assumptions!$C$78,0)))</f>
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="D11" s="33" t="n">
         <f aca="false">IF(Rollout!D$7=0,0,MAX(1,ROUNDUP(Rollout!D$7/Assumptions!$C$78,0)))</f>
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="E11" s="33" t="n">
         <f aca="false">IF(Rollout!E$7=0,0,MAX(1,ROUNDUP(Rollout!E$7/Assumptions!$C$78,0)))</f>
-        <v>15</v>
+        <v>69</v>
       </c>
       <c r="F11" s="33" t="n">
         <f aca="false">IF(Rollout!F$7=0,0,MAX(1,ROUNDUP(Rollout!F$7/Assumptions!$C$78,0)))</f>
-        <v>15</v>
+        <v>67</v>
       </c>
       <c r="G11" s="33" t="n">
         <f aca="false">IF(Rollout!G$7=0,0,MAX(1,ROUNDUP(Rollout!G$7/Assumptions!$C$78,0)))</f>
-        <v>15</v>
+        <v>67</v>
       </c>
       <c r="H11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="33" t="n">
         <f aca="false">IF(Rollout!C$5=0,0,ROUNDUP(Rollout!C$5/Assumptions!$C$19,0))</f>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D12" s="33" t="n">
         <f aca="false">IF(Rollout!D$5=0,0,ROUNDUP(Rollout!D$5/Assumptions!$C$19,0))</f>
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E12" s="33" t="n">
         <f aca="false">IF(Rollout!E$5=0,0,ROUNDUP(Rollout!E$5/Assumptions!$C$19,0))</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F12" s="33" t="n">
         <f aca="false">IF(Rollout!F$5=0,0,ROUNDUP(Rollout!F$5/Assumptions!$C$19,0))</f>
@@ -6986,55 +6983,55 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="39" t="n">
         <f aca="false">SUM(C6:C12)</f>
-        <v>89</v>
+        <v>214</v>
       </c>
       <c r="D13" s="39" t="n">
         <f aca="false">SUM(D6:D12)</f>
-        <v>130</v>
+        <v>411</v>
       </c>
       <c r="E13" s="39" t="n">
         <f aca="false">SUM(E6:E12)</f>
-        <v>130</v>
+        <v>568</v>
       </c>
       <c r="F13" s="39" t="n">
         <f aca="false">SUM(F6:F12)</f>
-        <v>134</v>
+        <v>554</v>
       </c>
       <c r="G13" s="39" t="n">
         <f aca="false">SUM(G6:G12)</f>
-        <v>138</v>
+        <v>554</v>
       </c>
       <c r="H13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="33" t="n">
         <f aca="false">C13</f>
-        <v>89</v>
+        <v>214</v>
       </c>
       <c r="D14" s="33" t="n">
         <f aca="false">MAX(0,D13-C13)</f>
-        <v>41</v>
+        <v>197</v>
       </c>
       <c r="E14" s="33" t="n">
         <f aca="false">MAX(0,E13-D13)</f>
-        <v>0</v>
+        <v>157</v>
       </c>
       <c r="F14" s="33" t="n">
         <f aca="false">MAX(0,F13-E13)</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G14" s="33" t="n">
         <f aca="false">MAX(0,G13-F13)</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H14" s="2"/>
     </row>
@@ -7050,7 +7047,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -7062,7 +7059,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="37" t="n">
@@ -7089,7 +7086,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="37" t="n">
@@ -7116,7 +7113,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="37" t="n">
@@ -7143,105 +7140,105 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="37" t="n">
         <f aca="false">C9*0.75*Assumptions!$C$83*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^0</f>
-        <v>1968750</v>
+        <v>4921875</v>
       </c>
       <c r="D20" s="37" t="n">
         <f aca="false">(C9+D9)/2*Assumptions!$C$83*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^1</f>
-        <v>3379687.5</v>
+        <v>10048937.5</v>
       </c>
       <c r="E20" s="37" t="n">
         <f aca="false">(D9+E9)/2*Assumptions!$C$83*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^2</f>
-        <v>4130879.375</v>
+        <v>16384274.375</v>
       </c>
       <c r="F20" s="37" t="n">
         <f aca="false">(E9+F9)/2*Assumptions!$C$83*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^3</f>
-        <v>4159192.14375</v>
+        <v>19409563.3375</v>
       </c>
       <c r="G20" s="37" t="n">
         <f aca="false">(F9+G9)/2*Assumptions!$C$83*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^4</f>
-        <v>4234726.897625</v>
+        <v>19696404.175</v>
       </c>
       <c r="H20" s="2"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" s="37" t="n">
         <f aca="false">C10*0.75*Assumptions!$C$84*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^0</f>
-        <v>2437500</v>
+        <v>6093750</v>
       </c>
       <c r="D21" s="37" t="n">
         <f aca="false">(C10+D10)/2*Assumptions!$C$84*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^1</f>
-        <v>4184375</v>
+        <v>12427593.75</v>
       </c>
       <c r="E21" s="37" t="n">
         <f aca="false">(D10+E10)/2*Assumptions!$C$84*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^2</f>
-        <v>5085689.375</v>
+        <v>20299658.4375</v>
       </c>
       <c r="F21" s="37" t="n">
         <f aca="false">(E10+F10)/2*Assumptions!$C$84*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^3</f>
-        <v>5149475.9875</v>
+        <v>24060482.63125</v>
       </c>
       <c r="G21" s="37" t="n">
         <f aca="false">(F10+G10)/2*Assumptions!$C$84*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^4</f>
-        <v>5258236.47171875</v>
+        <v>24370782.9515313</v>
       </c>
       <c r="H21" s="2"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="37" t="n">
         <f aca="false">C11*0.75*Assumptions!$C$85*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^0</f>
-        <v>515625</v>
+        <v>1289062.5</v>
       </c>
       <c r="D22" s="37" t="n">
         <f aca="false">(C11+D11)/2*Assumptions!$C$85*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^1</f>
-        <v>885156.25</v>
+        <v>2655468.75</v>
       </c>
       <c r="E22" s="37" t="n">
         <f aca="false">(D11+E11)/2*Assumptions!$C$85*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^2</f>
-        <v>1094053.125</v>
+        <v>4339744.0625</v>
       </c>
       <c r="F22" s="37" t="n">
         <f aca="false">(E11+F11)/2*Assumptions!$C$85*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^3</f>
-        <v>1126874.71875</v>
+        <v>5108498.725</v>
       </c>
       <c r="G22" s="37" t="n">
         <f aca="false">(F11+G11)/2*Assumptions!$C$85*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^4</f>
-        <v>1160680.9603125</v>
+        <v>5184374.9560625</v>
       </c>
       <c r="H22" s="2"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" s="37" t="n">
         <f aca="false">C12*0.75*Assumptions!$C$83*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^0</f>
-        <v>196875</v>
+        <v>525000</v>
       </c>
       <c r="D23" s="37" t="n">
         <f aca="false">(C12+D12)/2*Assumptions!$C$83*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^1</f>
-        <v>225312.5</v>
+        <v>721000</v>
       </c>
       <c r="E23" s="37" t="n">
         <f aca="false">(D12+E12)/2*Assumptions!$C$83*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^2</f>
-        <v>92828.75</v>
+        <v>696215.625</v>
       </c>
       <c r="F23" s="37" t="n">
         <f aca="false">(E12+F12)/2*Assumptions!$C$83*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^3</f>
-        <v>0</v>
+        <v>334647.64375</v>
       </c>
       <c r="G23" s="37" t="n">
         <f aca="false">(F12+G12)/2*Assumptions!$C$83*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^4</f>
@@ -7251,28 +7248,28 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" s="38" t="n">
         <f aca="false">SUM(C17:C23)</f>
-        <v>6000000</v>
+        <v>13710937.5</v>
       </c>
       <c r="D24" s="38" t="n">
         <f aca="false">SUM(D17:D23)</f>
-        <v>10103656.25</v>
+        <v>27282125</v>
       </c>
       <c r="E24" s="38" t="n">
         <f aca="false">SUM(E17:E23)</f>
-        <v>12618079.375</v>
+        <v>43934521.25</v>
       </c>
       <c r="F24" s="38" t="n">
         <f aca="false">SUM(F17:F23)</f>
-        <v>13782019.2875</v>
+        <v>52259668.775</v>
       </c>
       <c r="G24" s="38" t="n">
         <f aca="false">SUM(G17:G23)</f>
-        <v>15197886.1500313</v>
+        <v>53795803.9029688</v>
       </c>
       <c r="H24" s="2"/>
     </row>
@@ -7288,7 +7285,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="17" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -7325,7 +7322,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -7337,7 +7334,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -7381,7 +7378,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B5" s="16"/>
       <c r="C5" s="16"/>
@@ -7393,163 +7390,163 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$C$29</f>
-        <v>217773.6</v>
+        <v>512898</v>
       </c>
       <c r="D6" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$D$29+Rollout!$D$5*'Unit Economics'!$C$29</f>
-        <v>533726.798</v>
+        <v>1507920.12</v>
       </c>
       <c r="E6" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$E$29+Rollout!$D$5*'Unit Economics'!$D$29+Rollout!$E$5*'Unit Economics'!$C$29</f>
-        <v>629587.10716</v>
+        <v>2385488.598</v>
       </c>
       <c r="F6" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$F$29+Rollout!$D$5*'Unit Economics'!$E$29+Rollout!$E$5*'Unit Economics'!$D$29+Rollout!$F$5*'Unit Economics'!$C$29</f>
-        <v>620781.7946</v>
+        <v>2745717.37932</v>
       </c>
       <c r="G6" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$G$29+Rollout!$D$5*'Unit Economics'!$F$29+Rollout!$E$5*'Unit Economics'!$E$29+Rollout!$F$5*'Unit Economics'!$D$29+Rollout!$G$5*'Unit Economics'!$C$29</f>
-        <v>614201.40232</v>
+        <v>2708563.0482</v>
       </c>
       <c r="H6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$C$30</f>
-        <v>180000</v>
+        <v>450000</v>
       </c>
       <c r="D7" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$D$30+Rollout!$D$5*'Unit Economics'!$C$30</f>
-        <v>441150</v>
+        <v>1323000</v>
       </c>
       <c r="E7" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$E$30+Rollout!$D$5*'Unit Economics'!$D$30+Rollout!$E$5*'Unit Economics'!$C$30</f>
-        <v>520383</v>
+        <v>2092950</v>
       </c>
       <c r="F7" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$F$30+Rollout!$D$5*'Unit Economics'!$E$30+Rollout!$E$5*'Unit Economics'!$D$30+Rollout!$F$5*'Unit Economics'!$C$30</f>
-        <v>513105</v>
+        <v>2409003</v>
       </c>
       <c r="G7" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$G$30+Rollout!$D$5*'Unit Economics'!$F$30+Rollout!$E$5*'Unit Economics'!$E$30+Rollout!$F$5*'Unit Economics'!$D$30+Rollout!$G$5*'Unit Economics'!$C$30</f>
-        <v>507666</v>
+        <v>2376405</v>
       </c>
       <c r="H7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$C$31</f>
-        <v>2988.9</v>
+        <v>5462.1</v>
       </c>
       <c r="D8" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$D$31+Rollout!$D$5*'Unit Economics'!$C$31</f>
-        <v>16989.40575</v>
+        <v>33719.364</v>
       </c>
       <c r="E8" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$E$31+Rollout!$D$5*'Unit Economics'!$D$31+Rollout!$E$5*'Unit Economics'!$C$31</f>
-        <v>30614.43924</v>
+        <v>74198.9871</v>
       </c>
       <c r="F8" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$F$31+Rollout!$D$5*'Unit Economics'!$E$31+Rollout!$E$5*'Unit Economics'!$D$31+Rollout!$F$5*'Unit Economics'!$C$31</f>
-        <v>39699.5661</v>
+        <v>115772.341104</v>
       </c>
       <c r="G8" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$G$31+Rollout!$D$5*'Unit Economics'!$F$31+Rollout!$E$5*'Unit Economics'!$E$31+Rollout!$F$5*'Unit Economics'!$D$31+Rollout!$G$5*'Unit Economics'!$C$31</f>
-        <v>45855.20565</v>
+        <v>142580.47356</v>
       </c>
       <c r="H8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$C$32</f>
-        <v>28589.11488</v>
+        <v>65670.02496</v>
       </c>
       <c r="D9" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$D$32+Rollout!$D$5*'Unit Economics'!$C$32</f>
-        <v>194520.9406272</v>
+        <v>473246.599104</v>
       </c>
       <c r="E9" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$E$32+Rollout!$D$5*'Unit Economics'!$D$32+Rollout!$E$5*'Unit Economics'!$C$32</f>
-        <v>407667.65896224</v>
+        <v>1167546.17206656</v>
       </c>
       <c r="F9" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$F$32+Rollout!$D$5*'Unit Economics'!$E$32+Rollout!$E$5*'Unit Economics'!$D$32+Rollout!$F$5*'Unit Economics'!$C$32</f>
-        <v>579135.97776</v>
+        <v>1965933.45366278</v>
       </c>
       <c r="G9" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$G$32+Rollout!$D$5*'Unit Economics'!$F$32+Rollout!$E$5*'Unit Economics'!$E$32+Rollout!$F$5*'Unit Economics'!$D$32+Rollout!$G$5*'Unit Economics'!$C$32</f>
-        <v>719611.785863616</v>
+        <v>2621532.26049408</v>
       </c>
       <c r="H9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$C$33+Rollout!C5*Assumptions!$C$67*Assumptions!$F$10</f>
-        <v>18000</v>
+        <v>45000</v>
       </c>
       <c r="D10" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$D$33+Rollout!$D$5*'Unit Economics'!$C$33+Rollout!D5*Assumptions!$C$67*Assumptions!$F$10</f>
-        <v>32475</v>
+        <v>103200</v>
       </c>
       <c r="E10" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$E$33+Rollout!$D$5*'Unit Economics'!$D$33+Rollout!$E$5*'Unit Economics'!$C$33+Rollout!E5*Assumptions!$C$67*Assumptions!$F$10</f>
-        <v>34692.2</v>
+        <v>151695</v>
       </c>
       <c r="F10" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$F$33+Rollout!$D$5*'Unit Economics'!$E$33+Rollout!$E$5*'Unit Economics'!$D$33+Rollout!$F$5*'Unit Economics'!$C$33+Rollout!F5*Assumptions!$C$67*Assumptions!$F$10</f>
-        <v>34207</v>
+        <v>160600.2</v>
       </c>
       <c r="G10" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$G$33+Rollout!$D$5*'Unit Economics'!$F$33+Rollout!$E$5*'Unit Economics'!$E$33+Rollout!$F$5*'Unit Economics'!$D$33+Rollout!$G$5*'Unit Economics'!$C$33+Rollout!G5*Assumptions!$C$67*Assumptions!$F$10</f>
-        <v>33844.4</v>
+        <v>158427</v>
       </c>
       <c r="H10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="38" t="n">
         <f aca="false">SUM(C6:C10)</f>
-        <v>447351.61488</v>
+        <v>1079030.12496</v>
       </c>
       <c r="D11" s="38" t="n">
         <f aca="false">SUM(D6:D10)</f>
-        <v>1218862.1443772</v>
+        <v>3441086.083104</v>
       </c>
       <c r="E11" s="38" t="n">
         <f aca="false">SUM(E6:E10)</f>
-        <v>1622944.40536224</v>
+        <v>5871878.75716656</v>
       </c>
       <c r="F11" s="38" t="n">
         <f aca="false">SUM(F6:F10)</f>
-        <v>1786929.33846</v>
+        <v>7397026.37408678</v>
       </c>
       <c r="G11" s="38" t="n">
         <f aca="false">SUM(G6:G10)</f>
-        <v>1921178.79383362</v>
+        <v>8007507.78225408</v>
       </c>
       <c r="H11" s="2"/>
     </row>
@@ -7565,7 +7562,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B13" s="16"/>
       <c r="C13" s="16"/>
@@ -7577,132 +7574,132 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="9" t="n">
         <f aca="false">Headcount!C20</f>
-        <v>1968750</v>
+        <v>4921875</v>
       </c>
       <c r="D14" s="9" t="n">
         <f aca="false">Headcount!D20</f>
-        <v>3379687.5</v>
+        <v>10048937.5</v>
       </c>
       <c r="E14" s="9" t="n">
         <f aca="false">Headcount!E20</f>
-        <v>4130879.375</v>
+        <v>16384274.375</v>
       </c>
       <c r="F14" s="9" t="n">
         <f aca="false">Headcount!F20</f>
-        <v>4159192.14375</v>
+        <v>19409563.3375</v>
       </c>
       <c r="G14" s="9" t="n">
         <f aca="false">Headcount!G20</f>
-        <v>4234726.897625</v>
+        <v>19696404.175</v>
       </c>
       <c r="H14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="9" t="n">
         <f aca="false">Headcount!C21</f>
-        <v>2437500</v>
+        <v>6093750</v>
       </c>
       <c r="D15" s="9" t="n">
         <f aca="false">Headcount!D21</f>
-        <v>4184375</v>
+        <v>12427593.75</v>
       </c>
       <c r="E15" s="9" t="n">
         <f aca="false">Headcount!E21</f>
-        <v>5085689.375</v>
+        <v>20299658.4375</v>
       </c>
       <c r="F15" s="9" t="n">
         <f aca="false">Headcount!F21</f>
-        <v>5149475.9875</v>
+        <v>24060482.63125</v>
       </c>
       <c r="G15" s="9" t="n">
         <f aca="false">Headcount!G21</f>
-        <v>5258236.47171875</v>
+        <v>24370782.9515313</v>
       </c>
       <c r="H15" s="2"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="37" t="n">
         <f aca="false">(Rollout!$C$5*'Unit Economics'!$C$27)*Assumptions!$C$75</f>
-        <v>27326.7</v>
+        <v>54186.3</v>
       </c>
       <c r="D16" s="37" t="n">
         <f aca="false">(Rollout!$C$5*'Unit Economics'!$D$27+Rollout!$D$5*'Unit Economics'!$C$27)*Assumptions!$C$75</f>
-        <v>337416.36525</v>
+        <v>722094.156</v>
       </c>
       <c r="E16" s="37" t="n">
         <f aca="false">(Rollout!$C$5*'Unit Economics'!$E$27+Rollout!$D$5*'Unit Economics'!$D$27+Rollout!$E$5*'Unit Economics'!$C$27)*Assumptions!$C$75</f>
-        <v>835918.54524</v>
+        <v>2105376.4053</v>
       </c>
       <c r="F16" s="37" t="n">
         <f aca="false">(Rollout!$C$5*'Unit Economics'!$F$27+Rollout!$D$5*'Unit Economics'!$E$27+Rollout!$E$5*'Unit Economics'!$D$27+Rollout!$F$5*'Unit Economics'!$C$27)*Assumptions!$C$75</f>
-        <v>1313462.26035</v>
+        <v>3959188.281216</v>
       </c>
       <c r="G16" s="37" t="n">
         <f aca="false">(Rollout!$C$5*'Unit Economics'!$G$27+Rollout!$D$5*'Unit Economics'!$F$27+Rollout!$E$5*'Unit Economics'!$E$27+Rollout!$F$5*'Unit Economics'!$D$27+Rollout!$G$5*'Unit Economics'!$C$27)*Assumptions!$C$75</f>
-        <v>1656197.090865</v>
+        <v>5575476.28806</v>
       </c>
       <c r="H16" s="2"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="9" t="n">
         <f aca="false">Headcount!C22</f>
-        <v>515625</v>
+        <v>1289062.5</v>
       </c>
       <c r="D17" s="9" t="n">
         <f aca="false">Headcount!D22</f>
-        <v>885156.25</v>
+        <v>2655468.75</v>
       </c>
       <c r="E17" s="9" t="n">
         <f aca="false">Headcount!E22</f>
-        <v>1094053.125</v>
+        <v>4339744.0625</v>
       </c>
       <c r="F17" s="9" t="n">
         <f aca="false">Headcount!F22</f>
-        <v>1126874.71875</v>
+        <v>5108498.725</v>
       </c>
       <c r="G17" s="9" t="n">
         <f aca="false">Headcount!G22</f>
-        <v>1160680.9603125</v>
+        <v>5184374.9560625</v>
       </c>
       <c r="H17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="9" t="n">
         <f aca="false">Headcount!C23</f>
-        <v>196875</v>
+        <v>525000</v>
       </c>
       <c r="D18" s="9" t="n">
         <f aca="false">Headcount!D23</f>
-        <v>225312.5</v>
+        <v>721000</v>
       </c>
       <c r="E18" s="9" t="n">
         <f aca="false">Headcount!E23</f>
-        <v>92828.75</v>
+        <v>696215.625</v>
       </c>
       <c r="F18" s="9" t="n">
         <f aca="false">Headcount!F23</f>
-        <v>0</v>
+        <v>334647.64375</v>
       </c>
       <c r="G18" s="9" t="n">
         <f aca="false">Headcount!G23</f>
@@ -7712,20 +7709,20 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="37" t="n">
         <f aca="false">Rollout!C5*(Assumptions!$C$68+Assumptions!$C$66)*Assumptions!$F$10</f>
-        <v>1830000</v>
+        <v>4575000</v>
       </c>
       <c r="D19" s="37" t="n">
         <f aca="false">Rollout!D5*(Assumptions!$C$68+Assumptions!$C$66)*Assumptions!$F$10</f>
-        <v>934825</v>
+        <v>4575000</v>
       </c>
       <c r="E19" s="37" t="n">
         <f aca="false">Rollout!E5*(Assumptions!$C$68+Assumptions!$C$66)*Assumptions!$F$10</f>
-        <v>0</v>
+        <v>3710325</v>
       </c>
       <c r="F19" s="37" t="n">
         <f aca="false">Rollout!F5*(Assumptions!$C$68+Assumptions!$C$66)*Assumptions!$F$10</f>
@@ -7739,34 +7736,34 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$C$41</f>
-        <v>159408</v>
+        <v>291312</v>
       </c>
       <c r="D20" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$D$41+Rollout!$D$5*'Unit Economics'!$C$41</f>
-        <v>334358.28</v>
+        <v>753527.04</v>
       </c>
       <c r="E20" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$E$41+Rollout!$D$5*'Unit Economics'!$D$41+Rollout!$E$5*'Unit Economics'!$C$41</f>
-        <v>322618.7664</v>
+        <v>1051927.632</v>
       </c>
       <c r="F20" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$F$41+Rollout!$D$5*'Unit Economics'!$E$41+Rollout!$E$5*'Unit Economics'!$D$41+Rollout!$F$5*'Unit Economics'!$C$41</f>
-        <v>242270.0496</v>
+        <v>990495.75744</v>
       </c>
       <c r="G20" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$G$41+Rollout!$D$5*'Unit Economics'!$F$41+Rollout!$E$5*'Unit Economics'!$E$41+Rollout!$F$5*'Unit Economics'!$D$41+Rollout!$G$5*'Unit Economics'!$C$41</f>
-        <v>164150.388</v>
+        <v>714883.53216</v>
       </c>
       <c r="H20" s="2"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" s="9" t="n">
@@ -7793,7 +7790,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="11" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="9" t="n">
@@ -7820,7 +7817,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" s="9" t="n">
@@ -7847,7 +7844,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" s="9" t="n">
@@ -7874,82 +7871,82 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" s="37" t="n">
         <f aca="false">Assumptions!C$97+Rollout!C8*Assumptions!$C$98</f>
-        <v>120000</v>
+        <v>210000</v>
       </c>
       <c r="D25" s="37" t="n">
         <f aca="false">Assumptions!D$97+Rollout!D8*Assumptions!$C$98</f>
-        <v>238850</v>
+        <v>535500</v>
       </c>
       <c r="E25" s="37" t="n">
         <f aca="false">Assumptions!E$97+Rollout!E8*Assumptions!$C$98</f>
-        <v>315580.5</v>
+        <v>845150</v>
       </c>
       <c r="F25" s="37" t="n">
         <f aca="false">Assumptions!F$97+Rollout!F8*Assumptions!$C$98</f>
-        <v>372248</v>
+        <v>1011150.5</v>
       </c>
       <c r="G25" s="37" t="n">
         <f aca="false">Assumptions!G$97+Rollout!G8*Assumptions!$C$98</f>
-        <v>430128.5</v>
+        <v>1057568</v>
       </c>
       <c r="H25" s="2"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" s="37" t="n">
         <f aca="false">Headcount!C13*Assumptions!$C$99</f>
-        <v>267000</v>
+        <v>642000</v>
       </c>
       <c r="D26" s="37" t="n">
         <f aca="false">Headcount!D13*Assumptions!$C$99</f>
-        <v>390000</v>
+        <v>1233000</v>
       </c>
       <c r="E26" s="37" t="n">
         <f aca="false">Headcount!E13*Assumptions!$C$99</f>
-        <v>390000</v>
+        <v>1704000</v>
       </c>
       <c r="F26" s="37" t="n">
         <f aca="false">Headcount!F13*Assumptions!$C$99</f>
-        <v>402000</v>
+        <v>1662000</v>
       </c>
       <c r="G26" s="37" t="n">
         <f aca="false">Headcount!G13*Assumptions!$C$99</f>
-        <v>414000</v>
+        <v>1662000</v>
       </c>
       <c r="H26" s="2"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" s="38" t="n">
         <f aca="false">SUM(C14:C26)</f>
-        <v>8453734.7</v>
+        <v>19533435.8</v>
       </c>
       <c r="D27" s="38" t="n">
         <f aca="false">SUM(D14:D26)</f>
-        <v>12489105.89525</v>
+        <v>35251246.196</v>
       </c>
       <c r="E27" s="38" t="n">
         <f aca="false">SUM(E14:E26)</f>
-        <v>14782197.18664</v>
+        <v>53651300.2873</v>
       </c>
       <c r="F27" s="38" t="n">
         <f aca="false">SUM(F14:F26)</f>
-        <v>16611999.59745</v>
+        <v>60382503.313656</v>
       </c>
       <c r="G27" s="38" t="n">
         <f aca="false">SUM(G14:G26)</f>
-        <v>18562362.1288963</v>
+        <v>63505731.7231888</v>
       </c>
       <c r="H27" s="2"/>
     </row>
@@ -7980,7 +7977,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -7992,7 +7989,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -8036,82 +8033,82 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B5" s="2"/>
-      <c r="C5" s="27" t="n">
+      <c r="C5" s="28" t="n">
         <f aca="false">Revenue!C11</f>
-        <v>879057.72</v>
-      </c>
-      <c r="D5" s="27" t="n">
+        <v>1898193.24</v>
+      </c>
+      <c r="D5" s="28" t="n">
         <f aca="false">Revenue!D11</f>
-        <v>7578011.8893</v>
-      </c>
-      <c r="E5" s="27" t="n">
+        <v>17162730.936</v>
+      </c>
+      <c r="E5" s="28" t="n">
         <f aca="false">Revenue!E11</f>
-        <v>19487904.15096</v>
-      </c>
-      <c r="F5" s="27" t="n">
+        <v>49867349.09364</v>
+      </c>
+      <c r="F5" s="28" t="n">
         <f aca="false">Revenue!F11</f>
-        <v>29622252.2451</v>
-      </c>
-      <c r="G5" s="27" t="n">
+        <v>90378208.443456</v>
+      </c>
+      <c r="G5" s="28" t="n">
         <f aca="false">Revenue!G11</f>
-        <v>36790077.802794</v>
+        <v>125554175.48988</v>
       </c>
       <c r="H5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="9" t="n">
         <f aca="false">Costs!C11</f>
-        <v>447351.61488</v>
+        <v>1079030.12496</v>
       </c>
       <c r="D6" s="9" t="n">
         <f aca="false">Costs!D11</f>
-        <v>1218862.1443772</v>
+        <v>3441086.083104</v>
       </c>
       <c r="E6" s="9" t="n">
         <f aca="false">Costs!E11</f>
-        <v>1622944.40536224</v>
+        <v>5871878.75716656</v>
       </c>
       <c r="F6" s="9" t="n">
         <f aca="false">Costs!F11</f>
-        <v>1786929.33846</v>
+        <v>7397026.37408678</v>
       </c>
       <c r="G6" s="9" t="n">
         <f aca="false">Costs!G11</f>
-        <v>1921178.79383362</v>
+        <v>8007507.78225408</v>
       </c>
       <c r="H6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="38" t="n">
         <f aca="false">C5-C6</f>
-        <v>431706.10512</v>
+        <v>819163.11504</v>
       </c>
       <c r="D7" s="38" t="n">
         <f aca="false">D5-D6</f>
-        <v>6359149.7449228</v>
+        <v>13721644.852896</v>
       </c>
       <c r="E7" s="38" t="n">
         <f aca="false">E5-E6</f>
-        <v>17864959.7455978</v>
+        <v>43995470.3364734</v>
       </c>
       <c r="F7" s="38" t="n">
         <f aca="false">F5-F6</f>
-        <v>27835322.90664</v>
+        <v>82981182.0693692</v>
       </c>
       <c r="G7" s="38" t="n">
         <f aca="false">G5-G6</f>
-        <v>34868899.0089604</v>
+        <v>117546667.707626</v>
       </c>
       <c r="H7" s="2"/>
     </row>
@@ -8122,23 +8119,23 @@
       <c r="B8" s="2"/>
       <c r="C8" s="34" t="n">
         <f aca="false">IF(C5=0,0,C7/C5)</f>
-        <v>0.49110097698704</v>
+        <v>0.431548852760639</v>
       </c>
       <c r="D8" s="34" t="n">
         <f aca="false">IF(D5=0,0,D7/D5)</f>
-        <v>0.839158058580218</v>
+        <v>0.799502416256723</v>
       </c>
       <c r="E8" s="34" t="n">
         <f aca="false">IF(E5=0,0,E7/E5)</f>
-        <v>0.916720423459067</v>
+        <v>0.88225003205724</v>
       </c>
       <c r="F8" s="34" t="n">
         <f aca="false">IF(F5=0,0,F7/F5)</f>
-        <v>0.939676114980231</v>
+        <v>0.918154757640337</v>
       </c>
       <c r="G8" s="34" t="n">
         <f aca="false">IF(G5=0,0,G7/G5)</f>
-        <v>0.947779974695033</v>
+        <v>0.936222688325491</v>
       </c>
       <c r="H8" s="2"/>
     </row>
@@ -8154,61 +8151,61 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="9" t="n">
         <f aca="false">Costs!C14</f>
-        <v>1968750</v>
+        <v>4921875</v>
       </c>
       <c r="D10" s="9" t="n">
         <f aca="false">Costs!D14</f>
-        <v>3379687.5</v>
+        <v>10048937.5</v>
       </c>
       <c r="E10" s="9" t="n">
         <f aca="false">Costs!E14</f>
-        <v>4130879.375</v>
+        <v>16384274.375</v>
       </c>
       <c r="F10" s="9" t="n">
         <f aca="false">Costs!F14</f>
-        <v>4159192.14375</v>
+        <v>19409563.3375</v>
       </c>
       <c r="G10" s="9" t="n">
         <f aca="false">Costs!G14</f>
-        <v>4234726.897625</v>
+        <v>19696404.175</v>
       </c>
       <c r="H10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="9" t="n">
         <f aca="false">Costs!C15+Costs!C16+Costs!C17+Costs!C18+Costs!C19+Costs!C20+Costs!C21</f>
-        <v>5216734.7</v>
+        <v>12878310.8</v>
       </c>
       <c r="D11" s="9" t="n">
         <f aca="false">Costs!D15+Costs!D16+Costs!D17+Costs!D18+Costs!D19+Costs!D20+Costs!D21</f>
-        <v>7051443.39525</v>
+        <v>22004683.696</v>
       </c>
       <c r="E11" s="9" t="n">
         <f aca="false">Costs!E15+Costs!E16+Costs!E17+Costs!E18+Costs!E19+Costs!E20+Costs!E21</f>
-        <v>7731108.56164</v>
+        <v>32503247.1623</v>
       </c>
       <c r="F11" s="9" t="n">
         <f aca="false">Costs!F15+Costs!F16+Costs!F17+Costs!F18+Costs!F19+Costs!F20+Costs!F21</f>
-        <v>8332083.0162</v>
+        <v>34953313.038656</v>
       </c>
       <c r="G11" s="9" t="n">
         <f aca="false">Costs!G15+Costs!G16+Costs!G17+Costs!G18+Costs!G19+Costs!G20+Costs!G21</f>
-        <v>8939264.91089625</v>
+        <v>36545517.7278138</v>
       </c>
       <c r="H11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="9" t="n">
@@ -8235,55 +8232,55 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="9" t="n">
         <f aca="false">Costs!C23+Costs!C24+Costs!C25+Costs!C26</f>
-        <v>790125</v>
+        <v>1255125</v>
       </c>
       <c r="D13" s="9" t="n">
         <f aca="false">Costs!D23+Costs!D24+Costs!D25+Costs!D26</f>
-        <v>1182475</v>
+        <v>2322125</v>
       </c>
       <c r="E13" s="9" t="n">
         <f aca="false">Costs!E23+Costs!E24+Costs!E25+Costs!E26</f>
-        <v>1454841.125</v>
+        <v>3298410.625</v>
       </c>
       <c r="F13" s="9" t="n">
         <f aca="false">Costs!F23+Costs!F24+Costs!F25+Costs!F26</f>
-        <v>1914781.80625</v>
+        <v>3813684.30625</v>
       </c>
       <c r="G13" s="9" t="n">
         <f aca="false">Costs!G23+Costs!G24+Costs!G25+Costs!G26</f>
-        <v>2398737.5438125</v>
+        <v>4274177.0438125</v>
       </c>
       <c r="H13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="40" t="n">
         <f aca="false">SUM(C10:C13)</f>
-        <v>8453734.7</v>
+        <v>19533435.8</v>
       </c>
       <c r="D14" s="40" t="n">
         <f aca="false">SUM(D10:D13)</f>
-        <v>12489105.89525</v>
+        <v>35251246.196</v>
       </c>
       <c r="E14" s="40" t="n">
         <f aca="false">SUM(E10:E13)</f>
-        <v>14782197.18664</v>
+        <v>53651300.2873</v>
       </c>
       <c r="F14" s="40" t="n">
         <f aca="false">SUM(F10:F13)</f>
-        <v>16611999.59745</v>
+        <v>60382503.313656</v>
       </c>
       <c r="G14" s="40" t="n">
         <f aca="false">SUM(G10:G13)</f>
-        <v>18562362.1288963</v>
+        <v>63505731.7231888</v>
       </c>
       <c r="H14" s="2"/>
     </row>
@@ -8299,28 +8296,28 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B16" s="2"/>
-      <c r="C16" s="27" t="n">
+      <c r="C16" s="28" t="n">
         <f aca="false">C7-C14</f>
-        <v>-8022028.59488</v>
-      </c>
-      <c r="D16" s="27" t="n">
+        <v>-18714272.68496</v>
+      </c>
+      <c r="D16" s="28" t="n">
         <f aca="false">D7-D14</f>
-        <v>-6129956.1503272</v>
-      </c>
-      <c r="E16" s="27" t="n">
+        <v>-21529601.343104</v>
+      </c>
+      <c r="E16" s="28" t="n">
         <f aca="false">E7-E14</f>
-        <v>3082762.55895776</v>
-      </c>
-      <c r="F16" s="27" t="n">
+        <v>-9655829.95082656</v>
+      </c>
+      <c r="F16" s="28" t="n">
         <f aca="false">F7-F14</f>
-        <v>11223323.30919</v>
-      </c>
-      <c r="G16" s="27" t="n">
+        <v>22598678.7557132</v>
+      </c>
+      <c r="G16" s="28" t="n">
         <f aca="false">G7-G14</f>
-        <v>16306536.8800641</v>
+        <v>54040935.9844372</v>
       </c>
       <c r="H16" s="2"/>
     </row>
@@ -8331,110 +8328,110 @@
       <c r="B17" s="2"/>
       <c r="C17" s="34" t="n">
         <f aca="false">IF(C5=0,0,C16/C5)</f>
-        <v>-9.12571314984868</v>
+        <v>-9.85899237790985</v>
       </c>
       <c r="D17" s="34" t="n">
         <f aca="false">IF(D5=0,0,D16/D5)</f>
-        <v>-0.8089135039472</v>
+        <v>-1.25443913462188</v>
       </c>
       <c r="E17" s="34" t="n">
         <f aca="false">IF(E5=0,0,E16/E5)</f>
-        <v>0.158188511965044</v>
+        <v>-0.193630303722282</v>
       </c>
       <c r="F17" s="34" t="n">
         <f aca="false">IF(F5=0,0,F16/F5)</f>
-        <v>0.378881498149639</v>
+        <v>0.250045659732808</v>
       </c>
       <c r="G17" s="34" t="n">
         <f aca="false">IF(G5=0,0,G16/G5)</f>
-        <v>0.443231921592342</v>
+        <v>0.430419265417366</v>
       </c>
       <c r="H17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="37" t="n">
         <f aca="false">Headcount!C14*Assumptions!$C$100</f>
-        <v>222500</v>
+        <v>535000</v>
       </c>
       <c r="D18" s="37" t="n">
         <f aca="false">Headcount!D14*Assumptions!$C$100</f>
-        <v>102500</v>
+        <v>492500</v>
       </c>
       <c r="E18" s="37" t="n">
         <f aca="false">Headcount!E14*Assumptions!$C$100</f>
-        <v>0</v>
+        <v>392500</v>
       </c>
       <c r="F18" s="37" t="n">
         <f aca="false">Headcount!F14*Assumptions!$C$100</f>
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="G18" s="37" t="n">
         <f aca="false">Headcount!G14*Assumptions!$C$100</f>
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="H18" s="2"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="37" t="n">
         <f aca="false">(C18)/Assumptions!$C$101</f>
-        <v>74166.6666666667</v>
+        <v>178333.333333333</v>
       </c>
       <c r="D19" s="37" t="n">
         <f aca="false">(C18+D18)/Assumptions!$C$101</f>
-        <v>108333.333333333</v>
+        <v>342500</v>
       </c>
       <c r="E19" s="37" t="n">
         <f aca="false">(C18+D18+E18)/Assumptions!$C$101</f>
-        <v>108333.333333333</v>
+        <v>473333.333333333</v>
       </c>
       <c r="F19" s="37" t="n">
         <f aca="false">(D18+E18+F18)/Assumptions!$C$101</f>
-        <v>37500</v>
+        <v>295000</v>
       </c>
       <c r="G19" s="37" t="n">
         <f aca="false">(E18+F18+G18)/Assumptions!$C$101</f>
-        <v>6666.66666666667</v>
+        <v>130833.333333333</v>
       </c>
       <c r="H19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B20" s="2"/>
-      <c r="C20" s="27" t="n">
+      <c r="C20" s="28" t="n">
         <f aca="false">C16-C19</f>
-        <v>-8096195.26154667</v>
-      </c>
-      <c r="D20" s="27" t="n">
+        <v>-18892606.0182933</v>
+      </c>
+      <c r="D20" s="28" t="n">
         <f aca="false">D16-D19</f>
-        <v>-6238289.48366053</v>
-      </c>
-      <c r="E20" s="27" t="n">
+        <v>-21872101.343104</v>
+      </c>
+      <c r="E20" s="28" t="n">
         <f aca="false">E16-E19</f>
-        <v>2974429.22562442</v>
-      </c>
-      <c r="F20" s="27" t="n">
+        <v>-10129163.2841599</v>
+      </c>
+      <c r="F20" s="28" t="n">
         <f aca="false">F16-F19</f>
-        <v>11185823.30919</v>
-      </c>
-      <c r="G20" s="27" t="n">
+        <v>22303678.7557132</v>
+      </c>
+      <c r="G20" s="28" t="n">
         <f aca="false">G16-G19</f>
-        <v>16299870.2133975</v>
+        <v>53910102.6511038</v>
       </c>
       <c r="H20" s="2"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" s="37" t="n">
@@ -8443,25 +8440,25 @@
       </c>
       <c r="D21" s="37" t="n">
         <f aca="false">C23</f>
-        <v>8096195.26154667</v>
+        <v>18892606.0182933</v>
       </c>
       <c r="E21" s="37" t="n">
         <f aca="false">D23</f>
-        <v>14334484.7452072</v>
+        <v>40764707.3613973</v>
       </c>
       <c r="F21" s="37" t="n">
         <f aca="false">E23</f>
-        <v>11360055.5195828</v>
+        <v>50893870.6455572</v>
       </c>
       <c r="G21" s="37" t="n">
         <f aca="false">F23</f>
-        <v>174232.210392773</v>
+        <v>28590191.889844</v>
       </c>
       <c r="H21" s="2"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="11" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="37" t="n">
@@ -8482,30 +8479,30 @@
       </c>
       <c r="G22" s="37" t="n">
         <f aca="false">MAX(0,G20-G21)</f>
-        <v>16125638.0030047</v>
+        <v>25319910.7612598</v>
       </c>
       <c r="H22" s="2"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" s="37" t="n">
         <f aca="false">MAX(0,C21-MAX(0,C20))+MAX(0,-C20)</f>
-        <v>8096195.26154667</v>
+        <v>18892606.0182933</v>
       </c>
       <c r="D23" s="37" t="n">
         <f aca="false">MAX(0,D21-MAX(0,D20))+MAX(0,-D20)</f>
-        <v>14334484.7452072</v>
+        <v>40764707.3613973</v>
       </c>
       <c r="E23" s="37" t="n">
         <f aca="false">MAX(0,E21-MAX(0,E20))+MAX(0,-E20)</f>
-        <v>11360055.5195828</v>
+        <v>50893870.6455572</v>
       </c>
       <c r="F23" s="37" t="n">
         <f aca="false">MAX(0,F21-MAX(0,F20))+MAX(0,-F20)</f>
-        <v>174232.210392773</v>
+        <v>28590191.889844</v>
       </c>
       <c r="G23" s="37" t="n">
         <f aca="false">MAX(0,G21-MAX(0,G20))+MAX(0,-G20)</f>
@@ -8515,7 +8512,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" s="37" t="n">
@@ -8536,34 +8533,34 @@
       </c>
       <c r="G24" s="37" t="n">
         <f aca="false">G22*Assumptions!$C$104</f>
-        <v>4031409.50075117</v>
+        <v>6329977.69031496</v>
       </c>
       <c r="H24" s="2"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" s="38" t="n">
         <f aca="false">C20-C24</f>
-        <v>-8096195.26154667</v>
+        <v>-18892606.0182933</v>
       </c>
       <c r="D25" s="38" t="n">
         <f aca="false">D20-D24</f>
-        <v>-6238289.48366053</v>
+        <v>-21872101.343104</v>
       </c>
       <c r="E25" s="38" t="n">
         <f aca="false">E20-E24</f>
-        <v>2974429.22562442</v>
+        <v>-10129163.2841599</v>
       </c>
       <c r="F25" s="38" t="n">
         <f aca="false">F20-F24</f>
-        <v>11185823.30919</v>
+        <v>22303678.7557132</v>
       </c>
       <c r="G25" s="38" t="n">
         <f aca="false">G20-G24</f>
-        <v>12268460.7126463</v>
+        <v>47580124.9607889</v>
       </c>
       <c r="H25" s="2"/>
     </row>
@@ -8594,7 +8591,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -8606,7 +8603,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -8650,34 +8647,34 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="9" t="n">
         <f aca="false">'P&amp;L'!C16</f>
-        <v>-8022028.59488</v>
+        <v>-18714272.68496</v>
       </c>
       <c r="D5" s="9" t="n">
         <f aca="false">'P&amp;L'!D16</f>
-        <v>-6129956.1503272</v>
+        <v>-21529601.343104</v>
       </c>
       <c r="E5" s="9" t="n">
         <f aca="false">'P&amp;L'!E16</f>
-        <v>3082762.55895776</v>
+        <v>-9655829.95082656</v>
       </c>
       <c r="F5" s="9" t="n">
         <f aca="false">'P&amp;L'!F16</f>
-        <v>11223323.30919</v>
+        <v>22598678.7557132</v>
       </c>
       <c r="G5" s="9" t="n">
         <f aca="false">'P&amp;L'!G16</f>
-        <v>16306536.8800641</v>
+        <v>54040935.9844372</v>
       </c>
       <c r="H5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="9" t="n">
@@ -8698,103 +8695,103 @@
       </c>
       <c r="G6" s="9" t="n">
         <f aca="false">-'P&amp;L'!G24</f>
-        <v>-4031409.50075117</v>
+        <v>-6329977.69031496</v>
       </c>
       <c r="H6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="9" t="n">
         <f aca="false">-'P&amp;L'!C18</f>
-        <v>-222500</v>
+        <v>-535000</v>
       </c>
       <c r="D7" s="9" t="n">
         <f aca="false">-'P&amp;L'!D18</f>
-        <v>-102500</v>
+        <v>-492500</v>
       </c>
       <c r="E7" s="9" t="n">
         <f aca="false">-'P&amp;L'!E18</f>
-        <v>-0</v>
+        <v>-392500</v>
       </c>
       <c r="F7" s="9" t="n">
         <f aca="false">-'P&amp;L'!F18</f>
-        <v>-10000</v>
+        <v>-0</v>
       </c>
       <c r="G7" s="9" t="n">
         <f aca="false">-'P&amp;L'!G18</f>
-        <v>-10000</v>
+        <v>-0</v>
       </c>
       <c r="H7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="37" t="n">
         <f aca="false">-'P&amp;L'!C5*Assumptions!$C$105</f>
-        <v>-26371.7316</v>
+        <v>-56945.7972</v>
       </c>
       <c r="D8" s="37" t="n">
         <f aca="false">-('P&amp;L'!D5-'P&amp;L'!C5)*Assumptions!$C$105</f>
-        <v>-200968.625079</v>
+        <v>-457936.13088</v>
       </c>
       <c r="E8" s="37" t="n">
         <f aca="false">-('P&amp;L'!E5-'P&amp;L'!D5)*Assumptions!$C$105</f>
-        <v>-357296.7678498</v>
+        <v>-981138.5447292</v>
       </c>
       <c r="F8" s="37" t="n">
         <f aca="false">-('P&amp;L'!F5-'P&amp;L'!E5)*Assumptions!$C$105</f>
-        <v>-304030.4428242</v>
+        <v>-1215325.78049448</v>
       </c>
       <c r="G8" s="37" t="n">
         <f aca="false">-('P&amp;L'!G5-'P&amp;L'!F5)*Assumptions!$C$105</f>
-        <v>-215034.76673082</v>
+        <v>-1055279.01139272</v>
       </c>
       <c r="H8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="38" t="n">
         <f aca="false">SUM(C5:C8)</f>
-        <v>-8270900.32648</v>
+        <v>-19306218.48216</v>
       </c>
       <c r="D9" s="38" t="n">
         <f aca="false">SUM(D5:D8)</f>
-        <v>-6433424.7754062</v>
+        <v>-22480037.473984</v>
       </c>
       <c r="E9" s="38" t="n">
         <f aca="false">SUM(E5:E8)</f>
-        <v>2725465.79110796</v>
+        <v>-11029468.4955558</v>
       </c>
       <c r="F9" s="38" t="n">
         <f aca="false">SUM(F5:F8)</f>
-        <v>10909292.8663658</v>
+        <v>21383352.9752188</v>
       </c>
       <c r="G9" s="38" t="n">
         <f aca="false">SUM(G5:G8)</f>
-        <v>12050092.6125821</v>
+        <v>46655679.2827295</v>
       </c>
       <c r="H9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="9" t="n">
         <f aca="false">Assumptions!C$109</f>
-        <v>10000000</v>
+        <v>25000000</v>
       </c>
       <c r="D10" s="9" t="n">
         <f aca="false">Assumptions!D$109</f>
-        <v>6000000</v>
+        <v>35000000</v>
       </c>
       <c r="E10" s="9" t="n">
         <f aca="false">Assumptions!E$109</f>
@@ -8812,34 +8809,34 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="37" t="n">
         <f aca="false">C9+C10</f>
-        <v>1729099.67352</v>
+        <v>5693781.51784</v>
       </c>
       <c r="D11" s="37" t="n">
         <f aca="false">D9+D10</f>
-        <v>-433424.7754062</v>
+        <v>12519962.526016</v>
       </c>
       <c r="E11" s="37" t="n">
         <f aca="false">E9+E10</f>
-        <v>2725465.79110796</v>
+        <v>-11029468.4955558</v>
       </c>
       <c r="F11" s="37" t="n">
         <f aca="false">F9+F10</f>
-        <v>10909292.8663658</v>
+        <v>21383352.9752188</v>
       </c>
       <c r="G11" s="37" t="n">
         <f aca="false">G9+G10</f>
-        <v>12050092.6125821</v>
+        <v>46655679.2827295</v>
       </c>
       <c r="H11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="37" t="n">
@@ -8848,52 +8845,52 @@
       </c>
       <c r="D12" s="37" t="n">
         <f aca="false">C13</f>
-        <v>1979099.67352</v>
+        <v>5943781.51784</v>
       </c>
       <c r="E12" s="37" t="n">
         <f aca="false">D13</f>
-        <v>1545674.8981138</v>
+        <v>18463744.043856</v>
       </c>
       <c r="F12" s="37" t="n">
         <f aca="false">E13</f>
-        <v>4271140.68922176</v>
+        <v>7434275.54830025</v>
       </c>
       <c r="G12" s="37" t="n">
         <f aca="false">F13</f>
-        <v>15180433.5555876</v>
+        <v>28817628.523519</v>
       </c>
       <c r="H12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="38" t="n">
         <f aca="false">C12+C11</f>
-        <v>1979099.67352</v>
+        <v>5943781.51784</v>
       </c>
       <c r="D13" s="38" t="n">
         <f aca="false">D12+D11</f>
-        <v>1545674.8981138</v>
+        <v>18463744.043856</v>
       </c>
       <c r="E13" s="38" t="n">
         <f aca="false">E12+E11</f>
-        <v>4271140.68922176</v>
+        <v>7434275.54830025</v>
       </c>
       <c r="F13" s="38" t="n">
         <f aca="false">F12+F11</f>
-        <v>15180433.5555876</v>
+        <v>28817628.523519</v>
       </c>
       <c r="G13" s="38" t="n">
         <f aca="false">G12+G11</f>
-        <v>27230526.1681697</v>
+        <v>75473307.8062485</v>
       </c>
       <c r="H13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="41" t="n">
@@ -8930,12 +8927,12 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B16" s="2"/>
-      <c r="C16" s="27" t="n">
+      <c r="C16" s="28" t="n">
         <f aca="false">MIN(C13:G13)</f>
-        <v>1545674.8981138</v>
+        <v>5943781.51784</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
@@ -8945,19 +8942,19 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B17" s="2"/>
-      <c r="C17" s="27" t="n">
+      <c r="C17" s="28" t="n">
         <f aca="false">-MIN(0,C9,C9+D9,C9+D9+E9,C9+D9+E9+F9,C9+D9+E9+F9+G9)</f>
-        <v>14704325.1018862</v>
+        <v>52815724.4516998</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
       <c r="H17" s="17" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
   </sheetData>

--- a/docs/finance/TownCore-LRP.xlsx
+++ b/docs/finance/TownCore-LRP.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="358">
   <si>
     <t xml:space="preserve">TownCore long-range plan, FY2027-FY2031</t>
   </si>
@@ -187,7 +187,7 @@
     <t xml:space="preserve">Share that pass readiness (Rule 7)</t>
   </si>
   <si>
-    <t xml:space="preserve">Owner plan: every town. Rule 7 still stops a town below 3 real items a day (10 for large), and today almost none pass: Boca makes about 0.8 a day, Delray 0.53. Reaching 100% needs many more sources per town or a lower bar. Set lower to see the plan without that work.</t>
+    <t xml:space="preserve">Owner, 2026-10-17: every town in America can make 3 real items a day; Rule 7 is the target we build sources toward. Today Boca makes about 0.8 a day and Delray 0.53, so the source work continues. Set lower to see the plan if some towns stay short.</t>
   </si>
   <si>
     <t xml:space="preserve">Share allowed by the naming rule</t>
@@ -430,7 +430,7 @@
     <t xml:space="preserve">$/story</t>
   </si>
   <si>
-    <t xml:space="preserve">Estimate for writer + separate fact-check calls; verify against current Anthropic pricing (CLAUDE.md §8). Scaled by unit cost multiplier.</t>
+    <t xml:space="preserve">Writer, separate fact-check and an AI review pass (owner: article review becomes an AI agent). Measured ~$0.10 for writer + fact-check on repo pricing; verify against current Anthropic pricing (CLAUDE.md §8). Scaled by unit cost multiplier.</t>
   </si>
   <si>
     <t xml:space="preserve">AI overhead per town per day</t>
@@ -529,19 +529,19 @@
     <t xml:space="preserve">Sales commission on direct-sold revenue</t>
   </si>
   <si>
-    <t xml:space="preserve">Paid on banners, newsletter and category sponsorships. Estimate.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Towns per editorial reviewer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reviewers approve Tier 3 items and samples (§7). Estimate.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Towns per local account executive</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clustered towns share sales effort (§10a). Estimate.</t>
+    <t xml:space="preserve">Owner: advertisers sign up and pay on the site; no commissioned sales force.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Towns per editorial standards editor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owner, 2026-10-17: article review becomes an AI agent once we trust it. A small team audits the agent, handles corrections and reader reports. Until the agent ships, Tier 3 still needs a person (Rule 5).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Towns per advertiser partnerships manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owner, 2026-10-17: sales are self-serve on the site. A small team handles regional and multi-town advertisers.</t>
   </si>
   <si>
     <t xml:space="preserve">Towns per support and success rep</t>
@@ -556,10 +556,10 @@
     <t xml:space="preserve">Engineering</t>
   </si>
   <si>
-    <t xml:space="preserve">Editorial reviewer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Account executive (base)</t>
+    <t xml:space="preserve">Editorial standards and launch operations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Advertiser partnerships</t>
   </si>
   <si>
     <t xml:space="preserve">Support and success</t>
@@ -646,7 +646,7 @@
     <t xml:space="preserve">Equity raised</t>
   </si>
   <si>
-    <t xml:space="preserve">Plan: $25M in FY2027 and $35M in FY2028, sized to the every-town launch pace with a buffer. Adjust to keep cash above zero.</t>
+    <t xml:space="preserve">Plan: $10M in FY2027, the ~$7.7M the every-town plan needs plus a buffer. Adjust to keep cash above zero.</t>
   </si>
   <si>
     <t xml:space="preserve">Town rollout</t>
@@ -799,10 +799,10 @@
     <t xml:space="preserve">Town-level people and acquisition costs ($)</t>
   </si>
   <si>
-    <t xml:space="preserve">Editorial review (share of a reviewer)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Local sales (share of an AE) + commission</t>
+    <t xml:space="preserve">Editorial standards (share)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Advertiser partnerships (share) + commission</t>
   </si>
   <si>
     <t xml:space="preserve">Support and success (share)</t>
@@ -868,10 +868,7 @@
     <t xml:space="preserve">Heads (year end)</t>
   </si>
   <si>
-    <t xml:space="preserve">Editorial reviewers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Account executives</t>
+    <t xml:space="preserve">Editorial standards</t>
   </si>
   <si>
     <t xml:space="preserve">Launch operations</t>
@@ -910,10 +907,10 @@
     <t xml:space="preserve">Operating expenses</t>
   </si>
   <si>
-    <t xml:space="preserve">Editorial review (people)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sales (people)</t>
+    <t xml:space="preserve">Editorial standards (people)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Advertiser partnerships (people)</t>
   </si>
   <si>
     <t xml:space="preserve">Sales commission</t>
@@ -1883,23 +1880,23 @@
       <c r="B10" s="2"/>
       <c r="C10" s="10" t="n">
         <f aca="false">'P&amp;L'!C8</f>
-        <v>0.431548852760639</v>
+        <v>0.400052059525826</v>
       </c>
       <c r="D10" s="10" t="n">
         <f aca="false">'P&amp;L'!D8</f>
-        <v>0.799502416256723</v>
+        <v>0.789260818887664</v>
       </c>
       <c r="E10" s="10" t="n">
         <f aca="false">'P&amp;L'!E8</f>
-        <v>0.88225003205724</v>
+        <v>0.876673851609431</v>
       </c>
       <c r="F10" s="10" t="n">
         <f aca="false">'P&amp;L'!F8</f>
-        <v>0.918154757640337</v>
+        <v>0.914613415716302</v>
       </c>
       <c r="G10" s="10" t="n">
         <f aca="false">'P&amp;L'!G8</f>
-        <v>0.936222688325491</v>
+        <v>0.933708003592243</v>
       </c>
       <c r="H10" s="2"/>
     </row>
@@ -1910,23 +1907,23 @@
       <c r="B11" s="2"/>
       <c r="C11" s="9" t="n">
         <f aca="false">'P&amp;L'!C16</f>
-        <v>-18714272.68496</v>
+        <v>-7576935.88496</v>
       </c>
       <c r="D11" s="9" t="n">
         <f aca="false">'P&amp;L'!D16</f>
-        <v>-21529601.343104</v>
+        <v>1710094.032896</v>
       </c>
       <c r="E11" s="9" t="n">
         <f aca="false">'P&amp;L'!E16</f>
-        <v>-9655829.95082656</v>
+        <v>28895708.3674734</v>
       </c>
       <c r="F11" s="9" t="n">
         <f aca="false">'P&amp;L'!F16</f>
-        <v>22598678.7557132</v>
+        <v>69401273.7358492</v>
       </c>
       <c r="G11" s="9" t="n">
         <f aca="false">'P&amp;L'!G16</f>
-        <v>54040935.9844372</v>
+        <v>103097468.531385</v>
       </c>
       <c r="H11" s="2"/>
     </row>
@@ -1937,23 +1934,23 @@
       <c r="B12" s="2"/>
       <c r="C12" s="10" t="n">
         <f aca="false">'P&amp;L'!C17</f>
-        <v>-9.85899237790985</v>
+        <v>-3.99165676354426</v>
       </c>
       <c r="D12" s="10" t="n">
         <f aca="false">'P&amp;L'!D17</f>
-        <v>-1.25443913462188</v>
+        <v>0.0996399721741811</v>
       </c>
       <c r="E12" s="10" t="n">
         <f aca="false">'P&amp;L'!E17</f>
-        <v>-0.193630303722282</v>
+        <v>0.579451462583535</v>
       </c>
       <c r="F12" s="10" t="n">
         <f aca="false">'P&amp;L'!F17</f>
-        <v>0.250045659732808</v>
+        <v>0.76789831233786</v>
       </c>
       <c r="G12" s="10" t="n">
         <f aca="false">'P&amp;L'!G17</f>
-        <v>0.430419265417366</v>
+        <v>0.82113930603363</v>
       </c>
       <c r="H12" s="2"/>
     </row>
@@ -1964,23 +1961,23 @@
       <c r="B13" s="2"/>
       <c r="C13" s="9" t="n">
         <f aca="false">'P&amp;L'!C25</f>
-        <v>-18892606.0182933</v>
+        <v>-7614435.88496</v>
       </c>
       <c r="D13" s="9" t="n">
         <f aca="false">'P&amp;L'!D25</f>
-        <v>-21872101.343104</v>
+        <v>1645094.032896</v>
       </c>
       <c r="E13" s="9" t="n">
         <f aca="false">'P&amp;L'!E25</f>
-        <v>-10129163.2841599</v>
+        <v>23097241.7386211</v>
       </c>
       <c r="F13" s="9" t="n">
         <f aca="false">'P&amp;L'!F25</f>
-        <v>22303678.7557132</v>
+        <v>52012205.3018869</v>
       </c>
       <c r="G13" s="9" t="n">
         <f aca="false">'P&amp;L'!G25</f>
-        <v>47580124.9607889</v>
+        <v>77303101.3985385</v>
       </c>
       <c r="H13" s="2"/>
     </row>
@@ -1991,23 +1988,23 @@
       <c r="B14" s="2"/>
       <c r="C14" s="9" t="n">
         <f aca="false">'Cash Flow'!C13</f>
-        <v>5943781.51784</v>
+        <v>2503618.31784</v>
       </c>
       <c r="D14" s="9" t="n">
         <f aca="false">'Cash Flow'!D13</f>
-        <v>18463744.043856</v>
+        <v>3673276.219856</v>
       </c>
       <c r="E14" s="9" t="n">
         <f aca="false">'Cash Flow'!E13</f>
-        <v>7434275.54830025</v>
+        <v>25806046.0804145</v>
       </c>
       <c r="F14" s="9" t="n">
         <f aca="false">'Cash Flow'!F13</f>
-        <v>28817628.523519</v>
+        <v>76654592.2684737</v>
       </c>
       <c r="G14" s="9" t="n">
         <f aca="false">'Cash Flow'!G13</f>
-        <v>75473307.8062485</v>
+        <v>152921581.322286</v>
       </c>
       <c r="H14" s="2"/>
     </row>
@@ -2018,23 +2015,23 @@
       <c r="B15" s="2"/>
       <c r="C15" s="9" t="n">
         <f aca="false">KPIs!C22</f>
-        <v>33780959.8039639</v>
+        <v>50953224.2039639</v>
       </c>
       <c r="D15" s="9" t="n">
         <f aca="false">KPIs!D22</f>
-        <v>66863868.3138088</v>
+        <v>100693439.181809</v>
       </c>
       <c r="E15" s="9" t="n">
         <f aca="false">KPIs!E22</f>
-        <v>92357578.2246254</v>
+        <v>139253415.301025</v>
       </c>
       <c r="F15" s="9" t="n">
         <f aca="false">KPIs!F22</f>
-        <v>89083676.518476</v>
+        <v>135044089.780024</v>
       </c>
       <c r="G15" s="9" t="n">
         <f aca="false">KPIs!G22</f>
-        <v>86343208.4565014</v>
+        <v>131691005.841481</v>
       </c>
       <c r="H15" s="2"/>
     </row>
@@ -2229,7 +2226,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2241,7 +2238,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2285,7 +2282,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B5" s="16"/>
       <c r="C5" s="16"/>
@@ -2297,7 +2294,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="33" t="n">
@@ -2378,7 +2375,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="33" t="n">
@@ -2405,7 +2402,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B10" s="16"/>
       <c r="C10" s="16"/>
@@ -2417,7 +2414,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="33" t="n">
@@ -2444,7 +2441,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="42" t="n">
@@ -2471,7 +2468,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B13" s="16"/>
       <c r="C13" s="16"/>
@@ -2510,7 +2507,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="37" t="n">
@@ -2542,23 +2539,23 @@
       <c r="B16" s="2"/>
       <c r="C16" s="34" t="n">
         <f aca="false">'P&amp;L'!C8</f>
-        <v>0.431548852760639</v>
+        <v>0.400052059525826</v>
       </c>
       <c r="D16" s="34" t="n">
         <f aca="false">'P&amp;L'!D8</f>
-        <v>0.799502416256723</v>
+        <v>0.789260818887664</v>
       </c>
       <c r="E16" s="34" t="n">
         <f aca="false">'P&amp;L'!E8</f>
-        <v>0.88225003205724</v>
+        <v>0.876673851609431</v>
       </c>
       <c r="F16" s="34" t="n">
         <f aca="false">'P&amp;L'!F8</f>
-        <v>0.918154757640337</v>
+        <v>0.914613415716302</v>
       </c>
       <c r="G16" s="34" t="n">
         <f aca="false">'P&amp;L'!G8</f>
-        <v>0.936222688325491</v>
+        <v>0.933708003592243</v>
       </c>
       <c r="H16" s="2"/>
     </row>
@@ -2569,23 +2566,23 @@
       <c r="B17" s="2"/>
       <c r="C17" s="37" t="n">
         <f aca="false">'P&amp;L'!C16</f>
-        <v>-18714272.68496</v>
+        <v>-7576935.88496</v>
       </c>
       <c r="D17" s="37" t="n">
         <f aca="false">'P&amp;L'!D16</f>
-        <v>-21529601.343104</v>
+        <v>1710094.032896</v>
       </c>
       <c r="E17" s="37" t="n">
         <f aca="false">'P&amp;L'!E16</f>
-        <v>-9655829.95082656</v>
+        <v>28895708.3674734</v>
       </c>
       <c r="F17" s="37" t="n">
         <f aca="false">'P&amp;L'!F16</f>
-        <v>22598678.7557132</v>
+        <v>69401273.7358492</v>
       </c>
       <c r="G17" s="37" t="n">
         <f aca="false">'P&amp;L'!G16</f>
-        <v>54040935.9844372</v>
+        <v>103097468.531385</v>
       </c>
       <c r="H17" s="2"/>
     </row>
@@ -2596,23 +2593,23 @@
       <c r="B18" s="2"/>
       <c r="C18" s="34" t="n">
         <f aca="false">'P&amp;L'!C17</f>
-        <v>-9.85899237790985</v>
+        <v>-3.99165676354426</v>
       </c>
       <c r="D18" s="34" t="n">
         <f aca="false">'P&amp;L'!D17</f>
-        <v>-1.25443913462188</v>
+        <v>0.0996399721741811</v>
       </c>
       <c r="E18" s="34" t="n">
         <f aca="false">'P&amp;L'!E17</f>
-        <v>-0.193630303722282</v>
+        <v>0.579451462583535</v>
       </c>
       <c r="F18" s="34" t="n">
         <f aca="false">'P&amp;L'!F17</f>
-        <v>0.250045659732808</v>
+        <v>0.76789831233786</v>
       </c>
       <c r="G18" s="34" t="n">
         <f aca="false">'P&amp;L'!G17</f>
-        <v>0.430419265417366</v>
+        <v>0.82113930603363</v>
       </c>
       <c r="H18" s="2"/>
     </row>
@@ -2623,135 +2620,135 @@
       <c r="B19" s="2"/>
       <c r="C19" s="37" t="n">
         <f aca="false">'Cash Flow'!C13</f>
-        <v>5943781.51784</v>
+        <v>2503618.31784</v>
       </c>
       <c r="D19" s="37" t="n">
         <f aca="false">'Cash Flow'!D13</f>
-        <v>18463744.043856</v>
+        <v>3673276.219856</v>
       </c>
       <c r="E19" s="37" t="n">
         <f aca="false">'Cash Flow'!E13</f>
-        <v>7434275.54830025</v>
+        <v>25806046.0804145</v>
       </c>
       <c r="F19" s="37" t="n">
         <f aca="false">'Cash Flow'!F13</f>
-        <v>28817628.523519</v>
+        <v>76654592.2684737</v>
       </c>
       <c r="G19" s="37" t="n">
         <f aca="false">'Cash Flow'!G13</f>
-        <v>75473307.8062485</v>
+        <v>152921581.322286</v>
       </c>
       <c r="H19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="34" t="n">
         <f aca="false">IF('P&amp;L'!C5=0,0,Costs!C6/'P&amp;L'!C5)</f>
-        <v>0.270203259179239</v>
+        <v>0.301700052414052</v>
       </c>
       <c r="D20" s="34" t="n">
         <f aca="false">IF('P&amp;L'!D5=0,0,Costs!D6/'P&amp;L'!D5)</f>
-        <v>0.0878601503235732</v>
+        <v>0.0981017476926319</v>
       </c>
       <c r="E20" s="34" t="n">
         <f aca="false">IF('P&amp;L'!E5=0,0,Costs!E6/'P&amp;L'!E5)</f>
-        <v>0.0478366835485996</v>
+        <v>0.0534128639964081</v>
       </c>
       <c r="F20" s="34" t="n">
         <f aca="false">IF('P&amp;L'!F5=0,0,Costs!F6/'P&amp;L'!F5)</f>
-        <v>0.0303803032457523</v>
+        <v>0.0339216451697874</v>
       </c>
       <c r="G20" s="34" t="n">
         <f aca="false">IF('P&amp;L'!G5=0,0,Costs!G6/'P&amp;L'!G5)</f>
-        <v>0.0215728631694795</v>
+        <v>0.024087547902728</v>
       </c>
       <c r="H20" s="17" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" s="37" t="n">
         <f aca="false">Costs!C22+Costs!C23+Costs!C24+Costs!C21+Assumptions!C$97+Costs!C26</f>
-        <v>1633250</v>
+        <v>1126250</v>
       </c>
       <c r="D21" s="37" t="n">
         <f aca="false">Costs!D22+Costs!D23+Costs!D24+Costs!D21+Assumptions!D$97+Costs!D26</f>
-        <v>2902125</v>
+        <v>1903125</v>
       </c>
       <c r="E21" s="37" t="n">
         <f aca="false">Costs!E22+Costs!E23+Costs!E24+Costs!E21+Assumptions!E$97+Costs!E26</f>
-        <v>4358628.75</v>
+        <v>2975628.75</v>
       </c>
       <c r="F21" s="37" t="n">
         <f aca="false">Costs!F22+Costs!F23+Costs!F24+Costs!F21+Assumptions!F$97+Costs!F26</f>
-        <v>5708476.4375</v>
+        <v>4355476.4375</v>
       </c>
       <c r="G21" s="37" t="n">
         <f aca="false">Costs!G22+Costs!G23+Costs!G24+Costs!G21+Assumptions!G$97+Costs!G26</f>
-        <v>7166241.820375</v>
+        <v>5822241.820375</v>
       </c>
       <c r="H21" s="2"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="37" t="n">
         <f aca="false">Rollout!C7/'Unit Economics'!$G$7*'Unit Economics'!$G$42-C21</f>
-        <v>33780959.8039639</v>
+        <v>50953224.2039639</v>
       </c>
       <c r="D22" s="37" t="n">
         <f aca="false">Rollout!D7/'Unit Economics'!$G$7*'Unit Economics'!$G$42-D21</f>
-        <v>66863868.3138088</v>
+        <v>100693439.181809</v>
       </c>
       <c r="E22" s="37" t="n">
         <f aca="false">Rollout!E7/'Unit Economics'!$G$7*'Unit Economics'!$G$42-E21</f>
-        <v>92357578.2246254</v>
+        <v>139253415.301025</v>
       </c>
       <c r="F22" s="37" t="n">
         <f aca="false">Rollout!F7/'Unit Economics'!$G$7*'Unit Economics'!$G$42-F21</f>
-        <v>89083676.518476</v>
+        <v>135044089.780024</v>
       </c>
       <c r="G22" s="37" t="n">
         <f aca="false">Rollout!G7/'Unit Economics'!$G$7*'Unit Economics'!$G$42-G21</f>
-        <v>86343208.4565014</v>
+        <v>131691005.841481</v>
       </c>
       <c r="H22" s="17" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" s="33" t="n">
         <f aca="false">IF('Unit Economics'!$G$42&lt;=0,0,C21/('Unit Economics'!$G$42/'Unit Economics'!$G$7))</f>
-        <v>138.355480105943</v>
+        <v>64.8768070654376</v>
       </c>
       <c r="D23" s="33" t="n">
         <f aca="false">IF('Unit Economics'!$G$42&lt;=0,0,D21/('Unit Economics'!$G$42/'Unit Economics'!$G$7))</f>
-        <v>245.844113088908</v>
+        <v>109.628122926891</v>
       </c>
       <c r="E23" s="33" t="n">
         <f aca="false">IF('Unit Economics'!$G$42&lt;=0,0,E21/('Unit Economics'!$G$42/'Unit Economics'!$G$7))</f>
-        <v>369.227107491085</v>
+        <v>171.408916592337</v>
       </c>
       <c r="F23" s="33" t="n">
         <f aca="false">IF('Unit Economics'!$G$42&lt;=0,0,F21/('Unit Economics'!$G$42/'Unit Economics'!$G$7))</f>
-        <v>483.575079249211</v>
+        <v>250.894032864592</v>
       </c>
       <c r="G23" s="33" t="n">
         <f aca="false">IF('Unit Economics'!$G$42&lt;=0,0,G21/('Unit Economics'!$G$42/'Unit Economics'!$G$7))</f>
-        <v>607.064948791224</v>
+        <v>335.385979372956</v>
       </c>
       <c r="H23" s="2"/>
     </row>
@@ -2767,7 +2764,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="15" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B25" s="16"/>
       <c r="C25" s="16"/>
@@ -2779,7 +2776,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" s="9" t="n">
@@ -2794,12 +2791,12 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" s="9" t="n">
         <f aca="false">'Unit Economics'!G42</f>
-        <v>10978.4050392288</v>
+        <v>16144.6370032288</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
@@ -2809,12 +2806,12 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" s="10" t="n">
         <f aca="false">'Unit Economics'!G43</f>
-        <v>0.612127686524311</v>
+        <v>0.900183520579547</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
@@ -2824,7 +2821,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" s="9" t="n">
@@ -2839,29 +2836,29 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="41" t="n">
         <f aca="false">IFERROR(MATCH(TRUE(),INDEX('Unit Economics'!C45:G45&gt;0,0),0),"After Age 5")</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
       <c r="H30" s="17" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" s="2" t="str">
         <f aca="false">IFERROR(INDEX(C4:G4,MATCH(TRUE(),INDEX(C17:G17&gt;0,0),0)),"Not by FY2031")</f>
-        <v>2030</v>
+        <v>2028</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>
@@ -2871,12 +2868,12 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" s="9" t="n">
         <f aca="false">'Cash Flow'!C17</f>
-        <v>52815724.4516998</v>
+        <v>7746381.68216</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" s="2"/>
@@ -3939,7 +3936,7 @@
         <v>132</v>
       </c>
       <c r="C58" s="31" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" s="2"/>
@@ -4221,7 +4218,7 @@
       </c>
       <c r="B75" s="17"/>
       <c r="C75" s="23" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D75" s="2"/>
       <c r="E75" s="2"/>
@@ -4239,7 +4236,7 @@
         <v>49</v>
       </c>
       <c r="C76" s="24" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="D76" s="2"/>
       <c r="E76" s="2"/>
@@ -4257,7 +4254,7 @@
         <v>49</v>
       </c>
       <c r="C77" s="24" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="D77" s="2"/>
       <c r="E77" s="2"/>
@@ -4817,10 +4814,10 @@
         <v>185</v>
       </c>
       <c r="C109" s="32" t="n">
-        <v>25000000</v>
+        <v>10000000</v>
       </c>
       <c r="D109" s="32" t="n">
-        <v>35000000</v>
+        <v>0</v>
       </c>
       <c r="E109" s="32" t="n">
         <v>0</v>
@@ -5753,23 +5750,23 @@
       <c r="B29" s="2"/>
       <c r="C29" s="37" t="n">
         <f aca="false">MIN(Assumptions!$C$60,Assumptions!$F$26*Assumptions!$C$58+Assumptions!$C$59)*Assumptions!$F$10*365*C8</f>
-        <v>170.966</v>
+        <v>190.895</v>
       </c>
       <c r="D29" s="37" t="n">
         <f aca="false">MIN(Assumptions!$C$60,Assumptions!$F$26*Assumptions!$C$58+Assumptions!$C$59)*Assumptions!$F$10*365*D8</f>
-        <v>331.67404</v>
+        <v>370.3363</v>
       </c>
       <c r="E29" s="37" t="n">
         <f aca="false">MIN(Assumptions!$C$60,Assumptions!$F$26*Assumptions!$C$58+Assumptions!$C$59)*Assumptions!$F$10*365*E8</f>
-        <v>324.8354</v>
+        <v>362.7005</v>
       </c>
       <c r="F29" s="37" t="n">
         <f aca="false">MIN(Assumptions!$C$60,Assumptions!$F$26*Assumptions!$C$58+Assumptions!$C$59)*Assumptions!$F$10*365*F8</f>
-        <v>321.41608</v>
+        <v>358.8826</v>
       </c>
       <c r="G29" s="37" t="n">
         <f aca="false">MIN(Assumptions!$C$60,Assumptions!$F$26*Assumptions!$C$58+Assumptions!$C$59)*Assumptions!$F$10*365*G8</f>
-        <v>317.99676</v>
+        <v>355.0647</v>
       </c>
       <c r="H29" s="17" t="s">
         <v>247</v>
@@ -5892,23 +5889,23 @@
       <c r="B34" s="2"/>
       <c r="C34" s="38" t="n">
         <f aca="false">SUM(C29:C33)</f>
-        <v>344.67670832</v>
+        <v>364.60570832</v>
       </c>
       <c r="D34" s="38" t="n">
         <f aca="false">SUM(D29:D33)</f>
-        <v>787.351986048</v>
+        <v>826.014246048</v>
       </c>
       <c r="E34" s="38" t="n">
         <f aca="false">SUM(E29:E33)</f>
-        <v>878.24312256</v>
+        <v>916.10822256</v>
       </c>
       <c r="F34" s="38" t="n">
         <f aca="false">SUM(F29:F33)</f>
-        <v>948.889874784</v>
+        <v>986.356394784</v>
       </c>
       <c r="G34" s="38" t="n">
         <f aca="false">SUM(G29:G33)</f>
-        <v>1008.0242135712</v>
+        <v>1045.0921535712</v>
       </c>
       <c r="H34" s="2"/>
     </row>
@@ -5919,23 +5916,23 @@
       <c r="B35" s="2"/>
       <c r="C35" s="28" t="n">
         <f aca="false">C25-C34</f>
-        <v>288.05437168</v>
+        <v>268.12537168</v>
       </c>
       <c r="D35" s="28" t="n">
         <f aca="false">D25-D34</f>
-        <v>4300.827245952</v>
+        <v>4262.164985952</v>
       </c>
       <c r="E35" s="28" t="n">
         <f aca="false">E25-E34</f>
-        <v>10142.88243744</v>
+        <v>10105.01733744</v>
       </c>
       <c r="F35" s="28" t="n">
         <f aca="false">F25-F34</f>
-        <v>14029.540689216</v>
+        <v>13992.074169216</v>
       </c>
       <c r="G35" s="28" t="n">
         <f aca="false">G25-G34</f>
-        <v>16926.8042232288</v>
+        <v>16889.7362832288</v>
       </c>
       <c r="H35" s="2"/>
     </row>
@@ -5946,23 +5943,23 @@
       <c r="B36" s="2"/>
       <c r="C36" s="34" t="n">
         <f aca="false">IF(C25=0,0,C35/C25)</f>
-        <v>0.455255606663103</v>
+        <v>0.423758813428289</v>
       </c>
       <c r="D36" s="34" t="n">
         <f aca="false">IF(D25=0,0,D35/D25)</f>
-        <v>0.845258598381072</v>
+        <v>0.837660151424477</v>
       </c>
       <c r="E36" s="34" t="n">
         <f aca="false">IF(E25=0,0,E35/E25)</f>
-        <v>0.920312755917827</v>
+        <v>0.916877072348679</v>
       </c>
       <c r="F36" s="34" t="n">
         <f aca="false">IF(F25=0,0,F35/F25)</f>
-        <v>0.936649579491685</v>
+        <v>0.934148214623055</v>
       </c>
       <c r="G36" s="34" t="n">
         <f aca="false">IF(G25=0,0,G35/G25)</f>
-        <v>0.943795157164545</v>
+        <v>0.941728343973071</v>
       </c>
       <c r="H36" s="2"/>
     </row>
@@ -5985,23 +5982,23 @@
       <c r="B38" s="2"/>
       <c r="C38" s="37" t="n">
         <f aca="false">Assumptions!$C$83*(1+Assumptions!$C$73)/Assumptions!$C$76*C8</f>
-        <v>1093.75</v>
+        <v>43.75</v>
       </c>
       <c r="D38" s="37" t="n">
         <f aca="false">Assumptions!$C$83*(1+Assumptions!$C$73)/Assumptions!$C$76*D8</f>
-        <v>2121.875</v>
+        <v>84.875</v>
       </c>
       <c r="E38" s="37" t="n">
         <f aca="false">Assumptions!$C$83*(1+Assumptions!$C$73)/Assumptions!$C$76*E8</f>
-        <v>2078.125</v>
+        <v>83.125</v>
       </c>
       <c r="F38" s="37" t="n">
         <f aca="false">Assumptions!$C$83*(1+Assumptions!$C$73)/Assumptions!$C$76*F8</f>
-        <v>2056.25</v>
+        <v>82.25</v>
       </c>
       <c r="G38" s="37" t="n">
         <f aca="false">Assumptions!$C$83*(1+Assumptions!$C$73)/Assumptions!$C$76*G8</f>
-        <v>2034.375</v>
+        <v>81.375</v>
       </c>
       <c r="H38" s="2"/>
     </row>
@@ -6012,23 +6009,23 @@
       <c r="B39" s="2"/>
       <c r="C39" s="37" t="n">
         <f aca="false">Assumptions!$C$84*(1+Assumptions!$C$73)/Assumptions!$C$77*C8+C27*Assumptions!$C$75</f>
-        <v>1372.22876666667</v>
+        <v>40.625</v>
       </c>
       <c r="D39" s="37" t="n">
         <f aca="false">Assumptions!$C$84*(1+Assumptions!$C$73)/Assumptions!$C$77*D8+D27*Assumptions!$C$75</f>
-        <v>2849.71928533333</v>
+        <v>78.8125</v>
       </c>
       <c r="E39" s="37" t="n">
         <f aca="false">Assumptions!$C$84*(1+Assumptions!$C$73)/Assumptions!$C$77*E8+E27*Assumptions!$C$75</f>
-        <v>3037.42448666667</v>
+        <v>77.1875</v>
       </c>
       <c r="F39" s="37" t="n">
         <f aca="false">Assumptions!$C$84*(1+Assumptions!$C$73)/Assumptions!$C$77*F8+F27*Assumptions!$C$75</f>
-        <v>3220.49718333333</v>
+        <v>76.375</v>
       </c>
       <c r="G39" s="37" t="n">
         <f aca="false">Assumptions!$C$84*(1+Assumptions!$C$73)/Assumptions!$C$77*G8+G27*Assumptions!$C$75</f>
-        <v>3325.862404</v>
+        <v>75.5625</v>
       </c>
       <c r="H39" s="2"/>
     </row>
@@ -6093,23 +6090,23 @@
       <c r="B42" s="2"/>
       <c r="C42" s="38" t="n">
         <f aca="false">C35-SUM(C38:C41)</f>
-        <v>-2561.48672832</v>
+        <v>-199.811961653333</v>
       </c>
       <c r="D42" s="38" t="n">
         <f aca="false">D35-SUM(D38:D41)</f>
-        <v>-1380.567886048</v>
+        <v>3388.67663928533</v>
       </c>
       <c r="E42" s="38" t="n">
         <f aca="false">E35-SUM(E38:E41)</f>
-        <v>4365.24259744</v>
+        <v>9282.61448410667</v>
       </c>
       <c r="F42" s="38" t="n">
         <f aca="false">F35-SUM(F38:F41)</f>
-        <v>8126.858239216</v>
+        <v>13207.5139025493</v>
       </c>
       <c r="G42" s="38" t="n">
         <f aca="false">G35-SUM(G38:G41)</f>
-        <v>10978.4050392288</v>
+        <v>16144.6370032288</v>
       </c>
       <c r="H42" s="2"/>
     </row>
@@ -6120,23 +6117,23 @@
       <c r="B43" s="2"/>
       <c r="C43" s="34" t="n">
         <f aca="false">IF(C25=0,0,C42/C25)</f>
-        <v>-4.04830236618059</v>
+        <v>-0.315792866778938</v>
       </c>
       <c r="D43" s="34" t="n">
         <f aca="false">IF(D25=0,0,D42/D25)</f>
-        <v>-0.271328469988929</v>
+        <v>0.665990029984332</v>
       </c>
       <c r="E43" s="34" t="n">
         <f aca="false">IF(E25=0,0,E42/E25)</f>
-        <v>0.396079563169408</v>
+        <v>0.842256485834526</v>
       </c>
       <c r="F43" s="34" t="n">
         <f aca="false">IF(F25=0,0,F42/F25)</f>
-        <v>0.542570745612598</v>
+        <v>0.88176887732771</v>
       </c>
       <c r="G43" s="34" t="n">
         <f aca="false">IF(G25=0,0,G42/G25)</f>
-        <v>0.612127686524311</v>
+        <v>0.900183520579547</v>
       </c>
       <c r="H43" s="2"/>
     </row>
@@ -6174,23 +6171,23 @@
       <c r="B45" s="2"/>
       <c r="C45" s="28" t="n">
         <f aca="false">C42-C44</f>
-        <v>-4101.48672832</v>
+        <v>-1739.81196165333</v>
       </c>
       <c r="D45" s="28" t="n">
         <f aca="false">C45+D42-D44</f>
-        <v>-5482.054614368</v>
+        <v>1648.864677632</v>
       </c>
       <c r="E45" s="28" t="n">
         <f aca="false">D45+E42-E44</f>
-        <v>-1116.812016928</v>
+        <v>10931.4791617387</v>
       </c>
       <c r="F45" s="28" t="n">
         <f aca="false">E45+F42-F44</f>
-        <v>7010.046222288</v>
+        <v>24138.993064288</v>
       </c>
       <c r="G45" s="28" t="n">
         <f aca="false">F45+G42-G44</f>
-        <v>17988.4512615168</v>
+        <v>40283.6300675168</v>
       </c>
       <c r="H45" s="17" t="s">
         <v>264</v>
@@ -6880,50 +6877,50 @@
       <c r="B9" s="2"/>
       <c r="C9" s="33" t="n">
         <f aca="false">IF(Rollout!C$7=0,0,MAX(1,ROUNDUP(Rollout!C$7/Assumptions!$C$76,0)))</f>
-        <v>75</v>
+        <v>3</v>
       </c>
       <c r="D9" s="33" t="n">
         <f aca="false">IF(Rollout!D$7=0,0,MAX(1,ROUNDUP(Rollout!D$7/Assumptions!$C$76,0)))</f>
-        <v>148</v>
+        <v>6</v>
       </c>
       <c r="E9" s="33" t="n">
         <f aca="false">IF(Rollout!E$7=0,0,MAX(1,ROUNDUP(Rollout!E$7/Assumptions!$C$76,0)))</f>
-        <v>205</v>
+        <v>9</v>
       </c>
       <c r="F9" s="33" t="n">
         <f aca="false">IF(Rollout!F$7=0,0,MAX(1,ROUNDUP(Rollout!F$7/Assumptions!$C$76,0)))</f>
-        <v>201</v>
+        <v>9</v>
       </c>
       <c r="G9" s="33" t="n">
         <f aca="false">IF(Rollout!G$7=0,0,MAX(1,ROUNDUP(Rollout!G$7/Assumptions!$C$76,0)))</f>
-        <v>199</v>
+        <v>8</v>
       </c>
       <c r="H9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>280</v>
+        <v>176</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="33" t="n">
         <f aca="false">IF(Rollout!C$7=0,0,MAX(1,ROUNDUP(Rollout!C$7/Assumptions!$C$77,0)))</f>
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="D10" s="33" t="n">
         <f aca="false">IF(Rollout!D$7=0,0,MAX(1,ROUNDUP(Rollout!D$7/Assumptions!$C$77,0)))</f>
-        <v>197</v>
+        <v>6</v>
       </c>
       <c r="E10" s="33" t="n">
         <f aca="false">IF(Rollout!E$7=0,0,MAX(1,ROUNDUP(Rollout!E$7/Assumptions!$C$77,0)))</f>
-        <v>274</v>
+        <v>9</v>
       </c>
       <c r="F10" s="33" t="n">
         <f aca="false">IF(Rollout!F$7=0,0,MAX(1,ROUNDUP(Rollout!F$7/Assumptions!$C$77,0)))</f>
-        <v>268</v>
+        <v>9</v>
       </c>
       <c r="G10" s="33" t="n">
         <f aca="false">IF(Rollout!G$7=0,0,MAX(1,ROUNDUP(Rollout!G$7/Assumptions!$C$77,0)))</f>
-        <v>265</v>
+        <v>8</v>
       </c>
       <c r="H10" s="2"/>
     </row>
@@ -6956,7 +6953,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="33" t="n">
@@ -6983,47 +6980,47 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="39" t="n">
         <f aca="false">SUM(C6:C12)</f>
-        <v>214</v>
+        <v>45</v>
       </c>
       <c r="D13" s="39" t="n">
         <f aca="false">SUM(D6:D12)</f>
-        <v>411</v>
+        <v>78</v>
       </c>
       <c r="E13" s="39" t="n">
         <f aca="false">SUM(E6:E12)</f>
-        <v>568</v>
+        <v>107</v>
       </c>
       <c r="F13" s="39" t="n">
         <f aca="false">SUM(F6:F12)</f>
-        <v>554</v>
+        <v>103</v>
       </c>
       <c r="G13" s="39" t="n">
         <f aca="false">SUM(G6:G12)</f>
-        <v>554</v>
+        <v>106</v>
       </c>
       <c r="H13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="33" t="n">
         <f aca="false">C13</f>
-        <v>214</v>
+        <v>45</v>
       </c>
       <c r="D14" s="33" t="n">
         <f aca="false">MAX(0,D13-C13)</f>
-        <v>197</v>
+        <v>33</v>
       </c>
       <c r="E14" s="33" t="n">
         <f aca="false">MAX(0,E13-D13)</f>
-        <v>157</v>
+        <v>29</v>
       </c>
       <c r="F14" s="33" t="n">
         <f aca="false">MAX(0,F13-E13)</f>
@@ -7031,7 +7028,7 @@
       </c>
       <c r="G14" s="33" t="n">
         <f aca="false">MAX(0,G13-F13)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H14" s="2"/>
     </row>
@@ -7047,7 +7044,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -7145,50 +7142,50 @@
       <c r="B20" s="2"/>
       <c r="C20" s="37" t="n">
         <f aca="false">C9*0.75*Assumptions!$C$83*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^0</f>
-        <v>4921875</v>
+        <v>196875</v>
       </c>
       <c r="D20" s="37" t="n">
         <f aca="false">(C9+D9)/2*Assumptions!$C$83*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^1</f>
-        <v>10048937.5</v>
+        <v>405562.5</v>
       </c>
       <c r="E20" s="37" t="n">
         <f aca="false">(D9+E9)/2*Assumptions!$C$83*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^2</f>
-        <v>16384274.375</v>
+        <v>696215.625</v>
       </c>
       <c r="F20" s="37" t="n">
         <f aca="false">(E9+F9)/2*Assumptions!$C$83*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^3</f>
-        <v>19409563.3375</v>
+        <v>860522.5125</v>
       </c>
       <c r="G20" s="37" t="n">
         <f aca="false">(F9+G9)/2*Assumptions!$C$83*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^4</f>
-        <v>19696404.175</v>
+        <v>837097.1774375</v>
       </c>
       <c r="H20" s="2"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>280</v>
+        <v>176</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" s="37" t="n">
         <f aca="false">C10*0.75*Assumptions!$C$84*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^0</f>
-        <v>6093750</v>
+        <v>182812.5</v>
       </c>
       <c r="D21" s="37" t="n">
         <f aca="false">(C10+D10)/2*Assumptions!$C$84*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^1</f>
-        <v>12427593.75</v>
+        <v>376593.75</v>
       </c>
       <c r="E21" s="37" t="n">
         <f aca="false">(D10+E10)/2*Assumptions!$C$84*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^2</f>
-        <v>20299658.4375</v>
+        <v>646485.9375</v>
       </c>
       <c r="F21" s="37" t="n">
         <f aca="false">(E10+F10)/2*Assumptions!$C$84*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^3</f>
-        <v>24060482.63125</v>
+        <v>799056.61875</v>
       </c>
       <c r="G21" s="37" t="n">
         <f aca="false">(F10+G10)/2*Assumptions!$C$84*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^4</f>
-        <v>24370782.9515313</v>
+        <v>777304.52190625</v>
       </c>
       <c r="H21" s="2"/>
     </row>
@@ -7221,7 +7218,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" s="37" t="n">
@@ -7248,28 +7245,28 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" s="38" t="n">
         <f aca="false">SUM(C17:C23)</f>
-        <v>13710937.5</v>
+        <v>3075000</v>
       </c>
       <c r="D24" s="38" t="n">
         <f aca="false">SUM(D17:D23)</f>
-        <v>27282125</v>
+        <v>5587750</v>
       </c>
       <c r="E24" s="38" t="n">
         <f aca="false">SUM(E17:E23)</f>
-        <v>43934521.25</v>
+        <v>8593290</v>
       </c>
       <c r="F24" s="38" t="n">
         <f aca="false">SUM(F17:F23)</f>
-        <v>52259668.775</v>
+        <v>10449201.9375</v>
       </c>
       <c r="G24" s="38" t="n">
         <f aca="false">SUM(G17:G23)</f>
-        <v>53795803.9029688</v>
+        <v>11343018.4757813</v>
       </c>
       <c r="H24" s="2"/>
     </row>
@@ -7285,7 +7282,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="17" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -7322,7 +7319,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -7334,7 +7331,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -7378,7 +7375,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B5" s="16"/>
       <c r="C5" s="16"/>
@@ -7395,23 +7392,23 @@
       <c r="B6" s="2"/>
       <c r="C6" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$C$29</f>
-        <v>512898</v>
+        <v>572685</v>
       </c>
       <c r="D6" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$D$29+Rollout!$D$5*'Unit Economics'!$C$29</f>
-        <v>1507920.12</v>
+        <v>1683693.9</v>
       </c>
       <c r="E6" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$E$29+Rollout!$D$5*'Unit Economics'!$D$29+Rollout!$E$5*'Unit Economics'!$C$29</f>
-        <v>2385488.598</v>
+        <v>2663557.935</v>
       </c>
       <c r="F6" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$F$29+Rollout!$D$5*'Unit Economics'!$E$29+Rollout!$E$5*'Unit Economics'!$D$29+Rollout!$F$5*'Unit Economics'!$C$29</f>
-        <v>2745717.37932</v>
+        <v>3065777.5179</v>
       </c>
       <c r="G6" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$G$29+Rollout!$D$5*'Unit Economics'!$F$29+Rollout!$E$5*'Unit Economics'!$E$29+Rollout!$F$5*'Unit Economics'!$D$29+Rollout!$G$5*'Unit Economics'!$C$29</f>
-        <v>2708563.0482</v>
+        <v>3024292.2165</v>
       </c>
       <c r="H6" s="2"/>
     </row>
@@ -7498,7 +7495,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="37" t="n">
@@ -7525,28 +7522,28 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="38" t="n">
         <f aca="false">SUM(C6:C10)</f>
-        <v>1079030.12496</v>
+        <v>1138817.12496</v>
       </c>
       <c r="D11" s="38" t="n">
         <f aca="false">SUM(D6:D10)</f>
-        <v>3441086.083104</v>
+        <v>3616859.863104</v>
       </c>
       <c r="E11" s="38" t="n">
         <f aca="false">SUM(E6:E10)</f>
-        <v>5871878.75716656</v>
+        <v>6149948.09416656</v>
       </c>
       <c r="F11" s="38" t="n">
         <f aca="false">SUM(F6:F10)</f>
-        <v>7397026.37408678</v>
+        <v>7717086.51266678</v>
       </c>
       <c r="G11" s="38" t="n">
         <f aca="false">SUM(G6:G10)</f>
-        <v>8007507.78225408</v>
+        <v>8323236.95055408</v>
       </c>
       <c r="H11" s="2"/>
     </row>
@@ -7562,7 +7559,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B13" s="16"/>
       <c r="C13" s="16"/>
@@ -7574,88 +7571,88 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="9" t="n">
         <f aca="false">Headcount!C20</f>
-        <v>4921875</v>
+        <v>196875</v>
       </c>
       <c r="D14" s="9" t="n">
         <f aca="false">Headcount!D20</f>
-        <v>10048937.5</v>
+        <v>405562.5</v>
       </c>
       <c r="E14" s="9" t="n">
         <f aca="false">Headcount!E20</f>
-        <v>16384274.375</v>
+        <v>696215.625</v>
       </c>
       <c r="F14" s="9" t="n">
         <f aca="false">Headcount!F20</f>
-        <v>19409563.3375</v>
+        <v>860522.5125</v>
       </c>
       <c r="G14" s="9" t="n">
         <f aca="false">Headcount!G20</f>
-        <v>19696404.175</v>
+        <v>837097.1774375</v>
       </c>
       <c r="H14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="9" t="n">
         <f aca="false">Headcount!C21</f>
-        <v>6093750</v>
+        <v>182812.5</v>
       </c>
       <c r="D15" s="9" t="n">
         <f aca="false">Headcount!D21</f>
-        <v>12427593.75</v>
+        <v>376593.75</v>
       </c>
       <c r="E15" s="9" t="n">
         <f aca="false">Headcount!E21</f>
-        <v>20299658.4375</v>
+        <v>646485.9375</v>
       </c>
       <c r="F15" s="9" t="n">
         <f aca="false">Headcount!F21</f>
-        <v>24060482.63125</v>
+        <v>799056.61875</v>
       </c>
       <c r="G15" s="9" t="n">
         <f aca="false">Headcount!G21</f>
-        <v>24370782.9515313</v>
+        <v>777304.52190625</v>
       </c>
       <c r="H15" s="2"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="37" t="n">
         <f aca="false">(Rollout!$C$5*'Unit Economics'!$C$27)*Assumptions!$C$75</f>
-        <v>54186.3</v>
+        <v>0</v>
       </c>
       <c r="D16" s="37" t="n">
         <f aca="false">(Rollout!$C$5*'Unit Economics'!$D$27+Rollout!$D$5*'Unit Economics'!$C$27)*Assumptions!$C$75</f>
-        <v>722094.156</v>
+        <v>0</v>
       </c>
       <c r="E16" s="37" t="n">
         <f aca="false">(Rollout!$C$5*'Unit Economics'!$E$27+Rollout!$D$5*'Unit Economics'!$D$27+Rollout!$E$5*'Unit Economics'!$C$27)*Assumptions!$C$75</f>
-        <v>2105376.4053</v>
+        <v>0</v>
       </c>
       <c r="F16" s="37" t="n">
         <f aca="false">(Rollout!$C$5*'Unit Economics'!$F$27+Rollout!$D$5*'Unit Economics'!$E$27+Rollout!$E$5*'Unit Economics'!$D$27+Rollout!$F$5*'Unit Economics'!$C$27)*Assumptions!$C$75</f>
-        <v>3959188.281216</v>
+        <v>0</v>
       </c>
       <c r="G16" s="37" t="n">
         <f aca="false">(Rollout!$C$5*'Unit Economics'!$G$27+Rollout!$D$5*'Unit Economics'!$F$27+Rollout!$E$5*'Unit Economics'!$E$27+Rollout!$F$5*'Unit Economics'!$D$27+Rollout!$G$5*'Unit Economics'!$C$27)*Assumptions!$C$75</f>
-        <v>5575476.28806</v>
+        <v>0</v>
       </c>
       <c r="H16" s="2"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="9" t="n">
@@ -7682,7 +7679,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="9" t="n">
@@ -7709,7 +7706,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="37" t="n">
@@ -7790,7 +7787,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="11" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="9" t="n">
@@ -7817,7 +7814,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" s="9" t="n">
@@ -7844,7 +7841,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" s="9" t="n">
@@ -7871,7 +7868,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" s="37" t="n">
@@ -7898,55 +7895,55 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" s="37" t="n">
         <f aca="false">Headcount!C13*Assumptions!$C$99</f>
-        <v>642000</v>
+        <v>135000</v>
       </c>
       <c r="D26" s="37" t="n">
         <f aca="false">Headcount!D13*Assumptions!$C$99</f>
-        <v>1233000</v>
+        <v>234000</v>
       </c>
       <c r="E26" s="37" t="n">
         <f aca="false">Headcount!E13*Assumptions!$C$99</f>
-        <v>1704000</v>
+        <v>321000</v>
       </c>
       <c r="F26" s="37" t="n">
         <f aca="false">Headcount!F13*Assumptions!$C$99</f>
-        <v>1662000</v>
+        <v>309000</v>
       </c>
       <c r="G26" s="37" t="n">
         <f aca="false">Headcount!G13*Assumptions!$C$99</f>
-        <v>1662000</v>
+        <v>318000</v>
       </c>
       <c r="H26" s="2"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" s="38" t="n">
         <f aca="false">SUM(C14:C26)</f>
-        <v>19533435.8</v>
+        <v>8336312</v>
       </c>
       <c r="D27" s="38" t="n">
         <f aca="false">SUM(D14:D26)</f>
-        <v>35251246.196</v>
+        <v>11835777.04</v>
       </c>
       <c r="E27" s="38" t="n">
         <f aca="false">SUM(E14:E26)</f>
-        <v>53651300.2873</v>
+        <v>14821692.632</v>
       </c>
       <c r="F27" s="38" t="n">
         <f aca="false">SUM(F14:F26)</f>
-        <v>60382503.313656</v>
+        <v>13259848.19494</v>
       </c>
       <c r="G27" s="38" t="n">
         <f aca="false">SUM(G14:G26)</f>
-        <v>63505731.7231888</v>
+        <v>14133470.0079413</v>
       </c>
       <c r="H27" s="2"/>
     </row>
@@ -7977,7 +7974,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -7989,7 +7986,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -8033,7 +8030,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="28" t="n">
@@ -8060,55 +8057,55 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="9" t="n">
         <f aca="false">Costs!C11</f>
-        <v>1079030.12496</v>
+        <v>1138817.12496</v>
       </c>
       <c r="D6" s="9" t="n">
         <f aca="false">Costs!D11</f>
-        <v>3441086.083104</v>
+        <v>3616859.863104</v>
       </c>
       <c r="E6" s="9" t="n">
         <f aca="false">Costs!E11</f>
-        <v>5871878.75716656</v>
+        <v>6149948.09416656</v>
       </c>
       <c r="F6" s="9" t="n">
         <f aca="false">Costs!F11</f>
-        <v>7397026.37408678</v>
+        <v>7717086.51266678</v>
       </c>
       <c r="G6" s="9" t="n">
         <f aca="false">Costs!G11</f>
-        <v>8007507.78225408</v>
+        <v>8323236.95055408</v>
       </c>
       <c r="H6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="38" t="n">
         <f aca="false">C5-C6</f>
-        <v>819163.11504</v>
+        <v>759376.11504</v>
       </c>
       <c r="D7" s="38" t="n">
         <f aca="false">D5-D6</f>
-        <v>13721644.852896</v>
+        <v>13545871.072896</v>
       </c>
       <c r="E7" s="38" t="n">
         <f aca="false">E5-E6</f>
-        <v>43995470.3364734</v>
+        <v>43717400.9994734</v>
       </c>
       <c r="F7" s="38" t="n">
         <f aca="false">F5-F6</f>
-        <v>82981182.0693692</v>
+        <v>82661121.9307892</v>
       </c>
       <c r="G7" s="38" t="n">
         <f aca="false">G5-G6</f>
-        <v>117546667.707626</v>
+        <v>117230938.539326</v>
       </c>
       <c r="H7" s="2"/>
     </row>
@@ -8119,23 +8116,23 @@
       <c r="B8" s="2"/>
       <c r="C8" s="34" t="n">
         <f aca="false">IF(C5=0,0,C7/C5)</f>
-        <v>0.431548852760639</v>
+        <v>0.400052059525826</v>
       </c>
       <c r="D8" s="34" t="n">
         <f aca="false">IF(D5=0,0,D7/D5)</f>
-        <v>0.799502416256723</v>
+        <v>0.789260818887664</v>
       </c>
       <c r="E8" s="34" t="n">
         <f aca="false">IF(E5=0,0,E7/E5)</f>
-        <v>0.88225003205724</v>
+        <v>0.876673851609431</v>
       </c>
       <c r="F8" s="34" t="n">
         <f aca="false">IF(F5=0,0,F7/F5)</f>
-        <v>0.918154757640337</v>
+        <v>0.914613415716302</v>
       </c>
       <c r="G8" s="34" t="n">
         <f aca="false">IF(G5=0,0,G7/G5)</f>
-        <v>0.936222688325491</v>
+        <v>0.933708003592243</v>
       </c>
       <c r="H8" s="2"/>
     </row>
@@ -8151,55 +8148,55 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="9" t="n">
         <f aca="false">Costs!C14</f>
-        <v>4921875</v>
+        <v>196875</v>
       </c>
       <c r="D10" s="9" t="n">
         <f aca="false">Costs!D14</f>
-        <v>10048937.5</v>
+        <v>405562.5</v>
       </c>
       <c r="E10" s="9" t="n">
         <f aca="false">Costs!E14</f>
-        <v>16384274.375</v>
+        <v>696215.625</v>
       </c>
       <c r="F10" s="9" t="n">
         <f aca="false">Costs!F14</f>
-        <v>19409563.3375</v>
+        <v>860522.5125</v>
       </c>
       <c r="G10" s="9" t="n">
         <f aca="false">Costs!G14</f>
-        <v>19696404.175</v>
+        <v>837097.1774375</v>
       </c>
       <c r="H10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="9" t="n">
         <f aca="false">Costs!C15+Costs!C16+Costs!C17+Costs!C18+Costs!C19+Costs!C20+Costs!C21</f>
-        <v>12878310.8</v>
+        <v>6913187</v>
       </c>
       <c r="D11" s="9" t="n">
         <f aca="false">Costs!D15+Costs!D16+Costs!D17+Costs!D18+Costs!D19+Costs!D20+Costs!D21</f>
-        <v>22004683.696</v>
+        <v>9231589.54</v>
       </c>
       <c r="E11" s="9" t="n">
         <f aca="false">Costs!E15+Costs!E16+Costs!E17+Costs!E18+Costs!E19+Costs!E20+Costs!E21</f>
-        <v>32503247.1623</v>
+        <v>10744698.257</v>
       </c>
       <c r="F11" s="9" t="n">
         <f aca="false">Costs!F15+Costs!F16+Costs!F17+Costs!F18+Costs!F19+Costs!F20+Costs!F21</f>
-        <v>34953313.038656</v>
+        <v>7732698.74494</v>
       </c>
       <c r="G11" s="9" t="n">
         <f aca="false">Costs!G15+Costs!G16+Costs!G17+Costs!G18+Costs!G19+Costs!G20+Costs!G21</f>
-        <v>36545517.7278138</v>
+        <v>7376563.01012875</v>
       </c>
       <c r="H11" s="2"/>
     </row>
@@ -8232,55 +8229,55 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="9" t="n">
         <f aca="false">Costs!C23+Costs!C24+Costs!C25+Costs!C26</f>
-        <v>1255125</v>
+        <v>748125</v>
       </c>
       <c r="D13" s="9" t="n">
         <f aca="false">Costs!D23+Costs!D24+Costs!D25+Costs!D26</f>
-        <v>2322125</v>
+        <v>1323125</v>
       </c>
       <c r="E13" s="9" t="n">
         <f aca="false">Costs!E23+Costs!E24+Costs!E25+Costs!E26</f>
-        <v>3298410.625</v>
+        <v>1915410.625</v>
       </c>
       <c r="F13" s="9" t="n">
         <f aca="false">Costs!F23+Costs!F24+Costs!F25+Costs!F26</f>
-        <v>3813684.30625</v>
+        <v>2460684.30625</v>
       </c>
       <c r="G13" s="9" t="n">
         <f aca="false">Costs!G23+Costs!G24+Costs!G25+Costs!G26</f>
-        <v>4274177.0438125</v>
+        <v>2930177.0438125</v>
       </c>
       <c r="H13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="40" t="n">
         <f aca="false">SUM(C10:C13)</f>
-        <v>19533435.8</v>
+        <v>8336312</v>
       </c>
       <c r="D14" s="40" t="n">
         <f aca="false">SUM(D10:D13)</f>
-        <v>35251246.196</v>
+        <v>11835777.04</v>
       </c>
       <c r="E14" s="40" t="n">
         <f aca="false">SUM(E10:E13)</f>
-        <v>53651300.2873</v>
+        <v>14821692.632</v>
       </c>
       <c r="F14" s="40" t="n">
         <f aca="false">SUM(F10:F13)</f>
-        <v>60382503.313656</v>
+        <v>13259848.19494</v>
       </c>
       <c r="G14" s="40" t="n">
         <f aca="false">SUM(G10:G13)</f>
-        <v>63505731.7231888</v>
+        <v>14133470.0079413</v>
       </c>
       <c r="H14" s="2"/>
     </row>
@@ -8296,28 +8293,28 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="28" t="n">
         <f aca="false">C7-C14</f>
-        <v>-18714272.68496</v>
+        <v>-7576935.88496</v>
       </c>
       <c r="D16" s="28" t="n">
         <f aca="false">D7-D14</f>
-        <v>-21529601.343104</v>
+        <v>1710094.032896</v>
       </c>
       <c r="E16" s="28" t="n">
         <f aca="false">E7-E14</f>
-        <v>-9655829.95082656</v>
+        <v>28895708.3674734</v>
       </c>
       <c r="F16" s="28" t="n">
         <f aca="false">F7-F14</f>
-        <v>22598678.7557132</v>
+        <v>69401273.7358492</v>
       </c>
       <c r="G16" s="28" t="n">
         <f aca="false">G7-G14</f>
-        <v>54040935.9844372</v>
+        <v>103097468.531385</v>
       </c>
       <c r="H16" s="2"/>
     </row>
@@ -8328,42 +8325,42 @@
       <c r="B17" s="2"/>
       <c r="C17" s="34" t="n">
         <f aca="false">IF(C5=0,0,C16/C5)</f>
-        <v>-9.85899237790985</v>
+        <v>-3.99165676354426</v>
       </c>
       <c r="D17" s="34" t="n">
         <f aca="false">IF(D5=0,0,D16/D5)</f>
-        <v>-1.25443913462188</v>
+        <v>0.0996399721741811</v>
       </c>
       <c r="E17" s="34" t="n">
         <f aca="false">IF(E5=0,0,E16/E5)</f>
-        <v>-0.193630303722282</v>
+        <v>0.579451462583535</v>
       </c>
       <c r="F17" s="34" t="n">
         <f aca="false">IF(F5=0,0,F16/F5)</f>
-        <v>0.250045659732808</v>
+        <v>0.76789831233786</v>
       </c>
       <c r="G17" s="34" t="n">
         <f aca="false">IF(G5=0,0,G16/G5)</f>
-        <v>0.430419265417366</v>
+        <v>0.82113930603363</v>
       </c>
       <c r="H17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="37" t="n">
         <f aca="false">Headcount!C14*Assumptions!$C$100</f>
-        <v>535000</v>
+        <v>112500</v>
       </c>
       <c r="D18" s="37" t="n">
         <f aca="false">Headcount!D14*Assumptions!$C$100</f>
-        <v>492500</v>
+        <v>82500</v>
       </c>
       <c r="E18" s="37" t="n">
         <f aca="false">Headcount!E14*Assumptions!$C$100</f>
-        <v>392500</v>
+        <v>72500</v>
       </c>
       <c r="F18" s="37" t="n">
         <f aca="false">Headcount!F14*Assumptions!$C$100</f>
@@ -8371,67 +8368,67 @@
       </c>
       <c r="G18" s="37" t="n">
         <f aca="false">Headcount!G14*Assumptions!$C$100</f>
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="H18" s="2"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="37" t="n">
         <f aca="false">(C18)/Assumptions!$C$101</f>
-        <v>178333.333333333</v>
+        <v>37500</v>
       </c>
       <c r="D19" s="37" t="n">
         <f aca="false">(C18+D18)/Assumptions!$C$101</f>
-        <v>342500</v>
+        <v>65000</v>
       </c>
       <c r="E19" s="37" t="n">
         <f aca="false">(C18+D18+E18)/Assumptions!$C$101</f>
-        <v>473333.333333333</v>
+        <v>89166.6666666667</v>
       </c>
       <c r="F19" s="37" t="n">
         <f aca="false">(D18+E18+F18)/Assumptions!$C$101</f>
-        <v>295000</v>
+        <v>51666.6666666667</v>
       </c>
       <c r="G19" s="37" t="n">
         <f aca="false">(E18+F18+G18)/Assumptions!$C$101</f>
-        <v>130833.333333333</v>
+        <v>26666.6666666667</v>
       </c>
       <c r="H19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="28" t="n">
         <f aca="false">C16-C19</f>
-        <v>-18892606.0182933</v>
+        <v>-7614435.88496</v>
       </c>
       <c r="D20" s="28" t="n">
         <f aca="false">D16-D19</f>
-        <v>-21872101.343104</v>
+        <v>1645094.032896</v>
       </c>
       <c r="E20" s="28" t="n">
         <f aca="false">E16-E19</f>
-        <v>-10129163.2841599</v>
+        <v>28806541.7008068</v>
       </c>
       <c r="F20" s="28" t="n">
         <f aca="false">F16-F19</f>
-        <v>22303678.7557132</v>
+        <v>69349607.0691826</v>
       </c>
       <c r="G20" s="28" t="n">
         <f aca="false">G16-G19</f>
-        <v>53910102.6511038</v>
+        <v>103070801.864718</v>
       </c>
       <c r="H20" s="2"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" s="37" t="n">
@@ -8440,25 +8437,25 @@
       </c>
       <c r="D21" s="37" t="n">
         <f aca="false">C23</f>
-        <v>18892606.0182933</v>
+        <v>7614435.88496</v>
       </c>
       <c r="E21" s="37" t="n">
         <f aca="false">D23</f>
-        <v>40764707.3613973</v>
+        <v>5969341.852064</v>
       </c>
       <c r="F21" s="37" t="n">
         <f aca="false">E23</f>
-        <v>50893870.6455572</v>
+        <v>0</v>
       </c>
       <c r="G21" s="37" t="n">
         <f aca="false">F23</f>
-        <v>28590191.889844</v>
+        <v>0</v>
       </c>
       <c r="H21" s="2"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="11" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="37" t="n">
@@ -8471,38 +8468,38 @@
       </c>
       <c r="E22" s="37" t="n">
         <f aca="false">MAX(0,E20-E21)</f>
-        <v>0</v>
+        <v>22837199.8487428</v>
       </c>
       <c r="F22" s="37" t="n">
         <f aca="false">MAX(0,F20-F21)</f>
-        <v>0</v>
+        <v>69349607.0691826</v>
       </c>
       <c r="G22" s="37" t="n">
         <f aca="false">MAX(0,G20-G21)</f>
-        <v>25319910.7612598</v>
+        <v>103070801.864718</v>
       </c>
       <c r="H22" s="2"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" s="37" t="n">
         <f aca="false">MAX(0,C21-MAX(0,C20))+MAX(0,-C20)</f>
-        <v>18892606.0182933</v>
+        <v>7614435.88496</v>
       </c>
       <c r="D23" s="37" t="n">
         <f aca="false">MAX(0,D21-MAX(0,D20))+MAX(0,-D20)</f>
-        <v>40764707.3613973</v>
+        <v>5969341.852064</v>
       </c>
       <c r="E23" s="37" t="n">
         <f aca="false">MAX(0,E21-MAX(0,E20))+MAX(0,-E20)</f>
-        <v>50893870.6455572</v>
+        <v>0</v>
       </c>
       <c r="F23" s="37" t="n">
         <f aca="false">MAX(0,F21-MAX(0,F20))+MAX(0,-F20)</f>
-        <v>28590191.889844</v>
+        <v>0</v>
       </c>
       <c r="G23" s="37" t="n">
         <f aca="false">MAX(0,G21-MAX(0,G20))+MAX(0,-G20)</f>
@@ -8512,7 +8509,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" s="37" t="n">
@@ -8525,42 +8522,42 @@
       </c>
       <c r="E24" s="37" t="n">
         <f aca="false">E22*Assumptions!$C$104</f>
-        <v>0</v>
+        <v>5709299.96218569</v>
       </c>
       <c r="F24" s="37" t="n">
         <f aca="false">F22*Assumptions!$C$104</f>
-        <v>0</v>
+        <v>17337401.7672956</v>
       </c>
       <c r="G24" s="37" t="n">
         <f aca="false">G22*Assumptions!$C$104</f>
-        <v>6329977.69031496</v>
+        <v>25767700.4661795</v>
       </c>
       <c r="H24" s="2"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" s="38" t="n">
         <f aca="false">C20-C24</f>
-        <v>-18892606.0182933</v>
+        <v>-7614435.88496</v>
       </c>
       <c r="D25" s="38" t="n">
         <f aca="false">D20-D24</f>
-        <v>-21872101.343104</v>
+        <v>1645094.032896</v>
       </c>
       <c r="E25" s="38" t="n">
         <f aca="false">E20-E24</f>
-        <v>-10129163.2841599</v>
+        <v>23097241.7386211</v>
       </c>
       <c r="F25" s="38" t="n">
         <f aca="false">F20-F24</f>
-        <v>22303678.7557132</v>
+        <v>52012205.3018869</v>
       </c>
       <c r="G25" s="38" t="n">
         <f aca="false">G20-G24</f>
-        <v>47580124.9607889</v>
+        <v>77303101.3985385</v>
       </c>
       <c r="H25" s="2"/>
     </row>
@@ -8591,7 +8588,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -8603,7 +8600,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -8647,34 +8644,34 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="9" t="n">
         <f aca="false">'P&amp;L'!C16</f>
-        <v>-18714272.68496</v>
+        <v>-7576935.88496</v>
       </c>
       <c r="D5" s="9" t="n">
         <f aca="false">'P&amp;L'!D16</f>
-        <v>-21529601.343104</v>
+        <v>1710094.032896</v>
       </c>
       <c r="E5" s="9" t="n">
         <f aca="false">'P&amp;L'!E16</f>
-        <v>-9655829.95082656</v>
+        <v>28895708.3674734</v>
       </c>
       <c r="F5" s="9" t="n">
         <f aca="false">'P&amp;L'!F16</f>
-        <v>22598678.7557132</v>
+        <v>69401273.7358492</v>
       </c>
       <c r="G5" s="9" t="n">
         <f aca="false">'P&amp;L'!G16</f>
-        <v>54040935.9844372</v>
+        <v>103097468.531385</v>
       </c>
       <c r="H5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="9" t="n">
@@ -8687,34 +8684,34 @@
       </c>
       <c r="E6" s="9" t="n">
         <f aca="false">-'P&amp;L'!E24</f>
-        <v>-0</v>
+        <v>-5709299.96218569</v>
       </c>
       <c r="F6" s="9" t="n">
         <f aca="false">-'P&amp;L'!F24</f>
-        <v>-0</v>
+        <v>-17337401.7672956</v>
       </c>
       <c r="G6" s="9" t="n">
         <f aca="false">-'P&amp;L'!G24</f>
-        <v>-6329977.69031496</v>
+        <v>-25767700.4661795</v>
       </c>
       <c r="H6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="9" t="n">
         <f aca="false">-'P&amp;L'!C18</f>
-        <v>-535000</v>
+        <v>-112500</v>
       </c>
       <c r="D7" s="9" t="n">
         <f aca="false">-'P&amp;L'!D18</f>
-        <v>-492500</v>
+        <v>-82500</v>
       </c>
       <c r="E7" s="9" t="n">
         <f aca="false">-'P&amp;L'!E18</f>
-        <v>-392500</v>
+        <v>-72500</v>
       </c>
       <c r="F7" s="9" t="n">
         <f aca="false">-'P&amp;L'!F18</f>
@@ -8722,13 +8719,13 @@
       </c>
       <c r="G7" s="9" t="n">
         <f aca="false">-'P&amp;L'!G18</f>
-        <v>-0</v>
+        <v>-7500</v>
       </c>
       <c r="H7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="37" t="n">
@@ -8755,28 +8752,28 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="38" t="n">
         <f aca="false">SUM(C5:C8)</f>
-        <v>-19306218.48216</v>
+        <v>-7746381.68216</v>
       </c>
       <c r="D9" s="38" t="n">
         <f aca="false">SUM(D5:D8)</f>
-        <v>-22480037.473984</v>
+        <v>1169657.902016</v>
       </c>
       <c r="E9" s="38" t="n">
         <f aca="false">SUM(E5:E8)</f>
-        <v>-11029468.4955558</v>
+        <v>22132769.8605585</v>
       </c>
       <c r="F9" s="38" t="n">
         <f aca="false">SUM(F5:F8)</f>
-        <v>21383352.9752188</v>
+        <v>50848546.1880591</v>
       </c>
       <c r="G9" s="38" t="n">
         <f aca="false">SUM(G5:G8)</f>
-        <v>46655679.2827295</v>
+        <v>76266989.0538125</v>
       </c>
       <c r="H9" s="2"/>
     </row>
@@ -8787,11 +8784,11 @@
       <c r="B10" s="2"/>
       <c r="C10" s="9" t="n">
         <f aca="false">Assumptions!C$109</f>
-        <v>25000000</v>
+        <v>10000000</v>
       </c>
       <c r="D10" s="9" t="n">
         <f aca="false">Assumptions!D$109</f>
-        <v>35000000</v>
+        <v>0</v>
       </c>
       <c r="E10" s="9" t="n">
         <f aca="false">Assumptions!E$109</f>
@@ -8809,34 +8806,34 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="37" t="n">
         <f aca="false">C9+C10</f>
-        <v>5693781.51784</v>
+        <v>2253618.31784</v>
       </c>
       <c r="D11" s="37" t="n">
         <f aca="false">D9+D10</f>
-        <v>12519962.526016</v>
+        <v>1169657.902016</v>
       </c>
       <c r="E11" s="37" t="n">
         <f aca="false">E9+E10</f>
-        <v>-11029468.4955558</v>
+        <v>22132769.8605585</v>
       </c>
       <c r="F11" s="37" t="n">
         <f aca="false">F9+F10</f>
-        <v>21383352.9752188</v>
+        <v>50848546.1880591</v>
       </c>
       <c r="G11" s="37" t="n">
         <f aca="false">G9+G10</f>
-        <v>46655679.2827295</v>
+        <v>76266989.0538125</v>
       </c>
       <c r="H11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="37" t="n">
@@ -8845,52 +8842,52 @@
       </c>
       <c r="D12" s="37" t="n">
         <f aca="false">C13</f>
-        <v>5943781.51784</v>
+        <v>2503618.31784</v>
       </c>
       <c r="E12" s="37" t="n">
         <f aca="false">D13</f>
-        <v>18463744.043856</v>
+        <v>3673276.219856</v>
       </c>
       <c r="F12" s="37" t="n">
         <f aca="false">E13</f>
-        <v>7434275.54830025</v>
+        <v>25806046.0804145</v>
       </c>
       <c r="G12" s="37" t="n">
         <f aca="false">F13</f>
-        <v>28817628.523519</v>
+        <v>76654592.2684737</v>
       </c>
       <c r="H12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="38" t="n">
         <f aca="false">C12+C11</f>
-        <v>5943781.51784</v>
+        <v>2503618.31784</v>
       </c>
       <c r="D13" s="38" t="n">
         <f aca="false">D12+D11</f>
-        <v>18463744.043856</v>
+        <v>3673276.219856</v>
       </c>
       <c r="E13" s="38" t="n">
         <f aca="false">E12+E11</f>
-        <v>7434275.54830025</v>
+        <v>25806046.0804145</v>
       </c>
       <c r="F13" s="38" t="n">
         <f aca="false">F12+F11</f>
-        <v>28817628.523519</v>
+        <v>76654592.2684737</v>
       </c>
       <c r="G13" s="38" t="n">
         <f aca="false">G12+G11</f>
-        <v>75473307.8062485</v>
+        <v>152921581.322286</v>
       </c>
       <c r="H13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="41" t="n">
@@ -8927,12 +8924,12 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="28" t="n">
         <f aca="false">MIN(C13:G13)</f>
-        <v>5943781.51784</v>
+        <v>2503618.31784</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
@@ -8942,19 +8939,19 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="28" t="n">
         <f aca="false">-MIN(0,C9,C9+D9,C9+D9+E9,C9+D9+E9+F9,C9+D9+E9+F9+G9)</f>
-        <v>52815724.4516998</v>
+        <v>7746381.68216</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
       <c r="H17" s="17" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
   </sheetData>

--- a/docs/finance/TownCore-LRP.xlsx
+++ b/docs/finance/TownCore-LRP.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="358">
   <si>
     <t xml:space="preserve">TownCore long-range plan, FY2027-FY2031</t>
   </si>
@@ -172,19 +172,43 @@
     <t xml:space="preserve">Scales per-town direct costs and launch costs.</t>
   </si>
   <si>
-    <t xml:space="preserve">Town rollout (by fiscal year)</t>
+    <t xml:space="preserve">Launch capacity: how many towns can launch, and how fast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US towns with more than 2,000 people</t>
+  </si>
+  <si>
+    <t xml:space="preserve">towns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owner plan (2026-10-17): every US town over 2,000 people. Census Vintage 2025 (sub-est2025.csv): 7,683 incorporated places (SUMLEV 162; Florida 295) plus 750 New England towns (active county subdivisions with no place of their own).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share that pass readiness (Rule 7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owner, 2026-10-17: every town in America can make 3 real items a day; Rule 7 is the target we build sources toward. Today Boca makes about 0.8 a day and Delray 0.53, so the source work continues. Set lower to see the plan if some towns stay short.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share allowed by the naming rule</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owner, 2026-10-17: naming never stops a launch. 22 patterns; a neighbor's pattern is used only when nothing else is left.</t>
   </si>
   <si>
     <t xml:space="preserve">Fiscal year</t>
   </si>
   <si>
-    <t xml:space="preserve">New towns launched (base case)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">towns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Management target; CLAUDE.md goal is thousands of towns, one command per launch. Scaled by the launch multiplier.</t>
+    <t xml:space="preserve">Launches the team can do in a year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">About 250 a month: the launcher is automated, each launch needs ~45 minutes of people (approval, Facebook page, Google Publisher Center). A pacing choice too: launching hundreds of AI-written sites at once invites Google's scaled-content review. Scaled by the launch multiplier.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Launches per launch operator per year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~45 minutes of hands-on work per launch, plus fixes and follow-up. Estimate.</t>
   </si>
   <si>
     <t xml:space="preserve">Town size mix and size-driven inputs (CLAUDE.md §5 tiers)</t>
@@ -205,13 +229,13 @@
     <t xml:space="preserve">Share of launches</t>
   </si>
   <si>
-    <t xml:space="preserve">Ranked list (CLAUDE.md §10a) skews to smaller towns; population floor 5,000.</t>
+    <t xml:space="preserve">Census 2025, towns over 2,000: 7,067 under 30,000 (small, incl. the 750 New England towns), 1,023 of 30,000-100,000 (mid), 343 of 100,000+ (large); tiers from packages/config/src/launch.ts.</t>
   </si>
   <si>
     <t xml:space="preserve">Households per town</t>
   </si>
   <si>
-    <t xml:space="preserve">Estimate from Census place sizes; Boca Raton (large) is roughly 45,000 households.</t>
+    <t xml:space="preserve">Mean town population by tier (8,397 / 53,365 / 185,762, Census 2025, each town capped at 300,000) / ~2.5 people a household. Revenue scales with households, so the mean is used.</t>
   </si>
   <si>
     <t xml:space="preserve">Directory listings per town</t>
@@ -406,7 +430,7 @@
     <t xml:space="preserve">$/story</t>
   </si>
   <si>
-    <t xml:space="preserve">Estimate for writer + separate fact-check calls; verify against current Anthropic pricing (CLAUDE.md §8). Scaled by unit cost multiplier.</t>
+    <t xml:space="preserve">Writer, separate fact-check and an AI review pass (owner: article review becomes an AI agent). Measured ~$0.10 for writer + fact-check on repo pricing; verify against current Anthropic pricing (CLAUDE.md §8). Scaled by unit cost multiplier.</t>
   </si>
   <si>
     <t xml:space="preserve">AI overhead per town per day</t>
@@ -505,19 +529,19 @@
     <t xml:space="preserve">Sales commission on direct-sold revenue</t>
   </si>
   <si>
-    <t xml:space="preserve">Paid on banners, newsletter and category sponsorships. Estimate.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Towns per editorial reviewer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reviewers approve Tier 3 items and samples (§7). Estimate.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Towns per local account executive</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clustered towns share sales effort (§10a). Estimate.</t>
+    <t xml:space="preserve">Owner: advertisers sign up and pay on the site; no commissioned sales force.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Towns per editorial standards editor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owner, 2026-10-17: article review becomes an AI agent once we trust it. A small team audits the agent, handles corrections and reader reports. Until the agent ships, Tier 3 still needs a person (Rule 5).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Towns per advertiser partnerships manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owner, 2026-10-17: sales are self-serve on the site. A small team handles regional and multi-town advertisers.</t>
   </si>
   <si>
     <t xml:space="preserve">Towns per support and success rep</t>
@@ -532,10 +556,10 @@
     <t xml:space="preserve">Engineering</t>
   </si>
   <si>
-    <t xml:space="preserve">Editorial reviewer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Account executive (base)</t>
+    <t xml:space="preserve">Editorial standards and launch operations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Advertiser partnerships</t>
   </si>
   <si>
     <t xml:space="preserve">Support and success</t>
@@ -622,7 +646,7 @@
     <t xml:space="preserve">Equity raised</t>
   </si>
   <si>
-    <t xml:space="preserve">Plan: seed in FY2027, Series A in FY2028, Series B in FY2030. Adjust to keep cash above zero.</t>
+    <t xml:space="preserve">Plan: $10M in FY2027, the ~$7.7M the every-town plan needs plus a buffer. Adjust to keep cash above zero.</t>
   </si>
   <si>
     <t xml:space="preserve">Town rollout</t>
@@ -634,6 +658,9 @@
     <t xml:space="preserve">New towns launched</t>
   </si>
   <si>
+    <t xml:space="preserve">The smaller of the team's capacity and the towns left in the pool.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cumulative towns launched</t>
   </si>
   <si>
@@ -646,6 +673,15 @@
     <t xml:space="preserve">Used for people ratios.</t>
   </si>
   <si>
+    <t xml:space="preserve">Launchable towns (pool)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Places of 5,000+ x readiness pass rate x naming rule (x launch multiplier).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pool left at year end</t>
+  </si>
+  <si>
     <t xml:space="preserve">Unit economics: one average launched town, by age</t>
   </si>
   <si>
@@ -763,10 +799,10 @@
     <t xml:space="preserve">Town-level people and acquisition costs ($)</t>
   </si>
   <si>
-    <t xml:space="preserve">Editorial review (share of a reviewer)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Local sales (share of an AE) + commission</t>
+    <t xml:space="preserve">Editorial standards (share)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Advertiser partnerships (share) + commission</t>
   </si>
   <si>
     <t xml:space="preserve">Support and success (share)</t>
@@ -832,10 +868,10 @@
     <t xml:space="preserve">Heads (year end)</t>
   </si>
   <si>
-    <t xml:space="preserve">Editorial reviewers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Account executives</t>
+    <t xml:space="preserve">Editorial standards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Launch operations</t>
   </si>
   <si>
     <t xml:space="preserve">Total heads</t>
@@ -871,16 +907,19 @@
     <t xml:space="preserve">Operating expenses</t>
   </si>
   <si>
-    <t xml:space="preserve">Editorial review (people)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sales (people)</t>
+    <t xml:space="preserve">Editorial standards (people)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Advertiser partnerships (people)</t>
   </si>
   <si>
     <t xml:space="preserve">Sales commission</t>
   </si>
   <si>
     <t xml:space="preserve">Support and success (people)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Launch operations (people)</t>
   </si>
   <si>
     <t xml:space="preserve">Launch marketing and launch AI</t>
@@ -1323,7 +1362,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1331,11 +1370,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1352,10 +1395,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="169" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1760,23 +1799,23 @@
       <c r="B7" s="2"/>
       <c r="C7" s="8" t="n">
         <f aca="false">Rollout!C7</f>
-        <v>20</v>
+        <v>3000</v>
       </c>
       <c r="D7" s="8" t="n">
         <f aca="false">Rollout!D7</f>
-        <v>99.4</v>
+        <v>5910</v>
       </c>
       <c r="E7" s="8" t="n">
         <f aca="false">Rollout!E7</f>
-        <v>296.6</v>
+        <v>8193</v>
       </c>
       <c r="F7" s="8" t="n">
         <f aca="false">Rollout!F7</f>
-        <v>688.8</v>
+        <v>8030.01</v>
       </c>
       <c r="G7" s="8" t="n">
         <f aca="false">Rollout!G7</f>
-        <v>1371.8</v>
+        <v>7921.35</v>
       </c>
       <c r="H7" s="2"/>
     </row>
@@ -1787,23 +1826,23 @@
       <c r="B8" s="2"/>
       <c r="C8" s="8" t="n">
         <f aca="false">KPIs!C8</f>
-        <v>4200</v>
+        <v>364140</v>
       </c>
       <c r="D8" s="8" t="n">
         <f aca="false">KPIs!D8</f>
-        <v>27664</v>
+        <v>1306048.8</v>
       </c>
       <c r="E8" s="8" t="n">
         <f aca="false">KPIs!E8</f>
-        <v>101416</v>
+        <v>2620958.34</v>
       </c>
       <c r="F8" s="8" t="n">
         <f aca="false">KPIs!F8</f>
-        <v>276220</v>
+        <v>3859078.0368</v>
       </c>
       <c r="G8" s="8" t="n">
         <f aca="false">KPIs!G8</f>
-        <v>624974</v>
+        <v>4752682.452</v>
       </c>
       <c r="H8" s="2"/>
     </row>
@@ -1814,23 +1853,23 @@
       <c r="B9" s="2"/>
       <c r="C9" s="9" t="n">
         <f aca="false">'P&amp;L'!C5</f>
-        <v>18028.56</v>
+        <v>1898193.24</v>
       </c>
       <c r="D9" s="9" t="n">
         <f aca="false">'P&amp;L'!D5</f>
-        <v>217104.8736</v>
+        <v>17162730.936</v>
       </c>
       <c r="E9" s="9" t="n">
         <f aca="false">'P&amp;L'!E5</f>
-        <v>1084578.1344</v>
+        <v>49867349.09364</v>
       </c>
       <c r="F9" s="9" t="n">
         <f aca="false">'P&amp;L'!F5</f>
-        <v>3547797.98496</v>
+        <v>90378208.443456</v>
       </c>
       <c r="G9" s="9" t="n">
         <f aca="false">'P&amp;L'!G5</f>
-        <v>9061606.73472</v>
+        <v>125554175.48988</v>
       </c>
       <c r="H9" s="2"/>
     </row>
@@ -1841,23 +1880,23 @@
       <c r="B10" s="2"/>
       <c r="C10" s="10" t="n">
         <f aca="false">'P&amp;L'!C8</f>
-        <v>0.558152495817747</v>
+        <v>0.400052059525826</v>
       </c>
       <c r="D10" s="10" t="n">
         <f aca="false">'P&amp;L'!D8</f>
-        <v>0.77079367597209</v>
+        <v>0.789260818887664</v>
       </c>
       <c r="E10" s="10" t="n">
         <f aca="false">'P&amp;L'!E8</f>
-        <v>0.841645038989641</v>
+        <v>0.876673851609431</v>
       </c>
       <c r="F10" s="10" t="n">
         <f aca="false">'P&amp;L'!F8</f>
-        <v>0.875179278962009</v>
+        <v>0.914613415716302</v>
       </c>
       <c r="G10" s="10" t="n">
         <f aca="false">'P&amp;L'!G8</f>
-        <v>0.89447292180238</v>
+        <v>0.933708003592243</v>
       </c>
       <c r="H10" s="2"/>
     </row>
@@ -1868,23 +1907,23 @@
       <c r="B11" s="2"/>
       <c r="C11" s="9" t="n">
         <f aca="false">'P&amp;L'!C16</f>
-        <v>-1221781.31424</v>
+        <v>-7576935.88496</v>
       </c>
       <c r="D11" s="9" t="n">
         <f aca="false">'P&amp;L'!D16</f>
-        <v>-2165908.7096064</v>
+        <v>1710094.032896</v>
       </c>
       <c r="E11" s="9" t="n">
         <f aca="false">'P&amp;L'!E16</f>
-        <v>-3533796.4665856</v>
+        <v>28895708.3674734</v>
       </c>
       <c r="F11" s="9" t="n">
         <f aca="false">'P&amp;L'!F16</f>
-        <v>-5134437.42521984</v>
+        <v>69401273.7358492</v>
       </c>
       <c r="G11" s="9" t="n">
         <f aca="false">'P&amp;L'!G16</f>
-        <v>-6049621.93095213</v>
+        <v>103097468.531385</v>
       </c>
       <c r="H11" s="2"/>
     </row>
@@ -1895,23 +1934,23 @@
       <c r="B12" s="2"/>
       <c r="C12" s="10" t="n">
         <f aca="false">'P&amp;L'!C17</f>
-        <v>-67.7692125294533</v>
+        <v>-3.99165676354426</v>
       </c>
       <c r="D12" s="10" t="n">
         <f aca="false">'P&amp;L'!D17</f>
-        <v>-9.97632468443306</v>
+        <v>0.0996399721741811</v>
       </c>
       <c r="E12" s="10" t="n">
         <f aca="false">'P&amp;L'!E17</f>
-        <v>-3.25822211835437</v>
+        <v>0.579451462583535</v>
       </c>
       <c r="F12" s="10" t="n">
         <f aca="false">'P&amp;L'!F17</f>
-        <v>-1.44721809048486</v>
+        <v>0.76789831233786</v>
       </c>
       <c r="G12" s="10" t="n">
         <f aca="false">'P&amp;L'!G17</f>
-        <v>-0.667610293412172</v>
+        <v>0.82113930603363</v>
       </c>
       <c r="H12" s="2"/>
     </row>
@@ -1922,23 +1961,23 @@
       <c r="B13" s="2"/>
       <c r="C13" s="9" t="n">
         <f aca="false">'P&amp;L'!C25</f>
-        <v>-1229281.31424</v>
+        <v>-7614435.88496</v>
       </c>
       <c r="D13" s="9" t="n">
         <f aca="false">'P&amp;L'!D25</f>
-        <v>-2179242.04293973</v>
+        <v>1645094.032896</v>
       </c>
       <c r="E13" s="9" t="n">
         <f aca="false">'P&amp;L'!E25</f>
-        <v>-3562129.79991893</v>
+        <v>23097241.7386211</v>
       </c>
       <c r="F13" s="9" t="n">
         <f aca="false">'P&amp;L'!F25</f>
-        <v>-5181104.09188651</v>
+        <v>52012205.3018869</v>
       </c>
       <c r="G13" s="9" t="n">
         <f aca="false">'P&amp;L'!G25</f>
-        <v>-6132955.26428547</v>
+        <v>77303101.3985385</v>
       </c>
       <c r="H13" s="2"/>
     </row>
@@ -1949,23 +1988,23 @@
       <c r="B14" s="2"/>
       <c r="C14" s="9" t="n">
         <f aca="false">'Cash Flow'!C13</f>
-        <v>1005177.82896</v>
+        <v>2503618.31784</v>
       </c>
       <c r="D14" s="9" t="n">
         <f aca="false">'Cash Flow'!D13</f>
-        <v>6815796.8299456</v>
+        <v>3673276.219856</v>
       </c>
       <c r="E14" s="9" t="n">
         <f aca="false">'Cash Flow'!E13</f>
-        <v>3210976.165536</v>
+        <v>25806046.0804145</v>
       </c>
       <c r="F14" s="9" t="n">
         <f aca="false">'Cash Flow'!F13</f>
-        <v>12925142.1447994</v>
+        <v>76654592.2684737</v>
       </c>
       <c r="G14" s="9" t="n">
         <f aca="false">'Cash Flow'!G13</f>
-        <v>6582605.95135443</v>
+        <v>152921581.322286</v>
       </c>
       <c r="H14" s="2"/>
     </row>
@@ -1976,23 +2015,23 @@
       <c r="B15" s="2"/>
       <c r="C15" s="9" t="n">
         <f aca="false">KPIs!C22</f>
-        <v>-613580.34690271</v>
+        <v>50953224.2039639</v>
       </c>
       <c r="D15" s="9" t="n">
         <f aca="false">KPIs!D22</f>
-        <v>294083.175893533</v>
+        <v>100693439.181809</v>
       </c>
       <c r="E15" s="9" t="n">
         <f aca="false">KPIs!E22</f>
-        <v>3244622.20543282</v>
+        <v>139253415.301025</v>
       </c>
       <c r="F15" s="9" t="n">
         <f aca="false">KPIs!F22</f>
-        <v>9695346.41517068</v>
+        <v>135044089.780024</v>
       </c>
       <c r="G15" s="9" t="n">
         <f aca="false">KPIs!G22</f>
-        <v>21904049.6855681</v>
+        <v>131691005.841481</v>
       </c>
       <c r="H15" s="2"/>
     </row>
@@ -2187,7 +2226,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>320</v>
+        <v>333</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2199,7 +2238,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>321</v>
+        <v>334</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2221,7 +2260,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="7" t="s">
@@ -2243,7 +2282,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
-        <v>322</v>
+        <v>335</v>
       </c>
       <c r="B5" s="16"/>
       <c r="C5" s="16"/>
@@ -2255,28 +2294,28 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="33" t="n">
         <f aca="false">Rollout!C5</f>
-        <v>20</v>
+        <v>3000</v>
       </c>
       <c r="D6" s="33" t="n">
         <f aca="false">Rollout!D5</f>
-        <v>80</v>
+        <v>3000</v>
       </c>
       <c r="E6" s="33" t="n">
         <f aca="false">Rollout!E5</f>
-        <v>200</v>
+        <v>2433</v>
       </c>
       <c r="F6" s="33" t="n">
         <f aca="false">Rollout!F5</f>
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="G6" s="33" t="n">
         <f aca="false">Rollout!G5</f>
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="H6" s="2"/>
     </row>
@@ -2287,83 +2326,83 @@
       <c r="B7" s="2"/>
       <c r="C7" s="33" t="n">
         <f aca="false">Rollout!C7</f>
-        <v>20</v>
+        <v>3000</v>
       </c>
       <c r="D7" s="33" t="n">
         <f aca="false">Rollout!D7</f>
-        <v>99.4</v>
+        <v>5910</v>
       </c>
       <c r="E7" s="33" t="n">
         <f aca="false">Rollout!E7</f>
-        <v>296.6</v>
+        <v>8193</v>
       </c>
       <c r="F7" s="33" t="n">
         <f aca="false">Rollout!F7</f>
-        <v>688.8</v>
+        <v>8030.01</v>
       </c>
       <c r="G7" s="33" t="n">
         <f aca="false">Rollout!G7</f>
-        <v>1371.8</v>
+        <v>7921.35</v>
       </c>
       <c r="H7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="33" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$C$10</f>
-        <v>4200</v>
+        <v>364140</v>
       </c>
       <c r="D8" s="33" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$D$10+Rollout!$D$5*'Unit Economics'!$C$10</f>
-        <v>27664</v>
+        <v>1306048.8</v>
       </c>
       <c r="E8" s="33" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$E$10+Rollout!$D$5*'Unit Economics'!$D$10+Rollout!$E$5*'Unit Economics'!$C$10</f>
-        <v>101416</v>
+        <v>2620958.34</v>
       </c>
       <c r="F8" s="33" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$F$10+Rollout!$D$5*'Unit Economics'!$E$10+Rollout!$E$5*'Unit Economics'!$D$10+Rollout!$F$5*'Unit Economics'!$C$10</f>
-        <v>276220</v>
+        <v>3859078.0368</v>
       </c>
       <c r="G8" s="33" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$G$10+Rollout!$D$5*'Unit Economics'!$F$10+Rollout!$E$5*'Unit Economics'!$E$10+Rollout!$F$5*'Unit Economics'!$D$10+Rollout!$G$5*'Unit Economics'!$C$10</f>
-        <v>624974</v>
+        <v>4752682.452</v>
       </c>
       <c r="H8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>324</v>
+        <v>337</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="33" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$C$12</f>
-        <v>1680000</v>
+        <v>145656000</v>
       </c>
       <c r="D9" s="33" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$D$12+Rollout!$D$5*'Unit Economics'!$C$12</f>
-        <v>13238400</v>
+        <v>710801280</v>
       </c>
       <c r="E9" s="33" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$E$12+Rollout!$D$5*'Unit Economics'!$D$12+Rollout!$E$5*'Unit Economics'!$C$12</f>
-        <v>52449600</v>
+        <v>1513511496</v>
       </c>
       <c r="F9" s="33" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$F$12+Rollout!$D$5*'Unit Economics'!$E$12+Rollout!$E$5*'Unit Economics'!$D$12+Rollout!$F$5*'Unit Economics'!$C$12</f>
-        <v>148142400</v>
+        <v>2246988502.08</v>
       </c>
       <c r="G9" s="33" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$G$12+Rollout!$D$5*'Unit Economics'!$F$12+Rollout!$E$5*'Unit Economics'!$E$12+Rollout!$F$5*'Unit Economics'!$D$12+Rollout!$G$5*'Unit Economics'!$C$12</f>
-        <v>341644800</v>
+        <v>2715421111.2</v>
       </c>
       <c r="H9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
-        <v>325</v>
+        <v>338</v>
       </c>
       <c r="B10" s="16"/>
       <c r="C10" s="16"/>
@@ -2375,61 +2414,61 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>326</v>
+        <v>339</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="33" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$C$17</f>
-        <v>109.92</v>
+        <v>14631.36</v>
       </c>
       <c r="D11" s="33" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$D$17+Rollout!$D$5*'Unit Economics'!$C$17</f>
-        <v>789.268</v>
+        <v>60316.032</v>
       </c>
       <c r="E11" s="33" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$E$17+Rollout!$D$5*'Unit Economics'!$D$17+Rollout!$E$5*'Unit Economics'!$C$17</f>
-        <v>3107.832</v>
+        <v>135864.14496</v>
       </c>
       <c r="F11" s="33" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$F$17+Rollout!$D$5*'Unit Economics'!$E$17+Rollout!$E$5*'Unit Economics'!$D$17+Rollout!$F$5*'Unit Economics'!$C$17</f>
-        <v>8941.732</v>
+        <v>217770.316992</v>
       </c>
       <c r="G11" s="33" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$G$17+Rollout!$D$5*'Unit Economics'!$F$17+Rollout!$E$5*'Unit Economics'!$E$17+Rollout!$F$5*'Unit Economics'!$D$17+Rollout!$G$5*'Unit Economics'!$C$17</f>
-        <v>21138.3056</v>
+        <v>288291.33264</v>
       </c>
       <c r="H11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>327</v>
+        <v>340</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="42" t="n">
         <f aca="false">IF(C11=0,0,(Revenue!C5+Revenue!C6+Revenue!C7)/C11/12)</f>
-        <v>9.0509461426492</v>
+        <v>7.72501804343547</v>
       </c>
       <c r="D12" s="42" t="n">
         <f aca="false">IF(D11=0,0,(Revenue!D5+Revenue!D6+Revenue!D7)/D11/12)</f>
-        <v>14.6726749342429</v>
+        <v>16.410443710886</v>
       </c>
       <c r="E12" s="42" t="n">
         <f aca="false">IF(E11=0,0,(Revenue!E5+Revenue!E6+Revenue!E7)/E11/12)</f>
-        <v>17.6454233047346</v>
+        <v>19.3235441734311</v>
       </c>
       <c r="F12" s="42" t="n">
         <f aca="false">IF(F11=0,0,(Revenue!F5+Revenue!F6+Revenue!F7)/F11/12)</f>
-        <v>19.4599572073956</v>
+        <v>21.4351696295666</v>
       </c>
       <c r="G12" s="42" t="n">
         <f aca="false">IF(G11=0,0,(Revenue!G5+Revenue!G6+Revenue!G7)/G11/12)</f>
-        <v>20.677289979193</v>
+        <v>22.3716527441142</v>
       </c>
       <c r="H12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
-        <v>328</v>
+        <v>341</v>
       </c>
       <c r="B13" s="16"/>
       <c r="C13" s="16"/>
@@ -2446,50 +2485,50 @@
       <c r="B14" s="2"/>
       <c r="C14" s="37" t="n">
         <f aca="false">'P&amp;L'!C5</f>
-        <v>18028.56</v>
+        <v>1898193.24</v>
       </c>
       <c r="D14" s="37" t="n">
         <f aca="false">'P&amp;L'!D5</f>
-        <v>217104.8736</v>
+        <v>17162730.936</v>
       </c>
       <c r="E14" s="37" t="n">
         <f aca="false">'P&amp;L'!E5</f>
-        <v>1084578.1344</v>
+        <v>49867349.09364</v>
       </c>
       <c r="F14" s="37" t="n">
         <f aca="false">'P&amp;L'!F5</f>
-        <v>3547797.98496</v>
+        <v>90378208.443456</v>
       </c>
       <c r="G14" s="37" t="n">
         <f aca="false">'P&amp;L'!G5</f>
-        <v>9061606.73472</v>
+        <v>125554175.48988</v>
       </c>
       <c r="H14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>329</v>
+        <v>342</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="37" t="n">
         <f aca="false">IF(Rollout!C8=0,0,'P&amp;L'!C5/Rollout!C8)</f>
-        <v>1802.856</v>
+        <v>1265.46216</v>
       </c>
       <c r="D15" s="37" t="n">
         <f aca="false">IF(Rollout!D8=0,0,'P&amp;L'!D5/Rollout!D8)</f>
-        <v>3636.59754773869</v>
+        <v>3852.46485656566</v>
       </c>
       <c r="E15" s="37" t="n">
         <f aca="false">IF(Rollout!E8=0,0,'P&amp;L'!E5/Rollout!E8)</f>
-        <v>5477.66734545454</v>
+        <v>7071.87819522655</v>
       </c>
       <c r="F15" s="37" t="n">
         <f aca="false">IF(Rollout!F8=0,0,'P&amp;L'!F5/Rollout!F8)</f>
-        <v>7200.72657795819</v>
+        <v>11141.9777764368</v>
       </c>
       <c r="G15" s="37" t="n">
         <f aca="false">IF(Rollout!G8=0,0,'P&amp;L'!G5/Rollout!G8)</f>
-        <v>8795.11475756576</v>
+        <v>15742.1280053713</v>
       </c>
       <c r="H15" s="2"/>
     </row>
@@ -2500,23 +2539,23 @@
       <c r="B16" s="2"/>
       <c r="C16" s="34" t="n">
         <f aca="false">'P&amp;L'!C8</f>
-        <v>0.558152495817747</v>
+        <v>0.400052059525826</v>
       </c>
       <c r="D16" s="34" t="n">
         <f aca="false">'P&amp;L'!D8</f>
-        <v>0.77079367597209</v>
+        <v>0.789260818887664</v>
       </c>
       <c r="E16" s="34" t="n">
         <f aca="false">'P&amp;L'!E8</f>
-        <v>0.841645038989641</v>
+        <v>0.876673851609431</v>
       </c>
       <c r="F16" s="34" t="n">
         <f aca="false">'P&amp;L'!F8</f>
-        <v>0.875179278962009</v>
+        <v>0.914613415716302</v>
       </c>
       <c r="G16" s="34" t="n">
         <f aca="false">'P&amp;L'!G8</f>
-        <v>0.89447292180238</v>
+        <v>0.933708003592243</v>
       </c>
       <c r="H16" s="2"/>
     </row>
@@ -2527,23 +2566,23 @@
       <c r="B17" s="2"/>
       <c r="C17" s="37" t="n">
         <f aca="false">'P&amp;L'!C16</f>
-        <v>-1221781.31424</v>
+        <v>-7576935.88496</v>
       </c>
       <c r="D17" s="37" t="n">
         <f aca="false">'P&amp;L'!D16</f>
-        <v>-2165908.7096064</v>
+        <v>1710094.032896</v>
       </c>
       <c r="E17" s="37" t="n">
         <f aca="false">'P&amp;L'!E16</f>
-        <v>-3533796.4665856</v>
+        <v>28895708.3674734</v>
       </c>
       <c r="F17" s="37" t="n">
         <f aca="false">'P&amp;L'!F16</f>
-        <v>-5134437.42521984</v>
+        <v>69401273.7358492</v>
       </c>
       <c r="G17" s="37" t="n">
         <f aca="false">'P&amp;L'!G16</f>
-        <v>-6049621.93095213</v>
+        <v>103097468.531385</v>
       </c>
       <c r="H17" s="2"/>
     </row>
@@ -2554,23 +2593,23 @@
       <c r="B18" s="2"/>
       <c r="C18" s="34" t="n">
         <f aca="false">'P&amp;L'!C17</f>
-        <v>-67.7692125294533</v>
+        <v>-3.99165676354426</v>
       </c>
       <c r="D18" s="34" t="n">
         <f aca="false">'P&amp;L'!D17</f>
-        <v>-9.97632468443306</v>
+        <v>0.0996399721741811</v>
       </c>
       <c r="E18" s="34" t="n">
         <f aca="false">'P&amp;L'!E17</f>
-        <v>-3.25822211835437</v>
+        <v>0.579451462583535</v>
       </c>
       <c r="F18" s="34" t="n">
         <f aca="false">'P&amp;L'!F17</f>
-        <v>-1.44721809048486</v>
+        <v>0.76789831233786</v>
       </c>
       <c r="G18" s="34" t="n">
         <f aca="false">'P&amp;L'!G17</f>
-        <v>-0.667610293412172</v>
+        <v>0.82113930603363</v>
       </c>
       <c r="H18" s="2"/>
     </row>
@@ -2581,135 +2620,135 @@
       <c r="B19" s="2"/>
       <c r="C19" s="37" t="n">
         <f aca="false">'Cash Flow'!C13</f>
-        <v>1005177.82896</v>
+        <v>2503618.31784</v>
       </c>
       <c r="D19" s="37" t="n">
         <f aca="false">'Cash Flow'!D13</f>
-        <v>6815796.8299456</v>
+        <v>3673276.219856</v>
       </c>
       <c r="E19" s="37" t="n">
         <f aca="false">'Cash Flow'!E13</f>
-        <v>3210976.165536</v>
+        <v>25806046.0804145</v>
       </c>
       <c r="F19" s="37" t="n">
         <f aca="false">'Cash Flow'!F13</f>
-        <v>12925142.1447994</v>
+        <v>76654592.2684737</v>
       </c>
       <c r="G19" s="37" t="n">
         <f aca="false">'Cash Flow'!G13</f>
-        <v>6582605.95135443</v>
+        <v>152921581.322286</v>
       </c>
       <c r="H19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>330</v>
+        <v>343</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="34" t="n">
         <f aca="false">IF('P&amp;L'!C5=0,0,Costs!C6/'P&amp;L'!C5)</f>
-        <v>0.225131679956691</v>
+        <v>0.301700052414052</v>
       </c>
       <c r="D20" s="34" t="n">
         <f aca="false">IF('P&amp;L'!D5=0,0,Costs!D6/'P&amp;L'!D5)</f>
-        <v>0.111048967258191</v>
+        <v>0.0981017476926319</v>
       </c>
       <c r="E20" s="34" t="n">
         <f aca="false">IF('P&amp;L'!E5=0,0,Costs!E6/'P&amp;L'!E5)</f>
-        <v>0.0735733143321611</v>
+        <v>0.0534128639964081</v>
       </c>
       <c r="F20" s="34" t="n">
         <f aca="false">IF('P&amp;L'!F5=0,0,Costs!F6/'P&amp;L'!F5)</f>
-        <v>0.0559203609791319</v>
+        <v>0.0339216451697874</v>
       </c>
       <c r="G20" s="34" t="n">
         <f aca="false">IF('P&amp;L'!G5=0,0,Costs!G6/'P&amp;L'!G5)</f>
-        <v>0.0457676211450391</v>
+        <v>0.024087547902728</v>
       </c>
       <c r="H20" s="17" t="s">
-        <v>331</v>
+        <v>344</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>332</v>
+        <v>345</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" s="37" t="n">
-        <f aca="false">Costs!C21+Costs!C22+Costs!C23+Costs!C20+Assumptions!C$92+Costs!C25</f>
-        <v>1018250</v>
+        <f aca="false">Costs!C22+Costs!C23+Costs!C24+Costs!C21+Assumptions!C$97+Costs!C26</f>
+        <v>1126250</v>
       </c>
       <c r="D21" s="37" t="n">
-        <f aca="false">Costs!D21+Costs!D22+Costs!D23+Costs!D20+Assumptions!D$92+Costs!D25</f>
-        <v>1717125</v>
+        <f aca="false">Costs!D22+Costs!D23+Costs!D24+Costs!D21+Assumptions!D$97+Costs!D26</f>
+        <v>1903125</v>
       </c>
       <c r="E21" s="37" t="n">
-        <f aca="false">Costs!E21+Costs!E22+Costs!E23+Costs!E20+Assumptions!E$92+Costs!E25</f>
-        <v>2756628.75</v>
+        <f aca="false">Costs!E22+Costs!E23+Costs!E24+Costs!E21+Assumptions!E$97+Costs!E26</f>
+        <v>2975628.75</v>
       </c>
       <c r="F21" s="37" t="n">
-        <f aca="false">Costs!F21+Costs!F22+Costs!F23+Costs!F20+Assumptions!F$92+Costs!F25</f>
-        <v>4241476.4375</v>
+        <f aca="false">Costs!F22+Costs!F23+Costs!F24+Costs!F21+Assumptions!F$97+Costs!F26</f>
+        <v>4355476.4375</v>
       </c>
       <c r="G21" s="37" t="n">
-        <f aca="false">Costs!G21+Costs!G22+Costs!G23+Costs!G20+Assumptions!G$92+Costs!G25</f>
-        <v>5852241.820375</v>
+        <f aca="false">Costs!G22+Costs!G23+Costs!G24+Costs!G21+Assumptions!G$97+Costs!G26</f>
+        <v>5822241.820375</v>
       </c>
       <c r="H21" s="2"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>333</v>
+        <v>346</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="37" t="n">
         <f aca="false">Rollout!C7/'Unit Economics'!$G$7*'Unit Economics'!$G$42-C21</f>
-        <v>-613580.34690271</v>
+        <v>50953224.2039639</v>
       </c>
       <c r="D22" s="37" t="n">
         <f aca="false">Rollout!D7/'Unit Economics'!$G$7*'Unit Economics'!$G$42-D21</f>
-        <v>294083.175893533</v>
+        <v>100693439.181809</v>
       </c>
       <c r="E22" s="37" t="n">
         <f aca="false">Rollout!E7/'Unit Economics'!$G$7*'Unit Economics'!$G$42-E21</f>
-        <v>3244622.20543282</v>
+        <v>139253415.301025</v>
       </c>
       <c r="F22" s="37" t="n">
         <f aca="false">Rollout!F7/'Unit Economics'!$G$7*'Unit Economics'!$G$42-F21</f>
-        <v>9695346.41517068</v>
+        <v>135044089.780024</v>
       </c>
       <c r="G22" s="37" t="n">
         <f aca="false">Rollout!G7/'Unit Economics'!$G$7*'Unit Economics'!$G$42-G21</f>
-        <v>21904049.6855681</v>
+        <v>131691005.841481</v>
       </c>
       <c r="H22" s="17" t="s">
-        <v>334</v>
+        <v>347</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>335</v>
+        <v>348</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" s="33" t="n">
         <f aca="false">IF('Unit Economics'!$G$42&lt;=0,0,C21/('Unit Economics'!$G$42/'Unit Economics'!$G$7))</f>
-        <v>50.3249992781244</v>
+        <v>64.8768070654376</v>
       </c>
       <c r="D23" s="33" t="n">
         <f aca="false">IF('Unit Economics'!$G$42&lt;=0,0,D21/('Unit Economics'!$G$42/'Unit Economics'!$G$7))</f>
-        <v>84.8655186697269</v>
+        <v>109.628122926891</v>
       </c>
       <c r="E23" s="33" t="n">
         <f aca="false">IF('Unit Economics'!$G$42&lt;=0,0,E21/('Unit Economics'!$G$42/'Unit Economics'!$G$7))</f>
-        <v>136.240942650437</v>
+        <v>171.408916592337</v>
       </c>
       <c r="F23" s="33" t="n">
         <f aca="false">IF('Unit Economics'!$G$42&lt;=0,0,F21/('Unit Economics'!$G$42/'Unit Economics'!$G$7))</f>
-        <v>209.626612968691</v>
+        <v>250.894032864592</v>
       </c>
       <c r="G23" s="33" t="n">
         <f aca="false">IF('Unit Economics'!$G$42&lt;=0,0,G21/('Unit Economics'!$G$42/'Unit Economics'!$G$7))</f>
-        <v>289.235517196937</v>
+        <v>335.385979372956</v>
       </c>
       <c r="H23" s="2"/>
     </row>
@@ -2725,7 +2764,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="15" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
       <c r="B25" s="16"/>
       <c r="C25" s="16"/>
@@ -2737,12 +2776,12 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>337</v>
+        <v>350</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" s="9" t="n">
         <f aca="false">'Unit Economics'!G25</f>
-        <v>26374.633344</v>
+        <v>17934.8284368</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
@@ -2752,12 +2791,12 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>338</v>
+        <v>351</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" s="9" t="n">
         <f aca="false">'Unit Economics'!G42</f>
-        <v>18817.138869024</v>
+        <v>16144.6370032288</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
@@ -2767,12 +2806,12 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>339</v>
+        <v>352</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" s="10" t="n">
         <f aca="false">'Unit Economics'!G43</f>
-        <v>0.713455941684389</v>
+        <v>0.900183520579547</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
@@ -2782,7 +2821,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>340</v>
+        <v>353</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" s="9" t="n">
@@ -2797,29 +2836,29 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>341</v>
+        <v>354</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="41" t="n">
         <f aca="false">IFERROR(MATCH(TRUE(),INDEX('Unit Economics'!C45:G45&gt;0,0),0),"After Age 5")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
       <c r="H30" s="17" t="s">
-        <v>342</v>
+        <v>355</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>343</v>
+        <v>356</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" s="2" t="str">
         <f aca="false">IFERROR(INDEX(C4:G4,MATCH(TRUE(),INDEX(C17:G17&gt;0,0),0)),"Not by FY2031")</f>
-        <v>Not by FY2031</v>
+        <v>2028</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>
@@ -2829,12 +2868,12 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>344</v>
+        <v>357</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" s="9" t="n">
         <f aca="false">'Cash Flow'!C17</f>
-        <v>18667394.0486456</v>
+        <v>7746381.68216</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" s="2"/>
@@ -2858,7 +2897,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H104"/>
+  <dimension ref="A1:H109"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
@@ -3061,572 +3100,562 @@
       <c r="H12" s="16"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="B13" s="6"/>
-      <c r="C13" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H13" s="6"/>
+      <c r="B13" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" s="21" t="n">
+        <v>8433</v>
+      </c>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="17" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="B14" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="C14" s="21" t="n">
-        <v>20</v>
-      </c>
-      <c r="D14" s="21" t="n">
-        <v>80</v>
-      </c>
-      <c r="E14" s="21" t="n">
-        <v>200</v>
-      </c>
-      <c r="F14" s="21" t="n">
-        <v>400</v>
-      </c>
-      <c r="G14" s="21" t="n">
-        <v>700</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="B14" s="17"/>
+      <c r="C14" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
       <c r="H14" s="17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
+      <c r="A15" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B15" s="17"/>
+      <c r="C15" s="23" t="n">
+        <v>1</v>
+      </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
+      <c r="H15" s="17" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="B16" s="16"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="16"/>
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="D17" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="E17" s="18" t="s">
+      <c r="A17" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="F17" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="H17" s="6"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="B18" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="C18" s="24" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D18" s="24" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E18" s="24" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F18" s="24" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G18" s="24" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H18" s="17" t="s">
         <v>57</v>
-      </c>
-      <c r="B18" s="2"/>
-      <c r="C18" s="22" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D18" s="22" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E18" s="22" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="F18" s="23" t="n">
-        <f aca="false">SUM(C18:E18)</f>
-        <v>1</v>
-      </c>
-      <c r="G18" s="2"/>
-      <c r="H18" s="17" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="B19" s="2"/>
-      <c r="C19" s="24" t="n">
-        <v>4000</v>
-      </c>
-      <c r="D19" s="24" t="n">
-        <v>15000</v>
-      </c>
-      <c r="E19" s="24" t="n">
-        <v>45000</v>
-      </c>
-      <c r="F19" s="25" t="n">
-        <f aca="false">SUMPRODUCT(C19:E19,$C$18:$E$18)</f>
-        <v>14000</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="B19" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="C19" s="21" t="n">
+        <v>400</v>
+      </c>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
       <c r="G19" s="2"/>
       <c r="H19" s="17" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="15" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="11" t="s">
+      <c r="B21" s="16"/>
+      <c r="C21" s="16"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="16"/>
+      <c r="F21" s="16"/>
+      <c r="G21" s="16"/>
+      <c r="H21" s="16"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="B20" s="2"/>
-      <c r="C20" s="24" t="n">
-        <v>300</v>
-      </c>
-      <c r="D20" s="24" t="n">
-        <v>900</v>
-      </c>
-      <c r="E20" s="24" t="n">
-        <v>2300</v>
-      </c>
-      <c r="F20" s="25" t="n">
-        <f aca="false">SUMPRODUCT(C20:E20,$C$18:$E$18)</f>
-        <v>810</v>
-      </c>
-      <c r="G20" s="2"/>
-      <c r="H20" s="17" t="s">
+      <c r="D22" s="18" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="11" t="s">
+      <c r="E22" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="B21" s="2"/>
-      <c r="C21" s="24" t="n">
-        <v>3</v>
-      </c>
-      <c r="D21" s="24" t="n">
-        <v>6</v>
-      </c>
-      <c r="E21" s="24" t="n">
-        <v>10</v>
-      </c>
-      <c r="F21" s="25" t="n">
-        <f aca="false">SUMPRODUCT(C21:E21,$C$18:$E$18)</f>
-        <v>5.1</v>
-      </c>
-      <c r="G21" s="2"/>
-      <c r="H21" s="17" t="s">
+      <c r="F22" s="18" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="11" t="s">
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="B22" s="2"/>
-      <c r="C22" s="26" t="n">
-        <v>150</v>
-      </c>
-      <c r="D22" s="26" t="n">
-        <v>400</v>
-      </c>
-      <c r="E22" s="26" t="n">
-        <v>900</v>
-      </c>
-      <c r="F22" s="27" t="n">
-        <f aca="false">SUMPRODUCT(C22:E22,$C$18:$E$18)</f>
-        <v>350</v>
-      </c>
-      <c r="G22" s="2"/>
-      <c r="H22" s="17" t="s">
+      <c r="B23" s="2"/>
+      <c r="C23" s="22" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="D23" s="22" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E23" s="22" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F23" s="25" t="n">
+        <f aca="false">SUM(C23:E23)</f>
+        <v>1</v>
+      </c>
+      <c r="G23" s="2"/>
+      <c r="H23" s="17" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-    </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="15" t="s">
+      <c r="A24" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="B24" s="16"/>
-      <c r="C24" s="16"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="16"/>
-      <c r="G24" s="16"/>
-      <c r="H24" s="16"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="21" t="n">
+        <v>3300</v>
+      </c>
+      <c r="D24" s="21" t="n">
+        <v>21000</v>
+      </c>
+      <c r="E24" s="21" t="n">
+        <v>70000</v>
+      </c>
+      <c r="F24" s="26" t="n">
+        <f aca="false">SUMPRODUCT(C24:E24,$C$23:$E$23)</f>
+        <v>8092</v>
+      </c>
+      <c r="G24" s="2"/>
+      <c r="H24" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="B25" s="6"/>
-      <c r="C25" s="7" t="s">
+      <c r="A25" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="D25" s="7" t="s">
+      <c r="B25" s="2"/>
+      <c r="C25" s="21" t="n">
+        <v>180</v>
+      </c>
+      <c r="D25" s="21" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E25" s="21" t="n">
+        <v>3500</v>
+      </c>
+      <c r="F25" s="26" t="n">
+        <f aca="false">SUMPRODUCT(C25:E25,$C$23:$E$23)</f>
+        <v>423.2</v>
+      </c>
+      <c r="G25" s="2"/>
+      <c r="H25" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="E25" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="F25" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="G25" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="H25" s="6"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="B26" s="17"/>
-      <c r="C26" s="22" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="D26" s="22" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="E26" s="22" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="F26" s="22" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="G26" s="22" t="n">
-        <v>0.085</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="B26" s="2"/>
+      <c r="C26" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="E26" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="F26" s="26" t="n">
+        <f aca="false">SUMPRODUCT(C26:E26,$C$23:$E$23)</f>
+        <v>3.64</v>
+      </c>
+      <c r="G26" s="2"/>
       <c r="H26" s="17" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="B27" s="2"/>
+      <c r="C27" s="27" t="n">
+        <v>150</v>
+      </c>
+      <c r="D27" s="27" t="n">
+        <v>400</v>
+      </c>
+      <c r="E27" s="27" t="n">
+        <v>900</v>
+      </c>
+      <c r="F27" s="28" t="n">
+        <f aca="false">SUMPRODUCT(C27:E27,$C$23:$E$23)</f>
+        <v>210</v>
+      </c>
+      <c r="G27" s="2"/>
+      <c r="H27" s="17" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="2"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="B29" s="16"/>
+      <c r="C29" s="16"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="16"/>
+      <c r="G29" s="16"/>
+      <c r="H29" s="16"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="B27" s="17"/>
-      <c r="C27" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="E27" s="28" t="n">
-        <v>3</v>
-      </c>
-      <c r="F27" s="28" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="G27" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="H27" s="17" t="s">
+      <c r="B30" s="6"/>
+      <c r="C30" s="7" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="11" t="s">
+      <c r="D30" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="B28" s="17"/>
-      <c r="C28" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="D28" s="29" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="E28" s="29" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F28" s="29" t="n">
-        <v>0.94</v>
-      </c>
-      <c r="G28" s="29" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="H28" s="17" t="s">
+      <c r="E30" s="7" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="2"/>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="15" t="s">
+      <c r="F30" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="B30" s="16"/>
-      <c r="C30" s="16"/>
-      <c r="D30" s="16"/>
-      <c r="E30" s="16"/>
-      <c r="F30" s="16"/>
-      <c r="G30" s="16"/>
-      <c r="H30" s="16"/>
+      <c r="G30" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="H30" s="6"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="B31" s="6"/>
-      <c r="C31" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="E31" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="F31" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="G31" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="H31" s="6"/>
+      <c r="A31" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="B31" s="17"/>
+      <c r="C31" s="22" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D31" s="22" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E31" s="22" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F31" s="22" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="G31" s="22" t="n">
+        <v>0.085</v>
+      </c>
+      <c r="H31" s="17" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="11" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B32" s="17"/>
-      <c r="C32" s="22" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="D32" s="22" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="E32" s="22" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="F32" s="22" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="G32" s="22" t="n">
-        <v>0.38</v>
+      <c r="C32" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="E32" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="F32" s="29" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G32" s="29" t="n">
+        <v>4</v>
       </c>
       <c r="H32" s="17" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="11" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B33" s="17"/>
-      <c r="C33" s="29" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="D33" s="29" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E33" s="29" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="F33" s="29" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G33" s="29" t="n">
-        <v>0.12</v>
+      <c r="C33" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" s="23" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="E33" s="23" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F33" s="23" t="n">
+        <v>0.94</v>
+      </c>
+      <c r="G33" s="23" t="n">
+        <v>0.93</v>
       </c>
       <c r="H33" s="17" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="B34" s="17"/>
-      <c r="C34" s="22" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="D34" s="22" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="E34" s="22" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="F34" s="22" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="G34" s="22" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="H34" s="17" t="s">
-        <v>86</v>
-      </c>
+      <c r="A34" s="2"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="B35" s="17"/>
-      <c r="C35" s="29" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D35" s="29" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E35" s="29" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="F35" s="29" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="G35" s="29" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H35" s="17" t="s">
+      <c r="A35" s="15" t="s">
         <v>88</v>
       </c>
+      <c r="B35" s="16"/>
+      <c r="C35" s="16"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="16"/>
+      <c r="F35" s="16"/>
+      <c r="G35" s="16"/>
+      <c r="H35" s="16"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="B36" s="17"/>
-      <c r="C36" s="29" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D36" s="29" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E36" s="29" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F36" s="29" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="G36" s="29" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="H36" s="17" t="s">
-        <v>90</v>
-      </c>
+      <c r="A36" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B36" s="6"/>
+      <c r="C36" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="G36" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="H36" s="6"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="11" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B37" s="17"/>
-      <c r="C37" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" s="29" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="E37" s="29" t="n">
+      <c r="C37" s="22" t="n">
         <v>0.05</v>
       </c>
-      <c r="F37" s="29" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="G37" s="29" t="n">
-        <v>0.1</v>
+      <c r="D37" s="22" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E37" s="22" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F37" s="22" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="G37" s="22" t="n">
+        <v>0.38</v>
       </c>
       <c r="H37" s="17" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="B38" s="17"/>
+      <c r="C38" s="23" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D38" s="23" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E38" s="23" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="F38" s="23" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G38" s="23" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H38" s="17" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="B38" s="17"/>
-      <c r="C38" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="F38" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="G38" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="H38" s="17" t="s">
+      <c r="B39" s="17"/>
+      <c r="C39" s="22" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="D39" s="22" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E39" s="22" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F39" s="22" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="G39" s="22" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H39" s="17" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="2"/>
-      <c r="B39" s="2"/>
-      <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="2"/>
-      <c r="G39" s="2"/>
-      <c r="H39" s="2"/>
-    </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="15" t="s">
+      <c r="A40" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="B40" s="16"/>
-      <c r="C40" s="16"/>
-      <c r="D40" s="16"/>
-      <c r="E40" s="16"/>
-      <c r="F40" s="16"/>
-      <c r="G40" s="16"/>
-      <c r="H40" s="16"/>
+      <c r="B40" s="17"/>
+      <c r="C40" s="23" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D40" s="23" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E40" s="23" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F40" s="23" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G40" s="23" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H40" s="17" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="B41" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="C41" s="24" t="n">
-        <v>28</v>
-      </c>
-      <c r="D41" s="2"/>
-      <c r="E41" s="2"/>
-      <c r="F41" s="2"/>
-      <c r="G41" s="2"/>
+      <c r="B41" s="17"/>
+      <c r="C41" s="23" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D41" s="23" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E41" s="23" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F41" s="23" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G41" s="23" t="n">
+        <v>0.65</v>
+      </c>
       <c r="H41" s="17" t="s">
         <v>98</v>
       </c>
@@ -3635,116 +3664,116 @@
       <c r="A42" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="B42" s="17" t="s">
+      <c r="B42" s="17"/>
+      <c r="C42" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="23" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E42" s="23" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F42" s="23" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G42" s="23" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H42" s="17" t="s">
         <v>100</v>
-      </c>
-      <c r="C42" s="26" t="n">
-        <v>38</v>
-      </c>
-      <c r="D42" s="2"/>
-      <c r="E42" s="2"/>
-      <c r="F42" s="2"/>
-      <c r="G42" s="2"/>
-      <c r="H42" s="17" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="B43" s="17"/>
+      <c r="C43" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H43" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="B43" s="17" t="s">
-        <v>103</v>
-      </c>
-      <c r="C43" s="24" t="n">
-        <v>30</v>
-      </c>
-      <c r="D43" s="2"/>
-      <c r="E43" s="2"/>
-      <c r="F43" s="2"/>
-      <c r="G43" s="2"/>
-      <c r="H43" s="17" t="s">
-        <v>104</v>
-      </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="B44" s="17"/>
-      <c r="C44" s="29" t="n">
-        <v>0.08</v>
-      </c>
+      <c r="A44" s="2"/>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
       <c r="D44" s="2"/>
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
-      <c r="H44" s="17" t="s">
-        <v>106</v>
-      </c>
+      <c r="H44" s="2"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="B45" s="17" t="s">
-        <v>100</v>
-      </c>
-      <c r="C45" s="26" t="n">
-        <v>39</v>
-      </c>
-      <c r="D45" s="2"/>
-      <c r="E45" s="2"/>
-      <c r="F45" s="2"/>
-      <c r="G45" s="2"/>
-      <c r="H45" s="17" t="s">
-        <v>108</v>
-      </c>
+      <c r="A45" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="B45" s="16"/>
+      <c r="C45" s="16"/>
+      <c r="D45" s="16"/>
+      <c r="E45" s="16"/>
+      <c r="F45" s="16"/>
+      <c r="G45" s="16"/>
+      <c r="H45" s="16"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="11" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B46" s="17" t="s">
-        <v>100</v>
-      </c>
-      <c r="C46" s="26" t="n">
-        <v>99</v>
+        <v>105</v>
+      </c>
+      <c r="C46" s="21" t="n">
+        <v>28</v>
       </c>
       <c r="D46" s="2"/>
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
       <c r="H46" s="17" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="11" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B47" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="C47" s="24" t="n">
-        <v>300</v>
+        <v>108</v>
+      </c>
+      <c r="C47" s="27" t="n">
+        <v>38</v>
       </c>
       <c r="D47" s="2"/>
       <c r="E47" s="2"/>
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
       <c r="H47" s="17" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="11" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B48" s="17" t="s">
-        <v>115</v>
-      </c>
-      <c r="C48" s="26" t="n">
+        <v>111</v>
+      </c>
+      <c r="C48" s="21" t="n">
         <v>30</v>
       </c>
       <c r="D48" s="2"/>
@@ -3752,215 +3781,215 @@
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
       <c r="H48" s="17" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="B49" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="C49" s="30" t="n">
-        <v>6</v>
+        <v>113</v>
+      </c>
+      <c r="B49" s="17"/>
+      <c r="C49" s="23" t="n">
+        <v>0.08</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" s="2"/>
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
       <c r="H49" s="17" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="B50" s="17"/>
-      <c r="C50" s="29" t="n">
-        <v>0.8</v>
+        <v>115</v>
+      </c>
+      <c r="B50" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="C50" s="27" t="n">
+        <v>39</v>
       </c>
       <c r="D50" s="2"/>
       <c r="E50" s="2"/>
       <c r="F50" s="2"/>
       <c r="G50" s="2"/>
       <c r="H50" s="17" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="2"/>
-      <c r="B51" s="2"/>
-      <c r="C51" s="2"/>
+      <c r="A51" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="B51" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="C51" s="27" t="n">
+        <v>99</v>
+      </c>
       <c r="D51" s="2"/>
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
       <c r="G51" s="2"/>
-      <c r="H51" s="2"/>
+      <c r="H51" s="17" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="15" t="s">
-        <v>122</v>
-      </c>
-      <c r="B52" s="16"/>
-      <c r="C52" s="16"/>
-      <c r="D52" s="16"/>
-      <c r="E52" s="16"/>
-      <c r="F52" s="16"/>
-      <c r="G52" s="16"/>
-      <c r="H52" s="16"/>
+      <c r="A52" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="B52" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="C52" s="21" t="n">
+        <v>300</v>
+      </c>
+      <c r="D52" s="2"/>
+      <c r="E52" s="2"/>
+      <c r="F52" s="2"/>
+      <c r="G52" s="2"/>
+      <c r="H52" s="17" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="B53" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="B53" s="17" t="s">
-        <v>124</v>
-      </c>
-      <c r="C53" s="31" t="n">
-        <v>0.12</v>
+      <c r="C53" s="27" t="n">
+        <v>30</v>
       </c>
       <c r="D53" s="2"/>
       <c r="E53" s="2"/>
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
       <c r="H53" s="17" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="B54" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="B54" s="17" t="s">
-        <v>127</v>
-      </c>
       <c r="C54" s="30" t="n">
-        <v>0.5</v>
+        <v>6</v>
       </c>
       <c r="D54" s="2"/>
       <c r="E54" s="2"/>
       <c r="F54" s="2"/>
       <c r="G54" s="2"/>
       <c r="H54" s="17" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="B55" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="C55" s="30" t="n">
-        <v>5</v>
+        <v>128</v>
+      </c>
+      <c r="B55" s="17"/>
+      <c r="C55" s="23" t="n">
+        <v>0.8</v>
       </c>
       <c r="D55" s="2"/>
       <c r="E55" s="2"/>
       <c r="F55" s="2"/>
       <c r="G55" s="2"/>
       <c r="H55" s="17" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="B56" s="17" t="s">
-        <v>100</v>
-      </c>
-      <c r="C56" s="26" t="n">
-        <v>25</v>
-      </c>
+      <c r="A56" s="2"/>
+      <c r="B56" s="2"/>
+      <c r="C56" s="2"/>
       <c r="D56" s="2"/>
       <c r="E56" s="2"/>
       <c r="F56" s="2"/>
       <c r="G56" s="2"/>
-      <c r="H56" s="17" t="s">
-        <v>132</v>
-      </c>
+      <c r="H56" s="2"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="B57" s="17" t="s">
-        <v>134</v>
-      </c>
-      <c r="C57" s="30" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D57" s="2"/>
-      <c r="E57" s="2"/>
-      <c r="F57" s="2"/>
-      <c r="G57" s="2"/>
-      <c r="H57" s="17" t="s">
-        <v>135</v>
-      </c>
+      <c r="A57" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="B57" s="16"/>
+      <c r="C57" s="16"/>
+      <c r="D57" s="16"/>
+      <c r="E57" s="16"/>
+      <c r="F57" s="16"/>
+      <c r="G57" s="16"/>
+      <c r="H57" s="16"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="B58" s="17"/>
-      <c r="C58" s="29" t="n">
-        <v>0.029</v>
+        <v>131</v>
+      </c>
+      <c r="B58" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="C58" s="31" t="n">
+        <v>0.15</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" s="2"/>
       <c r="F58" s="2"/>
       <c r="G58" s="2"/>
       <c r="H58" s="17" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="11" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B59" s="17" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C59" s="30" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="D59" s="2"/>
       <c r="E59" s="2"/>
       <c r="F59" s="2"/>
       <c r="G59" s="2"/>
       <c r="H59" s="17" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="11" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B60" s="17" t="s">
-        <v>142</v>
-      </c>
-      <c r="C60" s="26" t="n">
-        <v>20</v>
+        <v>135</v>
+      </c>
+      <c r="C60" s="30" t="n">
+        <v>5</v>
       </c>
       <c r="D60" s="2"/>
       <c r="E60" s="2"/>
       <c r="F60" s="2"/>
       <c r="G60" s="2"/>
       <c r="H60" s="17" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="11" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="B61" s="17" t="s">
-        <v>145</v>
-      </c>
-      <c r="C61" s="26" t="n">
+        <v>108</v>
+      </c>
+      <c r="C61" s="27" t="n">
         <v>25</v>
       </c>
       <c r="D61" s="2"/>
@@ -3968,18 +3997,18 @@
       <c r="F61" s="2"/>
       <c r="G61" s="2"/>
       <c r="H61" s="17" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="11" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="B62" s="17" t="s">
-        <v>145</v>
-      </c>
-      <c r="C62" s="26" t="n">
-        <v>15</v>
+        <v>142</v>
+      </c>
+      <c r="C62" s="30" t="n">
+        <v>0.1</v>
       </c>
       <c r="D62" s="2"/>
       <c r="E62" s="2"/>
@@ -3991,652 +4020,668 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="11" t="s">
-        <v>148</v>
-      </c>
-      <c r="B63" s="17" t="s">
-        <v>145</v>
-      </c>
-      <c r="C63" s="32" t="n">
-        <v>1500</v>
+        <v>144</v>
+      </c>
+      <c r="B63" s="17"/>
+      <c r="C63" s="23" t="n">
+        <v>0.029</v>
       </c>
       <c r="D63" s="2"/>
       <c r="E63" s="2"/>
       <c r="F63" s="2"/>
       <c r="G63" s="2"/>
       <c r="H63" s="17" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="11" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="B64" s="17" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C64" s="30" t="n">
-        <v>2</v>
+        <v>0.3</v>
       </c>
       <c r="D64" s="2"/>
       <c r="E64" s="2"/>
       <c r="F64" s="2"/>
       <c r="G64" s="2"/>
       <c r="H64" s="17" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="11" t="s">
-        <v>152</v>
-      </c>
-      <c r="B65" s="17"/>
-      <c r="C65" s="29" t="n">
-        <v>0.4</v>
+        <v>149</v>
+      </c>
+      <c r="B65" s="17" t="s">
+        <v>150</v>
+      </c>
+      <c r="C65" s="27" t="n">
+        <v>20</v>
       </c>
       <c r="D65" s="2"/>
       <c r="E65" s="2"/>
       <c r="F65" s="2"/>
       <c r="G65" s="2"/>
       <c r="H65" s="17" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="B66" s="17" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="2"/>
-      <c r="B66" s="2"/>
-      <c r="C66" s="2"/>
+      <c r="C66" s="27" t="n">
+        <v>25</v>
+      </c>
       <c r="D66" s="2"/>
       <c r="E66" s="2"/>
       <c r="F66" s="2"/>
       <c r="G66" s="2"/>
-      <c r="H66" s="2"/>
+      <c r="H66" s="17" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="15" t="s">
-        <v>154</v>
-      </c>
-      <c r="B67" s="16"/>
-      <c r="C67" s="16"/>
-      <c r="D67" s="16"/>
-      <c r="E67" s="16"/>
-      <c r="F67" s="16"/>
-      <c r="G67" s="16"/>
-      <c r="H67" s="16"/>
+      <c r="A67" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="B67" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="C67" s="27" t="n">
+        <v>15</v>
+      </c>
+      <c r="D67" s="2"/>
+      <c r="E67" s="2"/>
+      <c r="F67" s="2"/>
+      <c r="G67" s="2"/>
+      <c r="H67" s="17" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="11" t="s">
-        <v>155</v>
-      </c>
-      <c r="B68" s="17"/>
-      <c r="C68" s="29" t="n">
-        <v>0.25</v>
+        <v>156</v>
+      </c>
+      <c r="B68" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="C68" s="32" t="n">
+        <v>1500</v>
       </c>
       <c r="D68" s="2"/>
       <c r="E68" s="2"/>
       <c r="F68" s="2"/>
       <c r="G68" s="2"/>
       <c r="H68" s="17" t="s">
-        <v>143</v>
+        <v>157</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="11" t="s">
-        <v>156</v>
-      </c>
-      <c r="B69" s="17"/>
-      <c r="C69" s="29" t="n">
-        <v>0.03</v>
+        <v>158</v>
+      </c>
+      <c r="B69" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="C69" s="30" t="n">
+        <v>2</v>
       </c>
       <c r="D69" s="2"/>
       <c r="E69" s="2"/>
       <c r="F69" s="2"/>
       <c r="G69" s="2"/>
       <c r="H69" s="17" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="11" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B70" s="17"/>
-      <c r="C70" s="29" t="n">
-        <v>0.1</v>
+      <c r="C70" s="23" t="n">
+        <v>0.4</v>
       </c>
       <c r="D70" s="2"/>
       <c r="E70" s="2"/>
       <c r="F70" s="2"/>
       <c r="G70" s="2"/>
       <c r="H70" s="17" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="B71" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="C71" s="21" t="n">
-        <v>40</v>
-      </c>
+      <c r="A71" s="2"/>
+      <c r="B71" s="2"/>
+      <c r="C71" s="2"/>
       <c r="D71" s="2"/>
       <c r="E71" s="2"/>
       <c r="F71" s="2"/>
       <c r="G71" s="2"/>
-      <c r="H71" s="17" t="s">
-        <v>160</v>
-      </c>
+      <c r="H71" s="2"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="11" t="s">
-        <v>161</v>
-      </c>
-      <c r="B72" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="C72" s="21" t="n">
-        <v>30</v>
-      </c>
-      <c r="D72" s="2"/>
-      <c r="E72" s="2"/>
-      <c r="F72" s="2"/>
-      <c r="G72" s="2"/>
-      <c r="H72" s="17" t="s">
+      <c r="A72" s="15" t="s">
         <v>162</v>
       </c>
+      <c r="B72" s="16"/>
+      <c r="C72" s="16"/>
+      <c r="D72" s="16"/>
+      <c r="E72" s="16"/>
+      <c r="F72" s="16"/>
+      <c r="G72" s="16"/>
+      <c r="H72" s="16"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="B73" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="C73" s="24" t="n">
-        <v>120</v>
+      <c r="B73" s="17"/>
+      <c r="C73" s="23" t="n">
+        <v>0.25</v>
       </c>
       <c r="D73" s="2"/>
       <c r="E73" s="2"/>
       <c r="F73" s="2"/>
       <c r="G73" s="2"/>
       <c r="H73" s="17" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="2"/>
-      <c r="B74" s="2"/>
-      <c r="C74" s="2"/>
+      <c r="A74" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="B74" s="17"/>
+      <c r="C74" s="23" t="n">
+        <v>0.03</v>
+      </c>
       <c r="D74" s="2"/>
       <c r="E74" s="2"/>
       <c r="F74" s="2"/>
       <c r="G74" s="2"/>
-      <c r="H74" s="2"/>
+      <c r="H74" s="17" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="15" t="s">
-        <v>164</v>
-      </c>
-      <c r="B75" s="16"/>
-      <c r="C75" s="16"/>
-      <c r="D75" s="16"/>
-      <c r="E75" s="16"/>
-      <c r="F75" s="16"/>
-      <c r="G75" s="16"/>
-      <c r="H75" s="16"/>
+      <c r="A75" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="B75" s="17"/>
+      <c r="C75" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D75" s="2"/>
+      <c r="E75" s="2"/>
+      <c r="F75" s="2"/>
+      <c r="G75" s="2"/>
+      <c r="H75" s="17" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="11" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B76" s="17" t="s">
-        <v>142</v>
-      </c>
-      <c r="C76" s="26" t="n">
-        <v>160000</v>
+        <v>49</v>
+      </c>
+      <c r="C76" s="24" t="n">
+        <v>1000</v>
       </c>
       <c r="D76" s="2"/>
       <c r="E76" s="2"/>
       <c r="F76" s="2"/>
       <c r="G76" s="2"/>
       <c r="H76" s="17" t="s">
-        <v>143</v>
+        <v>168</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="11" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B77" s="17" t="s">
-        <v>142</v>
-      </c>
-      <c r="C77" s="26" t="n">
-        <v>170000</v>
+        <v>49</v>
+      </c>
+      <c r="C77" s="24" t="n">
+        <v>1000</v>
       </c>
       <c r="D77" s="2"/>
       <c r="E77" s="2"/>
       <c r="F77" s="2"/>
       <c r="G77" s="2"/>
       <c r="H77" s="17" t="s">
-        <v>143</v>
+        <v>170</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="11" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B78" s="17" t="s">
-        <v>142</v>
-      </c>
-      <c r="C78" s="26" t="n">
-        <v>70000</v>
+        <v>49</v>
+      </c>
+      <c r="C78" s="21" t="n">
+        <v>120</v>
       </c>
       <c r="D78" s="2"/>
       <c r="E78" s="2"/>
       <c r="F78" s="2"/>
       <c r="G78" s="2"/>
       <c r="H78" s="17" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="B79" s="17" t="s">
-        <v>142</v>
-      </c>
-      <c r="C79" s="26" t="n">
-        <v>65000</v>
-      </c>
+      <c r="A79" s="2"/>
+      <c r="B79" s="2"/>
+      <c r="C79" s="2"/>
       <c r="D79" s="2"/>
       <c r="E79" s="2"/>
       <c r="F79" s="2"/>
       <c r="G79" s="2"/>
-      <c r="H79" s="17" t="s">
-        <v>143</v>
-      </c>
+      <c r="H79" s="2"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="11" t="s">
-        <v>169</v>
-      </c>
-      <c r="B80" s="17" t="s">
-        <v>142</v>
-      </c>
-      <c r="C80" s="26" t="n">
-        <v>55000</v>
-      </c>
-      <c r="D80" s="2"/>
-      <c r="E80" s="2"/>
-      <c r="F80" s="2"/>
-      <c r="G80" s="2"/>
-      <c r="H80" s="17" t="s">
-        <v>143</v>
-      </c>
+      <c r="A80" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="B80" s="16"/>
+      <c r="C80" s="16"/>
+      <c r="D80" s="16"/>
+      <c r="E80" s="16"/>
+      <c r="F80" s="16"/>
+      <c r="G80" s="16"/>
+      <c r="H80" s="16"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="11" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B81" s="17" t="s">
-        <v>142</v>
-      </c>
-      <c r="C81" s="26" t="n">
-        <v>110000</v>
+        <v>150</v>
+      </c>
+      <c r="C81" s="27" t="n">
+        <v>160000</v>
       </c>
       <c r="D81" s="2"/>
       <c r="E81" s="2"/>
       <c r="F81" s="2"/>
       <c r="G81" s="2"/>
       <c r="H81" s="17" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="2"/>
-      <c r="B82" s="2"/>
-      <c r="C82" s="2"/>
+      <c r="A82" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="B82" s="17" t="s">
+        <v>150</v>
+      </c>
+      <c r="C82" s="27" t="n">
+        <v>170000</v>
+      </c>
       <c r="D82" s="2"/>
       <c r="E82" s="2"/>
       <c r="F82" s="2"/>
       <c r="G82" s="2"/>
-      <c r="H82" s="2"/>
+      <c r="H82" s="17" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="B83" s="16"/>
-      <c r="C83" s="16"/>
-      <c r="D83" s="16"/>
-      <c r="E83" s="16"/>
-      <c r="F83" s="16"/>
-      <c r="G83" s="16"/>
-      <c r="H83" s="16"/>
+      <c r="A83" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="B83" s="17" t="s">
+        <v>150</v>
+      </c>
+      <c r="C83" s="27" t="n">
+        <v>70000</v>
+      </c>
+      <c r="D83" s="2"/>
+      <c r="E83" s="2"/>
+      <c r="F83" s="2"/>
+      <c r="G83" s="2"/>
+      <c r="H83" s="17" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B84" s="6"/>
-      <c r="C84" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="D84" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="E84" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F84" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G84" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H84" s="6"/>
+      <c r="A84" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="B84" s="17" t="s">
+        <v>150</v>
+      </c>
+      <c r="C84" s="27" t="n">
+        <v>65000</v>
+      </c>
+      <c r="D84" s="2"/>
+      <c r="E84" s="2"/>
+      <c r="F84" s="2"/>
+      <c r="G84" s="2"/>
+      <c r="H84" s="17" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="11" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="B85" s="17" t="s">
-        <v>172</v>
-      </c>
-      <c r="C85" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="D85" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="E85" s="24" t="n">
-        <v>3</v>
-      </c>
-      <c r="F85" s="24" t="n">
-        <v>4</v>
-      </c>
-      <c r="G85" s="24" t="n">
-        <v>5</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="C85" s="27" t="n">
+        <v>55000</v>
+      </c>
+      <c r="D85" s="2"/>
+      <c r="E85" s="2"/>
+      <c r="F85" s="2"/>
+      <c r="G85" s="2"/>
       <c r="H85" s="17" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="11" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B86" s="17" t="s">
-        <v>172</v>
-      </c>
-      <c r="C86" s="24" t="n">
+        <v>150</v>
+      </c>
+      <c r="C86" s="27" t="n">
+        <v>110000</v>
+      </c>
+      <c r="D86" s="2"/>
+      <c r="E86" s="2"/>
+      <c r="F86" s="2"/>
+      <c r="G86" s="2"/>
+      <c r="H86" s="17" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="2"/>
+      <c r="B87" s="2"/>
+      <c r="C87" s="2"/>
+      <c r="D87" s="2"/>
+      <c r="E87" s="2"/>
+      <c r="F87" s="2"/>
+      <c r="G87" s="2"/>
+      <c r="H87" s="2"/>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="B88" s="16"/>
+      <c r="C88" s="16"/>
+      <c r="D88" s="16"/>
+      <c r="E88" s="16"/>
+      <c r="F88" s="16"/>
+      <c r="G88" s="16"/>
+      <c r="H88" s="16"/>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B89" s="6"/>
+      <c r="C89" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D89" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E89" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F89" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="G89" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="H89" s="6"/>
+    </row>
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="B90" s="17" t="s">
+        <v>180</v>
+      </c>
+      <c r="C90" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D90" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E90" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="D86" s="24" t="n">
+      <c r="F90" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="G90" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="E86" s="24" t="n">
-        <v>8</v>
-      </c>
-      <c r="F86" s="24" t="n">
-        <v>11</v>
-      </c>
-      <c r="G86" s="24" t="n">
-        <v>14</v>
-      </c>
-      <c r="H86" s="17" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="11" t="s">
-        <v>170</v>
-      </c>
-      <c r="B87" s="17" t="s">
-        <v>172</v>
-      </c>
-      <c r="C87" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="D87" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E87" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="F87" s="24" t="n">
-        <v>3</v>
-      </c>
-      <c r="G87" s="24" t="n">
-        <v>4</v>
-      </c>
-      <c r="H87" s="17" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="2"/>
-      <c r="B88" s="2"/>
-      <c r="C88" s="2"/>
-      <c r="D88" s="2"/>
-      <c r="E88" s="2"/>
-      <c r="F88" s="2"/>
-      <c r="G88" s="2"/>
-      <c r="H88" s="2"/>
-    </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="15" t="s">
-        <v>175</v>
-      </c>
-      <c r="B89" s="16"/>
-      <c r="C89" s="16"/>
-      <c r="D89" s="16"/>
-      <c r="E89" s="16"/>
-      <c r="F89" s="16"/>
-      <c r="G89" s="16"/>
-      <c r="H89" s="16"/>
-    </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B90" s="6"/>
-      <c r="C90" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="D90" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="E90" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F90" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G90" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H90" s="6"/>
+      <c r="H90" s="17" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="11" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="B91" s="17" t="s">
-        <v>177</v>
-      </c>
-      <c r="C91" s="26" t="n">
-        <v>50000</v>
-      </c>
-      <c r="D91" s="26" t="n">
-        <v>150000</v>
-      </c>
-      <c r="E91" s="26" t="n">
-        <v>300000</v>
-      </c>
-      <c r="F91" s="26" t="n">
-        <v>500000</v>
-      </c>
-      <c r="G91" s="26" t="n">
-        <v>700000</v>
+        <v>180</v>
+      </c>
+      <c r="C91" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D91" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="E91" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="F91" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="G91" s="21" t="n">
+        <v>14</v>
       </c>
       <c r="H91" s="17" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="11" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B92" s="17" t="s">
-        <v>177</v>
-      </c>
-      <c r="C92" s="26" t="n">
-        <v>60000</v>
-      </c>
-      <c r="D92" s="26" t="n">
-        <v>90000</v>
-      </c>
-      <c r="E92" s="26" t="n">
-        <v>140000</v>
-      </c>
-      <c r="F92" s="26" t="n">
-        <v>200000</v>
-      </c>
-      <c r="G92" s="26" t="n">
-        <v>260000</v>
+        <v>180</v>
+      </c>
+      <c r="C92" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D92" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E92" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="F92" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="G92" s="21" t="n">
+        <v>4</v>
       </c>
       <c r="H92" s="17" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="B93" s="17" t="s">
-        <v>182</v>
-      </c>
-      <c r="C93" s="26" t="n">
-        <v>100</v>
-      </c>
+      <c r="A93" s="2"/>
+      <c r="B93" s="2"/>
+      <c r="C93" s="2"/>
       <c r="D93" s="2"/>
       <c r="E93" s="2"/>
       <c r="F93" s="2"/>
       <c r="G93" s="2"/>
-      <c r="H93" s="17" t="s">
-        <v>143</v>
-      </c>
+      <c r="H93" s="2"/>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="11" t="s">
+      <c r="A94" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="B94" s="17" t="s">
-        <v>142</v>
-      </c>
-      <c r="C94" s="26" t="n">
-        <v>3000</v>
-      </c>
-      <c r="D94" s="2"/>
-      <c r="E94" s="2"/>
-      <c r="F94" s="2"/>
-      <c r="G94" s="2"/>
-      <c r="H94" s="17" t="s">
-        <v>143</v>
-      </c>
+      <c r="B94" s="16"/>
+      <c r="C94" s="16"/>
+      <c r="D94" s="16"/>
+      <c r="E94" s="16"/>
+      <c r="F94" s="16"/>
+      <c r="G94" s="16"/>
+      <c r="H94" s="16"/>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="B95" s="17" t="s">
-        <v>185</v>
-      </c>
-      <c r="C95" s="26" t="n">
-        <v>2500</v>
-      </c>
-      <c r="D95" s="2"/>
-      <c r="E95" s="2"/>
-      <c r="F95" s="2"/>
-      <c r="G95" s="2"/>
-      <c r="H95" s="17" t="s">
-        <v>143</v>
-      </c>
+      <c r="A95" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B95" s="6"/>
+      <c r="C95" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D95" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E95" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F95" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="G95" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="H95" s="6"/>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="B96" s="17" t="s">
+        <v>185</v>
+      </c>
+      <c r="C96" s="27" t="n">
+        <v>50000</v>
+      </c>
+      <c r="D96" s="27" t="n">
+        <v>150000</v>
+      </c>
+      <c r="E96" s="27" t="n">
+        <v>300000</v>
+      </c>
+      <c r="F96" s="27" t="n">
+        <v>500000</v>
+      </c>
+      <c r="G96" s="27" t="n">
+        <v>700000</v>
+      </c>
+      <c r="H96" s="17" t="s">
         <v>186</v>
       </c>
-      <c r="B96" s="17" t="s">
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="11" t="s">
         <v>187</v>
       </c>
-      <c r="C96" s="24" t="n">
-        <v>3</v>
-      </c>
-      <c r="D96" s="2"/>
-      <c r="E96" s="2"/>
-      <c r="F96" s="2"/>
-      <c r="G96" s="2"/>
-      <c r="H96" s="17" t="s">
+      <c r="B97" s="17" t="s">
+        <v>185</v>
+      </c>
+      <c r="C97" s="27" t="n">
+        <v>60000</v>
+      </c>
+      <c r="D97" s="27" t="n">
+        <v>90000</v>
+      </c>
+      <c r="E97" s="27" t="n">
+        <v>140000</v>
+      </c>
+      <c r="F97" s="27" t="n">
+        <v>200000</v>
+      </c>
+      <c r="G97" s="27" t="n">
+        <v>260000</v>
+      </c>
+      <c r="H97" s="17" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="2"/>
-      <c r="B97" s="2"/>
-      <c r="C97" s="2"/>
-      <c r="D97" s="2"/>
-      <c r="E97" s="2"/>
-      <c r="F97" s="2"/>
-      <c r="G97" s="2"/>
-      <c r="H97" s="2"/>
-    </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="15" t="s">
+      <c r="A98" s="11" t="s">
         <v>189</v>
       </c>
-      <c r="B98" s="16"/>
-      <c r="C98" s="16"/>
-      <c r="D98" s="16"/>
-      <c r="E98" s="16"/>
-      <c r="F98" s="16"/>
-      <c r="G98" s="16"/>
-      <c r="H98" s="16"/>
+      <c r="B98" s="17" t="s">
+        <v>190</v>
+      </c>
+      <c r="C98" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="D98" s="2"/>
+      <c r="E98" s="2"/>
+      <c r="F98" s="2"/>
+      <c r="G98" s="2"/>
+      <c r="H98" s="17" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="11" t="s">
-        <v>190</v>
-      </c>
-      <c r="B99" s="17"/>
-      <c r="C99" s="29" t="n">
-        <v>0.25</v>
+        <v>191</v>
+      </c>
+      <c r="B99" s="17" t="s">
+        <v>150</v>
+      </c>
+      <c r="C99" s="27" t="n">
+        <v>3000</v>
       </c>
       <c r="D99" s="2"/>
       <c r="E99" s="2"/>
       <c r="F99" s="2"/>
       <c r="G99" s="2"/>
       <c r="H99" s="17" t="s">
-        <v>191</v>
+        <v>151</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="11" t="s">
         <v>192</v>
       </c>
-      <c r="B100" s="17"/>
-      <c r="C100" s="29" t="n">
-        <v>0.03</v>
+      <c r="B100" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="C100" s="27" t="n">
+        <v>2500</v>
       </c>
       <c r="D100" s="2"/>
       <c r="E100" s="2"/>
       <c r="F100" s="2"/>
       <c r="G100" s="2"/>
       <c r="H100" s="17" t="s">
-        <v>193</v>
+        <v>151</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4644,17 +4689,17 @@
         <v>194</v>
       </c>
       <c r="B101" s="17" t="s">
-        <v>177</v>
-      </c>
-      <c r="C101" s="32" t="n">
-        <v>250000</v>
+        <v>195</v>
+      </c>
+      <c r="C101" s="21" t="n">
+        <v>3</v>
       </c>
       <c r="D101" s="2"/>
       <c r="E101" s="2"/>
       <c r="F101" s="2"/>
       <c r="G101" s="2"/>
       <c r="H101" s="17" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4668,51 +4713,123 @@
       <c r="H102" s="2"/>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B103" s="6"/>
-      <c r="C103" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="D103" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="E103" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F103" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G103" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H103" s="6"/>
+      <c r="A103" s="15" t="s">
+        <v>197</v>
+      </c>
+      <c r="B103" s="16"/>
+      <c r="C103" s="16"/>
+      <c r="D103" s="16"/>
+      <c r="E103" s="16"/>
+      <c r="F103" s="16"/>
+      <c r="G103" s="16"/>
+      <c r="H103" s="16"/>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="B104" s="17" t="s">
-        <v>177</v>
-      </c>
-      <c r="C104" s="32" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="D104" s="32" t="n">
-        <v>8000000</v>
-      </c>
-      <c r="E104" s="32" t="n">
+        <v>198</v>
+      </c>
+      <c r="B104" s="17"/>
+      <c r="C104" s="23" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D104" s="2"/>
+      <c r="E104" s="2"/>
+      <c r="F104" s="2"/>
+      <c r="G104" s="2"/>
+      <c r="H104" s="17" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="B105" s="17"/>
+      <c r="C105" s="23" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D105" s="2"/>
+      <c r="E105" s="2"/>
+      <c r="F105" s="2"/>
+      <c r="G105" s="2"/>
+      <c r="H105" s="17" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="B106" s="17" t="s">
+        <v>185</v>
+      </c>
+      <c r="C106" s="32" t="n">
+        <v>250000</v>
+      </c>
+      <c r="D106" s="2"/>
+      <c r="E106" s="2"/>
+      <c r="F106" s="2"/>
+      <c r="G106" s="2"/>
+      <c r="H106" s="17" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="2"/>
+      <c r="B107" s="2"/>
+      <c r="C107" s="2"/>
+      <c r="D107" s="2"/>
+      <c r="E107" s="2"/>
+      <c r="F107" s="2"/>
+      <c r="G107" s="2"/>
+      <c r="H107" s="2"/>
+    </row>
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B108" s="6"/>
+      <c r="C108" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D108" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E108" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F108" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="G108" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="H108" s="6"/>
+    </row>
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="11" t="s">
+        <v>204</v>
+      </c>
+      <c r="B109" s="17" t="s">
+        <v>185</v>
+      </c>
+      <c r="C109" s="32" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="D109" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="F104" s="32" t="n">
-        <v>15000000</v>
-      </c>
-      <c r="G104" s="32" t="n">
+      <c r="E109" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="H104" s="17" t="s">
-        <v>197</v>
+      <c r="F109" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G109" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" s="17" t="s">
+        <v>205</v>
       </c>
     </row>
   </sheetData>
@@ -4731,7 +4848,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
@@ -4742,7 +4859,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -4754,7 +4871,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4776,7 +4893,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="7" t="s">
@@ -4798,55 +4915,57 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="B5" s="2"/>
-      <c r="C5" s="8" t="n">
-        <f aca="false">ROUND(Assumptions!C$14*Assumptions!$F$7,0)</f>
-        <v>20</v>
-      </c>
-      <c r="D5" s="8" t="n">
-        <f aca="false">ROUND(Assumptions!D$14*Assumptions!$F$7,0)</f>
-        <v>80</v>
-      </c>
-      <c r="E5" s="8" t="n">
-        <f aca="false">ROUND(Assumptions!E$14*Assumptions!$F$7,0)</f>
-        <v>200</v>
-      </c>
-      <c r="F5" s="8" t="n">
-        <f aca="false">ROUND(Assumptions!F$14*Assumptions!$F$7,0)</f>
-        <v>400</v>
-      </c>
-      <c r="G5" s="8" t="n">
-        <f aca="false">ROUND(Assumptions!G$14*Assumptions!$F$7,0)</f>
-        <v>700</v>
-      </c>
-      <c r="H5" s="2"/>
+      <c r="C5" s="33" t="n">
+        <f aca="false">MAX(0,MIN(ROUND(Assumptions!C$18*Assumptions!$F$7,0),$C$10))</f>
+        <v>3000</v>
+      </c>
+      <c r="D5" s="33" t="n">
+        <f aca="false">MAX(0,MIN(ROUND(Assumptions!D$18*Assumptions!$F$7,0),$C$10-C6))</f>
+        <v>3000</v>
+      </c>
+      <c r="E5" s="33" t="n">
+        <f aca="false">MAX(0,MIN(ROUND(Assumptions!E$18*Assumptions!$F$7,0),$C$10-D6))</f>
+        <v>2433</v>
+      </c>
+      <c r="F5" s="33" t="n">
+        <f aca="false">MAX(0,MIN(ROUND(Assumptions!F$18*Assumptions!$F$7,0),$C$10-E6))</f>
+        <v>0</v>
+      </c>
+      <c r="G5" s="33" t="n">
+        <f aca="false">MAX(0,MIN(ROUND(Assumptions!G$18*Assumptions!$F$7,0),$C$10-F6))</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>209</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="33" t="n">
         <f aca="false">C5</f>
-        <v>20</v>
+        <v>3000</v>
       </c>
       <c r="D6" s="33" t="n">
         <f aca="false">C6+D5</f>
-        <v>100</v>
+        <v>6000</v>
       </c>
       <c r="E6" s="33" t="n">
         <f aca="false">D6+E5</f>
-        <v>300</v>
+        <v>8433</v>
       </c>
       <c r="F6" s="33" t="n">
         <f aca="false">E6+F5</f>
-        <v>700</v>
+        <v>8433</v>
       </c>
       <c r="G6" s="33" t="n">
         <f aca="false">F6+G5</f>
-        <v>1400</v>
+        <v>8433</v>
       </c>
       <c r="H6" s="2"/>
     </row>
@@ -4856,57 +4975,111 @@
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="33" t="n">
-        <f aca="false">C$5*Assumptions!$C$28</f>
-        <v>20</v>
+        <f aca="false">C$5*Assumptions!$C$33</f>
+        <v>3000</v>
       </c>
       <c r="D7" s="33" t="n">
-        <f aca="false">C$5*Assumptions!$D$28+D$5*Assumptions!$C$28</f>
-        <v>99.4</v>
+        <f aca="false">C$5*Assumptions!$D$33+D$5*Assumptions!$C$33</f>
+        <v>5910</v>
       </c>
       <c r="E7" s="33" t="n">
-        <f aca="false">C$5*Assumptions!$E$28+D$5*Assumptions!$D$28+E$5*Assumptions!$C$28</f>
-        <v>296.6</v>
+        <f aca="false">C$5*Assumptions!$E$33+D$5*Assumptions!$D$33+E$5*Assumptions!$C$33</f>
+        <v>8193</v>
       </c>
       <c r="F7" s="33" t="n">
-        <f aca="false">C$5*Assumptions!$F$28+D$5*Assumptions!$E$28+E$5*Assumptions!$D$28+F$5*Assumptions!$C$28</f>
-        <v>688.8</v>
+        <f aca="false">C$5*Assumptions!$F$33+D$5*Assumptions!$E$33+E$5*Assumptions!$D$33+F$5*Assumptions!$C$33</f>
+        <v>8030.01</v>
       </c>
       <c r="G7" s="33" t="n">
-        <f aca="false">C$5*Assumptions!$G$28+D$5*Assumptions!$F$28+E$5*Assumptions!$E$28+F$5*Assumptions!$D$28+G$5*Assumptions!$C$28</f>
-        <v>1371.8</v>
+        <f aca="false">C$5*Assumptions!$G$33+D$5*Assumptions!$F$33+E$5*Assumptions!$E$33+F$5*Assumptions!$D$33+G$5*Assumptions!$C$33</f>
+        <v>7921.35</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="33" t="n">
         <f aca="false">C7/2</f>
-        <v>10</v>
+        <v>1500</v>
       </c>
       <c r="D8" s="33" t="n">
         <f aca="false">(C7+D7)/2</f>
-        <v>59.7</v>
+        <v>4455</v>
       </c>
       <c r="E8" s="33" t="n">
         <f aca="false">(D7+E7)/2</f>
-        <v>198</v>
+        <v>7051.5</v>
       </c>
       <c r="F8" s="33" t="n">
         <f aca="false">(E7+F7)/2</f>
-        <v>492.7</v>
+        <v>8111.505</v>
       </c>
       <c r="G8" s="33" t="n">
         <f aca="false">(F7+G7)/2</f>
-        <v>1030.3</v>
+        <v>7975.68</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>204</v>
-      </c>
+        <v>213</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" s="26" t="n">
+        <f aca="false">ROUND(MIN(Assumptions!$C$13,Assumptions!$C$13*Assumptions!$C$14*Assumptions!$C$15*Assumptions!$F$7),0)</f>
+        <v>8433</v>
+      </c>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B11" s="2"/>
+      <c r="C11" s="33" t="n">
+        <f aca="false">$C$10-C6</f>
+        <v>5433</v>
+      </c>
+      <c r="D11" s="33" t="n">
+        <f aca="false">$C$10-D6</f>
+        <v>2433</v>
+      </c>
+      <c r="E11" s="33" t="n">
+        <f aca="false">$C$10-E6</f>
+        <v>0</v>
+      </c>
+      <c r="F11" s="33" t="n">
+        <f aca="false">$C$10-F6</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="33" t="n">
+        <f aca="false">$C$10-G6</f>
+        <v>0</v>
+      </c>
+      <c r="H11" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -4935,7 +5108,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -4947,7 +5120,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4969,29 +5142,29 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="7" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="H4" s="6"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="B5" s="16"/>
       <c r="C5" s="16"/>
@@ -5003,7 +5176,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="34" t="n">
@@ -5027,39 +5200,39 @@
         <v>1</v>
       </c>
       <c r="H6" s="17" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="34" t="n">
-        <f aca="false">Assumptions!C$28</f>
+        <f aca="false">Assumptions!C$33</f>
         <v>1</v>
       </c>
       <c r="D7" s="34" t="n">
-        <f aca="false">Assumptions!D$28</f>
+        <f aca="false">Assumptions!D$33</f>
         <v>0.97</v>
       </c>
       <c r="E7" s="34" t="n">
-        <f aca="false">Assumptions!E$28</f>
+        <f aca="false">Assumptions!E$33</f>
         <v>0.95</v>
       </c>
       <c r="F7" s="34" t="n">
-        <f aca="false">Assumptions!F$28</f>
+        <f aca="false">Assumptions!F$33</f>
         <v>0.94</v>
       </c>
       <c r="G7" s="34" t="n">
-        <f aca="false">Assumptions!G$28</f>
+        <f aca="false">Assumptions!G$33</f>
         <v>0.93</v>
       </c>
       <c r="H7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="35" t="n">
@@ -5086,7 +5259,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="B9" s="16"/>
       <c r="C9" s="16"/>
@@ -5098,88 +5271,88 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="33" t="n">
-        <f aca="false">Assumptions!$F$19*Assumptions!C$26*Assumptions!$F$8*C7</f>
-        <v>210</v>
+        <f aca="false">Assumptions!$F$24*Assumptions!C$31*Assumptions!$F$8*C7</f>
+        <v>121.38</v>
       </c>
       <c r="D10" s="33" t="n">
-        <f aca="false">Assumptions!$F$19*Assumptions!D$26*Assumptions!$F$8*D7</f>
-        <v>543.2</v>
+        <f aca="false">Assumptions!$F$24*Assumptions!D$31*Assumptions!$F$8*D7</f>
+        <v>313.9696</v>
       </c>
       <c r="E10" s="33" t="n">
-        <f aca="false">Assumptions!$F$19*Assumptions!E$26*Assumptions!$F$8*E7</f>
-        <v>798</v>
+        <f aca="false">Assumptions!$F$24*Assumptions!E$31*Assumptions!$F$8*E7</f>
+        <v>461.244</v>
       </c>
       <c r="F10" s="33" t="n">
-        <f aca="false">Assumptions!$F$19*Assumptions!F$26*Assumptions!$F$8*F7</f>
-        <v>987</v>
+        <f aca="false">Assumptions!$F$24*Assumptions!F$31*Assumptions!$F$8*F7</f>
+        <v>570.486</v>
       </c>
       <c r="G10" s="33" t="n">
-        <f aca="false">Assumptions!$F$19*Assumptions!G$26*Assumptions!$F$8*G7</f>
-        <v>1106.7</v>
+        <f aca="false">Assumptions!$F$24*Assumptions!G$31*Assumptions!$F$8*G7</f>
+        <v>639.6726</v>
       </c>
       <c r="H10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="33" t="n">
         <f aca="false">C10</f>
-        <v>210</v>
+        <v>121.38</v>
       </c>
       <c r="D11" s="33" t="n">
         <f aca="false">MAX(0,D10-C10)</f>
-        <v>333.2</v>
+        <v>192.5896</v>
       </c>
       <c r="E11" s="33" t="n">
         <f aca="false">MAX(0,E10-D10)</f>
-        <v>254.8</v>
+        <v>147.2744</v>
       </c>
       <c r="F11" s="33" t="n">
         <f aca="false">MAX(0,F10-E10)</f>
-        <v>189</v>
+        <v>109.242</v>
       </c>
       <c r="G11" s="33" t="n">
         <f aca="false">MAX(0,G10-F10)</f>
-        <v>119.7</v>
+        <v>69.1866000000001</v>
       </c>
       <c r="H11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="33" t="n">
-        <f aca="false">Assumptions!$F$19*Assumptions!C$27*Assumptions!$F$8*12*C8</f>
-        <v>84000</v>
+        <f aca="false">Assumptions!$F$24*Assumptions!C$32*Assumptions!$F$8*12*C8</f>
+        <v>48552</v>
       </c>
       <c r="D12" s="33" t="n">
-        <f aca="false">Assumptions!$F$19*Assumptions!D$27*Assumptions!$F$8*12*D8</f>
-        <v>325920</v>
+        <f aca="false">Assumptions!$F$24*Assumptions!D$32*Assumptions!$F$8*12*D8</f>
+        <v>188381.76</v>
       </c>
       <c r="E12" s="33" t="n">
-        <f aca="false">Assumptions!$F$19*Assumptions!E$27*Assumptions!$F$8*12*E8</f>
-        <v>478800</v>
+        <f aca="false">Assumptions!$F$24*Assumptions!E$32*Assumptions!$F$8*12*E8</f>
+        <v>276746.4</v>
       </c>
       <c r="F12" s="33" t="n">
-        <f aca="false">Assumptions!$F$19*Assumptions!F$27*Assumptions!$F$8*12*F8</f>
-        <v>552720</v>
+        <f aca="false">Assumptions!$F$24*Assumptions!F$32*Assumptions!$F$8*12*F8</f>
+        <v>319472.16</v>
       </c>
       <c r="G12" s="33" t="n">
-        <f aca="false">Assumptions!$F$19*Assumptions!G$27*Assumptions!$F$8*12*G8</f>
-        <v>624960</v>
+        <f aca="false">Assumptions!$F$24*Assumptions!G$32*Assumptions!$F$8*12*G8</f>
+        <v>361226.88</v>
       </c>
       <c r="H12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="B13" s="16"/>
       <c r="C13" s="16"/>
@@ -5191,117 +5364,117 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="36" t="n">
-        <f aca="false">Assumptions!$C$41*3*MIN(1,Assumptions!C$32*Assumptions!$F$9)*C7</f>
+        <f aca="false">Assumptions!$C$46*3*MIN(1,Assumptions!C$37*Assumptions!$F$9)*C7</f>
         <v>4.2</v>
       </c>
       <c r="D14" s="36" t="n">
-        <f aca="false">Assumptions!$C$41*3*MIN(1,Assumptions!D$32*Assumptions!$F$9)*D7</f>
+        <f aca="false">Assumptions!$C$46*3*MIN(1,Assumptions!D$37*Assumptions!$F$9)*D7</f>
         <v>12.222</v>
       </c>
       <c r="E14" s="36" t="n">
-        <f aca="false">Assumptions!$C$41*3*MIN(1,Assumptions!E$32*Assumptions!$F$9)*E7</f>
+        <f aca="false">Assumptions!$C$46*3*MIN(1,Assumptions!E$37*Assumptions!$F$9)*E7</f>
         <v>19.95</v>
       </c>
       <c r="F14" s="36" t="n">
-        <f aca="false">Assumptions!$C$41*3*MIN(1,Assumptions!F$32*Assumptions!$F$9)*F7</f>
+        <f aca="false">Assumptions!$C$46*3*MIN(1,Assumptions!F$37*Assumptions!$F$9)*F7</f>
         <v>25.2672</v>
       </c>
       <c r="G14" s="36" t="n">
-        <f aca="false">Assumptions!$C$41*3*MIN(1,Assumptions!G$32*Assumptions!$F$9)*G7</f>
+        <f aca="false">Assumptions!$C$46*3*MIN(1,Assumptions!G$37*Assumptions!$F$9)*G7</f>
         <v>29.6856</v>
       </c>
       <c r="H14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="36" t="n">
-        <f aca="false">Assumptions!$F$20*Assumptions!C$33*MIN(1,Assumptions!C$34*Assumptions!$F$9)*C7</f>
-        <v>1.296</v>
+        <f aca="false">Assumptions!$F$25*Assumptions!C$38*MIN(1,Assumptions!C$39*Assumptions!$F$9)*C7</f>
+        <v>0.67712</v>
       </c>
       <c r="D15" s="36" t="n">
-        <f aca="false">Assumptions!$F$20*Assumptions!D$33*MIN(1,Assumptions!D$34*Assumptions!$F$9)*D7</f>
-        <v>4.7142</v>
+        <f aca="false">Assumptions!$F$25*Assumptions!D$38*MIN(1,Assumptions!D$39*Assumptions!$F$9)*D7</f>
+        <v>2.463024</v>
       </c>
       <c r="E15" s="36" t="n">
-        <f aca="false">Assumptions!$F$20*Assumptions!E$33*MIN(1,Assumptions!E$34*Assumptions!$F$9)*E7</f>
-        <v>9.234</v>
+        <f aca="false">Assumptions!$F$25*Assumptions!E$38*MIN(1,Assumptions!E$39*Assumptions!$F$9)*E7</f>
+        <v>4.82448</v>
       </c>
       <c r="F15" s="36" t="n">
-        <f aca="false">Assumptions!$F$20*Assumptions!F$33*MIN(1,Assumptions!F$34*Assumptions!$F$9)*F7</f>
-        <v>12.9438</v>
+        <f aca="false">Assumptions!$F$25*Assumptions!F$38*MIN(1,Assumptions!F$39*Assumptions!$F$9)*F7</f>
+        <v>6.762736</v>
       </c>
       <c r="G15" s="36" t="n">
-        <f aca="false">Assumptions!$F$20*Assumptions!G$33*MIN(1,Assumptions!G$34*Assumptions!$F$9)*G7</f>
-        <v>16.27128</v>
+        <f aca="false">Assumptions!$F$25*Assumptions!G$38*MIN(1,Assumptions!G$39*Assumptions!$F$9)*G7</f>
+        <v>8.5012416</v>
       </c>
       <c r="H15" s="2"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="36" t="n">
-        <f aca="false">Assumptions!$C$41*MIN(1,Assumptions!C$37*Assumptions!$F$9)*C7</f>
+        <f aca="false">Assumptions!$C$46*MIN(1,Assumptions!C$42*Assumptions!$F$9)*C7</f>
         <v>0</v>
       </c>
       <c r="D16" s="36" t="n">
-        <f aca="false">Assumptions!$C$41*MIN(1,Assumptions!D$37*Assumptions!$F$9)*D7</f>
+        <f aca="false">Assumptions!$C$46*MIN(1,Assumptions!D$42*Assumptions!$F$9)*D7</f>
         <v>0.5432</v>
       </c>
       <c r="E16" s="36" t="n">
-        <f aca="false">Assumptions!$C$41*MIN(1,Assumptions!E$37*Assumptions!$F$9)*E7</f>
+        <f aca="false">Assumptions!$C$46*MIN(1,Assumptions!E$42*Assumptions!$F$9)*E7</f>
         <v>1.33</v>
       </c>
       <c r="F16" s="36" t="n">
-        <f aca="false">Assumptions!$C$41*MIN(1,Assumptions!F$37*Assumptions!$F$9)*F7</f>
+        <f aca="false">Assumptions!$C$46*MIN(1,Assumptions!F$42*Assumptions!$F$9)*F7</f>
         <v>2.1056</v>
       </c>
       <c r="G16" s="36" t="n">
-        <f aca="false">Assumptions!$C$41*MIN(1,Assumptions!G$37*Assumptions!$F$9)*G7</f>
+        <f aca="false">Assumptions!$C$46*MIN(1,Assumptions!G$42*Assumptions!$F$9)*G7</f>
         <v>2.604</v>
       </c>
       <c r="H16" s="2"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="36" t="n">
         <f aca="false">C14+C15+C16</f>
-        <v>5.496</v>
+        <v>4.87712</v>
       </c>
       <c r="D17" s="36" t="n">
         <f aca="false">D14+D15+D16</f>
-        <v>17.4794</v>
+        <v>15.228224</v>
       </c>
       <c r="E17" s="36" t="n">
         <f aca="false">E14+E15+E16</f>
-        <v>30.514</v>
+        <v>26.10448</v>
       </c>
       <c r="F17" s="36" t="n">
         <f aca="false">F14+F15+F16</f>
-        <v>40.3166</v>
+        <v>34.135536</v>
       </c>
       <c r="G17" s="36" t="n">
         <f aca="false">G14+G15+G16</f>
-        <v>48.56088</v>
+        <v>40.7908416</v>
       </c>
       <c r="H17" s="17" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="15" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="B18" s="16"/>
       <c r="C18" s="16"/>
@@ -5313,254 +5486,254 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="37" t="n">
-        <f aca="false">C14/3*Assumptions!$C$42*12*(1-Assumptions!$C$44)*C6</f>
+        <f aca="false">C14/3*Assumptions!$C$47*12*(1-Assumptions!$C$49)*C6</f>
         <v>293.664</v>
       </c>
       <c r="D19" s="37" t="n">
-        <f aca="false">D14/3*Assumptions!$C$42*12*(1-Assumptions!$C$44)*D6</f>
+        <f aca="false">D14/3*Assumptions!$C$47*12*(1-Assumptions!$C$49)*D6</f>
         <v>1709.12448</v>
       </c>
       <c r="E19" s="37" t="n">
-        <f aca="false">E14/3*Assumptions!$C$42*12*(1-Assumptions!$C$44)*E6</f>
+        <f aca="false">E14/3*Assumptions!$C$47*12*(1-Assumptions!$C$49)*E6</f>
         <v>2789.808</v>
       </c>
       <c r="F19" s="37" t="n">
-        <f aca="false">F14/3*Assumptions!$C$42*12*(1-Assumptions!$C$44)*F6</f>
+        <f aca="false">F14/3*Assumptions!$C$47*12*(1-Assumptions!$C$49)*F6</f>
         <v>3533.365248</v>
       </c>
       <c r="G19" s="37" t="n">
-        <f aca="false">G14/3*Assumptions!$C$42*12*(1-Assumptions!$C$44)*G6</f>
+        <f aca="false">G14/3*Assumptions!$C$47*12*(1-Assumptions!$C$49)*G6</f>
         <v>4151.234304</v>
       </c>
       <c r="H19" s="17" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="37" t="n">
-        <f aca="false">C15*Assumptions!$C$45*12*C6</f>
-        <v>303.264</v>
+        <f aca="false">C15*Assumptions!$C$50*12*C6</f>
+        <v>158.44608</v>
       </c>
       <c r="D20" s="37" t="n">
-        <f aca="false">D15*Assumptions!$C$45*12*D6</f>
-        <v>2206.2456</v>
+        <f aca="false">D15*Assumptions!$C$50*12*D6</f>
+        <v>1152.695232</v>
       </c>
       <c r="E20" s="37" t="n">
-        <f aca="false">E15*Assumptions!$C$45*12*E6</f>
-        <v>4321.512</v>
+        <f aca="false">E15*Assumptions!$C$50*12*E6</f>
+        <v>2257.85664</v>
       </c>
       <c r="F20" s="37" t="n">
-        <f aca="false">F15*Assumptions!$C$45*12*F6</f>
-        <v>6057.6984</v>
+        <f aca="false">F15*Assumptions!$C$50*12*F6</f>
+        <v>3164.960448</v>
       </c>
       <c r="G20" s="37" t="n">
-        <f aca="false">G15*Assumptions!$C$45*12*G6</f>
-        <v>7614.95904</v>
+        <f aca="false">G15*Assumptions!$C$50*12*G6</f>
+        <v>3978.5810688</v>
       </c>
       <c r="H20" s="2"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" s="37" t="n">
-        <f aca="false">C16*Assumptions!$C$46*12*C6</f>
+        <f aca="false">C16*Assumptions!$C$51*12*C6</f>
         <v>0</v>
       </c>
       <c r="D21" s="37" t="n">
-        <f aca="false">D16*Assumptions!$C$46*12*D6</f>
+        <f aca="false">D16*Assumptions!$C$51*12*D6</f>
         <v>645.3216</v>
       </c>
       <c r="E21" s="37" t="n">
-        <f aca="false">E16*Assumptions!$C$46*12*E6</f>
+        <f aca="false">E16*Assumptions!$C$51*12*E6</f>
         <v>1580.04</v>
       </c>
       <c r="F21" s="37" t="n">
-        <f aca="false">F16*Assumptions!$C$46*12*F6</f>
+        <f aca="false">F16*Assumptions!$C$51*12*F6</f>
         <v>2501.4528</v>
       </c>
       <c r="G21" s="37" t="n">
-        <f aca="false">G16*Assumptions!$C$46*12*G6</f>
+        <f aca="false">G16*Assumptions!$C$51*12*G6</f>
         <v>3093.552</v>
       </c>
       <c r="H21" s="2"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="11" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="37" t="n">
-        <f aca="false">C10/1000*Assumptions!$C$48*Assumptions!$C$47*MIN(1,Assumptions!C$35*Assumptions!$F$9)*C6</f>
-        <v>94.5</v>
+        <f aca="false">C10/1000*Assumptions!$C$53*Assumptions!$C$52*MIN(1,Assumptions!C$40*Assumptions!$F$9)*C6</f>
+        <v>54.621</v>
       </c>
       <c r="D22" s="37" t="n">
-        <f aca="false">D10/1000*Assumptions!$C$48*Assumptions!$C$47*MIN(1,Assumptions!D$35*Assumptions!$F$9)*D6</f>
-        <v>1466.64</v>
+        <f aca="false">D10/1000*Assumptions!$C$53*Assumptions!$C$52*MIN(1,Assumptions!D$40*Assumptions!$F$9)*D6</f>
+        <v>847.71792</v>
       </c>
       <c r="E22" s="37" t="n">
-        <f aca="false">E10/1000*Assumptions!$C$48*Assumptions!$C$47*MIN(1,Assumptions!E$35*Assumptions!$F$9)*E6</f>
-        <v>3231.9</v>
+        <f aca="false">E10/1000*Assumptions!$C$53*Assumptions!$C$52*MIN(1,Assumptions!E$40*Assumptions!$F$9)*E6</f>
+        <v>1868.0382</v>
       </c>
       <c r="F22" s="37" t="n">
-        <f aca="false">F10/1000*Assumptions!$C$48*Assumptions!$C$47*MIN(1,Assumptions!F$35*Assumptions!$F$9)*F6</f>
-        <v>4885.65</v>
+        <f aca="false">F10/1000*Assumptions!$C$53*Assumptions!$C$52*MIN(1,Assumptions!F$40*Assumptions!$F$9)*F6</f>
+        <v>2823.9057</v>
       </c>
       <c r="G22" s="37" t="n">
-        <f aca="false">G10/1000*Assumptions!$C$48*Assumptions!$C$47*MIN(1,Assumptions!G$35*Assumptions!$F$9)*G6</f>
-        <v>5976.18</v>
+        <f aca="false">G10/1000*Assumptions!$C$53*Assumptions!$C$52*MIN(1,Assumptions!G$40*Assumptions!$F$9)*G6</f>
+        <v>3454.23204</v>
       </c>
       <c r="H22" s="17" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" s="37" t="n">
-        <f aca="false">Assumptions!$F$22*12*MIN(1,Assumptions!C$36*Assumptions!$F$9)*C8</f>
-        <v>210</v>
+        <f aca="false">Assumptions!$F$27*12*MIN(1,Assumptions!C$41*Assumptions!$F$9)*C8</f>
+        <v>126</v>
       </c>
       <c r="D23" s="37" t="n">
-        <f aca="false">Assumptions!$F$22*12*MIN(1,Assumptions!D$36*Assumptions!$F$9)*D8</f>
-        <v>1222.2</v>
+        <f aca="false">Assumptions!$F$27*12*MIN(1,Assumptions!D$41*Assumptions!$F$9)*D8</f>
+        <v>733.32</v>
       </c>
       <c r="E23" s="37" t="n">
-        <f aca="false">Assumptions!$F$22*12*MIN(1,Assumptions!E$36*Assumptions!$F$9)*E8</f>
-        <v>1995</v>
+        <f aca="false">Assumptions!$F$27*12*MIN(1,Assumptions!E$41*Assumptions!$F$9)*E8</f>
+        <v>1197</v>
       </c>
       <c r="F23" s="37" t="n">
-        <f aca="false">Assumptions!$F$22*12*MIN(1,Assumptions!F$36*Assumptions!$F$9)*F8</f>
-        <v>2368.8</v>
+        <f aca="false">Assumptions!$F$27*12*MIN(1,Assumptions!F$41*Assumptions!$F$9)*F8</f>
+        <v>1421.28</v>
       </c>
       <c r="G23" s="37" t="n">
-        <f aca="false">Assumptions!$F$22*12*MIN(1,Assumptions!G$36*Assumptions!$F$9)*G8</f>
-        <v>2538.9</v>
+        <f aca="false">Assumptions!$F$27*12*MIN(1,Assumptions!G$41*Assumptions!$F$9)*G8</f>
+        <v>1523.34</v>
       </c>
       <c r="H23" s="2"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" s="37" t="n">
-        <f aca="false">C12/1000*Assumptions!$C$49*Assumptions!$C$50*Assumptions!C$38</f>
+        <f aca="false">C12/1000*Assumptions!$C$54*Assumptions!$C$55*Assumptions!C$43</f>
         <v>0</v>
       </c>
       <c r="D24" s="37" t="n">
-        <f aca="false">D12/1000*Assumptions!$C$49*Assumptions!$C$50*Assumptions!D$38</f>
+        <f aca="false">D12/1000*Assumptions!$C$54*Assumptions!$C$55*Assumptions!D$43</f>
         <v>0</v>
       </c>
       <c r="E24" s="37" t="n">
-        <f aca="false">E12/1000*Assumptions!$C$49*Assumptions!$C$50*Assumptions!E$38</f>
-        <v>2298.24</v>
+        <f aca="false">E12/1000*Assumptions!$C$54*Assumptions!$C$55*Assumptions!E$43</f>
+        <v>1328.38272</v>
       </c>
       <c r="F24" s="37" t="n">
-        <f aca="false">F12/1000*Assumptions!$C$49*Assumptions!$C$50*Assumptions!F$38</f>
-        <v>2653.056</v>
+        <f aca="false">F12/1000*Assumptions!$C$54*Assumptions!$C$55*Assumptions!F$43</f>
+        <v>1533.466368</v>
       </c>
       <c r="G24" s="37" t="n">
-        <f aca="false">G12/1000*Assumptions!$C$49*Assumptions!$C$50*Assumptions!G$38</f>
-        <v>2999.808</v>
+        <f aca="false">G12/1000*Assumptions!$C$54*Assumptions!$C$55*Assumptions!G$43</f>
+        <v>1733.889024</v>
       </c>
       <c r="H24" s="2"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" s="38" t="n">
         <f aca="false">SUM(C19:C24)</f>
-        <v>901.428</v>
+        <v>632.73108</v>
       </c>
       <c r="D25" s="38" t="n">
         <f aca="false">SUM(D19:D24)</f>
-        <v>7249.53168</v>
+        <v>5088.179232</v>
       </c>
       <c r="E25" s="38" t="n">
         <f aca="false">SUM(E19:E24)</f>
-        <v>16216.5</v>
+        <v>11021.12556</v>
       </c>
       <c r="F25" s="38" t="n">
         <f aca="false">SUM(F19:F24)</f>
-        <v>22000.022448</v>
+        <v>14978.430564</v>
       </c>
       <c r="G25" s="38" t="n">
         <f aca="false">SUM(G19:G24)</f>
-        <v>26374.633344</v>
+        <v>17934.8284368</v>
       </c>
       <c r="H25" s="2"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="s">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" s="37" t="n">
         <f aca="false">C19+C20</f>
-        <v>596.928</v>
+        <v>452.11008</v>
       </c>
       <c r="D26" s="37" t="n">
         <f aca="false">D19+D20</f>
-        <v>3915.37008</v>
+        <v>2861.819712</v>
       </c>
       <c r="E26" s="37" t="n">
         <f aca="false">E19+E20</f>
-        <v>7111.32</v>
+        <v>5047.66464</v>
       </c>
       <c r="F26" s="37" t="n">
         <f aca="false">F19+F20</f>
-        <v>9591.063648</v>
+        <v>6698.325696</v>
       </c>
       <c r="G26" s="37" t="n">
         <f aca="false">G19+G20</f>
-        <v>11766.193344</v>
+        <v>8129.8153728</v>
       </c>
       <c r="H26" s="2"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" s="37" t="n">
         <f aca="false">C21+C22+C23</f>
-        <v>304.5</v>
+        <v>180.621</v>
       </c>
       <c r="D27" s="37" t="n">
         <f aca="false">D21+D22+D23</f>
-        <v>3334.1616</v>
+        <v>2226.35952</v>
       </c>
       <c r="E27" s="37" t="n">
         <f aca="false">E21+E22+E23</f>
-        <v>6806.94</v>
+        <v>4645.0782</v>
       </c>
       <c r="F27" s="37" t="n">
         <f aca="false">F21+F22+F23</f>
-        <v>9755.9028</v>
+        <v>6746.6385</v>
       </c>
       <c r="G27" s="37" t="n">
         <f aca="false">G21+G22+G23</f>
-        <v>11608.632</v>
+        <v>8071.12404</v>
       </c>
       <c r="H27" s="2"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="15" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="B28" s="16"/>
       <c r="C28" s="16"/>
@@ -5572,117 +5745,117 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="11" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" s="37" t="n">
-        <f aca="false">MIN(Assumptions!$C$55,Assumptions!$F$21*Assumptions!$C$53+Assumptions!$C$54)*Assumptions!$F$10*365*C8</f>
-        <v>202.94</v>
+        <f aca="false">MIN(Assumptions!$C$60,Assumptions!$F$26*Assumptions!$C$58+Assumptions!$C$59)*Assumptions!$F$10*365*C8</f>
+        <v>190.895</v>
       </c>
       <c r="D29" s="37" t="n">
-        <f aca="false">MIN(Assumptions!$C$55,Assumptions!$F$21*Assumptions!$C$53+Assumptions!$C$54)*Assumptions!$F$10*365*D8</f>
-        <v>393.7036</v>
+        <f aca="false">MIN(Assumptions!$C$60,Assumptions!$F$26*Assumptions!$C$58+Assumptions!$C$59)*Assumptions!$F$10*365*D8</f>
+        <v>370.3363</v>
       </c>
       <c r="E29" s="37" t="n">
-        <f aca="false">MIN(Assumptions!$C$55,Assumptions!$F$21*Assumptions!$C$53+Assumptions!$C$54)*Assumptions!$F$10*365*E8</f>
-        <v>385.586</v>
+        <f aca="false">MIN(Assumptions!$C$60,Assumptions!$F$26*Assumptions!$C$58+Assumptions!$C$59)*Assumptions!$F$10*365*E8</f>
+        <v>362.7005</v>
       </c>
       <c r="F29" s="37" t="n">
-        <f aca="false">MIN(Assumptions!$C$55,Assumptions!$F$21*Assumptions!$C$53+Assumptions!$C$54)*Assumptions!$F$10*365*F8</f>
-        <v>381.5272</v>
+        <f aca="false">MIN(Assumptions!$C$60,Assumptions!$F$26*Assumptions!$C$58+Assumptions!$C$59)*Assumptions!$F$10*365*F8</f>
+        <v>358.8826</v>
       </c>
       <c r="G29" s="37" t="n">
-        <f aca="false">MIN(Assumptions!$C$55,Assumptions!$F$21*Assumptions!$C$53+Assumptions!$C$54)*Assumptions!$F$10*365*G8</f>
-        <v>377.4684</v>
+        <f aca="false">MIN(Assumptions!$C$60,Assumptions!$F$26*Assumptions!$C$58+Assumptions!$C$59)*Assumptions!$F$10*365*G8</f>
+        <v>355.0647</v>
       </c>
       <c r="H29" s="17" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="11" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="37" t="n">
-        <f aca="false">Assumptions!$C$56*12*Assumptions!$F$10*C8</f>
+        <f aca="false">Assumptions!$C$61*12*Assumptions!$F$10*C8</f>
         <v>150</v>
       </c>
       <c r="D30" s="37" t="n">
-        <f aca="false">Assumptions!$C$56*12*Assumptions!$F$10*D8</f>
+        <f aca="false">Assumptions!$C$61*12*Assumptions!$F$10*D8</f>
         <v>291</v>
       </c>
       <c r="E30" s="37" t="n">
-        <f aca="false">Assumptions!$C$56*12*Assumptions!$F$10*E8</f>
+        <f aca="false">Assumptions!$C$61*12*Assumptions!$F$10*E8</f>
         <v>285</v>
       </c>
       <c r="F30" s="37" t="n">
-        <f aca="false">Assumptions!$C$56*12*Assumptions!$F$10*F8</f>
+        <f aca="false">Assumptions!$C$61*12*Assumptions!$F$10*F8</f>
         <v>282</v>
       </c>
       <c r="G30" s="37" t="n">
-        <f aca="false">Assumptions!$C$56*12*Assumptions!$F$10*G8</f>
+        <f aca="false">Assumptions!$C$61*12*Assumptions!$F$10*G8</f>
         <v>279</v>
       </c>
       <c r="H30" s="2"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="11" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" s="37" t="n">
-        <f aca="false">C10*Assumptions!$C$47/1000*Assumptions!$C$57*C6</f>
-        <v>3.15</v>
+        <f aca="false">C10*Assumptions!$C$52/1000*Assumptions!$C$62*C6</f>
+        <v>1.8207</v>
       </c>
       <c r="D31" s="37" t="n">
-        <f aca="false">D10*Assumptions!$C$47/1000*Assumptions!$C$57*D6</f>
-        <v>16.296</v>
+        <f aca="false">D10*Assumptions!$C$52/1000*Assumptions!$C$62*D6</f>
+        <v>9.419088</v>
       </c>
       <c r="E31" s="37" t="n">
-        <f aca="false">E10*Assumptions!$C$47/1000*Assumptions!$C$57*E6</f>
-        <v>23.94</v>
+        <f aca="false">E10*Assumptions!$C$52/1000*Assumptions!$C$62*E6</f>
+        <v>13.83732</v>
       </c>
       <c r="F31" s="37" t="n">
-        <f aca="false">F10*Assumptions!$C$47/1000*Assumptions!$C$57*F6</f>
-        <v>29.61</v>
+        <f aca="false">F10*Assumptions!$C$52/1000*Assumptions!$C$62*F6</f>
+        <v>17.11458</v>
       </c>
       <c r="G31" s="37" t="n">
-        <f aca="false">G10*Assumptions!$C$47/1000*Assumptions!$C$57*G6</f>
-        <v>33.201</v>
+        <f aca="false">G10*Assumptions!$C$52/1000*Assumptions!$C$62*G6</f>
+        <v>19.190178</v>
       </c>
       <c r="H31" s="2"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="11" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" s="37" t="n">
-        <f aca="false">C26*Assumptions!$C$58+(C14+C15)*12*Assumptions!$C$59*C6</f>
-        <v>27.203712</v>
+        <f aca="false">C26*Assumptions!$C$63+(C14+C15)*12*Assumptions!$C$64*C6</f>
+        <v>21.89000832</v>
       </c>
       <c r="D32" s="37" t="n">
-        <f aca="false">D26*Assumptions!$C$58+(D14+D15)*12*Assumptions!$C$59*D6</f>
-        <v>174.51605232</v>
+        <f aca="false">D26*Assumptions!$C$63+(D14+D15)*12*Assumptions!$C$64*D6</f>
+        <v>135.858858048</v>
       </c>
       <c r="E32" s="37" t="n">
-        <f aca="false">E26*Assumptions!$C$58+(E14+E15)*12*Assumptions!$C$59*E6</f>
-        <v>311.29068</v>
+        <f aca="false">E26*Assumptions!$C$63+(E14+E15)*12*Assumptions!$C$64*E6</f>
+        <v>235.57040256</v>
       </c>
       <c r="F32" s="37" t="n">
-        <f aca="false">F26*Assumptions!$C$58+(F14+F15)*12*Assumptions!$C$59*F6</f>
-        <v>415.700445792</v>
+        <f aca="false">F26*Assumptions!$C$63+(F14+F15)*12*Assumptions!$C$64*F6</f>
+        <v>309.559214784</v>
       </c>
       <c r="G32" s="37" t="n">
-        <f aca="false">G26*Assumptions!$C$58+(G14+G15)*12*Assumptions!$C$59*G6</f>
-        <v>506.664374976</v>
+        <f aca="false">G26*Assumptions!$C$63+(G14+G15)*12*Assumptions!$C$64*G6</f>
+        <v>373.2372755712</v>
       </c>
       <c r="H32" s="2"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="11" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" s="37" t="n">
@@ -5690,76 +5863,76 @@
         <v>0</v>
       </c>
       <c r="D33" s="37" t="n">
-        <f aca="false">Assumptions!$C$60*D7</f>
+        <f aca="false">Assumptions!$C$65*D7</f>
         <v>19.4</v>
       </c>
       <c r="E33" s="37" t="n">
-        <f aca="false">Assumptions!$C$60*E7</f>
+        <f aca="false">Assumptions!$C$65*E7</f>
         <v>19</v>
       </c>
       <c r="F33" s="37" t="n">
-        <f aca="false">Assumptions!$C$60*F7</f>
+        <f aca="false">Assumptions!$C$65*F7</f>
         <v>18.8</v>
       </c>
       <c r="G33" s="37" t="n">
-        <f aca="false">Assumptions!$C$60*G7</f>
+        <f aca="false">Assumptions!$C$65*G7</f>
         <v>18.6</v>
       </c>
       <c r="H33" s="17" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" s="38" t="n">
         <f aca="false">SUM(C29:C33)</f>
-        <v>383.293712</v>
+        <v>364.60570832</v>
       </c>
       <c r="D34" s="38" t="n">
         <f aca="false">SUM(D29:D33)</f>
-        <v>894.91565232</v>
+        <v>826.014246048</v>
       </c>
       <c r="E34" s="38" t="n">
         <f aca="false">SUM(E29:E33)</f>
-        <v>1024.81668</v>
+        <v>916.10822256</v>
       </c>
       <c r="F34" s="38" t="n">
         <f aca="false">SUM(F29:F33)</f>
-        <v>1127.637645792</v>
+        <v>986.356394784</v>
       </c>
       <c r="G34" s="38" t="n">
         <f aca="false">SUM(G29:G33)</f>
-        <v>1214.933774976</v>
+        <v>1045.0921535712</v>
       </c>
       <c r="H34" s="2"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="B35" s="2"/>
-      <c r="C35" s="27" t="n">
+      <c r="C35" s="28" t="n">
         <f aca="false">C25-C34</f>
-        <v>518.134288</v>
-      </c>
-      <c r="D35" s="27" t="n">
+        <v>268.12537168</v>
+      </c>
+      <c r="D35" s="28" t="n">
         <f aca="false">D25-D34</f>
-        <v>6354.61602768</v>
-      </c>
-      <c r="E35" s="27" t="n">
+        <v>4262.164985952</v>
+      </c>
+      <c r="E35" s="28" t="n">
         <f aca="false">E25-E34</f>
-        <v>15191.68332</v>
-      </c>
-      <c r="F35" s="27" t="n">
+        <v>10105.01733744</v>
+      </c>
+      <c r="F35" s="28" t="n">
         <f aca="false">F25-F34</f>
-        <v>20872.384802208</v>
-      </c>
-      <c r="G35" s="27" t="n">
+        <v>13992.074169216</v>
+      </c>
+      <c r="G35" s="28" t="n">
         <f aca="false">G25-G34</f>
-        <v>25159.699569024</v>
+        <v>16889.7362832288</v>
       </c>
       <c r="H35" s="2"/>
     </row>
@@ -5770,29 +5943,29 @@
       <c r="B36" s="2"/>
       <c r="C36" s="34" t="n">
         <f aca="false">IF(C25=0,0,C35/C25)</f>
-        <v>0.574792759932019</v>
+        <v>0.423758813428289</v>
       </c>
       <c r="D36" s="34" t="n">
         <f aca="false">IF(D25=0,0,D35/D25)</f>
-        <v>0.87655538428932</v>
+        <v>0.837660151424477</v>
       </c>
       <c r="E36" s="34" t="n">
         <f aca="false">IF(E25=0,0,E35/E25)</f>
-        <v>0.936804077328647</v>
+        <v>0.916877072348679</v>
       </c>
       <c r="F36" s="34" t="n">
         <f aca="false">IF(F25=0,0,F35/F25)</f>
-        <v>0.948743795673058</v>
+        <v>0.934148214623055</v>
       </c>
       <c r="G36" s="34" t="n">
         <f aca="false">IF(G25=0,0,G35/G25)</f>
-        <v>0.953935519818235</v>
+        <v>0.941728343973071</v>
       </c>
       <c r="H36" s="2"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="15" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="B37" s="16"/>
       <c r="C37" s="16"/>
@@ -5804,173 +5977,173 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="11" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" s="37" t="n">
-        <f aca="false">Assumptions!$C$78*(1+Assumptions!$C$68)/Assumptions!$C$71*C8</f>
-        <v>1093.75</v>
+        <f aca="false">Assumptions!$C$83*(1+Assumptions!$C$73)/Assumptions!$C$76*C8</f>
+        <v>43.75</v>
       </c>
       <c r="D38" s="37" t="n">
-        <f aca="false">Assumptions!$C$78*(1+Assumptions!$C$68)/Assumptions!$C$71*D8</f>
-        <v>2121.875</v>
+        <f aca="false">Assumptions!$C$83*(1+Assumptions!$C$73)/Assumptions!$C$76*D8</f>
+        <v>84.875</v>
       </c>
       <c r="E38" s="37" t="n">
-        <f aca="false">Assumptions!$C$78*(1+Assumptions!$C$68)/Assumptions!$C$71*E8</f>
-        <v>2078.125</v>
+        <f aca="false">Assumptions!$C$83*(1+Assumptions!$C$73)/Assumptions!$C$76*E8</f>
+        <v>83.125</v>
       </c>
       <c r="F38" s="37" t="n">
-        <f aca="false">Assumptions!$C$78*(1+Assumptions!$C$68)/Assumptions!$C$71*F8</f>
-        <v>2056.25</v>
+        <f aca="false">Assumptions!$C$83*(1+Assumptions!$C$73)/Assumptions!$C$76*F8</f>
+        <v>82.25</v>
       </c>
       <c r="G38" s="37" t="n">
-        <f aca="false">Assumptions!$C$78*(1+Assumptions!$C$68)/Assumptions!$C$71*G8</f>
-        <v>2034.375</v>
+        <f aca="false">Assumptions!$C$83*(1+Assumptions!$C$73)/Assumptions!$C$76*G8</f>
+        <v>81.375</v>
       </c>
       <c r="H38" s="2"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="11" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" s="37" t="n">
-        <f aca="false">Assumptions!$C$79*(1+Assumptions!$C$68)/Assumptions!$C$72*C8+C27*Assumptions!$C$70</f>
-        <v>1384.61666666667</v>
+        <f aca="false">Assumptions!$C$84*(1+Assumptions!$C$73)/Assumptions!$C$77*C8+C27*Assumptions!$C$75</f>
+        <v>40.625</v>
       </c>
       <c r="D39" s="37" t="n">
-        <f aca="false">Assumptions!$C$79*(1+Assumptions!$C$68)/Assumptions!$C$72*D8+D27*Assumptions!$C$70</f>
-        <v>2960.49949333333</v>
+        <f aca="false">Assumptions!$C$84*(1+Assumptions!$C$73)/Assumptions!$C$77*D8+D27*Assumptions!$C$75</f>
+        <v>78.8125</v>
       </c>
       <c r="E39" s="37" t="n">
-        <f aca="false">Assumptions!$C$79*(1+Assumptions!$C$68)/Assumptions!$C$72*E8+E27*Assumptions!$C$70</f>
-        <v>3253.61066666667</v>
+        <f aca="false">Assumptions!$C$84*(1+Assumptions!$C$73)/Assumptions!$C$77*E8+E27*Assumptions!$C$75</f>
+        <v>77.1875</v>
       </c>
       <c r="F39" s="37" t="n">
-        <f aca="false">Assumptions!$C$79*(1+Assumptions!$C$68)/Assumptions!$C$72*F8+F27*Assumptions!$C$70</f>
-        <v>3521.42361333333</v>
+        <f aca="false">Assumptions!$C$84*(1+Assumptions!$C$73)/Assumptions!$C$77*F8+F27*Assumptions!$C$75</f>
+        <v>76.375</v>
       </c>
       <c r="G39" s="37" t="n">
-        <f aca="false">Assumptions!$C$79*(1+Assumptions!$C$68)/Assumptions!$C$72*G8+G27*Assumptions!$C$70</f>
-        <v>3679.6132</v>
+        <f aca="false">Assumptions!$C$84*(1+Assumptions!$C$73)/Assumptions!$C$77*G8+G27*Assumptions!$C$75</f>
+        <v>75.5625</v>
       </c>
       <c r="H39" s="2"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="11" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" s="37" t="n">
-        <f aca="false">Assumptions!$C$80*(1+Assumptions!$C$68)/Assumptions!$C$73*C8</f>
+        <f aca="false">Assumptions!$C$85*(1+Assumptions!$C$73)/Assumptions!$C$78*C8</f>
         <v>286.458333333333</v>
       </c>
       <c r="D40" s="37" t="n">
-        <f aca="false">Assumptions!$C$80*(1+Assumptions!$C$68)/Assumptions!$C$73*D8</f>
+        <f aca="false">Assumptions!$C$85*(1+Assumptions!$C$73)/Assumptions!$C$78*D8</f>
         <v>555.729166666667</v>
       </c>
       <c r="E40" s="37" t="n">
-        <f aca="false">Assumptions!$C$80*(1+Assumptions!$C$68)/Assumptions!$C$73*E8</f>
+        <f aca="false">Assumptions!$C$85*(1+Assumptions!$C$73)/Assumptions!$C$78*E8</f>
         <v>544.270833333333</v>
       </c>
       <c r="F40" s="37" t="n">
-        <f aca="false">Assumptions!$C$80*(1+Assumptions!$C$68)/Assumptions!$C$73*F8</f>
+        <f aca="false">Assumptions!$C$85*(1+Assumptions!$C$73)/Assumptions!$C$78*F8</f>
         <v>538.541666666667</v>
       </c>
       <c r="G40" s="37" t="n">
-        <f aca="false">Assumptions!$C$80*(1+Assumptions!$C$68)/Assumptions!$C$73*G8</f>
+        <f aca="false">Assumptions!$C$85*(1+Assumptions!$C$73)/Assumptions!$C$78*G8</f>
         <v>532.8125</v>
       </c>
       <c r="H40" s="2"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="11" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="B41" s="2"/>
       <c r="C41" s="37" t="n">
-        <f aca="false">C11*Assumptions!$C$65*Assumptions!$C$64</f>
-        <v>168</v>
+        <f aca="false">C11*Assumptions!$C$70*Assumptions!$C$69</f>
+        <v>97.104</v>
       </c>
       <c r="D41" s="37" t="n">
-        <f aca="false">D11*Assumptions!$C$65*Assumptions!$C$64</f>
-        <v>266.56</v>
+        <f aca="false">D11*Assumptions!$C$70*Assumptions!$C$69</f>
+        <v>154.07168</v>
       </c>
       <c r="E41" s="37" t="n">
-        <f aca="false">E11*Assumptions!$C$65*Assumptions!$C$64</f>
-        <v>203.84</v>
+        <f aca="false">E11*Assumptions!$C$70*Assumptions!$C$69</f>
+        <v>117.81952</v>
       </c>
       <c r="F41" s="37" t="n">
-        <f aca="false">F11*Assumptions!$C$65*Assumptions!$C$64</f>
-        <v>151.2</v>
+        <f aca="false">F11*Assumptions!$C$70*Assumptions!$C$69</f>
+        <v>87.3936</v>
       </c>
       <c r="G41" s="37" t="n">
-        <f aca="false">G11*Assumptions!$C$65*Assumptions!$C$64</f>
-        <v>95.7600000000001</v>
+        <f aca="false">G11*Assumptions!$C$70*Assumptions!$C$69</f>
+        <v>55.3492800000001</v>
       </c>
       <c r="H41" s="2"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" s="38" t="n">
         <f aca="false">C35-SUM(C38:C41)</f>
-        <v>-2414.690712</v>
+        <v>-199.811961653333</v>
       </c>
       <c r="D42" s="38" t="n">
         <f aca="false">D35-SUM(D38:D41)</f>
-        <v>449.952367679998</v>
+        <v>3388.67663928533</v>
       </c>
       <c r="E42" s="38" t="n">
         <f aca="false">E35-SUM(E38:E41)</f>
-        <v>9111.83682</v>
+        <v>9282.61448410667</v>
       </c>
       <c r="F42" s="38" t="n">
         <f aca="false">F35-SUM(F38:F41)</f>
-        <v>14604.969522208</v>
+        <v>13207.5139025493</v>
       </c>
       <c r="G42" s="38" t="n">
         <f aca="false">G35-SUM(G38:G41)</f>
-        <v>18817.138869024</v>
+        <v>16144.6370032288</v>
       </c>
       <c r="H42" s="2"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="11" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="B43" s="2"/>
       <c r="C43" s="34" t="n">
         <f aca="false">IF(C25=0,0,C42/C25)</f>
-        <v>-2.67873941346397</v>
+        <v>-0.315792866778938</v>
       </c>
       <c r="D43" s="34" t="n">
         <f aca="false">IF(D25=0,0,D42/D25)</f>
-        <v>0.0620664047749907</v>
+        <v>0.665990029984332</v>
       </c>
       <c r="E43" s="34" t="n">
         <f aca="false">IF(E25=0,0,E42/E25)</f>
-        <v>0.56188677088151</v>
+        <v>0.842256485834526</v>
       </c>
       <c r="F43" s="34" t="n">
         <f aca="false">IF(F25=0,0,F42/F25)</f>
-        <v>0.663861573629245</v>
+        <v>0.88176887732771</v>
       </c>
       <c r="G43" s="34" t="n">
         <f aca="false">IF(G25=0,0,G42/G25)</f>
-        <v>0.713455941684389</v>
+        <v>0.900183520579547</v>
       </c>
       <c r="H43" s="2"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="11" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="B44" s="2"/>
       <c r="C44" s="37" t="n">
-        <f aca="false">(Assumptions!$C$61+Assumptions!$C$62+Assumptions!$C$63)*Assumptions!$F$10</f>
+        <f aca="false">(Assumptions!$C$66+Assumptions!$C$67+Assumptions!$C$68)*Assumptions!$F$10</f>
         <v>1540</v>
       </c>
       <c r="D44" s="37" t="n">
@@ -5993,31 +6166,31 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="4" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="B45" s="2"/>
-      <c r="C45" s="27" t="n">
+      <c r="C45" s="28" t="n">
         <f aca="false">C42-C44</f>
-        <v>-3954.690712</v>
-      </c>
-      <c r="D45" s="27" t="n">
+        <v>-1739.81196165333</v>
+      </c>
+      <c r="D45" s="28" t="n">
         <f aca="false">C45+D42-D44</f>
-        <v>-3504.73834432</v>
-      </c>
-      <c r="E45" s="27" t="n">
+        <v>1648.864677632</v>
+      </c>
+      <c r="E45" s="28" t="n">
         <f aca="false">D45+E42-E44</f>
-        <v>5607.09847568</v>
-      </c>
-      <c r="F45" s="27" t="n">
+        <v>10931.4791617387</v>
+      </c>
+      <c r="F45" s="28" t="n">
         <f aca="false">E45+F42-F44</f>
-        <v>20212.067997888</v>
-      </c>
-      <c r="G45" s="27" t="n">
+        <v>24138.993064288</v>
+      </c>
+      <c r="G45" s="28" t="n">
         <f aca="false">F45+G42-G44</f>
-        <v>39029.206866912</v>
+        <v>40283.6300675168</v>
       </c>
       <c r="H45" s="17" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6032,7 +6205,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="17" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -6069,7 +6242,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -6081,7 +6254,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -6103,7 +6276,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="7" t="s">
@@ -6125,61 +6298,61 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$C$19</f>
-        <v>5873.28</v>
+        <v>880992</v>
       </c>
       <c r="D5" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$D$19+Rollout!$D$5*'Unit Economics'!$C$19</f>
-        <v>57675.6096</v>
+        <v>6008365.44</v>
       </c>
       <c r="E5" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$E$19+Rollout!$D$5*'Unit Economics'!$D$19+Rollout!$E$5*'Unit Economics'!$C$19</f>
-        <v>251258.9184</v>
+        <v>14211281.952</v>
       </c>
       <c r="F5" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$F$19+Rollout!$D$5*'Unit Economics'!$E$19+Rollout!$E$5*'Unit Economics'!$D$19+Rollout!$F$5*'Unit Economics'!$C$19</f>
-        <v>753142.44096</v>
+        <v>23127819.60384</v>
       </c>
       <c r="G5" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$G$19+Rollout!$D$5*'Unit Economics'!$F$19+Rollout!$E$5*'Unit Economics'!$E$19+Rollout!$F$5*'Unit Economics'!$D$19+Rollout!$G$5*'Unit Economics'!$C$19</f>
-        <v>1812870.09792</v>
+        <v>29841401.52</v>
       </c>
       <c r="H5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$C$20</f>
-        <v>6065.28</v>
+        <v>475338.24</v>
       </c>
       <c r="D6" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$D$20+Rollout!$D$5*'Unit Economics'!$C$20</f>
-        <v>68386.032</v>
+        <v>3933423.936</v>
       </c>
       <c r="E6" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$E$20+Rollout!$D$5*'Unit Economics'!$D$20+Rollout!$E$5*'Unit Economics'!$C$20</f>
-        <v>323582.688</v>
+        <v>10617154.92864</v>
       </c>
       <c r="F6" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$F$20+Rollout!$D$5*'Unit Economics'!$E$20+Rollout!$E$5*'Unit Economics'!$D$20+Rollout!$F$5*'Unit Economics'!$C$20</f>
-        <v>1029429.648</v>
+        <v>19072958.763456</v>
       </c>
       <c r="G6" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$G$20+Rollout!$D$5*'Unit Economics'!$F$20+Rollout!$E$5*'Unit Economics'!$E$20+Rollout!$F$5*'Unit Economics'!$D$20+Rollout!$G$5*'Unit Economics'!$C$20</f>
-        <v>2596000.4928</v>
+        <v>26923989.75552</v>
       </c>
       <c r="H6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="37" t="n">
@@ -6188,79 +6361,79 @@
       </c>
       <c r="D7" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$D$21+Rollout!$D$5*'Unit Economics'!$C$21</f>
-        <v>12906.432</v>
+        <v>1935964.8</v>
       </c>
       <c r="E7" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$E$21+Rollout!$D$5*'Unit Economics'!$D$21+Rollout!$E$5*'Unit Economics'!$C$21</f>
-        <v>83226.528</v>
+        <v>6676084.8</v>
       </c>
       <c r="F7" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$F$21+Rollout!$D$5*'Unit Economics'!$E$21+Rollout!$E$5*'Unit Economics'!$D$21+Rollout!$F$5*'Unit Economics'!$C$21</f>
-        <v>305496.576</v>
+        <v>13814545.8528</v>
       </c>
       <c r="G7" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$G$21+Rollout!$D$5*'Unit Economics'!$F$21+Rollout!$E$5*'Unit Economics'!$E$21+Rollout!$F$5*'Unit Economics'!$D$21+Rollout!$G$5*'Unit Economics'!$C$21</f>
-        <v>836123.904</v>
+        <v>20629251.72</v>
       </c>
       <c r="H7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$C$22</f>
-        <v>1890</v>
+        <v>163863</v>
       </c>
       <c r="D8" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$D$22+Rollout!$D$5*'Unit Economics'!$C$22</f>
-        <v>36892.8</v>
+        <v>2707016.76</v>
       </c>
       <c r="E8" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$E$22+Rollout!$D$5*'Unit Economics'!$D$22+Rollout!$E$5*'Unit Economics'!$C$22</f>
-        <v>200869.2</v>
+        <v>8280161.253</v>
       </c>
       <c r="F8" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$F$22+Rollout!$D$5*'Unit Economics'!$E$22+Rollout!$E$5*'Unit Economics'!$D$22+Rollout!$F$5*'Unit Economics'!$C$22</f>
-        <v>687393</v>
+        <v>16138329.39936</v>
       </c>
       <c r="G8" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$G$22+Rollout!$D$5*'Unit Economics'!$F$22+Rollout!$E$5*'Unit Economics'!$E$22+Rollout!$F$5*'Unit Economics'!$D$22+Rollout!$G$5*'Unit Economics'!$C$22</f>
-        <v>1809561.6</v>
+        <v>23379350.1606</v>
       </c>
       <c r="H8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$C$23</f>
-        <v>4200</v>
+        <v>378000</v>
       </c>
       <c r="D9" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$D$23+Rollout!$D$5*'Unit Economics'!$C$23</f>
-        <v>41244</v>
+        <v>2577960</v>
       </c>
       <c r="E9" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$E$23+Rollout!$D$5*'Unit Economics'!$D$23+Rollout!$E$5*'Unit Economics'!$C$23</f>
-        <v>179676</v>
+        <v>6097518</v>
       </c>
       <c r="F9" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$F$23+Rollout!$D$5*'Unit Economics'!$E$23+Rollout!$E$5*'Unit Economics'!$D$23+Rollout!$F$5*'Unit Economics'!$C$23</f>
-        <v>535416</v>
+        <v>9639007.56</v>
       </c>
       <c r="G9" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$G$23+Rollout!$D$5*'Unit Economics'!$F$23+Rollout!$E$5*'Unit Economics'!$E$23+Rollout!$F$5*'Unit Economics'!$D$23+Rollout!$G$5*'Unit Economics'!$C$23</f>
-        <v>1275162</v>
+        <v>11746161</v>
       </c>
       <c r="H9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="37" t="n">
@@ -6273,48 +6446,48 @@
       </c>
       <c r="E10" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$E$24+Rollout!$D$5*'Unit Economics'!$D$24+Rollout!$E$5*'Unit Economics'!$C$24</f>
-        <v>45964.8</v>
+        <v>3985148.16</v>
       </c>
       <c r="F10" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$F$24+Rollout!$D$5*'Unit Economics'!$E$24+Rollout!$E$5*'Unit Economics'!$D$24+Rollout!$F$5*'Unit Economics'!$C$24</f>
-        <v>236920.32</v>
+        <v>8585547.264</v>
       </c>
       <c r="G10" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$G$24+Rollout!$D$5*'Unit Economics'!$F$24+Rollout!$E$5*'Unit Economics'!$E$24+Rollout!$F$5*'Unit Economics'!$D$24+Rollout!$G$5*'Unit Economics'!$C$24</f>
-        <v>731888.64</v>
+        <v>13034021.33376</v>
       </c>
       <c r="H10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="38" t="n">
         <f aca="false">SUM(C5:C10)</f>
-        <v>18028.56</v>
+        <v>1898193.24</v>
       </c>
       <c r="D11" s="38" t="n">
         <f aca="false">SUM(D5:D10)</f>
-        <v>217104.8736</v>
+        <v>17162730.936</v>
       </c>
       <c r="E11" s="38" t="n">
         <f aca="false">SUM(E5:E10)</f>
-        <v>1084578.1344</v>
+        <v>49867349.09364</v>
       </c>
       <c r="F11" s="38" t="n">
         <f aca="false">SUM(F5:F10)</f>
-        <v>3547797.98496</v>
+        <v>90378208.443456</v>
       </c>
       <c r="G11" s="38" t="n">
         <f aca="false">SUM(G5:G10)</f>
-        <v>9061606.73472</v>
+        <v>125554175.48988</v>
       </c>
       <c r="H11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="34" t="n">
@@ -6323,19 +6496,19 @@
       </c>
       <c r="D12" s="34" t="n">
         <f aca="false">IF(C11=0,0,D11/C11-1)</f>
-        <v>11.0422747906655</v>
+        <v>8.04161419097668</v>
       </c>
       <c r="E12" s="34" t="n">
         <f aca="false">IF(D11=0,0,E11/D11-1)</f>
-        <v>3.99564158287048</v>
+        <v>1.90556026774503</v>
       </c>
       <c r="F12" s="34" t="n">
         <f aca="false">IF(E11=0,0,F11/E11-1)</f>
-        <v>2.27113176306351</v>
+        <v>0.81237242576792</v>
       </c>
       <c r="G12" s="34" t="n">
         <f aca="false">IF(F11=0,0,G11/F11-1)</f>
-        <v>1.5541495804255</v>
+        <v>0.389208501166865</v>
       </c>
       <c r="H12" s="2"/>
     </row>
@@ -6351,7 +6524,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -6363,61 +6536,61 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="34" t="n">
         <f aca="false">IF(C$11=0,0,C5/C$11)</f>
-        <v>0.325776434723572</v>
+        <v>0.464121345200871</v>
       </c>
       <c r="D15" s="34" t="n">
         <f aca="false">IF(D$11=0,0,D5/D$11)</f>
-        <v>0.265657829986181</v>
+        <v>0.350082132173793</v>
       </c>
       <c r="E15" s="34" t="n">
         <f aca="false">IF(E$11=0,0,E5/E$11)</f>
-        <v>0.231665115154658</v>
+        <v>0.284981700657765</v>
       </c>
       <c r="F15" s="34" t="n">
         <f aca="false">IF(F$11=0,0,F5/F$11)</f>
-        <v>0.212284477344189</v>
+        <v>0.255900399024945</v>
       </c>
       <c r="G15" s="34" t="n">
         <f aca="false">IF(G$11=0,0,G5/G$11)</f>
-        <v>0.200060557800848</v>
+        <v>0.237677491836226</v>
       </c>
       <c r="H15" s="2"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="34" t="n">
         <f aca="false">IF(C$11=0,0,C6/C$11)</f>
-        <v>0.336426203756706</v>
+        <v>0.250416148358004</v>
       </c>
       <c r="D16" s="34" t="n">
         <f aca="false">IF(D$11=0,0,D6/D$11)</f>
-        <v>0.314990773196535</v>
+        <v>0.229184035493406</v>
       </c>
       <c r="E16" s="34" t="n">
         <f aca="false">IF(E$11=0,0,E6/E$11)</f>
-        <v>0.298348895055873</v>
+        <v>0.21290794721619</v>
       </c>
       <c r="F16" s="34" t="n">
         <f aca="false">IF(F$11=0,0,F6/F$11)</f>
-        <v>0.290160164801944</v>
+        <v>0.211034928573393</v>
       </c>
       <c r="G16" s="34" t="n">
         <f aca="false">IF(G$11=0,0,G6/G$11)</f>
-        <v>0.286483464665631</v>
+        <v>0.214441213527703</v>
       </c>
       <c r="H16" s="2"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="34" t="n">
@@ -6426,79 +6599,79 @@
       </c>
       <c r="D17" s="34" t="n">
         <f aca="false">IF(D$11=0,0,D7/D$11)</f>
-        <v>0.0594479146690146</v>
+        <v>0.112800509850049</v>
       </c>
       <c r="E17" s="34" t="n">
         <f aca="false">IF(E$11=0,0,E7/E$11)</f>
-        <v>0.076736313742893</v>
+        <v>0.133876873772932</v>
       </c>
       <c r="F17" s="34" t="n">
         <f aca="false">IF(F$11=0,0,F7/F$11)</f>
-        <v>0.0861087855889981</v>
+        <v>0.152852618908051</v>
       </c>
       <c r="G17" s="34" t="n">
         <f aca="false">IF(G$11=0,0,G7/G$11)</f>
-        <v>0.092271042926234</v>
+        <v>0.164305580754364</v>
       </c>
       <c r="H17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="34" t="n">
         <f aca="false">IF(C$11=0,0,C8/C$11)</f>
-        <v>0.104833663919914</v>
+        <v>0.0863257736604309</v>
       </c>
       <c r="D18" s="34" t="n">
         <f aca="false">IF(D$11=0,0,D8/D$11)</f>
-        <v>0.169930777638701</v>
+        <v>0.157726457991709</v>
       </c>
       <c r="E18" s="34" t="n">
         <f aca="false">IF(E$11=0,0,E8/E$11)</f>
-        <v>0.185204913900577</v>
+        <v>0.166043742117747</v>
       </c>
       <c r="F18" s="34" t="n">
         <f aca="false">IF(F$11=0,0,F8/F$11)</f>
-        <v>0.193752012632633</v>
+        <v>0.178564387116135</v>
       </c>
       <c r="G18" s="34" t="n">
         <f aca="false">IF(G$11=0,0,G8/G$11)</f>
-        <v>0.199695446180265</v>
+        <v>0.186209260419893</v>
       </c>
       <c r="H18" s="2"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="34" t="n">
         <f aca="false">IF(C$11=0,0,C9/C$11)</f>
-        <v>0.232963697599808</v>
+        <v>0.199136732780694</v>
       </c>
       <c r="D19" s="34" t="n">
         <f aca="false">IF(D$11=0,0,D9/D$11)</f>
-        <v>0.189972704509568</v>
+        <v>0.150206864491044</v>
       </c>
       <c r="E19" s="34" t="n">
         <f aca="false">IF(E$11=0,0,E9/E$11)</f>
-        <v>0.165664413011054</v>
+        <v>0.122274757147211</v>
       </c>
       <c r="F19" s="34" t="n">
         <f aca="false">IF(F$11=0,0,F9/F$11)</f>
-        <v>0.150915018913073</v>
+        <v>0.106651899014247</v>
       </c>
       <c r="G19" s="34" t="n">
         <f aca="false">IF(G$11=0,0,G9/G$11)</f>
-        <v>0.140721401549479</v>
+        <v>0.093554523011039</v>
       </c>
       <c r="H19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="34" t="n">
@@ -6511,15 +6684,15 @@
       </c>
       <c r="E20" s="34" t="n">
         <f aca="false">IF(E$11=0,0,E10/E$11)</f>
-        <v>0.0423803491349457</v>
+        <v>0.0799149790881557</v>
       </c>
       <c r="F20" s="34" t="n">
         <f aca="false">IF(F$11=0,0,F10/F$11)</f>
-        <v>0.0667795407191628</v>
+        <v>0.0949957673632294</v>
       </c>
       <c r="G20" s="34" t="n">
         <f aca="false">IF(G$11=0,0,G10/G$11)</f>
-        <v>0.0807680868775437</v>
+        <v>0.103811930450776</v>
       </c>
       <c r="H20" s="2"/>
     </row>
@@ -6539,7 +6712,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
@@ -6550,7 +6723,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -6562,7 +6735,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -6584,7 +6757,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="7" t="s">
@@ -6606,7 +6779,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -6618,234 +6791,249 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="8" t="n">
-        <f aca="false">Assumptions!C$85</f>
+        <f aca="false">Assumptions!C$90</f>
         <v>2</v>
       </c>
       <c r="D6" s="8" t="n">
-        <f aca="false">Assumptions!D$85</f>
+        <f aca="false">Assumptions!D$90</f>
         <v>2</v>
       </c>
       <c r="E6" s="8" t="n">
-        <f aca="false">Assumptions!E$85</f>
+        <f aca="false">Assumptions!E$90</f>
         <v>3</v>
       </c>
       <c r="F6" s="8" t="n">
-        <f aca="false">Assumptions!F$85</f>
+        <f aca="false">Assumptions!F$90</f>
         <v>4</v>
       </c>
       <c r="G6" s="8" t="n">
-        <f aca="false">Assumptions!G$85</f>
+        <f aca="false">Assumptions!G$90</f>
         <v>5</v>
       </c>
       <c r="H6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="8" t="n">
-        <f aca="false">Assumptions!C$86</f>
+        <f aca="false">Assumptions!C$91</f>
         <v>3</v>
       </c>
       <c r="D7" s="8" t="n">
-        <f aca="false">Assumptions!D$86</f>
+        <f aca="false">Assumptions!D$91</f>
         <v>5</v>
       </c>
       <c r="E7" s="8" t="n">
-        <f aca="false">Assumptions!E$86</f>
+        <f aca="false">Assumptions!E$91</f>
         <v>8</v>
       </c>
       <c r="F7" s="8" t="n">
-        <f aca="false">Assumptions!F$86</f>
+        <f aca="false">Assumptions!F$91</f>
         <v>11</v>
       </c>
       <c r="G7" s="8" t="n">
-        <f aca="false">Assumptions!G$86</f>
+        <f aca="false">Assumptions!G$91</f>
         <v>14</v>
       </c>
       <c r="H7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="8" t="n">
-        <f aca="false">Assumptions!C$87</f>
+        <f aca="false">Assumptions!C$92</f>
         <v>1</v>
       </c>
       <c r="D8" s="8" t="n">
-        <f aca="false">Assumptions!D$87</f>
+        <f aca="false">Assumptions!D$92</f>
         <v>1</v>
       </c>
       <c r="E8" s="8" t="n">
-        <f aca="false">Assumptions!E$87</f>
+        <f aca="false">Assumptions!E$92</f>
         <v>2</v>
       </c>
       <c r="F8" s="8" t="n">
-        <f aca="false">Assumptions!F$87</f>
+        <f aca="false">Assumptions!F$92</f>
         <v>3</v>
       </c>
       <c r="G8" s="8" t="n">
-        <f aca="false">Assumptions!G$87</f>
+        <f aca="false">Assumptions!G$92</f>
         <v>4</v>
       </c>
       <c r="H8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="33" t="n">
-        <f aca="false">IF(Rollout!C$7=0,0,MAX(1,ROUNDUP(Rollout!C$7/Assumptions!$C$71,0)))</f>
-        <v>1</v>
+        <f aca="false">IF(Rollout!C$7=0,0,MAX(1,ROUNDUP(Rollout!C$7/Assumptions!$C$76,0)))</f>
+        <v>3</v>
       </c>
       <c r="D9" s="33" t="n">
-        <f aca="false">IF(Rollout!D$7=0,0,MAX(1,ROUNDUP(Rollout!D$7/Assumptions!$C$71,0)))</f>
-        <v>3</v>
+        <f aca="false">IF(Rollout!D$7=0,0,MAX(1,ROUNDUP(Rollout!D$7/Assumptions!$C$76,0)))</f>
+        <v>6</v>
       </c>
       <c r="E9" s="33" t="n">
-        <f aca="false">IF(Rollout!E$7=0,0,MAX(1,ROUNDUP(Rollout!E$7/Assumptions!$C$71,0)))</f>
+        <f aca="false">IF(Rollout!E$7=0,0,MAX(1,ROUNDUP(Rollout!E$7/Assumptions!$C$76,0)))</f>
+        <v>9</v>
+      </c>
+      <c r="F9" s="33" t="n">
+        <f aca="false">IF(Rollout!F$7=0,0,MAX(1,ROUNDUP(Rollout!F$7/Assumptions!$C$76,0)))</f>
+        <v>9</v>
+      </c>
+      <c r="G9" s="33" t="n">
+        <f aca="false">IF(Rollout!G$7=0,0,MAX(1,ROUNDUP(Rollout!G$7/Assumptions!$C$76,0)))</f>
         <v>8</v>
-      </c>
-      <c r="F9" s="33" t="n">
-        <f aca="false">IF(Rollout!F$7=0,0,MAX(1,ROUNDUP(Rollout!F$7/Assumptions!$C$71,0)))</f>
-        <v>18</v>
-      </c>
-      <c r="G9" s="33" t="n">
-        <f aca="false">IF(Rollout!G$7=0,0,MAX(1,ROUNDUP(Rollout!G$7/Assumptions!$C$71,0)))</f>
-        <v>35</v>
       </c>
       <c r="H9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>268</v>
+        <v>176</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="33" t="n">
-        <f aca="false">IF(Rollout!C$7=0,0,MAX(1,ROUNDUP(Rollout!C$7/Assumptions!$C$72,0)))</f>
-        <v>1</v>
+        <f aca="false">IF(Rollout!C$7=0,0,MAX(1,ROUNDUP(Rollout!C$7/Assumptions!$C$77,0)))</f>
+        <v>3</v>
       </c>
       <c r="D10" s="33" t="n">
-        <f aca="false">IF(Rollout!D$7=0,0,MAX(1,ROUNDUP(Rollout!D$7/Assumptions!$C$72,0)))</f>
-        <v>4</v>
+        <f aca="false">IF(Rollout!D$7=0,0,MAX(1,ROUNDUP(Rollout!D$7/Assumptions!$C$77,0)))</f>
+        <v>6</v>
       </c>
       <c r="E10" s="33" t="n">
-        <f aca="false">IF(Rollout!E$7=0,0,MAX(1,ROUNDUP(Rollout!E$7/Assumptions!$C$72,0)))</f>
-        <v>10</v>
+        <f aca="false">IF(Rollout!E$7=0,0,MAX(1,ROUNDUP(Rollout!E$7/Assumptions!$C$77,0)))</f>
+        <v>9</v>
       </c>
       <c r="F10" s="33" t="n">
-        <f aca="false">IF(Rollout!F$7=0,0,MAX(1,ROUNDUP(Rollout!F$7/Assumptions!$C$72,0)))</f>
-        <v>23</v>
+        <f aca="false">IF(Rollout!F$7=0,0,MAX(1,ROUNDUP(Rollout!F$7/Assumptions!$C$77,0)))</f>
+        <v>9</v>
       </c>
       <c r="G10" s="33" t="n">
-        <f aca="false">IF(Rollout!G$7=0,0,MAX(1,ROUNDUP(Rollout!G$7/Assumptions!$C$72,0)))</f>
-        <v>46</v>
+        <f aca="false">IF(Rollout!G$7=0,0,MAX(1,ROUNDUP(Rollout!G$7/Assumptions!$C$77,0)))</f>
+        <v>8</v>
       </c>
       <c r="H10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="33" t="n">
-        <f aca="false">IF(Rollout!C$7=0,0,MAX(1,ROUNDUP(Rollout!C$7/Assumptions!$C$73,0)))</f>
-        <v>1</v>
+        <f aca="false">IF(Rollout!C$7=0,0,MAX(1,ROUNDUP(Rollout!C$7/Assumptions!$C$78,0)))</f>
+        <v>25</v>
       </c>
       <c r="D11" s="33" t="n">
-        <f aca="false">IF(Rollout!D$7=0,0,MAX(1,ROUNDUP(Rollout!D$7/Assumptions!$C$73,0)))</f>
-        <v>1</v>
+        <f aca="false">IF(Rollout!D$7=0,0,MAX(1,ROUNDUP(Rollout!D$7/Assumptions!$C$78,0)))</f>
+        <v>50</v>
       </c>
       <c r="E11" s="33" t="n">
-        <f aca="false">IF(Rollout!E$7=0,0,MAX(1,ROUNDUP(Rollout!E$7/Assumptions!$C$73,0)))</f>
+        <f aca="false">IF(Rollout!E$7=0,0,MAX(1,ROUNDUP(Rollout!E$7/Assumptions!$C$78,0)))</f>
+        <v>69</v>
+      </c>
+      <c r="F11" s="33" t="n">
+        <f aca="false">IF(Rollout!F$7=0,0,MAX(1,ROUNDUP(Rollout!F$7/Assumptions!$C$78,0)))</f>
+        <v>67</v>
+      </c>
+      <c r="G11" s="33" t="n">
+        <f aca="false">IF(Rollout!G$7=0,0,MAX(1,ROUNDUP(Rollout!G$7/Assumptions!$C$78,0)))</f>
+        <v>67</v>
+      </c>
+      <c r="H11" s="2"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="B12" s="2"/>
+      <c r="C12" s="33" t="n">
+        <f aca="false">IF(Rollout!C$5=0,0,ROUNDUP(Rollout!C$5/Assumptions!$C$19,0))</f>
+        <v>8</v>
+      </c>
+      <c r="D12" s="33" t="n">
+        <f aca="false">IF(Rollout!D$5=0,0,ROUNDUP(Rollout!D$5/Assumptions!$C$19,0))</f>
+        <v>8</v>
+      </c>
+      <c r="E12" s="33" t="n">
+        <f aca="false">IF(Rollout!E$5=0,0,ROUNDUP(Rollout!E$5/Assumptions!$C$19,0))</f>
+        <v>7</v>
+      </c>
+      <c r="F12" s="33" t="n">
+        <f aca="false">IF(Rollout!F$5=0,0,ROUNDUP(Rollout!F$5/Assumptions!$C$19,0))</f>
+        <v>0</v>
+      </c>
+      <c r="G12" s="33" t="n">
+        <f aca="false">IF(Rollout!G$5=0,0,ROUNDUP(Rollout!G$5/Assumptions!$C$19,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H12" s="2"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="B13" s="2"/>
+      <c r="C13" s="39" t="n">
+        <f aca="false">SUM(C6:C12)</f>
+        <v>45</v>
+      </c>
+      <c r="D13" s="39" t="n">
+        <f aca="false">SUM(D6:D12)</f>
+        <v>78</v>
+      </c>
+      <c r="E13" s="39" t="n">
+        <f aca="false">SUM(E6:E12)</f>
+        <v>107</v>
+      </c>
+      <c r="F13" s="39" t="n">
+        <f aca="false">SUM(F6:F12)</f>
+        <v>103</v>
+      </c>
+      <c r="G13" s="39" t="n">
+        <f aca="false">SUM(G6:G12)</f>
+        <v>106</v>
+      </c>
+      <c r="H13" s="2"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="B14" s="2"/>
+      <c r="C14" s="33" t="n">
+        <f aca="false">C13</f>
+        <v>45</v>
+      </c>
+      <c r="D14" s="33" t="n">
+        <f aca="false">MAX(0,D13-C13)</f>
+        <v>33</v>
+      </c>
+      <c r="E14" s="33" t="n">
+        <f aca="false">MAX(0,E13-D13)</f>
+        <v>29</v>
+      </c>
+      <c r="F14" s="33" t="n">
+        <f aca="false">MAX(0,F13-E13)</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="33" t="n">
+        <f aca="false">MAX(0,G13-F13)</f>
         <v>3</v>
       </c>
-      <c r="F11" s="33" t="n">
-        <f aca="false">IF(Rollout!F$7=0,0,MAX(1,ROUNDUP(Rollout!F$7/Assumptions!$C$73,0)))</f>
-        <v>6</v>
-      </c>
-      <c r="G11" s="33" t="n">
-        <f aca="false">IF(Rollout!G$7=0,0,MAX(1,ROUNDUP(Rollout!G$7/Assumptions!$C$73,0)))</f>
-        <v>12</v>
-      </c>
-      <c r="H11" s="2"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
-        <v>269</v>
-      </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="39" t="n">
-        <f aca="false">SUM(C6:C11)</f>
-        <v>9</v>
-      </c>
-      <c r="D12" s="39" t="n">
-        <f aca="false">SUM(D6:D11)</f>
-        <v>16</v>
-      </c>
-      <c r="E12" s="39" t="n">
-        <f aca="false">SUM(E6:E11)</f>
-        <v>34</v>
-      </c>
-      <c r="F12" s="39" t="n">
-        <f aca="false">SUM(F6:F11)</f>
-        <v>65</v>
-      </c>
-      <c r="G12" s="39" t="n">
-        <f aca="false">SUM(G6:G11)</f>
-        <v>116</v>
-      </c>
-      <c r="H12" s="2"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="33" t="n">
-        <f aca="false">C12</f>
-        <v>9</v>
-      </c>
-      <c r="D13" s="33" t="n">
-        <f aca="false">MAX(0,D12-C12)</f>
-        <v>7</v>
-      </c>
-      <c r="E13" s="33" t="n">
-        <f aca="false">MAX(0,E12-D12)</f>
-        <v>18</v>
-      </c>
-      <c r="F13" s="33" t="n">
-        <f aca="false">MAX(0,F12-E12)</f>
-        <v>31</v>
-      </c>
-      <c r="G13" s="33" t="n">
-        <f aca="false">MAX(0,G12-F12)</f>
-        <v>51</v>
-      </c>
-      <c r="H13" s="2"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
       <c r="H14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
-        <v>271</v>
-      </c>
+      <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
@@ -6855,215 +7043,254 @@
       <c r="H15" s="2"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="s">
-        <v>165</v>
+      <c r="A16" s="4" t="s">
+        <v>283</v>
       </c>
       <c r="B16" s="2"/>
-      <c r="C16" s="37" t="n">
-        <f aca="false">C6*0.75*Assumptions!$C$76*(1+Assumptions!$C$68)*(1+Assumptions!$C$69)^0</f>
-        <v>300000</v>
-      </c>
-      <c r="D16" s="37" t="n">
-        <f aca="false">(C6+D6)/2*Assumptions!$C$76*(1+Assumptions!$C$68)*(1+Assumptions!$C$69)^1</f>
-        <v>412000</v>
-      </c>
-      <c r="E16" s="37" t="n">
-        <f aca="false">(D6+E6)/2*Assumptions!$C$76*(1+Assumptions!$C$68)*(1+Assumptions!$C$69)^2</f>
-        <v>530450</v>
-      </c>
-      <c r="F16" s="37" t="n">
-        <f aca="false">(E6+F6)/2*Assumptions!$C$76*(1+Assumptions!$C$68)*(1+Assumptions!$C$69)^3</f>
-        <v>764908.9</v>
-      </c>
-      <c r="G16" s="37" t="n">
-        <f aca="false">(F6+G6)/2*Assumptions!$C$76*(1+Assumptions!$C$68)*(1+Assumptions!$C$69)^4</f>
-        <v>1012957.929</v>
-      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
       <c r="H16" s="2"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="37" t="n">
-        <f aca="false">C7*0.75*Assumptions!$C$77*(1+Assumptions!$C$68)*(1+Assumptions!$C$69)^0</f>
-        <v>478125</v>
+        <f aca="false">C6*0.75*Assumptions!$C$81*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^0</f>
+        <v>300000</v>
       </c>
       <c r="D17" s="37" t="n">
-        <f aca="false">(C7+D7)/2*Assumptions!$C$77*(1+Assumptions!$C$68)*(1+Assumptions!$C$69)^1</f>
-        <v>875500</v>
+        <f aca="false">(C6+D6)/2*Assumptions!$C$81*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^1</f>
+        <v>412000</v>
       </c>
       <c r="E17" s="37" t="n">
-        <f aca="false">(D7+E7)/2*Assumptions!$C$77*(1+Assumptions!$C$68)*(1+Assumptions!$C$69)^2</f>
-        <v>1465368.125</v>
+        <f aca="false">(D6+E6)/2*Assumptions!$C$81*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^2</f>
+        <v>530450</v>
       </c>
       <c r="F17" s="37" t="n">
-        <f aca="false">(E7+F7)/2*Assumptions!$C$77*(1+Assumptions!$C$68)*(1+Assumptions!$C$69)^3</f>
-        <v>2205942.63125</v>
+        <f aca="false">(E6+F6)/2*Assumptions!$C$81*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^3</f>
+        <v>764908.9</v>
       </c>
       <c r="G17" s="37" t="n">
-        <f aca="false">(F7+G7)/2*Assumptions!$C$77*(1+Assumptions!$C$68)*(1+Assumptions!$C$69)^4</f>
-        <v>2989632.7765625</v>
+        <f aca="false">(F6+G6)/2*Assumptions!$C$81*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^4</f>
+        <v>1012957.929</v>
       </c>
       <c r="H17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="37" t="n">
-        <f aca="false">C8*0.75*Assumptions!$C$81*(1+Assumptions!$C$68)*(1+Assumptions!$C$69)^0</f>
-        <v>103125</v>
+        <f aca="false">C7*0.75*Assumptions!$C$82*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^0</f>
+        <v>478125</v>
       </c>
       <c r="D18" s="37" t="n">
-        <f aca="false">(C8+D8)/2*Assumptions!$C$81*(1+Assumptions!$C$68)*(1+Assumptions!$C$69)^1</f>
-        <v>141625</v>
+        <f aca="false">(C7+D7)/2*Assumptions!$C$82*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^1</f>
+        <v>875500</v>
       </c>
       <c r="E18" s="37" t="n">
-        <f aca="false">(D8+E8)/2*Assumptions!$C$81*(1+Assumptions!$C$68)*(1+Assumptions!$C$69)^2</f>
-        <v>218810.625</v>
+        <f aca="false">(D7+E7)/2*Assumptions!$C$82*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^2</f>
+        <v>1465368.125</v>
       </c>
       <c r="F18" s="37" t="n">
-        <f aca="false">(E8+F8)/2*Assumptions!$C$81*(1+Assumptions!$C$68)*(1+Assumptions!$C$69)^3</f>
-        <v>375624.90625</v>
+        <f aca="false">(E7+F7)/2*Assumptions!$C$82*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^3</f>
+        <v>2205942.63125</v>
       </c>
       <c r="G18" s="37" t="n">
-        <f aca="false">(F8+G8)/2*Assumptions!$C$81*(1+Assumptions!$C$68)*(1+Assumptions!$C$69)^4</f>
-        <v>541651.1148125</v>
+        <f aca="false">(F7+G7)/2*Assumptions!$C$82*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^4</f>
+        <v>2989632.7765625</v>
       </c>
       <c r="H18" s="2"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>267</v>
+        <v>178</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="37" t="n">
-        <f aca="false">C9*0.75*Assumptions!$C$78*(1+Assumptions!$C$68)*(1+Assumptions!$C$69)^0</f>
-        <v>65625</v>
+        <f aca="false">C8*0.75*Assumptions!$C$86*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^0</f>
+        <v>103125</v>
       </c>
       <c r="D19" s="37" t="n">
-        <f aca="false">(C9+D9)/2*Assumptions!$C$78*(1+Assumptions!$C$68)*(1+Assumptions!$C$69)^1</f>
-        <v>180250</v>
+        <f aca="false">(C8+D8)/2*Assumptions!$C$86*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^1</f>
+        <v>141625</v>
       </c>
       <c r="E19" s="37" t="n">
-        <f aca="false">(D9+E9)/2*Assumptions!$C$78*(1+Assumptions!$C$68)*(1+Assumptions!$C$69)^2</f>
-        <v>510558.125</v>
+        <f aca="false">(D8+E8)/2*Assumptions!$C$86*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^2</f>
+        <v>218810.625</v>
       </c>
       <c r="F19" s="37" t="n">
-        <f aca="false">(E9+F9)/2*Assumptions!$C$78*(1+Assumptions!$C$68)*(1+Assumptions!$C$69)^3</f>
-        <v>1242976.9625</v>
+        <f aca="false">(E8+F8)/2*Assumptions!$C$86*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^3</f>
+        <v>375624.90625</v>
       </c>
       <c r="G19" s="37" t="n">
-        <f aca="false">(F9+G9)/2*Assumptions!$C$78*(1+Assumptions!$C$68)*(1+Assumptions!$C$69)^4</f>
-        <v>2609773.5531875</v>
+        <f aca="false">(F8+G8)/2*Assumptions!$C$86*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^4</f>
+        <v>541651.1148125</v>
       </c>
       <c r="H19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="37" t="n">
-        <f aca="false">C10*0.75*Assumptions!$C$79*(1+Assumptions!$C$68)*(1+Assumptions!$C$69)^0</f>
-        <v>60937.5</v>
+        <f aca="false">C9*0.75*Assumptions!$C$83*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^0</f>
+        <v>196875</v>
       </c>
       <c r="D20" s="37" t="n">
-        <f aca="false">(C10+D10)/2*Assumptions!$C$79*(1+Assumptions!$C$68)*(1+Assumptions!$C$69)^1</f>
-        <v>209218.75</v>
+        <f aca="false">(C9+D9)/2*Assumptions!$C$83*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^1</f>
+        <v>405562.5</v>
       </c>
       <c r="E20" s="37" t="n">
-        <f aca="false">(D10+E10)/2*Assumptions!$C$79*(1+Assumptions!$C$68)*(1+Assumptions!$C$69)^2</f>
-        <v>603386.875</v>
+        <f aca="false">(D9+E9)/2*Assumptions!$C$83*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^2</f>
+        <v>696215.625</v>
       </c>
       <c r="F20" s="37" t="n">
-        <f aca="false">(E10+F10)/2*Assumptions!$C$79*(1+Assumptions!$C$68)*(1+Assumptions!$C$69)^3</f>
-        <v>1464937.134375</v>
+        <f aca="false">(E9+F9)/2*Assumptions!$C$83*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^3</f>
+        <v>860522.5125</v>
       </c>
       <c r="G20" s="37" t="n">
-        <f aca="false">(F10+G10)/2*Assumptions!$C$79*(1+Assumptions!$C$68)*(1+Assumptions!$C$69)^4</f>
-        <v>3154941.88303125</v>
+        <f aca="false">(F9+G9)/2*Assumptions!$C$83*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^4</f>
+        <v>837097.1774375</v>
       </c>
       <c r="H20" s="2"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" s="37" t="n">
-        <f aca="false">C11*0.75*Assumptions!$C$80*(1+Assumptions!$C$68)*(1+Assumptions!$C$69)^0</f>
-        <v>51562.5</v>
+        <f aca="false">C10*0.75*Assumptions!$C$84*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^0</f>
+        <v>182812.5</v>
       </c>
       <c r="D21" s="37" t="n">
-        <f aca="false">(C11+D11)/2*Assumptions!$C$80*(1+Assumptions!$C$68)*(1+Assumptions!$C$69)^1</f>
-        <v>70812.5</v>
+        <f aca="false">(C10+D10)/2*Assumptions!$C$84*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^1</f>
+        <v>376593.75</v>
       </c>
       <c r="E21" s="37" t="n">
-        <f aca="false">(D11+E11)/2*Assumptions!$C$80*(1+Assumptions!$C$68)*(1+Assumptions!$C$69)^2</f>
-        <v>145873.75</v>
+        <f aca="false">(D10+E10)/2*Assumptions!$C$84*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^2</f>
+        <v>646485.9375</v>
       </c>
       <c r="F21" s="37" t="n">
-        <f aca="false">(E11+F11)/2*Assumptions!$C$80*(1+Assumptions!$C$68)*(1+Assumptions!$C$69)^3</f>
-        <v>338062.415625</v>
+        <f aca="false">(E10+F10)/2*Assumptions!$C$84*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^3</f>
+        <v>799056.61875</v>
       </c>
       <c r="G21" s="37" t="n">
-        <f aca="false">(F11+G11)/2*Assumptions!$C$80*(1+Assumptions!$C$68)*(1+Assumptions!$C$69)^4</f>
-        <v>696408.5761875</v>
+        <f aca="false">(F10+G10)/2*Assumptions!$C$84*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^4</f>
+        <v>777304.52190625</v>
       </c>
       <c r="H21" s="2"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4" t="s">
-        <v>272</v>
+      <c r="A22" s="2" t="s">
+        <v>177</v>
       </c>
       <c r="B22" s="2"/>
-      <c r="C22" s="38" t="n">
-        <f aca="false">SUM(C16:C21)</f>
-        <v>1059375</v>
-      </c>
-      <c r="D22" s="38" t="n">
-        <f aca="false">SUM(D16:D21)</f>
-        <v>1889406.25</v>
-      </c>
-      <c r="E22" s="38" t="n">
-        <f aca="false">SUM(E16:E21)</f>
-        <v>3474447.5</v>
-      </c>
-      <c r="F22" s="38" t="n">
-        <f aca="false">SUM(F16:F21)</f>
-        <v>6392452.95</v>
-      </c>
-      <c r="G22" s="38" t="n">
-        <f aca="false">SUM(G16:G21)</f>
-        <v>11005365.8327813</v>
+      <c r="C22" s="37" t="n">
+        <f aca="false">C11*0.75*Assumptions!$C$85*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^0</f>
+        <v>1289062.5</v>
+      </c>
+      <c r="D22" s="37" t="n">
+        <f aca="false">(C11+D11)/2*Assumptions!$C$85*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^1</f>
+        <v>2655468.75</v>
+      </c>
+      <c r="E22" s="37" t="n">
+        <f aca="false">(D11+E11)/2*Assumptions!$C$85*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^2</f>
+        <v>4339744.0625</v>
+      </c>
+      <c r="F22" s="37" t="n">
+        <f aca="false">(E11+F11)/2*Assumptions!$C$85*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^3</f>
+        <v>5108498.725</v>
+      </c>
+      <c r="G22" s="37" t="n">
+        <f aca="false">(F11+G11)/2*Assumptions!$C$85*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^4</f>
+        <v>5184374.9560625</v>
       </c>
       <c r="H22" s="2"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2"/>
+      <c r="A23" s="2" t="s">
+        <v>280</v>
+      </c>
       <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
+      <c r="C23" s="37" t="n">
+        <f aca="false">C12*0.75*Assumptions!$C$83*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^0</f>
+        <v>525000</v>
+      </c>
+      <c r="D23" s="37" t="n">
+        <f aca="false">(C12+D12)/2*Assumptions!$C$83*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^1</f>
+        <v>721000</v>
+      </c>
+      <c r="E23" s="37" t="n">
+        <f aca="false">(D12+E12)/2*Assumptions!$C$83*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^2</f>
+        <v>696215.625</v>
+      </c>
+      <c r="F23" s="37" t="n">
+        <f aca="false">(E12+F12)/2*Assumptions!$C$83*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^3</f>
+        <v>334647.64375</v>
+      </c>
+      <c r="G23" s="37" t="n">
+        <f aca="false">(F12+G12)/2*Assumptions!$C$83*(1+Assumptions!$C$73)*(1+Assumptions!$C$74)^4</f>
+        <v>0</v>
+      </c>
       <c r="H23" s="2"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="17" t="s">
-        <v>273</v>
+      <c r="A24" s="4" t="s">
+        <v>284</v>
       </c>
       <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
+      <c r="C24" s="38" t="n">
+        <f aca="false">SUM(C17:C23)</f>
+        <v>3075000</v>
+      </c>
+      <c r="D24" s="38" t="n">
+        <f aca="false">SUM(D17:D23)</f>
+        <v>5587750</v>
+      </c>
+      <c r="E24" s="38" t="n">
+        <f aca="false">SUM(E17:E23)</f>
+        <v>8593290</v>
+      </c>
+      <c r="F24" s="38" t="n">
+        <f aca="false">SUM(F17:F23)</f>
+        <v>10449201.9375</v>
+      </c>
+      <c r="G24" s="38" t="n">
+        <f aca="false">SUM(G17:G23)</f>
+        <v>11343018.4757813</v>
+      </c>
       <c r="H24" s="2"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="17" t="s">
+        <v>285</v>
+      </c>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -7081,7 +7308,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
@@ -7092,7 +7319,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -7104,7 +7331,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -7126,7 +7353,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="7" t="s">
@@ -7148,7 +7375,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="B5" s="16"/>
       <c r="C5" s="16"/>
@@ -7160,163 +7387,163 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$C$29</f>
-        <v>4058.8</v>
+        <v>572685</v>
       </c>
       <c r="D6" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$D$29+Rollout!$D$5*'Unit Economics'!$C$29</f>
-        <v>24109.272</v>
+        <v>1683693.9</v>
       </c>
       <c r="E6" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$E$29+Rollout!$D$5*'Unit Economics'!$D$29+Rollout!$E$5*'Unit Economics'!$C$29</f>
-        <v>79796.008</v>
+        <v>2663557.935</v>
       </c>
       <c r="F6" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$F$29+Rollout!$D$5*'Unit Economics'!$E$29+Rollout!$E$5*'Unit Economics'!$D$29+Rollout!$F$5*'Unit Economics'!$C$29</f>
-        <v>198394.144</v>
+        <v>3065777.5179</v>
       </c>
       <c r="G6" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$G$29+Rollout!$D$5*'Unit Economics'!$F$29+Rollout!$E$5*'Unit Economics'!$E$29+Rollout!$F$5*'Unit Economics'!$D$29+Rollout!$G$5*'Unit Economics'!$C$29</f>
-        <v>414728.184</v>
+        <v>3024292.2165</v>
       </c>
       <c r="H6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$C$30</f>
-        <v>3000</v>
+        <v>450000</v>
       </c>
       <c r="D7" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$D$30+Rollout!$D$5*'Unit Economics'!$C$30</f>
-        <v>17820</v>
+        <v>1323000</v>
       </c>
       <c r="E7" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$E$30+Rollout!$D$5*'Unit Economics'!$D$30+Rollout!$E$5*'Unit Economics'!$C$30</f>
-        <v>58980</v>
+        <v>2092950</v>
       </c>
       <c r="F7" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$F$30+Rollout!$D$5*'Unit Economics'!$E$30+Rollout!$E$5*'Unit Economics'!$D$30+Rollout!$F$5*'Unit Economics'!$C$30</f>
-        <v>146640</v>
+        <v>2409003</v>
       </c>
       <c r="G7" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$G$30+Rollout!$D$5*'Unit Economics'!$F$30+Rollout!$E$5*'Unit Economics'!$E$30+Rollout!$F$5*'Unit Economics'!$D$30+Rollout!$G$5*'Unit Economics'!$C$30</f>
-        <v>306540</v>
+        <v>2376405</v>
       </c>
       <c r="H7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$C$31</f>
-        <v>63</v>
+        <v>5462.1</v>
       </c>
       <c r="D8" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$D$31+Rollout!$D$5*'Unit Economics'!$C$31</f>
-        <v>577.92</v>
+        <v>33719.364</v>
       </c>
       <c r="E8" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$E$31+Rollout!$D$5*'Unit Economics'!$D$31+Rollout!$E$5*'Unit Economics'!$C$31</f>
-        <v>2412.48</v>
+        <v>74198.9871</v>
       </c>
       <c r="F8" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$F$31+Rollout!$D$5*'Unit Economics'!$E$31+Rollout!$E$5*'Unit Economics'!$D$31+Rollout!$F$5*'Unit Economics'!$C$31</f>
-        <v>7026.6</v>
+        <v>115772.341104</v>
       </c>
       <c r="G8" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$G$31+Rollout!$D$5*'Unit Economics'!$F$31+Rollout!$E$5*'Unit Economics'!$E$31+Rollout!$F$5*'Unit Economics'!$D$31+Rollout!$G$5*'Unit Economics'!$C$31</f>
-        <v>16544.22</v>
+        <v>142580.47356</v>
       </c>
       <c r="H8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$C$32</f>
-        <v>544.07424</v>
+        <v>65670.02496</v>
       </c>
       <c r="D9" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$D$32+Rollout!$D$5*'Unit Economics'!$C$32</f>
-        <v>5666.6180064</v>
+        <v>473246.599104</v>
       </c>
       <c r="E9" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$E$32+Rollout!$D$5*'Unit Economics'!$D$32+Rollout!$E$5*'Unit Economics'!$C$32</f>
-        <v>25627.8401856</v>
+        <v>1167546.17206656</v>
       </c>
       <c r="F9" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$F$32+Rollout!$D$5*'Unit Economics'!$E$32+Rollout!$E$5*'Unit Economics'!$D$32+Rollout!$F$5*'Unit Economics'!$C$32</f>
-        <v>79001.95857984</v>
+        <v>1965933.45366278</v>
       </c>
       <c r="G9" s="37" t="n">
         <f aca="false">Rollout!$C$5*'Unit Economics'!$G$32+Rollout!$D$5*'Unit Economics'!$F$32+Rollout!$E$5*'Unit Economics'!$E$32+Rollout!$F$5*'Unit Economics'!$D$32+Rollout!$G$5*'Unit Economics'!$C$32</f>
-        <v>194496.47849088</v>
+        <v>2621532.26049408</v>
       </c>
       <c r="H9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="37" t="n">
-        <f aca="false">Rollout!$C$5*'Unit Economics'!$C$33+Rollout!C5*Assumptions!$C$62*Assumptions!$F$10</f>
-        <v>300</v>
+        <f aca="false">Rollout!$C$5*'Unit Economics'!$C$33+Rollout!C5*Assumptions!$C$67*Assumptions!$F$10</f>
+        <v>45000</v>
       </c>
       <c r="D10" s="37" t="n">
-        <f aca="false">Rollout!$C$5*'Unit Economics'!$D$33+Rollout!$D$5*'Unit Economics'!$C$33+Rollout!D5*Assumptions!$C$62*Assumptions!$F$10</f>
-        <v>1588</v>
+        <f aca="false">Rollout!$C$5*'Unit Economics'!$D$33+Rollout!$D$5*'Unit Economics'!$C$33+Rollout!D5*Assumptions!$C$67*Assumptions!$F$10</f>
+        <v>103200</v>
       </c>
       <c r="E10" s="37" t="n">
-        <f aca="false">Rollout!$C$5*'Unit Economics'!$E$33+Rollout!$D$5*'Unit Economics'!$D$33+Rollout!$E$5*'Unit Economics'!$C$33+Rollout!E5*Assumptions!$C$62*Assumptions!$F$10</f>
-        <v>4932</v>
+        <f aca="false">Rollout!$C$5*'Unit Economics'!$E$33+Rollout!$D$5*'Unit Economics'!$D$33+Rollout!$E$5*'Unit Economics'!$C$33+Rollout!E5*Assumptions!$C$67*Assumptions!$F$10</f>
+        <v>151695</v>
       </c>
       <c r="F10" s="37" t="n">
-        <f aca="false">Rollout!$C$5*'Unit Economics'!$F$33+Rollout!$D$5*'Unit Economics'!$E$33+Rollout!$E$5*'Unit Economics'!$D$33+Rollout!$F$5*'Unit Economics'!$C$33+Rollout!F5*Assumptions!$C$62*Assumptions!$F$10</f>
-        <v>11776</v>
+        <f aca="false">Rollout!$C$5*'Unit Economics'!$F$33+Rollout!$D$5*'Unit Economics'!$E$33+Rollout!$E$5*'Unit Economics'!$D$33+Rollout!$F$5*'Unit Economics'!$C$33+Rollout!F5*Assumptions!$C$67*Assumptions!$F$10</f>
+        <v>160600.2</v>
       </c>
       <c r="G10" s="37" t="n">
-        <f aca="false">Rollout!$C$5*'Unit Economics'!$G$33+Rollout!$D$5*'Unit Economics'!$F$33+Rollout!$E$5*'Unit Economics'!$E$33+Rollout!$F$5*'Unit Economics'!$D$33+Rollout!$G$5*'Unit Economics'!$C$33+Rollout!G5*Assumptions!$C$62*Assumptions!$F$10</f>
-        <v>23936</v>
+        <f aca="false">Rollout!$C$5*'Unit Economics'!$G$33+Rollout!$D$5*'Unit Economics'!$F$33+Rollout!$E$5*'Unit Economics'!$E$33+Rollout!$F$5*'Unit Economics'!$D$33+Rollout!$G$5*'Unit Economics'!$C$33+Rollout!G5*Assumptions!$C$67*Assumptions!$F$10</f>
+        <v>158427</v>
       </c>
       <c r="H10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="38" t="n">
         <f aca="false">SUM(C6:C10)</f>
-        <v>7965.87424</v>
+        <v>1138817.12496</v>
       </c>
       <c r="D11" s="38" t="n">
         <f aca="false">SUM(D6:D10)</f>
-        <v>49761.8100064</v>
+        <v>3616859.863104</v>
       </c>
       <c r="E11" s="38" t="n">
         <f aca="false">SUM(E6:E10)</f>
-        <v>171748.3281856</v>
+        <v>6149948.09416656</v>
       </c>
       <c r="F11" s="38" t="n">
         <f aca="false">SUM(F6:F10)</f>
-        <v>442838.70257984</v>
+        <v>7717086.51266678</v>
       </c>
       <c r="G11" s="38" t="n">
         <f aca="false">SUM(G6:G10)</f>
-        <v>956244.88249088</v>
+        <v>8323236.95055408</v>
       </c>
       <c r="H11" s="2"/>
     </row>
@@ -7332,7 +7559,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="B13" s="16"/>
       <c r="C13" s="16"/>
@@ -7344,354 +7571,381 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="9" t="n">
-        <f aca="false">Headcount!C19</f>
-        <v>65625</v>
+        <f aca="false">Headcount!C20</f>
+        <v>196875</v>
       </c>
       <c r="D14" s="9" t="n">
-        <f aca="false">Headcount!D19</f>
-        <v>180250</v>
+        <f aca="false">Headcount!D20</f>
+        <v>405562.5</v>
       </c>
       <c r="E14" s="9" t="n">
-        <f aca="false">Headcount!E19</f>
-        <v>510558.125</v>
+        <f aca="false">Headcount!E20</f>
+        <v>696215.625</v>
       </c>
       <c r="F14" s="9" t="n">
-        <f aca="false">Headcount!F19</f>
-        <v>1242976.9625</v>
+        <f aca="false">Headcount!F20</f>
+        <v>860522.5125</v>
       </c>
       <c r="G14" s="9" t="n">
-        <f aca="false">Headcount!G19</f>
-        <v>2609773.5531875</v>
+        <f aca="false">Headcount!G20</f>
+        <v>837097.1774375</v>
       </c>
       <c r="H14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="9" t="n">
-        <f aca="false">Headcount!C20</f>
-        <v>60937.5</v>
+        <f aca="false">Headcount!C21</f>
+        <v>182812.5</v>
       </c>
       <c r="D15" s="9" t="n">
-        <f aca="false">Headcount!D20</f>
-        <v>209218.75</v>
+        <f aca="false">Headcount!D21</f>
+        <v>376593.75</v>
       </c>
       <c r="E15" s="9" t="n">
-        <f aca="false">Headcount!E20</f>
-        <v>603386.875</v>
+        <f aca="false">Headcount!E21</f>
+        <v>646485.9375</v>
       </c>
       <c r="F15" s="9" t="n">
-        <f aca="false">Headcount!F20</f>
-        <v>1464937.134375</v>
+        <f aca="false">Headcount!F21</f>
+        <v>799056.61875</v>
       </c>
       <c r="G15" s="9" t="n">
-        <f aca="false">Headcount!G20</f>
-        <v>3154941.88303125</v>
+        <f aca="false">Headcount!G21</f>
+        <v>777304.52190625</v>
       </c>
       <c r="H15" s="2"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="37" t="n">
-        <f aca="false">(Rollout!$C$5*'Unit Economics'!$C$27)*Assumptions!$C$70</f>
-        <v>609</v>
+        <f aca="false">(Rollout!$C$5*'Unit Economics'!$C$27)*Assumptions!$C$75</f>
+        <v>0</v>
       </c>
       <c r="D16" s="37" t="n">
-        <f aca="false">(Rollout!$C$5*'Unit Economics'!$D$27+Rollout!$D$5*'Unit Economics'!$C$27)*Assumptions!$C$70</f>
-        <v>9104.3232</v>
+        <f aca="false">(Rollout!$C$5*'Unit Economics'!$D$27+Rollout!$D$5*'Unit Economics'!$C$27)*Assumptions!$C$75</f>
+        <v>0</v>
       </c>
       <c r="E16" s="37" t="n">
-        <f aca="false">(Rollout!$C$5*'Unit Economics'!$E$27+Rollout!$D$5*'Unit Economics'!$D$27+Rollout!$E$5*'Unit Economics'!$C$27)*Assumptions!$C$70</f>
-        <v>46377.1728</v>
+        <f aca="false">(Rollout!$C$5*'Unit Economics'!$E$27+Rollout!$D$5*'Unit Economics'!$D$27+Rollout!$E$5*'Unit Economics'!$C$27)*Assumptions!$C$75</f>
+        <v>0</v>
       </c>
       <c r="F16" s="37" t="n">
-        <f aca="false">(Rollout!$C$5*'Unit Economics'!$F$27+Rollout!$D$5*'Unit Economics'!$E$27+Rollout!$E$5*'Unit Economics'!$D$27+Rollout!$F$5*'Unit Economics'!$C$27)*Assumptions!$C$70</f>
-        <v>152830.5576</v>
+        <f aca="false">(Rollout!$C$5*'Unit Economics'!$F$27+Rollout!$D$5*'Unit Economics'!$E$27+Rollout!$E$5*'Unit Economics'!$D$27+Rollout!$F$5*'Unit Economics'!$C$27)*Assumptions!$C$75</f>
+        <v>0</v>
       </c>
       <c r="G16" s="37" t="n">
-        <f aca="false">(Rollout!$C$5*'Unit Economics'!$G$27+Rollout!$D$5*'Unit Economics'!$F$27+Rollout!$E$5*'Unit Economics'!$E$27+Rollout!$F$5*'Unit Economics'!$D$27+Rollout!$G$5*'Unit Economics'!$C$27)*Assumptions!$C$70</f>
-        <v>392084.7504</v>
+        <f aca="false">(Rollout!$C$5*'Unit Economics'!$G$27+Rollout!$D$5*'Unit Economics'!$F$27+Rollout!$E$5*'Unit Economics'!$E$27+Rollout!$F$5*'Unit Economics'!$D$27+Rollout!$G$5*'Unit Economics'!$C$27)*Assumptions!$C$75</f>
+        <v>0</v>
       </c>
       <c r="H16" s="2"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="9" t="n">
-        <f aca="false">Headcount!C21</f>
-        <v>51562.5</v>
+        <f aca="false">Headcount!C22</f>
+        <v>1289062.5</v>
       </c>
       <c r="D17" s="9" t="n">
-        <f aca="false">Headcount!D21</f>
-        <v>70812.5</v>
+        <f aca="false">Headcount!D22</f>
+        <v>2655468.75</v>
       </c>
       <c r="E17" s="9" t="n">
-        <f aca="false">Headcount!E21</f>
-        <v>145873.75</v>
+        <f aca="false">Headcount!E22</f>
+        <v>4339744.0625</v>
       </c>
       <c r="F17" s="9" t="n">
-        <f aca="false">Headcount!F21</f>
-        <v>338062.415625</v>
+        <f aca="false">Headcount!F22</f>
+        <v>5108498.725</v>
       </c>
       <c r="G17" s="9" t="n">
-        <f aca="false">Headcount!G21</f>
-        <v>696408.5761875</v>
+        <f aca="false">Headcount!G22</f>
+        <v>5184374.9560625</v>
       </c>
       <c r="H17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="B18" s="2"/>
-      <c r="C18" s="37" t="n">
-        <f aca="false">Rollout!C5*(Assumptions!$C$63+Assumptions!$C$61)*Assumptions!$F$10</f>
-        <v>30500</v>
-      </c>
-      <c r="D18" s="37" t="n">
-        <f aca="false">Rollout!D5*(Assumptions!$C$63+Assumptions!$C$61)*Assumptions!$F$10</f>
-        <v>122000</v>
-      </c>
-      <c r="E18" s="37" t="n">
-        <f aca="false">Rollout!E5*(Assumptions!$C$63+Assumptions!$C$61)*Assumptions!$F$10</f>
-        <v>305000</v>
-      </c>
-      <c r="F18" s="37" t="n">
-        <f aca="false">Rollout!F5*(Assumptions!$C$63+Assumptions!$C$61)*Assumptions!$F$10</f>
-        <v>610000</v>
-      </c>
-      <c r="G18" s="37" t="n">
-        <f aca="false">Rollout!G5*(Assumptions!$C$63+Assumptions!$C$61)*Assumptions!$F$10</f>
-        <v>1067500</v>
+      <c r="C18" s="9" t="n">
+        <f aca="false">Headcount!C23</f>
+        <v>525000</v>
+      </c>
+      <c r="D18" s="9" t="n">
+        <f aca="false">Headcount!D23</f>
+        <v>721000</v>
+      </c>
+      <c r="E18" s="9" t="n">
+        <f aca="false">Headcount!E23</f>
+        <v>696215.625</v>
+      </c>
+      <c r="F18" s="9" t="n">
+        <f aca="false">Headcount!F23</f>
+        <v>334647.64375</v>
+      </c>
+      <c r="G18" s="9" t="n">
+        <f aca="false">Headcount!G23</f>
+        <v>0</v>
       </c>
       <c r="H18" s="2"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>247</v>
+        <v>297</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="37" t="n">
-        <f aca="false">Rollout!$C$5*'Unit Economics'!$C$41</f>
-        <v>3360</v>
+        <f aca="false">Rollout!C5*(Assumptions!$C$68+Assumptions!$C$66)*Assumptions!$F$10</f>
+        <v>4575000</v>
       </c>
       <c r="D19" s="37" t="n">
-        <f aca="false">Rollout!$C$5*'Unit Economics'!$D$41+Rollout!$D$5*'Unit Economics'!$C$41</f>
-        <v>18771.2</v>
+        <f aca="false">Rollout!D5*(Assumptions!$C$68+Assumptions!$C$66)*Assumptions!$F$10</f>
+        <v>4575000</v>
       </c>
       <c r="E19" s="37" t="n">
-        <f aca="false">Rollout!$C$5*'Unit Economics'!$E$41+Rollout!$D$5*'Unit Economics'!$D$41+Rollout!$E$5*'Unit Economics'!$C$41</f>
-        <v>59001.6</v>
+        <f aca="false">Rollout!E5*(Assumptions!$C$68+Assumptions!$C$66)*Assumptions!$F$10</f>
+        <v>3710325</v>
       </c>
       <c r="F19" s="37" t="n">
-        <f aca="false">Rollout!$C$5*'Unit Economics'!$F$41+Rollout!$D$5*'Unit Economics'!$E$41+Rollout!$E$5*'Unit Economics'!$D$41+Rollout!$F$5*'Unit Economics'!$C$41</f>
-        <v>139843.2</v>
+        <f aca="false">Rollout!F5*(Assumptions!$C$68+Assumptions!$C$66)*Assumptions!$F$10</f>
+        <v>0</v>
       </c>
       <c r="G19" s="37" t="n">
-        <f aca="false">Rollout!$C$5*'Unit Economics'!$G$41+Rollout!$D$5*'Unit Economics'!$F$41+Rollout!$E$5*'Unit Economics'!$E$41+Rollout!$F$5*'Unit Economics'!$D$41+Rollout!$G$5*'Unit Economics'!$C$41</f>
-        <v>279003.2</v>
+        <f aca="false">Rollout!G5*(Assumptions!$C$68+Assumptions!$C$66)*Assumptions!$F$10</f>
+        <v>0</v>
       </c>
       <c r="H19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
-        <v>176</v>
+        <v>259</v>
       </c>
       <c r="B20" s="2"/>
-      <c r="C20" s="9" t="n">
-        <f aca="false">Assumptions!C$91</f>
-        <v>50000</v>
-      </c>
-      <c r="D20" s="9" t="n">
-        <f aca="false">Assumptions!D$91</f>
-        <v>150000</v>
-      </c>
-      <c r="E20" s="9" t="n">
-        <f aca="false">Assumptions!E$91</f>
-        <v>300000</v>
-      </c>
-      <c r="F20" s="9" t="n">
-        <f aca="false">Assumptions!F$91</f>
-        <v>500000</v>
-      </c>
-      <c r="G20" s="9" t="n">
-        <f aca="false">Assumptions!G$91</f>
-        <v>700000</v>
+      <c r="C20" s="37" t="n">
+        <f aca="false">Rollout!$C$5*'Unit Economics'!$C$41</f>
+        <v>291312</v>
+      </c>
+      <c r="D20" s="37" t="n">
+        <f aca="false">Rollout!$C$5*'Unit Economics'!$D$41+Rollout!$D$5*'Unit Economics'!$C$41</f>
+        <v>753527.04</v>
+      </c>
+      <c r="E20" s="37" t="n">
+        <f aca="false">Rollout!$C$5*'Unit Economics'!$E$41+Rollout!$D$5*'Unit Economics'!$D$41+Rollout!$E$5*'Unit Economics'!$C$41</f>
+        <v>1051927.632</v>
+      </c>
+      <c r="F20" s="37" t="n">
+        <f aca="false">Rollout!$C$5*'Unit Economics'!$F$41+Rollout!$D$5*'Unit Economics'!$E$41+Rollout!$E$5*'Unit Economics'!$D$41+Rollout!$F$5*'Unit Economics'!$C$41</f>
+        <v>990495.75744</v>
+      </c>
+      <c r="G20" s="37" t="n">
+        <f aca="false">Rollout!$C$5*'Unit Economics'!$G$41+Rollout!$D$5*'Unit Economics'!$F$41+Rollout!$E$5*'Unit Economics'!$E$41+Rollout!$F$5*'Unit Economics'!$D$41+Rollout!$G$5*'Unit Economics'!$C$41</f>
+        <v>714883.53216</v>
       </c>
       <c r="H20" s="2"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>285</v>
+        <v>184</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" s="9" t="n">
-        <f aca="false">Headcount!C17</f>
-        <v>478125</v>
+        <f aca="false">Assumptions!C$96</f>
+        <v>50000</v>
       </c>
       <c r="D21" s="9" t="n">
-        <f aca="false">Headcount!D17</f>
-        <v>875500</v>
+        <f aca="false">Assumptions!D$96</f>
+        <v>150000</v>
       </c>
       <c r="E21" s="9" t="n">
-        <f aca="false">Headcount!E17</f>
-        <v>1465368.125</v>
+        <f aca="false">Assumptions!E$96</f>
+        <v>300000</v>
       </c>
       <c r="F21" s="9" t="n">
-        <f aca="false">Headcount!F17</f>
-        <v>2205942.63125</v>
+        <f aca="false">Assumptions!F$96</f>
+        <v>500000</v>
       </c>
       <c r="G21" s="9" t="n">
-        <f aca="false">Headcount!G17</f>
-        <v>2989632.7765625</v>
+        <f aca="false">Assumptions!G$96</f>
+        <v>700000</v>
       </c>
       <c r="H21" s="2"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="11" t="s">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="9" t="n">
-        <f aca="false">Headcount!C16</f>
-        <v>300000</v>
+        <f aca="false">Headcount!C18</f>
+        <v>478125</v>
       </c>
       <c r="D22" s="9" t="n">
-        <f aca="false">Headcount!D16</f>
-        <v>412000</v>
+        <f aca="false">Headcount!D18</f>
+        <v>875500</v>
       </c>
       <c r="E22" s="9" t="n">
-        <f aca="false">Headcount!E16</f>
-        <v>530450</v>
+        <f aca="false">Headcount!E18</f>
+        <v>1465368.125</v>
       </c>
       <c r="F22" s="9" t="n">
-        <f aca="false">Headcount!F16</f>
-        <v>764908.9</v>
+        <f aca="false">Headcount!F18</f>
+        <v>2205942.63125</v>
       </c>
       <c r="G22" s="9" t="n">
-        <f aca="false">Headcount!G16</f>
-        <v>1012957.929</v>
+        <f aca="false">Headcount!G18</f>
+        <v>2989632.7765625</v>
       </c>
       <c r="H22" s="2"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" s="9" t="n">
-        <f aca="false">Headcount!C18</f>
-        <v>103125</v>
+        <f aca="false">Headcount!C17</f>
+        <v>300000</v>
       </c>
       <c r="D23" s="9" t="n">
-        <f aca="false">Headcount!D18</f>
-        <v>141625</v>
+        <f aca="false">Headcount!D17</f>
+        <v>412000</v>
       </c>
       <c r="E23" s="9" t="n">
-        <f aca="false">Headcount!E18</f>
-        <v>218810.625</v>
+        <f aca="false">Headcount!E17</f>
+        <v>530450</v>
       </c>
       <c r="F23" s="9" t="n">
-        <f aca="false">Headcount!F18</f>
-        <v>375624.90625</v>
+        <f aca="false">Headcount!F17</f>
+        <v>764908.9</v>
       </c>
       <c r="G23" s="9" t="n">
-        <f aca="false">Headcount!G18</f>
-        <v>541651.1148125</v>
+        <f aca="false">Headcount!G17</f>
+        <v>1012957.929</v>
       </c>
       <c r="H23" s="2"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="B24" s="2"/>
-      <c r="C24" s="37" t="n">
-        <f aca="false">Assumptions!C$92+Rollout!C8*Assumptions!$C$93</f>
-        <v>61000</v>
-      </c>
-      <c r="D24" s="37" t="n">
-        <f aca="false">Assumptions!D$92+Rollout!D8*Assumptions!$C$93</f>
-        <v>95970</v>
-      </c>
-      <c r="E24" s="37" t="n">
-        <f aca="false">Assumptions!E$92+Rollout!E8*Assumptions!$C$93</f>
-        <v>159800</v>
-      </c>
-      <c r="F24" s="37" t="n">
-        <f aca="false">Assumptions!F$92+Rollout!F8*Assumptions!$C$93</f>
-        <v>249270</v>
-      </c>
-      <c r="G24" s="37" t="n">
-        <f aca="false">Assumptions!G$92+Rollout!G8*Assumptions!$C$93</f>
-        <v>363030</v>
+      <c r="C24" s="9" t="n">
+        <f aca="false">Headcount!C19</f>
+        <v>103125</v>
+      </c>
+      <c r="D24" s="9" t="n">
+        <f aca="false">Headcount!D19</f>
+        <v>141625</v>
+      </c>
+      <c r="E24" s="9" t="n">
+        <f aca="false">Headcount!E19</f>
+        <v>218810.625</v>
+      </c>
+      <c r="F24" s="9" t="n">
+        <f aca="false">Headcount!F19</f>
+        <v>375624.90625</v>
+      </c>
+      <c r="G24" s="9" t="n">
+        <f aca="false">Headcount!G19</f>
+        <v>541651.1148125</v>
       </c>
       <c r="H24" s="2"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" s="37" t="n">
-        <f aca="false">Headcount!C12*Assumptions!$C$94</f>
-        <v>27000</v>
+        <f aca="false">Assumptions!C$97+Rollout!C8*Assumptions!$C$98</f>
+        <v>210000</v>
       </c>
       <c r="D25" s="37" t="n">
-        <f aca="false">Headcount!D12*Assumptions!$C$94</f>
-        <v>48000</v>
+        <f aca="false">Assumptions!D$97+Rollout!D8*Assumptions!$C$98</f>
+        <v>535500</v>
       </c>
       <c r="E25" s="37" t="n">
-        <f aca="false">Headcount!E12*Assumptions!$C$94</f>
-        <v>102000</v>
+        <f aca="false">Assumptions!E$97+Rollout!E8*Assumptions!$C$98</f>
+        <v>845150</v>
       </c>
       <c r="F25" s="37" t="n">
-        <f aca="false">Headcount!F12*Assumptions!$C$94</f>
-        <v>195000</v>
+        <f aca="false">Assumptions!F$97+Rollout!F8*Assumptions!$C$98</f>
+        <v>1011150.5</v>
       </c>
       <c r="G25" s="37" t="n">
-        <f aca="false">Headcount!G12*Assumptions!$C$94</f>
-        <v>348000</v>
+        <f aca="false">Assumptions!G$97+Rollout!G8*Assumptions!$C$98</f>
+        <v>1057568</v>
       </c>
       <c r="H25" s="2"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="4" t="s">
-        <v>290</v>
+      <c r="A26" s="11" t="s">
+        <v>302</v>
       </c>
       <c r="B26" s="2"/>
-      <c r="C26" s="38" t="n">
-        <f aca="false">SUM(C14:C25)</f>
-        <v>1231844</v>
-      </c>
-      <c r="D26" s="38" t="n">
-        <f aca="false">SUM(D14:D25)</f>
-        <v>2333251.7732</v>
-      </c>
-      <c r="E26" s="38" t="n">
-        <f aca="false">SUM(E14:E25)</f>
-        <v>4446626.2728</v>
-      </c>
-      <c r="F26" s="38" t="n">
-        <f aca="false">SUM(F14:F25)</f>
-        <v>8239396.7076</v>
-      </c>
-      <c r="G26" s="38" t="n">
-        <f aca="false">SUM(G14:G25)</f>
-        <v>14154983.7831813</v>
+      <c r="C26" s="37" t="n">
+        <f aca="false">Headcount!C13*Assumptions!$C$99</f>
+        <v>135000</v>
+      </c>
+      <c r="D26" s="37" t="n">
+        <f aca="false">Headcount!D13*Assumptions!$C$99</f>
+        <v>234000</v>
+      </c>
+      <c r="E26" s="37" t="n">
+        <f aca="false">Headcount!E13*Assumptions!$C$99</f>
+        <v>321000</v>
+      </c>
+      <c r="F26" s="37" t="n">
+        <f aca="false">Headcount!F13*Assumptions!$C$99</f>
+        <v>309000</v>
+      </c>
+      <c r="G26" s="37" t="n">
+        <f aca="false">Headcount!G13*Assumptions!$C$99</f>
+        <v>318000</v>
       </c>
       <c r="H26" s="2"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="B27" s="2"/>
+      <c r="C27" s="38" t="n">
+        <f aca="false">SUM(C14:C26)</f>
+        <v>8336312</v>
+      </c>
+      <c r="D27" s="38" t="n">
+        <f aca="false">SUM(D14:D26)</f>
+        <v>11835777.04</v>
+      </c>
+      <c r="E27" s="38" t="n">
+        <f aca="false">SUM(E14:E26)</f>
+        <v>14821692.632</v>
+      </c>
+      <c r="F27" s="38" t="n">
+        <f aca="false">SUM(F14:F26)</f>
+        <v>13259848.19494</v>
+      </c>
+      <c r="G27" s="38" t="n">
+        <f aca="false">SUM(G14:G26)</f>
+        <v>14133470.0079413</v>
+      </c>
+      <c r="H27" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -7720,7 +7974,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>291</v>
+        <v>304</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -7732,7 +7986,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -7754,7 +8008,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="7" t="s">
@@ -7776,82 +8030,82 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="B5" s="2"/>
-      <c r="C5" s="27" t="n">
+      <c r="C5" s="28" t="n">
         <f aca="false">Revenue!C11</f>
-        <v>18028.56</v>
-      </c>
-      <c r="D5" s="27" t="n">
+        <v>1898193.24</v>
+      </c>
+      <c r="D5" s="28" t="n">
         <f aca="false">Revenue!D11</f>
-        <v>217104.8736</v>
-      </c>
-      <c r="E5" s="27" t="n">
+        <v>17162730.936</v>
+      </c>
+      <c r="E5" s="28" t="n">
         <f aca="false">Revenue!E11</f>
-        <v>1084578.1344</v>
-      </c>
-      <c r="F5" s="27" t="n">
+        <v>49867349.09364</v>
+      </c>
+      <c r="F5" s="28" t="n">
         <f aca="false">Revenue!F11</f>
-        <v>3547797.98496</v>
-      </c>
-      <c r="G5" s="27" t="n">
+        <v>90378208.443456</v>
+      </c>
+      <c r="G5" s="28" t="n">
         <f aca="false">Revenue!G11</f>
-        <v>9061606.73472</v>
+        <v>125554175.48988</v>
       </c>
       <c r="H5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="9" t="n">
         <f aca="false">Costs!C11</f>
-        <v>7965.87424</v>
+        <v>1138817.12496</v>
       </c>
       <c r="D6" s="9" t="n">
         <f aca="false">Costs!D11</f>
-        <v>49761.8100064</v>
+        <v>3616859.863104</v>
       </c>
       <c r="E6" s="9" t="n">
         <f aca="false">Costs!E11</f>
-        <v>171748.3281856</v>
+        <v>6149948.09416656</v>
       </c>
       <c r="F6" s="9" t="n">
         <f aca="false">Costs!F11</f>
-        <v>442838.70257984</v>
+        <v>7717086.51266678</v>
       </c>
       <c r="G6" s="9" t="n">
         <f aca="false">Costs!G11</f>
-        <v>956244.88249088</v>
+        <v>8323236.95055408</v>
       </c>
       <c r="H6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>294</v>
+        <v>307</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="38" t="n">
         <f aca="false">C5-C6</f>
-        <v>10062.68576</v>
+        <v>759376.11504</v>
       </c>
       <c r="D7" s="38" t="n">
         <f aca="false">D5-D6</f>
-        <v>167343.0635936</v>
+        <v>13545871.072896</v>
       </c>
       <c r="E7" s="38" t="n">
         <f aca="false">E5-E6</f>
-        <v>912829.8062144</v>
+        <v>43717400.9994734</v>
       </c>
       <c r="F7" s="38" t="n">
         <f aca="false">F5-F6</f>
-        <v>3104959.28238016</v>
+        <v>82661121.9307892</v>
       </c>
       <c r="G7" s="38" t="n">
         <f aca="false">G5-G6</f>
-        <v>8105361.85222912</v>
+        <v>117230938.539326</v>
       </c>
       <c r="H7" s="2"/>
     </row>
@@ -7862,23 +8116,23 @@
       <c r="B8" s="2"/>
       <c r="C8" s="34" t="n">
         <f aca="false">IF(C5=0,0,C7/C5)</f>
-        <v>0.558152495817747</v>
+        <v>0.400052059525826</v>
       </c>
       <c r="D8" s="34" t="n">
         <f aca="false">IF(D5=0,0,D7/D5)</f>
-        <v>0.77079367597209</v>
+        <v>0.789260818887664</v>
       </c>
       <c r="E8" s="34" t="n">
         <f aca="false">IF(E5=0,0,E7/E5)</f>
-        <v>0.841645038989641</v>
+        <v>0.876673851609431</v>
       </c>
       <c r="F8" s="34" t="n">
         <f aca="false">IF(F5=0,0,F7/F5)</f>
-        <v>0.875179278962009</v>
+        <v>0.914613415716302</v>
       </c>
       <c r="G8" s="34" t="n">
         <f aca="false">IF(G5=0,0,G7/G5)</f>
-        <v>0.89447292180238</v>
+        <v>0.933708003592243</v>
       </c>
       <c r="H8" s="2"/>
     </row>
@@ -7894,136 +8148,136 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>295</v>
+        <v>308</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="9" t="n">
         <f aca="false">Costs!C14</f>
-        <v>65625</v>
+        <v>196875</v>
       </c>
       <c r="D10" s="9" t="n">
         <f aca="false">Costs!D14</f>
-        <v>180250</v>
+        <v>405562.5</v>
       </c>
       <c r="E10" s="9" t="n">
         <f aca="false">Costs!E14</f>
-        <v>510558.125</v>
+        <v>696215.625</v>
       </c>
       <c r="F10" s="9" t="n">
         <f aca="false">Costs!F14</f>
-        <v>1242976.9625</v>
+        <v>860522.5125</v>
       </c>
       <c r="G10" s="9" t="n">
         <f aca="false">Costs!G14</f>
-        <v>2609773.5531875</v>
+        <v>837097.1774375</v>
       </c>
       <c r="H10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>296</v>
+        <v>309</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="9" t="n">
-        <f aca="false">Costs!C15+Costs!C16+Costs!C17+Costs!C18+Costs!C19+Costs!C20</f>
-        <v>196969</v>
+        <f aca="false">Costs!C15+Costs!C16+Costs!C17+Costs!C18+Costs!C19+Costs!C20+Costs!C21</f>
+        <v>6913187</v>
       </c>
       <c r="D11" s="9" t="n">
-        <f aca="false">Costs!D15+Costs!D16+Costs!D17+Costs!D18+Costs!D19+Costs!D20</f>
-        <v>579906.7732</v>
+        <f aca="false">Costs!D15+Costs!D16+Costs!D17+Costs!D18+Costs!D19+Costs!D20+Costs!D21</f>
+        <v>9231589.54</v>
       </c>
       <c r="E11" s="9" t="n">
-        <f aca="false">Costs!E15+Costs!E16+Costs!E17+Costs!E18+Costs!E19+Costs!E20</f>
-        <v>1459639.3978</v>
+        <f aca="false">Costs!E15+Costs!E16+Costs!E17+Costs!E18+Costs!E19+Costs!E20+Costs!E21</f>
+        <v>10744698.257</v>
       </c>
       <c r="F11" s="9" t="n">
-        <f aca="false">Costs!F15+Costs!F16+Costs!F17+Costs!F18+Costs!F19+Costs!F20</f>
-        <v>3205673.3076</v>
+        <f aca="false">Costs!F15+Costs!F16+Costs!F17+Costs!F18+Costs!F19+Costs!F20+Costs!F21</f>
+        <v>7732698.74494</v>
       </c>
       <c r="G11" s="9" t="n">
-        <f aca="false">Costs!G15+Costs!G16+Costs!G17+Costs!G18+Costs!G19+Costs!G20</f>
-        <v>6289938.40961875</v>
+        <f aca="false">Costs!G15+Costs!G16+Costs!G17+Costs!G18+Costs!G19+Costs!G20+Costs!G21</f>
+        <v>7376563.01012875</v>
       </c>
       <c r="H11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="9" t="n">
-        <f aca="false">Costs!C21</f>
+        <f aca="false">Costs!C22</f>
         <v>478125</v>
       </c>
       <c r="D12" s="9" t="n">
-        <f aca="false">Costs!D21</f>
+        <f aca="false">Costs!D22</f>
         <v>875500</v>
       </c>
       <c r="E12" s="9" t="n">
-        <f aca="false">Costs!E21</f>
+        <f aca="false">Costs!E22</f>
         <v>1465368.125</v>
       </c>
       <c r="F12" s="9" t="n">
-        <f aca="false">Costs!F21</f>
+        <f aca="false">Costs!F22</f>
         <v>2205942.63125</v>
       </c>
       <c r="G12" s="9" t="n">
-        <f aca="false">Costs!G21</f>
+        <f aca="false">Costs!G22</f>
         <v>2989632.7765625</v>
       </c>
       <c r="H12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>297</v>
+        <v>310</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="9" t="n">
-        <f aca="false">Costs!C22+Costs!C23+Costs!C24+Costs!C25</f>
-        <v>491125</v>
+        <f aca="false">Costs!C23+Costs!C24+Costs!C25+Costs!C26</f>
+        <v>748125</v>
       </c>
       <c r="D13" s="9" t="n">
-        <f aca="false">Costs!D22+Costs!D23+Costs!D24+Costs!D25</f>
-        <v>697595</v>
+        <f aca="false">Costs!D23+Costs!D24+Costs!D25+Costs!D26</f>
+        <v>1323125</v>
       </c>
       <c r="E13" s="9" t="n">
-        <f aca="false">Costs!E22+Costs!E23+Costs!E24+Costs!E25</f>
-        <v>1011060.625</v>
+        <f aca="false">Costs!E23+Costs!E24+Costs!E25+Costs!E26</f>
+        <v>1915410.625</v>
       </c>
       <c r="F13" s="9" t="n">
-        <f aca="false">Costs!F22+Costs!F23+Costs!F24+Costs!F25</f>
-        <v>1584803.80625</v>
+        <f aca="false">Costs!F23+Costs!F24+Costs!F25+Costs!F26</f>
+        <v>2460684.30625</v>
       </c>
       <c r="G13" s="9" t="n">
-        <f aca="false">Costs!G22+Costs!G23+Costs!G24+Costs!G25</f>
-        <v>2265639.0438125</v>
+        <f aca="false">Costs!G23+Costs!G24+Costs!G25+Costs!G26</f>
+        <v>2930177.0438125</v>
       </c>
       <c r="H13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>290</v>
+        <v>303</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="40" t="n">
         <f aca="false">SUM(C10:C13)</f>
-        <v>1231844</v>
+        <v>8336312</v>
       </c>
       <c r="D14" s="40" t="n">
         <f aca="false">SUM(D10:D13)</f>
-        <v>2333251.7732</v>
+        <v>11835777.04</v>
       </c>
       <c r="E14" s="40" t="n">
         <f aca="false">SUM(E10:E13)</f>
-        <v>4446626.2728</v>
+        <v>14821692.632</v>
       </c>
       <c r="F14" s="40" t="n">
         <f aca="false">SUM(F10:F13)</f>
-        <v>8239396.7076</v>
+        <v>13259848.19494</v>
       </c>
       <c r="G14" s="40" t="n">
         <f aca="false">SUM(G10:G13)</f>
-        <v>14154983.7831813</v>
+        <v>14133470.0079413</v>
       </c>
       <c r="H14" s="2"/>
     </row>
@@ -8039,28 +8293,28 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="B16" s="2"/>
-      <c r="C16" s="27" t="n">
+      <c r="C16" s="28" t="n">
         <f aca="false">C7-C14</f>
-        <v>-1221781.31424</v>
-      </c>
-      <c r="D16" s="27" t="n">
+        <v>-7576935.88496</v>
+      </c>
+      <c r="D16" s="28" t="n">
         <f aca="false">D7-D14</f>
-        <v>-2165908.7096064</v>
-      </c>
-      <c r="E16" s="27" t="n">
+        <v>1710094.032896</v>
+      </c>
+      <c r="E16" s="28" t="n">
         <f aca="false">E7-E14</f>
-        <v>-3533796.4665856</v>
-      </c>
-      <c r="F16" s="27" t="n">
+        <v>28895708.3674734</v>
+      </c>
+      <c r="F16" s="28" t="n">
         <f aca="false">F7-F14</f>
-        <v>-5134437.42521984</v>
-      </c>
-      <c r="G16" s="27" t="n">
+        <v>69401273.7358492</v>
+      </c>
+      <c r="G16" s="28" t="n">
         <f aca="false">G7-G14</f>
-        <v>-6049621.93095213</v>
+        <v>103097468.531385</v>
       </c>
       <c r="H16" s="2"/>
     </row>
@@ -8071,110 +8325,110 @@
       <c r="B17" s="2"/>
       <c r="C17" s="34" t="n">
         <f aca="false">IF(C5=0,0,C16/C5)</f>
-        <v>-67.7692125294533</v>
+        <v>-3.99165676354426</v>
       </c>
       <c r="D17" s="34" t="n">
         <f aca="false">IF(D5=0,0,D16/D5)</f>
-        <v>-9.97632468443306</v>
+        <v>0.0996399721741811</v>
       </c>
       <c r="E17" s="34" t="n">
         <f aca="false">IF(E5=0,0,E16/E5)</f>
-        <v>-3.25822211835437</v>
+        <v>0.579451462583535</v>
       </c>
       <c r="F17" s="34" t="n">
         <f aca="false">IF(F5=0,0,F16/F5)</f>
-        <v>-1.44721809048486</v>
+        <v>0.76789831233786</v>
       </c>
       <c r="G17" s="34" t="n">
         <f aca="false">IF(G5=0,0,G16/G5)</f>
-        <v>-0.667610293412172</v>
+        <v>0.82113930603363</v>
       </c>
       <c r="H17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>299</v>
+        <v>312</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="37" t="n">
-        <f aca="false">Headcount!C13*Assumptions!$C$95</f>
-        <v>22500</v>
+        <f aca="false">Headcount!C14*Assumptions!$C$100</f>
+        <v>112500</v>
       </c>
       <c r="D18" s="37" t="n">
-        <f aca="false">Headcount!D13*Assumptions!$C$95</f>
-        <v>17500</v>
+        <f aca="false">Headcount!D14*Assumptions!$C$100</f>
+        <v>82500</v>
       </c>
       <c r="E18" s="37" t="n">
-        <f aca="false">Headcount!E13*Assumptions!$C$95</f>
-        <v>45000</v>
+        <f aca="false">Headcount!E14*Assumptions!$C$100</f>
+        <v>72500</v>
       </c>
       <c r="F18" s="37" t="n">
-        <f aca="false">Headcount!F13*Assumptions!$C$95</f>
-        <v>77500</v>
+        <f aca="false">Headcount!F14*Assumptions!$C$100</f>
+        <v>0</v>
       </c>
       <c r="G18" s="37" t="n">
-        <f aca="false">Headcount!G13*Assumptions!$C$95</f>
-        <v>127500</v>
+        <f aca="false">Headcount!G14*Assumptions!$C$100</f>
+        <v>7500</v>
       </c>
       <c r="H18" s="2"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="37" t="n">
-        <f aca="false">(C18)/Assumptions!$C$96</f>
-        <v>7500</v>
+        <f aca="false">(C18)/Assumptions!$C$101</f>
+        <v>37500</v>
       </c>
       <c r="D19" s="37" t="n">
-        <f aca="false">(C18+D18)/Assumptions!$C$96</f>
-        <v>13333.3333333333</v>
+        <f aca="false">(C18+D18)/Assumptions!$C$101</f>
+        <v>65000</v>
       </c>
       <c r="E19" s="37" t="n">
-        <f aca="false">(C18+D18+E18)/Assumptions!$C$96</f>
-        <v>28333.3333333333</v>
+        <f aca="false">(C18+D18+E18)/Assumptions!$C$101</f>
+        <v>89166.6666666667</v>
       </c>
       <c r="F19" s="37" t="n">
-        <f aca="false">(D18+E18+F18)/Assumptions!$C$96</f>
-        <v>46666.6666666667</v>
+        <f aca="false">(D18+E18+F18)/Assumptions!$C$101</f>
+        <v>51666.6666666667</v>
       </c>
       <c r="G19" s="37" t="n">
-        <f aca="false">(E18+F18+G18)/Assumptions!$C$96</f>
-        <v>83333.3333333333</v>
+        <f aca="false">(E18+F18+G18)/Assumptions!$C$101</f>
+        <v>26666.6666666667</v>
       </c>
       <c r="H19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="B20" s="2"/>
-      <c r="C20" s="27" t="n">
+      <c r="C20" s="28" t="n">
         <f aca="false">C16-C19</f>
-        <v>-1229281.31424</v>
-      </c>
-      <c r="D20" s="27" t="n">
+        <v>-7614435.88496</v>
+      </c>
+      <c r="D20" s="28" t="n">
         <f aca="false">D16-D19</f>
-        <v>-2179242.04293973</v>
-      </c>
-      <c r="E20" s="27" t="n">
+        <v>1645094.032896</v>
+      </c>
+      <c r="E20" s="28" t="n">
         <f aca="false">E16-E19</f>
-        <v>-3562129.79991893</v>
-      </c>
-      <c r="F20" s="27" t="n">
+        <v>28806541.7008068</v>
+      </c>
+      <c r="F20" s="28" t="n">
         <f aca="false">F16-F19</f>
-        <v>-5181104.09188651</v>
-      </c>
-      <c r="G20" s="27" t="n">
+        <v>69349607.0691826</v>
+      </c>
+      <c r="G20" s="28" t="n">
         <f aca="false">G16-G19</f>
-        <v>-6132955.26428547</v>
+        <v>103070801.864718</v>
       </c>
       <c r="H20" s="2"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" s="37" t="n">
@@ -8183,25 +8437,25 @@
       </c>
       <c r="D21" s="37" t="n">
         <f aca="false">C23</f>
-        <v>1229281.31424</v>
+        <v>7614435.88496</v>
       </c>
       <c r="E21" s="37" t="n">
         <f aca="false">D23</f>
-        <v>3408523.35717973</v>
+        <v>5969341.852064</v>
       </c>
       <c r="F21" s="37" t="n">
         <f aca="false">E23</f>
-        <v>6970653.15709867</v>
+        <v>0</v>
       </c>
       <c r="G21" s="37" t="n">
         <f aca="false">F23</f>
-        <v>12151757.2489852</v>
+        <v>0</v>
       </c>
       <c r="H21" s="2"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="11" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="37" t="n">
@@ -8214,96 +8468,96 @@
       </c>
       <c r="E22" s="37" t="n">
         <f aca="false">MAX(0,E20-E21)</f>
-        <v>0</v>
+        <v>22837199.8487428</v>
       </c>
       <c r="F22" s="37" t="n">
         <f aca="false">MAX(0,F20-F21)</f>
-        <v>0</v>
+        <v>69349607.0691826</v>
       </c>
       <c r="G22" s="37" t="n">
         <f aca="false">MAX(0,G20-G21)</f>
-        <v>0</v>
+        <v>103070801.864718</v>
       </c>
       <c r="H22" s="2"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>304</v>
+        <v>317</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" s="37" t="n">
         <f aca="false">MAX(0,C21-MAX(0,C20))+MAX(0,-C20)</f>
-        <v>1229281.31424</v>
+        <v>7614435.88496</v>
       </c>
       <c r="D23" s="37" t="n">
         <f aca="false">MAX(0,D21-MAX(0,D20))+MAX(0,-D20)</f>
-        <v>3408523.35717973</v>
+        <v>5969341.852064</v>
       </c>
       <c r="E23" s="37" t="n">
         <f aca="false">MAX(0,E21-MAX(0,E20))+MAX(0,-E20)</f>
-        <v>6970653.15709867</v>
+        <v>0</v>
       </c>
       <c r="F23" s="37" t="n">
         <f aca="false">MAX(0,F21-MAX(0,F20))+MAX(0,-F20)</f>
-        <v>12151757.2489852</v>
+        <v>0</v>
       </c>
       <c r="G23" s="37" t="n">
         <f aca="false">MAX(0,G21-MAX(0,G20))+MAX(0,-G20)</f>
-        <v>18284712.5132706</v>
+        <v>0</v>
       </c>
       <c r="H23" s="2"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
-        <v>305</v>
+        <v>318</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" s="37" t="n">
-        <f aca="false">C22*Assumptions!$C$99</f>
+        <f aca="false">C22*Assumptions!$C$104</f>
         <v>0</v>
       </c>
       <c r="D24" s="37" t="n">
-        <f aca="false">D22*Assumptions!$C$99</f>
+        <f aca="false">D22*Assumptions!$C$104</f>
         <v>0</v>
       </c>
       <c r="E24" s="37" t="n">
-        <f aca="false">E22*Assumptions!$C$99</f>
-        <v>0</v>
+        <f aca="false">E22*Assumptions!$C$104</f>
+        <v>5709299.96218569</v>
       </c>
       <c r="F24" s="37" t="n">
-        <f aca="false">F22*Assumptions!$C$99</f>
-        <v>0</v>
+        <f aca="false">F22*Assumptions!$C$104</f>
+        <v>17337401.7672956</v>
       </c>
       <c r="G24" s="37" t="n">
-        <f aca="false">G22*Assumptions!$C$99</f>
-        <v>0</v>
+        <f aca="false">G22*Assumptions!$C$104</f>
+        <v>25767700.4661795</v>
       </c>
       <c r="H24" s="2"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>306</v>
+        <v>319</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" s="38" t="n">
         <f aca="false">C20-C24</f>
-        <v>-1229281.31424</v>
+        <v>-7614435.88496</v>
       </c>
       <c r="D25" s="38" t="n">
         <f aca="false">D20-D24</f>
-        <v>-2179242.04293973</v>
+        <v>1645094.032896</v>
       </c>
       <c r="E25" s="38" t="n">
         <f aca="false">E20-E24</f>
-        <v>-3562129.79991893</v>
+        <v>23097241.7386211</v>
       </c>
       <c r="F25" s="38" t="n">
         <f aca="false">F20-F24</f>
-        <v>-5181104.09188651</v>
+        <v>52012205.3018869</v>
       </c>
       <c r="G25" s="38" t="n">
         <f aca="false">G20-G24</f>
-        <v>-6132955.26428547</v>
+        <v>77303101.3985385</v>
       </c>
       <c r="H25" s="2"/>
     </row>
@@ -8334,7 +8588,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>307</v>
+        <v>320</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -8346,7 +8600,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>308</v>
+        <v>321</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -8368,7 +8622,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="7" t="s">
@@ -8390,34 +8644,34 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="9" t="n">
         <f aca="false">'P&amp;L'!C16</f>
-        <v>-1221781.31424</v>
+        <v>-7576935.88496</v>
       </c>
       <c r="D5" s="9" t="n">
         <f aca="false">'P&amp;L'!D16</f>
-        <v>-2165908.7096064</v>
+        <v>1710094.032896</v>
       </c>
       <c r="E5" s="9" t="n">
         <f aca="false">'P&amp;L'!E16</f>
-        <v>-3533796.4665856</v>
+        <v>28895708.3674734</v>
       </c>
       <c r="F5" s="9" t="n">
         <f aca="false">'P&amp;L'!F16</f>
-        <v>-5134437.42521984</v>
+        <v>69401273.7358492</v>
       </c>
       <c r="G5" s="9" t="n">
         <f aca="false">'P&amp;L'!G16</f>
-        <v>-6049621.93095213</v>
+        <v>103097468.531385</v>
       </c>
       <c r="H5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>309</v>
+        <v>322</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="9" t="n">
@@ -8430,210 +8684,210 @@
       </c>
       <c r="E6" s="9" t="n">
         <f aca="false">-'P&amp;L'!E24</f>
-        <v>-0</v>
+        <v>-5709299.96218569</v>
       </c>
       <c r="F6" s="9" t="n">
         <f aca="false">-'P&amp;L'!F24</f>
-        <v>-0</v>
+        <v>-17337401.7672956</v>
       </c>
       <c r="G6" s="9" t="n">
         <f aca="false">-'P&amp;L'!G24</f>
-        <v>-0</v>
+        <v>-25767700.4661795</v>
       </c>
       <c r="H6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>310</v>
+        <v>323</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="9" t="n">
         <f aca="false">-'P&amp;L'!C18</f>
-        <v>-22500</v>
+        <v>-112500</v>
       </c>
       <c r="D7" s="9" t="n">
         <f aca="false">-'P&amp;L'!D18</f>
-        <v>-17500</v>
+        <v>-82500</v>
       </c>
       <c r="E7" s="9" t="n">
         <f aca="false">-'P&amp;L'!E18</f>
-        <v>-45000</v>
+        <v>-72500</v>
       </c>
       <c r="F7" s="9" t="n">
         <f aca="false">-'P&amp;L'!F18</f>
-        <v>-77500</v>
+        <v>-0</v>
       </c>
       <c r="G7" s="9" t="n">
         <f aca="false">-'P&amp;L'!G18</f>
-        <v>-127500</v>
+        <v>-7500</v>
       </c>
       <c r="H7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>311</v>
+        <v>324</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="37" t="n">
-        <f aca="false">-'P&amp;L'!C5*Assumptions!$C$100</f>
-        <v>-540.8568</v>
+        <f aca="false">-'P&amp;L'!C5*Assumptions!$C$105</f>
+        <v>-56945.7972</v>
       </c>
       <c r="D8" s="37" t="n">
-        <f aca="false">-('P&amp;L'!D5-'P&amp;L'!C5)*Assumptions!$C$100</f>
-        <v>-5972.289408</v>
+        <f aca="false">-('P&amp;L'!D5-'P&amp;L'!C5)*Assumptions!$C$105</f>
+        <v>-457936.13088</v>
       </c>
       <c r="E8" s="37" t="n">
-        <f aca="false">-('P&amp;L'!E5-'P&amp;L'!D5)*Assumptions!$C$100</f>
-        <v>-26024.197824</v>
+        <f aca="false">-('P&amp;L'!E5-'P&amp;L'!D5)*Assumptions!$C$105</f>
+        <v>-981138.5447292</v>
       </c>
       <c r="F8" s="37" t="n">
-        <f aca="false">-('P&amp;L'!F5-'P&amp;L'!E5)*Assumptions!$C$100</f>
-        <v>-73896.5955168</v>
+        <f aca="false">-('P&amp;L'!F5-'P&amp;L'!E5)*Assumptions!$C$105</f>
+        <v>-1215325.78049448</v>
       </c>
       <c r="G8" s="37" t="n">
-        <f aca="false">-('P&amp;L'!G5-'P&amp;L'!F5)*Assumptions!$C$100</f>
-        <v>-165414.2624928</v>
+        <f aca="false">-('P&amp;L'!G5-'P&amp;L'!F5)*Assumptions!$C$105</f>
+        <v>-1055279.01139272</v>
       </c>
       <c r="H8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>312</v>
+        <v>325</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="38" t="n">
         <f aca="false">SUM(C5:C8)</f>
-        <v>-1244822.17104</v>
+        <v>-7746381.68216</v>
       </c>
       <c r="D9" s="38" t="n">
         <f aca="false">SUM(D5:D8)</f>
-        <v>-2189380.9990144</v>
+        <v>1169657.902016</v>
       </c>
       <c r="E9" s="38" t="n">
         <f aca="false">SUM(E5:E8)</f>
-        <v>-3604820.6644096</v>
+        <v>22132769.8605585</v>
       </c>
       <c r="F9" s="38" t="n">
         <f aca="false">SUM(F5:F8)</f>
-        <v>-5285834.02073664</v>
+        <v>50848546.1880591</v>
       </c>
       <c r="G9" s="38" t="n">
         <f aca="false">SUM(G5:G8)</f>
-        <v>-6342536.19344493</v>
+        <v>76266989.0538125</v>
       </c>
       <c r="H9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="9" t="n">
-        <f aca="false">Assumptions!C$104</f>
-        <v>2000000</v>
+        <f aca="false">Assumptions!C$109</f>
+        <v>10000000</v>
       </c>
       <c r="D10" s="9" t="n">
-        <f aca="false">Assumptions!D$104</f>
-        <v>8000000</v>
+        <f aca="false">Assumptions!D$109</f>
+        <v>0</v>
       </c>
       <c r="E10" s="9" t="n">
-        <f aca="false">Assumptions!E$104</f>
+        <f aca="false">Assumptions!E$109</f>
         <v>0</v>
       </c>
       <c r="F10" s="9" t="n">
-        <f aca="false">Assumptions!F$104</f>
-        <v>15000000</v>
+        <f aca="false">Assumptions!F$109</f>
+        <v>0</v>
       </c>
       <c r="G10" s="9" t="n">
-        <f aca="false">Assumptions!G$104</f>
+        <f aca="false">Assumptions!G$109</f>
         <v>0</v>
       </c>
       <c r="H10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>313</v>
+        <v>326</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="37" t="n">
         <f aca="false">C9+C10</f>
-        <v>755177.82896</v>
+        <v>2253618.31784</v>
       </c>
       <c r="D11" s="37" t="n">
         <f aca="false">D9+D10</f>
-        <v>5810619.0009856</v>
+        <v>1169657.902016</v>
       </c>
       <c r="E11" s="37" t="n">
         <f aca="false">E9+E10</f>
-        <v>-3604820.6644096</v>
+        <v>22132769.8605585</v>
       </c>
       <c r="F11" s="37" t="n">
         <f aca="false">F9+F10</f>
-        <v>9714165.97926336</v>
+        <v>50848546.1880591</v>
       </c>
       <c r="G11" s="37" t="n">
         <f aca="false">G9+G10</f>
-        <v>-6342536.19344493</v>
+        <v>76266989.0538125</v>
       </c>
       <c r="H11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>314</v>
+        <v>327</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="37" t="n">
-        <f aca="false">Assumptions!$C$101</f>
+        <f aca="false">Assumptions!$C$106</f>
         <v>250000</v>
       </c>
       <c r="D12" s="37" t="n">
         <f aca="false">C13</f>
-        <v>1005177.82896</v>
+        <v>2503618.31784</v>
       </c>
       <c r="E12" s="37" t="n">
         <f aca="false">D13</f>
-        <v>6815796.8299456</v>
+        <v>3673276.219856</v>
       </c>
       <c r="F12" s="37" t="n">
         <f aca="false">E13</f>
-        <v>3210976.165536</v>
+        <v>25806046.0804145</v>
       </c>
       <c r="G12" s="37" t="n">
         <f aca="false">F13</f>
-        <v>12925142.1447994</v>
+        <v>76654592.2684737</v>
       </c>
       <c r="H12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>315</v>
+        <v>328</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="38" t="n">
         <f aca="false">C12+C11</f>
-        <v>1005177.82896</v>
+        <v>2503618.31784</v>
       </c>
       <c r="D13" s="38" t="n">
         <f aca="false">D12+D11</f>
-        <v>6815796.8299456</v>
+        <v>3673276.219856</v>
       </c>
       <c r="E13" s="38" t="n">
         <f aca="false">E12+E11</f>
-        <v>3210976.165536</v>
+        <v>25806046.0804145</v>
       </c>
       <c r="F13" s="38" t="n">
         <f aca="false">F12+F11</f>
-        <v>12925142.1447994</v>
+        <v>76654592.2684737</v>
       </c>
       <c r="G13" s="38" t="n">
         <f aca="false">G12+G11</f>
-        <v>6582605.95135443</v>
+        <v>152921581.322286</v>
       </c>
       <c r="H13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="41" t="n">
@@ -8670,12 +8924,12 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>317</v>
+        <v>330</v>
       </c>
       <c r="B16" s="2"/>
-      <c r="C16" s="27" t="n">
+      <c r="C16" s="28" t="n">
         <f aca="false">MIN(C13:G13)</f>
-        <v>1005177.82896</v>
+        <v>2503618.31784</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
@@ -8685,19 +8939,19 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>318</v>
+        <v>331</v>
       </c>
       <c r="B17" s="2"/>
-      <c r="C17" s="27" t="n">
+      <c r="C17" s="28" t="n">
         <f aca="false">-MIN(0,C9,C9+D9,C9+D9+E9,C9+D9+E9+F9,C9+D9+E9+F9+G9)</f>
-        <v>18667394.0486456</v>
+        <v>7746381.68216</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
       <c r="H17" s="17" t="s">
-        <v>319</v>
+        <v>332</v>
       </c>
     </row>
   </sheetData>
